--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA032B3-D8F7-486D-8C75-424AB235EC64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1910ADFF-45B9-469D-A6C7-3A4A722A9733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha2" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="78">
   <si>
     <t>Data</t>
   </si>
@@ -274,6 +274,9 @@
   </si>
   <si>
     <t>13,13,13,13,13,13,13,13</t>
+  </si>
+  <si>
+    <t>13,13,38,38,38,38,10</t>
   </si>
 </sst>
 </file>
@@ -536,9 +539,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="44" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -550,10 +550,13 @@
     <xf numFmtId="44" fontId="3" fillId="2" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -563,59 +566,7 @@
     <cellStyle name="Normal 2 2 2" xfId="3" xr:uid="{F6D7429B-6BC2-41D1-B818-FB0128371036}"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="134">
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="145">
     <dxf>
       <font>
         <b/>
@@ -694,507 +645,81 @@
       </font>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
     </dxf>
     <dxf>
       <font>
-        <name val="Calibri"/>
+        <b/>
+        <color rgb="FFFF0000"/>
         <family val="2"/>
-        <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
-        <name val="Calibri"/>
+        <b/>
+        <color rgb="FF00B050"/>
         <family val="2"/>
-        <scheme val="none"/>
       </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[h]:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[h]:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="25" formatCode="hh:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
     </dxf>
     <dxf>
       <font>
         <b/>
         <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
+        <color rgb="FF00B050"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0070C0"/>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1821,7 +1346,6 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -1846,6 +1370,424 @@
         </left>
         <right style="thin">
           <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[h]:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[h]:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0070C0"/>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
         </right>
         <top style="thin">
           <color indexed="64"/>
@@ -1976,6 +1918,128 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -1989,6 +2053,22 @@
         <bottom/>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -2078,94 +2158,94 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V9" totalsRowShown="0" headerRowDxfId="133" dataDxfId="131" headerRowBorderDxfId="132" tableBorderDxfId="130" totalsRowBorderDxfId="129" headerRowCellStyle="Normal 2 2 2">
-  <autoFilter ref="A1:V9" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V10" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
+  <autoFilter ref="A1:V10" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="2"/>
-    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="128"/>
-    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="127"/>
-    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="126"/>
-    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="0" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="1" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="125"/>
-    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="124" dataCellStyle="Porcentagem">
+    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="139"/>
+    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="138"/>
+    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="137"/>
+    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="136"/>
+    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="135" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="134" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="133"/>
+    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="132" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="123"/>
-    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="122"/>
-    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="121">
+    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="131"/>
+    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="130"/>
+    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="129">
       <calculatedColumnFormula>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="120" dataCellStyle="Moeda"/>
-    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="119" dataCellStyle="Porcentagem">
+    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="128" dataCellStyle="Moeda"/>
+    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="127" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="118"/>
-    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="117"/>
-    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="116"/>
-    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="115">
+    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="126"/>
+    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="125"/>
+    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="124"/>
+    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="123">
       <calculatedColumnFormula>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="114" dataCellStyle="Moeda 2 2">
+    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="122" dataCellStyle="Moeda 2 2">
       <calculatedColumnFormula>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="113" dataCellStyle="Moeda 3">
+    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="121" dataCellStyle="Moeda 3">
       <calculatedColumnFormula>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="112"/>
-    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="111"/>
-    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="110"/>
+    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="120"/>
+    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="119"/>
+    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="118"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y242" totalsRowShown="0" headerRowDxfId="43" dataDxfId="42" headerRowBorderDxfId="40" tableBorderDxfId="41" totalsRowBorderDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y254" totalsRowShown="0" headerRowDxfId="117" dataDxfId="115" headerRowBorderDxfId="116" tableBorderDxfId="114" totalsRowBorderDxfId="113">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="38"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="37">
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="112"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="111">
       <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="36">
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="110">
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="33">
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="109"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="108"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="107">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="32" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="31" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="30"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="29" dataCellStyle="Normal 2 2 2">
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="106" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="105" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="104"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="103" dataCellStyle="Normal 2 2 2">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="28"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="27"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="26">
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="102"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="101"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="100">
       <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="25"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="24"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="23">
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="99"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="98"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="97">
       <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="22"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="21"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="20"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="19">
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="96"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="95"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="94"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="93">
       <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="18" dataCellStyle="Moeda">
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="92" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="17">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="91">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="16"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="15"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="14"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="90"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="89"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="88"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2594,20 +2674,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A050DE7D-8F3F-47CF-9E37-B95AFD2ED76A}">
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" style="24" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" style="23" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.42578125" customWidth="1"/>
     <col min="3" max="3" width="9.5703125" customWidth="1"/>
     <col min="4" max="4" width="11.85546875" customWidth="1"/>
-    <col min="5" max="5" width="13" style="27" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" style="27" customWidth="1"/>
+    <col min="5" max="5" width="13" style="25" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="25" customWidth="1"/>
     <col min="8" max="8" width="9.85546875" customWidth="1"/>
     <col min="9" max="9" width="10.28515625" customWidth="1"/>
     <col min="10" max="10" width="13.140625" customWidth="1"/>
     <col min="11" max="11" width="9.28515625" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" style="21" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" style="20" customWidth="1"/>
     <col min="13" max="13" width="14" customWidth="1"/>
     <col min="14" max="14" width="15.85546875" customWidth="1"/>
     <col min="15" max="15" width="15.5703125" customWidth="1"/>
@@ -2621,7 +2701,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -2633,10 +2713,10 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="24" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
@@ -2654,7 +2734,7 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="22" t="s">
+      <c r="L1" s="21" t="s">
         <v>48</v>
       </c>
       <c r="M1" s="2" t="s">
@@ -2699,10 +2779,10 @@
       <c r="D2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="10">
         <v>4275.3</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="10">
         <v>77009.210000000006</v>
       </c>
       <c r="G2" s="4">
@@ -2771,10 +2851,10 @@
       <c r="D3" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="10">
         <v>7461.93</v>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="10">
         <v>46748.29</v>
       </c>
       <c r="G3" s="4">
@@ -2825,10 +2905,10 @@
       <c r="D4" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="10">
         <v>4770.58</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="10">
         <v>89040.79</v>
       </c>
       <c r="G4" s="4">
@@ -2893,10 +2973,10 @@
       <c r="D5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="10">
         <v>7701.21</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="10">
         <v>160981.76000000001</v>
       </c>
       <c r="G5" s="4">
@@ -2957,10 +3037,10 @@
       <c r="D6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="10">
         <v>5668.48</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="10">
         <v>94110.1</v>
       </c>
       <c r="G6" s="4">
@@ -3025,10 +3105,10 @@
       <c r="D7" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="10">
         <v>8639.84</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="10">
         <v>131603.82</v>
       </c>
       <c r="G7" s="4">
@@ -3093,10 +3173,10 @@
       <c r="D8" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="10">
         <v>8971</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="10">
         <v>79084.990000000005</v>
       </c>
       <c r="G8" s="4">
@@ -3155,10 +3235,10 @@
       <c r="D9" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="10">
         <v>5954.82</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="10">
         <v>69924.039999999994</v>
       </c>
       <c r="G9" s="4">
@@ -3200,40 +3280,96 @@
       <c r="U9" s="4"/>
       <c r="V9" s="5"/>
     </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="27">
+        <v>24238.02</v>
+      </c>
+      <c r="F10" s="27">
+        <v>167202.07</v>
+      </c>
+      <c r="G10" s="4">
+        <v>2185</v>
+      </c>
+      <c r="H10" s="9">
+        <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
+        <v>0.14496243975926854</v>
+      </c>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4">
+        <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="10">
+        <v>500</v>
+      </c>
+      <c r="M10" s="9">
+        <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
+        <v>2.0628747727743438E-2</v>
+      </c>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="12">
+        <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="R10" s="13" t="e">
+        <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S10" s="14" t="e">
+        <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="5"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H9">
-    <cfRule type="cellIs" dxfId="109" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="H2:H10">
+    <cfRule type="cellIs" dxfId="87" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="86" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R9">
-    <cfRule type="cellIs" dxfId="107" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="R2:R10">
+    <cfRule type="cellIs" dxfId="85" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="84" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="83" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="104" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="82" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="81" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="80" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="79" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S9">
-    <cfRule type="expression" dxfId="100" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="S2:S10">
+    <cfRule type="expression" dxfId="78" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -3242,7 +3378,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="99" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3256,15 +3392,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y242"/>
+  <dimension ref="A1:Y254"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="10.42578125" customWidth="1"/>
     <col min="5" max="5" width="9.5703125" customWidth="1"/>
     <col min="6" max="6" width="11.85546875" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="21" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.42578125" style="21" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" style="20" customWidth="1"/>
     <col min="10" max="10" width="9.85546875" customWidth="1"/>
     <col min="11" max="11" width="10.28515625" customWidth="1"/>
     <col min="12" max="12" width="13.140625" customWidth="1"/>
@@ -3302,10 +3438,10 @@
       <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="21" t="s">
         <v>5</v>
       </c>
       <c r="I1" s="2" t="s">
@@ -23315,11 +23451,11 @@
       <c r="A234" s="8">
         <v>46268</v>
       </c>
-      <c r="B234" s="20">
+      <c r="B234" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C234" s="20">
+      <c r="C234" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -23401,11 +23537,11 @@
       <c r="A235" s="8">
         <v>46268</v>
       </c>
-      <c r="B235" s="20">
+      <c r="B235" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C235" s="20">
+      <c r="C235" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -23487,11 +23623,11 @@
       <c r="A236" s="8">
         <v>46268</v>
       </c>
-      <c r="B236" s="20">
+      <c r="B236" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C236" s="20">
+      <c r="C236" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -23573,11 +23709,11 @@
       <c r="A237" s="8">
         <v>46268</v>
       </c>
-      <c r="B237" s="20">
+      <c r="B237" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C237" s="20">
+      <c r="C237" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -23659,11 +23795,11 @@
       <c r="A238" s="8">
         <v>46268</v>
       </c>
-      <c r="B238" s="20">
+      <c r="B238" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C238" s="20">
+      <c r="C238" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -23745,11 +23881,11 @@
       <c r="A239" s="8">
         <v>46268</v>
       </c>
-      <c r="B239" s="20">
+      <c r="B239" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C239" s="20">
+      <c r="C239" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -23831,11 +23967,11 @@
       <c r="A240" s="8">
         <v>46268</v>
       </c>
-      <c r="B240" s="20">
+      <c r="B240" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C240" s="20">
+      <c r="C240" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -23917,11 +24053,11 @@
       <c r="A241" s="8">
         <v>46268</v>
       </c>
-      <c r="B241" s="20">
+      <c r="B241" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C241" s="20">
+      <c r="C241" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -24003,11 +24139,11 @@
       <c r="A242" s="8">
         <v>46268</v>
       </c>
-      <c r="B242" s="20">
+      <c r="B242" s="16">
         <f>YEAR(Tabela32[[#This Row],[Data]])</f>
         <v>2026</v>
       </c>
-      <c r="C242" s="20">
+      <c r="C242" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -24085,40 +24221,1072 @@
         <v>0</v>
       </c>
     </row>
+    <row r="243" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A243" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B243" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C243" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D243" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E243" s="4">
+        <v>4</v>
+      </c>
+      <c r="F243" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G243" s="10">
+        <v>6774.06</v>
+      </c>
+      <c r="H243" s="10">
+        <v>127133.29</v>
+      </c>
+      <c r="I243" s="4">
+        <v>635</v>
+      </c>
+      <c r="J243" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.3283133001592271E-2</v>
+      </c>
+      <c r="K243" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L243" s="15">
+        <v>0.74652777777777779</v>
+      </c>
+      <c r="M243" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4548611111111111</v>
+      </c>
+      <c r="N243" s="4">
+        <v>124827</v>
+      </c>
+      <c r="O243" s="4">
+        <v>124897</v>
+      </c>
+      <c r="P243" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>70</v>
+      </c>
+      <c r="Q243" s="4">
+        <v>166</v>
+      </c>
+      <c r="R243" s="4">
+        <v>22</v>
+      </c>
+      <c r="S243" s="4">
+        <v>22</v>
+      </c>
+      <c r="T243" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U243" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V243" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W243" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X243" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y243" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A244" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B244" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C244" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D244" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E244" s="4">
+        <v>1</v>
+      </c>
+      <c r="F244" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G244" s="10">
+        <v>7614.5</v>
+      </c>
+      <c r="H244" s="10">
+        <v>153601.28</v>
+      </c>
+      <c r="I244" s="4">
+        <v>1581</v>
+      </c>
+      <c r="J244" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.9573154598711679E-2</v>
+      </c>
+      <c r="K244" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L244" s="15">
+        <v>0.75694444444444442</v>
+      </c>
+      <c r="M244" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.46527777777777773</v>
+      </c>
+      <c r="N244" s="4">
+        <v>275420</v>
+      </c>
+      <c r="O244" s="4">
+        <v>275489</v>
+      </c>
+      <c r="P244" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>69</v>
+      </c>
+      <c r="Q244" s="4">
+        <v>157</v>
+      </c>
+      <c r="R244" s="4">
+        <v>18</v>
+      </c>
+      <c r="S244" s="4">
+        <v>18</v>
+      </c>
+      <c r="T244" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U244" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V244" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W244" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X244" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y244" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A245" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B245" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C245" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D245" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E245" s="4">
+        <v>2</v>
+      </c>
+      <c r="F245" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G245" s="10">
+        <v>7360.28</v>
+      </c>
+      <c r="H245" s="10">
+        <v>135750.18</v>
+      </c>
+      <c r="I245" s="4">
+        <v>1580</v>
+      </c>
+      <c r="J245" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.4219301955990042E-2</v>
+      </c>
+      <c r="K245" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L245" s="15">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="M245" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="N245" s="4">
+        <v>119276</v>
+      </c>
+      <c r="O245" s="4">
+        <v>119324</v>
+      </c>
+      <c r="P245" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>48</v>
+      </c>
+      <c r="Q245" s="4">
+        <v>399</v>
+      </c>
+      <c r="R245" s="4">
+        <v>22</v>
+      </c>
+      <c r="S245" s="4">
+        <v>22</v>
+      </c>
+      <c r="T245" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U245" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V245" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W245" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X245" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y245" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A246" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B246" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C246" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D246" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E246" s="4">
+        <v>5</v>
+      </c>
+      <c r="F246" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G246" s="10">
+        <v>6620.29</v>
+      </c>
+      <c r="H246" s="10">
+        <v>80748.009999999995</v>
+      </c>
+      <c r="I246" s="4">
+        <v>650</v>
+      </c>
+      <c r="J246" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.198703596534454E-2</v>
+      </c>
+      <c r="K246" s="11">
+        <v>0.30208333333333331</v>
+      </c>
+      <c r="L246" s="15">
+        <v>0.80694444444444446</v>
+      </c>
+      <c r="M246" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.5048611111111112</v>
+      </c>
+      <c r="N246" s="4">
+        <v>13010</v>
+      </c>
+      <c r="O246" s="4">
+        <v>13124</v>
+      </c>
+      <c r="P246" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>114</v>
+      </c>
+      <c r="Q246" s="4">
+        <v>104</v>
+      </c>
+      <c r="R246" s="4">
+        <v>22</v>
+      </c>
+      <c r="S246" s="4">
+        <v>22</v>
+      </c>
+      <c r="T246" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U246" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V246" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W246" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X246" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y246" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="247" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A247" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B247" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C247" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D247" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E247" s="4">
+        <v>1</v>
+      </c>
+      <c r="F247" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G247" s="10">
+        <v>9678.7000000000007</v>
+      </c>
+      <c r="H247" s="10">
+        <v>69994.460000000006</v>
+      </c>
+      <c r="I247" s="4">
+        <v>1492</v>
+      </c>
+      <c r="J247" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.13827808657999505</v>
+      </c>
+      <c r="K247" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L247" s="15">
+        <v>0.69444444444444442</v>
+      </c>
+      <c r="M247" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="N247" s="4">
+        <v>304114</v>
+      </c>
+      <c r="O247" s="4">
+        <v>304178</v>
+      </c>
+      <c r="P247" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>64</v>
+      </c>
+      <c r="Q247" s="4">
+        <v>176</v>
+      </c>
+      <c r="R247" s="4">
+        <v>16</v>
+      </c>
+      <c r="S247" s="4">
+        <v>16</v>
+      </c>
+      <c r="T247" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U247" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V247" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W247" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X247" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y247" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A248" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B248" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C248" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D248" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E248" s="4">
+        <v>1</v>
+      </c>
+      <c r="F248" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G248" s="10">
+        <v>13683.27</v>
+      </c>
+      <c r="H248" s="10">
+        <v>404291.08</v>
+      </c>
+      <c r="I248" s="4">
+        <v>2046</v>
+      </c>
+      <c r="J248" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.3845094974640548E-2</v>
+      </c>
+      <c r="K248" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L248" s="15">
+        <v>0.76388888888888884</v>
+      </c>
+      <c r="M248" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47222222222222215</v>
+      </c>
+      <c r="N248" s="4">
+        <v>291074</v>
+      </c>
+      <c r="O248" s="4">
+        <v>291117</v>
+      </c>
+      <c r="P248" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>43</v>
+      </c>
+      <c r="Q248" s="4">
+        <v>368</v>
+      </c>
+      <c r="R248" s="4">
+        <v>7</v>
+      </c>
+      <c r="S248" s="4">
+        <v>7</v>
+      </c>
+      <c r="T248" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U248" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V248" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W248" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="X248" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y248" s="5">
+        <v>38.380000000000003</v>
+      </c>
+    </row>
+    <row r="249" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A249" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B249" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C249" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D249" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E249" s="4">
+        <v>1</v>
+      </c>
+      <c r="F249" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G249" s="10">
+        <v>5115.93</v>
+      </c>
+      <c r="H249" s="10">
+        <v>80920.03</v>
+      </c>
+      <c r="I249" s="4">
+        <v>772</v>
+      </c>
+      <c r="J249" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.3222047742691148E-2</v>
+      </c>
+      <c r="K249" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L249" s="15">
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="M249" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.38750000000000001</v>
+      </c>
+      <c r="N249" s="4">
+        <v>154949</v>
+      </c>
+      <c r="O249" s="4">
+        <v>155111</v>
+      </c>
+      <c r="P249" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>162</v>
+      </c>
+      <c r="Q249" s="4">
+        <v>121</v>
+      </c>
+      <c r="R249" s="4">
+        <v>16</v>
+      </c>
+      <c r="S249" s="4">
+        <v>16</v>
+      </c>
+      <c r="T249" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U249" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V249" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W249" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X249" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y249" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="250" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A250" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B250" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C250" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D250" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E250" s="4">
+        <v>11</v>
+      </c>
+      <c r="F250" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G250" s="10">
+        <v>13686.92</v>
+      </c>
+      <c r="H250" s="10">
+        <v>172691.62</v>
+      </c>
+      <c r="I250" s="4">
+        <v>2972</v>
+      </c>
+      <c r="J250" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.9256422517780548E-2</v>
+      </c>
+      <c r="K250" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L250" s="15">
+        <v>0.66041666666666665</v>
+      </c>
+      <c r="M250" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.38958333333333334</v>
+      </c>
+      <c r="N250" s="4">
+        <v>142732</v>
+      </c>
+      <c r="O250" s="4">
+        <v>142876</v>
+      </c>
+      <c r="P250" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>144</v>
+      </c>
+      <c r="Q250" s="4">
+        <v>478</v>
+      </c>
+      <c r="R250" s="4">
+        <v>35</v>
+      </c>
+      <c r="S250" s="4">
+        <v>35</v>
+      </c>
+      <c r="T250" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U250" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V250" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W250" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X250" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y250" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A251" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B251" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C251" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D251" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E251" s="4">
+        <v>5</v>
+      </c>
+      <c r="F251" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G251" s="10">
+        <v>15341.53</v>
+      </c>
+      <c r="H251" s="10">
+        <v>277171.03000000003</v>
+      </c>
+      <c r="I251" s="4">
+        <v>2647</v>
+      </c>
+      <c r="J251" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.5350409456572713E-2</v>
+      </c>
+      <c r="K251" s="11">
+        <v>0.27361111111111114</v>
+      </c>
+      <c r="L251" s="15">
+        <v>0.71250000000000002</v>
+      </c>
+      <c r="M251" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.43888888888888888</v>
+      </c>
+      <c r="N251" s="4">
+        <v>104895</v>
+      </c>
+      <c r="O251" s="4">
+        <v>104935</v>
+      </c>
+      <c r="P251" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>40</v>
+      </c>
+      <c r="Q251" s="4">
+        <v>351</v>
+      </c>
+      <c r="R251" s="4">
+        <v>15</v>
+      </c>
+      <c r="S251" s="4">
+        <v>15</v>
+      </c>
+      <c r="T251" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U251" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V251" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W251" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X251" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y251" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A252" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B252" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C252" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D252" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E252" s="4">
+        <v>3</v>
+      </c>
+      <c r="F252" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G252" s="10">
+        <v>9489.41</v>
+      </c>
+      <c r="H252" s="10">
+        <v>112265.27</v>
+      </c>
+      <c r="I252" s="4">
+        <v>850</v>
+      </c>
+      <c r="J252" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.4526675079479155E-2</v>
+      </c>
+      <c r="K252" s="11">
+        <v>0.32291666666666669</v>
+      </c>
+      <c r="L252" s="15">
+        <v>0.71527777777777779</v>
+      </c>
+      <c r="M252" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="N252" s="4">
+        <v>280154</v>
+      </c>
+      <c r="O252" s="4">
+        <v>280202</v>
+      </c>
+      <c r="P252" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>48</v>
+      </c>
+      <c r="Q252" s="4">
+        <v>162</v>
+      </c>
+      <c r="R252" s="4">
+        <v>28</v>
+      </c>
+      <c r="S252" s="4">
+        <v>26</v>
+      </c>
+      <c r="T252" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>2</v>
+      </c>
+      <c r="U252" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="V252" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W252" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X252" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y252" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="253" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A253" s="8">
+        <v>46270</v>
+      </c>
+      <c r="B253" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C253" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D253" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E253" s="4">
+        <v>11</v>
+      </c>
+      <c r="F253" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G253" s="10">
+        <v>6635.38</v>
+      </c>
+      <c r="H253" s="10">
+        <v>76221.34</v>
+      </c>
+      <c r="I253" s="4">
+        <v>649</v>
+      </c>
+      <c r="J253" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.705409797308733E-2</v>
+      </c>
+      <c r="K253" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L253" s="15">
+        <v>0.57986111111111116</v>
+      </c>
+      <c r="M253" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.28819444444444448</v>
+      </c>
+      <c r="N253" s="4">
+        <v>119324</v>
+      </c>
+      <c r="O253" s="4">
+        <v>119471</v>
+      </c>
+      <c r="P253" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>147</v>
+      </c>
+      <c r="Q253" s="4">
+        <v>89</v>
+      </c>
+      <c r="R253" s="4">
+        <v>33</v>
+      </c>
+      <c r="S253" s="4">
+        <v>33</v>
+      </c>
+      <c r="T253" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U253" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V253" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W253" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X253" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y253" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A254" s="8">
+        <v>46270</v>
+      </c>
+      <c r="B254" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C254" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D254" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E254" s="4">
+        <v>3</v>
+      </c>
+      <c r="F254" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G254" s="10">
+        <v>2820.94</v>
+      </c>
+      <c r="H254" s="10">
+        <v>134648.97</v>
+      </c>
+      <c r="I254" s="4">
+        <v>414</v>
+      </c>
+      <c r="J254" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.0950327358612547E-2</v>
+      </c>
+      <c r="K254" s="11">
+        <v>0.31527777777777777</v>
+      </c>
+      <c r="L254" s="15">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="M254" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.2055555555555556</v>
+      </c>
+      <c r="N254" s="4">
+        <v>13124</v>
+      </c>
+      <c r="O254" s="4">
+        <v>13171</v>
+      </c>
+      <c r="P254" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>47</v>
+      </c>
+      <c r="Q254" s="4">
+        <v>138</v>
+      </c>
+      <c r="R254" s="4">
+        <v>7</v>
+      </c>
+      <c r="S254" s="4">
+        <v>7</v>
+      </c>
+      <c r="T254" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U254" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V254" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W254" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X254" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y254" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J242">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="J2:J254">
+    <cfRule type="cellIs" dxfId="76" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="75" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U242">
-    <cfRule type="cellIs" dxfId="11" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="U2:U254">
+    <cfRule type="cellIs" dxfId="74" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="73" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="72" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="71" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="70" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="69" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="68" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V242">
-    <cfRule type="expression" dxfId="4" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="V2:V254">
+    <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -24127,7 +25295,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24143,7 +25311,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D242</xm:sqref>
+          <xm:sqref>D2:D254</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1910ADFF-45B9-469D-A6C7-3A4A722A9733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C0AF570-CCB5-4528-8D2D-D8FC8AE36109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha2" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="80">
   <si>
     <t>Data</t>
   </si>
@@ -278,6 +278,12 @@
   <si>
     <t>13,13,38,38,38,38,10</t>
   </si>
+  <si>
+    <t>38,38,38,38,38</t>
+  </si>
+  <si>
+    <t>13,13,13,13,13,13,13,13,13</t>
+  </si>
 </sst>
 </file>
 
@@ -480,7 +486,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -551,12 +557,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -566,469 +566,7 @@
     <cellStyle name="Normal 2 2 2" xfId="3" xr:uid="{F6D7429B-6BC2-41D1-B818-FB0128371036}"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="145">
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="79">
     <dxf>
       <font>
         <b/>
@@ -2158,94 +1696,94 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V10" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V10" totalsRowShown="0" headerRowDxfId="78" dataDxfId="76" headerRowBorderDxfId="77" tableBorderDxfId="75" totalsRowBorderDxfId="74" headerRowCellStyle="Normal 2 2 2">
   <autoFilter ref="A1:V10" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="139"/>
-    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="138"/>
-    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="137"/>
-    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="136"/>
-    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="135" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="134" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="133"/>
-    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="132" dataCellStyle="Porcentagem">
+    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="73"/>
+    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="72"/>
+    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="71"/>
+    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="70"/>
+    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="69" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="68" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="67"/>
+    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="66" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="131"/>
-    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="130"/>
-    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="129">
+    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="65"/>
+    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="64"/>
+    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="63">
       <calculatedColumnFormula>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="128" dataCellStyle="Moeda"/>
-    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="127" dataCellStyle="Porcentagem">
+    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="62" dataCellStyle="Moeda"/>
+    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="61" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="126"/>
-    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="125"/>
-    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="124"/>
-    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="123">
+    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="60"/>
+    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="59"/>
+    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="58"/>
+    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="57">
       <calculatedColumnFormula>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="122" dataCellStyle="Moeda 2 2">
+    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="56" dataCellStyle="Moeda 2 2">
       <calculatedColumnFormula>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="121" dataCellStyle="Moeda 3">
+    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="55" dataCellStyle="Moeda 3">
       <calculatedColumnFormula>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="120"/>
-    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="119"/>
-    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="118"/>
+    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="54"/>
+    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="53"/>
+    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="52"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y254" totalsRowShown="0" headerRowDxfId="117" dataDxfId="115" headerRowBorderDxfId="116" tableBorderDxfId="114" totalsRowBorderDxfId="113">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y265" totalsRowShown="0" headerRowDxfId="51" dataDxfId="49" headerRowBorderDxfId="50" tableBorderDxfId="48" totalsRowBorderDxfId="47">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="112"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="111">
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="46"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="45">
       <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="110">
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="44">
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="109"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="108"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="107">
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="41">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="106" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="105" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="104"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="103" dataCellStyle="Normal 2 2 2">
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="40" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="39" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="38"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="37" dataCellStyle="Normal 2 2 2">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="102"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="101"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="100">
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="36"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="35"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="34">
       <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="99"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="98"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="97">
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="33"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="32"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="31">
       <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="96"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="95"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="94"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="93">
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="30"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="29"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="28"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="27">
       <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="92" dataCellStyle="Moeda">
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="26" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="91">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="25">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="90"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="89"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="88"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="24"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="23"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3291,10 +2829,10 @@
       <c r="D10" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="10">
         <v>24238.02</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="10">
         <v>167202.07</v>
       </c>
       <c r="G10" s="4">
@@ -3338,38 +2876,38 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H10">
-    <cfRule type="cellIs" dxfId="87" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="20" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R10">
-    <cfRule type="cellIs" dxfId="85" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="19" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="18" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="17" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S10">
-    <cfRule type="expression" dxfId="78" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -3378,7 +2916,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3392,7 +2930,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y254"/>
+  <dimension ref="A1:Y265"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -24225,11 +23763,11 @@
       <c r="A243" s="8">
         <v>46269</v>
       </c>
-      <c r="B243" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C243" s="26">
+      <c r="B243" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C243" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -24311,11 +23849,11 @@
       <c r="A244" s="8">
         <v>46269</v>
       </c>
-      <c r="B244" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C244" s="26">
+      <c r="B244" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C244" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -24397,11 +23935,11 @@
       <c r="A245" s="8">
         <v>46269</v>
       </c>
-      <c r="B245" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C245" s="26">
+      <c r="B245" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C245" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -24483,11 +24021,11 @@
       <c r="A246" s="8">
         <v>46269</v>
       </c>
-      <c r="B246" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C246" s="26">
+      <c r="B246" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C246" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -24569,11 +24107,11 @@
       <c r="A247" s="8">
         <v>46269</v>
       </c>
-      <c r="B247" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C247" s="26">
+      <c r="B247" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C247" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -24655,11 +24193,11 @@
       <c r="A248" s="8">
         <v>46269</v>
       </c>
-      <c r="B248" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C248" s="26">
+      <c r="B248" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C248" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -24741,11 +24279,11 @@
       <c r="A249" s="8">
         <v>46269</v>
       </c>
-      <c r="B249" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C249" s="26">
+      <c r="B249" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C249" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -24827,11 +24365,11 @@
       <c r="A250" s="8">
         <v>46269</v>
       </c>
-      <c r="B250" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C250" s="26">
+      <c r="B250" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C250" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -24913,11 +24451,11 @@
       <c r="A251" s="8">
         <v>46269</v>
       </c>
-      <c r="B251" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C251" s="26">
+      <c r="B251" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C251" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -24999,11 +24537,11 @@
       <c r="A252" s="8">
         <v>46269</v>
       </c>
-      <c r="B252" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C252" s="26">
+      <c r="B252" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C252" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -25085,11 +24623,11 @@
       <c r="A253" s="8">
         <v>46270</v>
       </c>
-      <c r="B253" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C253" s="26">
+      <c r="B253" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C253" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -25171,11 +24709,11 @@
       <c r="A254" s="8">
         <v>46270</v>
       </c>
-      <c r="B254" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C254" s="26">
+      <c r="B254" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C254" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -25253,40 +24791,986 @@
         <v>0</v>
       </c>
     </row>
+    <row r="255" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A255" s="8">
+        <v>46273</v>
+      </c>
+      <c r="B255" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C255" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D255" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E255" s="4">
+        <v>11</v>
+      </c>
+      <c r="F255" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G255" s="10">
+        <v>23365.5</v>
+      </c>
+      <c r="H255" s="10">
+        <v>451090.2</v>
+      </c>
+      <c r="I255" s="4">
+        <v>3867</v>
+      </c>
+      <c r="J255" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.1797844422246372E-2</v>
+      </c>
+      <c r="K255" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L255" s="15">
+        <v>0.75694444444444442</v>
+      </c>
+      <c r="M255" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="N255" s="4">
+        <v>104946</v>
+      </c>
+      <c r="O255" s="4">
+        <v>105079</v>
+      </c>
+      <c r="P255" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>133</v>
+      </c>
+      <c r="Q255" s="4">
+        <v>258</v>
+      </c>
+      <c r="R255" s="4">
+        <v>33</v>
+      </c>
+      <c r="S255" s="4">
+        <v>33</v>
+      </c>
+      <c r="T255" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U255" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V255" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W255" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="X255" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y255" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="256" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A256" s="8">
+        <v>46273</v>
+      </c>
+      <c r="B256" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C256" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D256" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E256" s="4">
+        <v>5</v>
+      </c>
+      <c r="F256" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G256" s="10">
+        <v>11347.38</v>
+      </c>
+      <c r="H256" s="10">
+        <v>232310.73</v>
+      </c>
+      <c r="I256" s="4">
+        <v>2674</v>
+      </c>
+      <c r="J256" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.8845699034220237E-2</v>
+      </c>
+      <c r="K256" s="11">
+        <v>0.32291666666666669</v>
+      </c>
+      <c r="L256" s="15">
+        <v>0.83819444444444446</v>
+      </c>
+      <c r="M256" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.51527777777777772</v>
+      </c>
+      <c r="N256" s="4">
+        <v>280202</v>
+      </c>
+      <c r="O256" s="4">
+        <v>280284</v>
+      </c>
+      <c r="P256" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>82</v>
+      </c>
+      <c r="Q256" s="4">
+        <v>513</v>
+      </c>
+      <c r="R256" s="4">
+        <v>30</v>
+      </c>
+      <c r="S256" s="4">
+        <v>21</v>
+      </c>
+      <c r="T256" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>9</v>
+      </c>
+      <c r="U256" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.7</v>
+      </c>
+      <c r="V256" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W256" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X256" s="4">
+        <v>9</v>
+      </c>
+      <c r="Y256" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="257" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A257" s="8">
+        <v>46273</v>
+      </c>
+      <c r="B257" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C257" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D257" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E257" s="4">
+        <v>1</v>
+      </c>
+      <c r="F257" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G257" s="10">
+        <v>1646.69</v>
+      </c>
+      <c r="H257" s="10">
+        <v>65738.399999999994</v>
+      </c>
+      <c r="I257" s="4">
+        <v>92</v>
+      </c>
+      <c r="J257" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.5049134143818531E-2</v>
+      </c>
+      <c r="K257" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L257" s="15">
+        <v>0.51527777777777772</v>
+      </c>
+      <c r="M257" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.22361111111111104</v>
+      </c>
+      <c r="N257" s="4">
+        <v>155111</v>
+      </c>
+      <c r="O257" s="4">
+        <v>155166</v>
+      </c>
+      <c r="P257" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>55</v>
+      </c>
+      <c r="Q257" s="4">
+        <v>1</v>
+      </c>
+      <c r="R257" s="4">
+        <v>1</v>
+      </c>
+      <c r="S257" s="4">
+        <v>1</v>
+      </c>
+      <c r="T257" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U257" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V257" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W257" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X257" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y257" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A258" s="8">
+        <v>46273</v>
+      </c>
+      <c r="B258" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C258" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D258" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E258" s="4">
+        <v>2</v>
+      </c>
+      <c r="F258" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G258" s="10">
+        <v>1519.38</v>
+      </c>
+      <c r="H258" s="10">
+        <v>27295.91</v>
+      </c>
+      <c r="I258" s="4">
+        <v>295</v>
+      </c>
+      <c r="J258" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.5663284352857265E-2</v>
+      </c>
+      <c r="K258" s="11">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="L258" s="15">
+        <v>0.71458333333333335</v>
+      </c>
+      <c r="M258" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.13819444444444451</v>
+      </c>
+      <c r="N258" s="4">
+        <v>155166</v>
+      </c>
+      <c r="O258" s="4">
+        <v>155216</v>
+      </c>
+      <c r="P258" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>50</v>
+      </c>
+      <c r="Q258" s="4">
+        <v>61</v>
+      </c>
+      <c r="R258" s="4">
+        <v>3</v>
+      </c>
+      <c r="S258" s="4">
+        <v>3</v>
+      </c>
+      <c r="T258" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U258" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V258" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W258" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X258" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y258" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A259" s="8">
+        <v>46273</v>
+      </c>
+      <c r="B259" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C259" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D259" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E259" s="4">
+        <v>3</v>
+      </c>
+      <c r="F259" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G259" s="10">
+        <v>10547.9</v>
+      </c>
+      <c r="H259" s="10">
+        <v>164711</v>
+      </c>
+      <c r="I259" s="4">
+        <v>3106</v>
+      </c>
+      <c r="J259" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.4038831650587991E-2</v>
+      </c>
+      <c r="K259" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L259" s="15">
+        <v>0.75416666666666665</v>
+      </c>
+      <c r="M259" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.46249999999999997</v>
+      </c>
+      <c r="N259" s="4">
+        <v>291117</v>
+      </c>
+      <c r="O259" s="4">
+        <v>291171</v>
+      </c>
+      <c r="P259" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>54</v>
+      </c>
+      <c r="Q259" s="4">
+        <v>351</v>
+      </c>
+      <c r="R259" s="4">
+        <v>16</v>
+      </c>
+      <c r="S259" s="4">
+        <v>16</v>
+      </c>
+      <c r="T259" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U259" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V259" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W259" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X259" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y259" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="260" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A260" s="8">
+        <v>46273</v>
+      </c>
+      <c r="B260" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C260" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D260" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E260" s="4">
+        <v>1</v>
+      </c>
+      <c r="F260" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Juscelino</v>
+      </c>
+      <c r="G260" s="10">
+        <v>8483.69</v>
+      </c>
+      <c r="H260" s="10">
+        <v>135088.44</v>
+      </c>
+      <c r="I260" s="4">
+        <v>1182</v>
+      </c>
+      <c r="J260" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.2801006510993837E-2</v>
+      </c>
+      <c r="K260" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L260" s="15">
+        <v>0.75</v>
+      </c>
+      <c r="M260" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4375</v>
+      </c>
+      <c r="N260" s="4">
+        <v>304179</v>
+      </c>
+      <c r="O260" s="4">
+        <v>304242</v>
+      </c>
+      <c r="P260" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>63</v>
+      </c>
+      <c r="Q260" s="4">
+        <v>177</v>
+      </c>
+      <c r="R260" s="4">
+        <v>21</v>
+      </c>
+      <c r="S260" s="4">
+        <v>21</v>
+      </c>
+      <c r="T260" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U260" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V260" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W260" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X260" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y260" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A261" s="8">
+        <v>46273</v>
+      </c>
+      <c r="B261" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C261" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D261" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E261" s="4">
+        <v>1</v>
+      </c>
+      <c r="F261" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G261" s="10">
+        <v>4900.75</v>
+      </c>
+      <c r="H261" s="10">
+        <v>150112.95000000001</v>
+      </c>
+      <c r="I261" s="4">
+        <v>1018</v>
+      </c>
+      <c r="J261" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.2647083412856784E-2</v>
+      </c>
+      <c r="K261" s="11">
+        <v>0.30208333333333331</v>
+      </c>
+      <c r="L261" s="15">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="M261" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4201388888888889</v>
+      </c>
+      <c r="N261" s="4">
+        <v>13171</v>
+      </c>
+      <c r="O261" s="4">
+        <v>13214</v>
+      </c>
+      <c r="P261" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>43</v>
+      </c>
+      <c r="Q261" s="4">
+        <v>2</v>
+      </c>
+      <c r="R261" s="4">
+        <v>1</v>
+      </c>
+      <c r="S261" s="4">
+        <v>1</v>
+      </c>
+      <c r="T261" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U261" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V261" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W261" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X261" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y261" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A262" s="8">
+        <v>46273</v>
+      </c>
+      <c r="B262" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C262" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D262" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E262" s="4">
+        <v>1</v>
+      </c>
+      <c r="F262" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G262" s="10">
+        <v>5507.61</v>
+      </c>
+      <c r="H262" s="10">
+        <v>63027.56</v>
+      </c>
+      <c r="I262" s="4">
+        <v>1394</v>
+      </c>
+      <c r="J262" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.7384153852695545E-2</v>
+      </c>
+      <c r="K262" s="11">
+        <v>0.30208333333333331</v>
+      </c>
+      <c r="L262" s="15">
+        <v>0.69444444444444442</v>
+      </c>
+      <c r="M262" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="N262" s="4">
+        <v>119471</v>
+      </c>
+      <c r="O262" s="4">
+        <v>119603</v>
+      </c>
+      <c r="P262" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>132</v>
+      </c>
+      <c r="Q262" s="4">
+        <v>131</v>
+      </c>
+      <c r="R262" s="4">
+        <v>8</v>
+      </c>
+      <c r="S262" s="4">
+        <v>8</v>
+      </c>
+      <c r="T262" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U262" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V262" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W262" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X262" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y262" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A263" s="8">
+        <v>46273</v>
+      </c>
+      <c r="B263" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C263" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D263" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E263" s="4">
+        <v>1</v>
+      </c>
+      <c r="F263" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G263" s="10">
+        <v>8389.24</v>
+      </c>
+      <c r="H263" s="10">
+        <v>348817.6</v>
+      </c>
+      <c r="I263" s="4">
+        <v>944</v>
+      </c>
+      <c r="J263" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.405050662581246E-2</v>
+      </c>
+      <c r="K263" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L263" s="15">
+        <v>0.79236111111111107</v>
+      </c>
+      <c r="M263" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.50069444444444433</v>
+      </c>
+      <c r="N263" s="4">
+        <v>275489</v>
+      </c>
+      <c r="O263" s="4">
+        <v>275543</v>
+      </c>
+      <c r="P263" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>54</v>
+      </c>
+      <c r="Q263" s="4">
+        <v>242</v>
+      </c>
+      <c r="R263" s="4">
+        <v>5</v>
+      </c>
+      <c r="S263" s="4">
+        <v>5</v>
+      </c>
+      <c r="T263" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U263" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V263" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W263" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X263" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y263" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A264" s="8">
+        <v>46273</v>
+      </c>
+      <c r="B264" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C264" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D264" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E264" s="4">
+        <v>5</v>
+      </c>
+      <c r="F264" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G264" s="10">
+        <v>15317.32</v>
+      </c>
+      <c r="H264" s="10">
+        <v>221667.21</v>
+      </c>
+      <c r="I264" s="4">
+        <v>3157</v>
+      </c>
+      <c r="J264" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.9100522355110619E-2</v>
+      </c>
+      <c r="K264" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L264" s="15">
+        <v>0.78819444444444442</v>
+      </c>
+      <c r="M264" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47569444444444442</v>
+      </c>
+      <c r="N264" s="4">
+        <v>124897</v>
+      </c>
+      <c r="O264" s="4">
+        <v>124972</v>
+      </c>
+      <c r="P264" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>75</v>
+      </c>
+      <c r="Q264" s="4">
+        <v>391</v>
+      </c>
+      <c r="R264" s="4">
+        <v>27</v>
+      </c>
+      <c r="S264" s="4">
+        <v>27</v>
+      </c>
+      <c r="T264" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U264" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V264" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W264" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X264" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y264" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A265" s="8">
+        <v>46273</v>
+      </c>
+      <c r="B265" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C265" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D265" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E265" s="4">
+        <v>2</v>
+      </c>
+      <c r="F265" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G265" s="10">
+        <v>9200.61</v>
+      </c>
+      <c r="H265" s="10">
+        <v>273734.77</v>
+      </c>
+      <c r="I265" s="4">
+        <v>1694</v>
+      </c>
+      <c r="J265" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.3611404207072412E-2</v>
+      </c>
+      <c r="K265" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L265" s="15">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="M265" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="N265" s="4">
+        <v>142899</v>
+      </c>
+      <c r="O265" s="4">
+        <v>142979</v>
+      </c>
+      <c r="P265" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>80</v>
+      </c>
+      <c r="Q265" s="4">
+        <v>224</v>
+      </c>
+      <c r="R265" s="4">
+        <v>31</v>
+      </c>
+      <c r="S265" s="4">
+        <v>31</v>
+      </c>
+      <c r="T265" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U265" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V265" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W265" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X265" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y265" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J254">
-    <cfRule type="cellIs" dxfId="76" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="J2:J265">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U254">
-    <cfRule type="cellIs" dxfId="74" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="U2:U265">
+    <cfRule type="cellIs" dxfId="8" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="6" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V254">
-    <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="V2:V265">
+    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -25295,7 +25779,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25311,7 +25795,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D254</xm:sqref>
+          <xm:sqref>D2:D265</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C0AF570-CCB5-4528-8D2D-D8FC8AE36109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755360BE-6166-49E8-A0AD-13075DCCC61D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="80">
   <si>
     <t>Data</t>
   </si>
@@ -112,9 +112,6 @@
   </si>
   <si>
     <t>IUG8882</t>
-  </si>
-  <si>
-    <t>Juscelino</t>
   </si>
   <si>
     <t>RKV1173</t>
@@ -283,6 +280,9 @@
   </si>
   <si>
     <t>13,13,13,13,13,13,13,13,13</t>
+  </si>
+  <si>
+    <t>William</t>
   </si>
 </sst>
 </file>
@@ -486,7 +486,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -557,6 +557,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -566,7 +569,392 @@
     <cellStyle name="Normal 2 2 2" xfId="3" xr:uid="{F6D7429B-6BC2-41D1-B818-FB0128371036}"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="79">
+  <dxfs count="134">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1696,94 +2084,94 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V10" totalsRowShown="0" headerRowDxfId="78" dataDxfId="76" headerRowBorderDxfId="77" tableBorderDxfId="75" totalsRowBorderDxfId="74" headerRowCellStyle="Normal 2 2 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V10" totalsRowShown="0" headerRowDxfId="133" dataDxfId="131" headerRowBorderDxfId="132" tableBorderDxfId="130" totalsRowBorderDxfId="129" headerRowCellStyle="Normal 2 2 2">
   <autoFilter ref="A1:V10" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="73"/>
-    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="72"/>
-    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="71"/>
-    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="70"/>
-    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="69" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="68" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="67"/>
-    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="66" dataCellStyle="Porcentagem">
+    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="128"/>
+    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="127"/>
+    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="126"/>
+    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="125"/>
+    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="124" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="123" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="122"/>
+    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="121" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="65"/>
-    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="64"/>
-    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="63">
+    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="120"/>
+    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="119"/>
+    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="118">
       <calculatedColumnFormula>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="62" dataCellStyle="Moeda"/>
-    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="61" dataCellStyle="Porcentagem">
+    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="117" dataCellStyle="Moeda"/>
+    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="116" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="60"/>
-    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="59"/>
-    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="58"/>
-    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="57">
+    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="115"/>
+    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="114"/>
+    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="113"/>
+    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="112">
       <calculatedColumnFormula>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="56" dataCellStyle="Moeda 2 2">
+    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="111" dataCellStyle="Moeda 2 2">
       <calculatedColumnFormula>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="55" dataCellStyle="Moeda 3">
+    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="110" dataCellStyle="Moeda 3">
       <calculatedColumnFormula>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="54"/>
-    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="53"/>
-    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="52"/>
+    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="109"/>
+    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="108"/>
+    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="107"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y265" totalsRowShown="0" headerRowDxfId="51" dataDxfId="49" headerRowBorderDxfId="50" tableBorderDxfId="48" totalsRowBorderDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y286" totalsRowShown="0" headerRowDxfId="106" dataDxfId="104" headerRowBorderDxfId="105" tableBorderDxfId="103" totalsRowBorderDxfId="102">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="46"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="45">
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="101"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="100">
       <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="44">
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="99">
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="41">
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="98"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="97"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="96">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="40" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="39" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="38"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="37" dataCellStyle="Normal 2 2 2">
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="95" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="94" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="93"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="92" dataCellStyle="Normal 2 2 2">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="36"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="35"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="34">
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="91"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="90"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="89">
       <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="33"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="32"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="31">
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="88"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="87"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="86">
       <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="30"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="29"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="28"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="27">
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="85"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="84"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="83"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="82">
       <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="26" dataCellStyle="Moeda">
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="81" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="25">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="80">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="24"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="23"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="22"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="79"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="78"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="77"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2114,95 +2502,95 @@
         <v>22</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
         <v>26</v>
-      </c>
-      <c r="B3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
         <v>30</v>
-      </c>
-      <c r="B6" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
         <v>32</v>
-      </c>
-      <c r="B7" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
         <v>34</v>
-      </c>
-      <c r="B8" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s">
         <v>38</v>
-      </c>
-      <c r="B11" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -2273,13 +2661,13 @@
         <v>10</v>
       </c>
       <c r="L1" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="N1" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>14</v>
@@ -2311,11 +2699,11 @@
         <v>46027</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E2" s="10">
         <v>4275.3</v>
@@ -2369,7 +2757,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U2" s="4">
         <v>0</v>
@@ -2383,11 +2771,11 @@
         <v>46238</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E3" s="10">
         <v>7461.93</v>
@@ -2437,11 +2825,11 @@
         <v>46241</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E4" s="10">
         <v>4770.58</v>
@@ -2491,7 +2879,7 @@
         <v>Não Atendeu a Meta</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U4" s="4">
         <v>2</v>
@@ -2505,11 +2893,11 @@
         <v>46245</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E5" s="10">
         <v>7701.21</v>
@@ -2559,7 +2947,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="U5" s="4"/>
       <c r="V5" s="5"/>
@@ -2569,11 +2957,11 @@
         <v>46247</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E6" s="10">
         <v>5668.48</v>
@@ -2623,7 +3011,7 @@
         <v>Não Atendeu a Meta</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="U6" s="4">
         <v>1</v>
@@ -2637,11 +3025,11 @@
         <v>46252</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E7" s="10">
         <v>8639.84</v>
@@ -2691,7 +3079,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="U7" s="4">
         <v>1</v>
@@ -2705,11 +3093,11 @@
         <v>46253</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E8" s="10">
         <v>8971</v>
@@ -2767,11 +3155,11 @@
         <v>46268</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E9" s="10">
         <v>5954.82</v>
@@ -2823,11 +3211,11 @@
         <v>46269</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E10" s="10">
         <v>24238.02</v>
@@ -2876,38 +3264,38 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H10">
-    <cfRule type="cellIs" dxfId="21" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="76" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="75" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R10">
-    <cfRule type="cellIs" dxfId="19" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="74" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="73" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="72" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="71" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="70" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="69" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="68" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S10">
-    <cfRule type="expression" dxfId="12" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -2916,7 +3304,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2930,7 +3318,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y265"/>
+  <dimension ref="A1:Y286"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -2962,16 +3350,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -3007,13 +3395,13 @@
         <v>13</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="R1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="S1" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>16</v>
@@ -3031,7 +3419,7 @@
         <v>20</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
@@ -3047,14 +3435,14 @@
         <v>8</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E2" s="4">
         <v>3</v>
       </c>
       <c r="F2" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>William</v>
       </c>
       <c r="G2" s="10">
         <v>8845.4</v>
@@ -3111,7 +3499,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X2" s="4">
         <v>0</v>
@@ -3133,7 +3521,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E3" s="4">
         <v>1</v>
@@ -3197,7 +3585,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W3" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X3" s="4">
         <v>0</v>
@@ -3219,7 +3607,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E4" s="4">
         <v>1</v>
@@ -3283,7 +3671,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X4" s="4">
         <v>0</v>
@@ -3305,7 +3693,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E5" s="4">
         <v>2</v>
@@ -3369,7 +3757,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X5" s="4">
         <v>0</v>
@@ -3391,7 +3779,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E6" s="4">
         <v>5</v>
@@ -3455,7 +3843,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W6" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X6" s="4">
         <v>0</v>
@@ -3477,7 +3865,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E7" s="4">
         <v>1</v>
@@ -3541,7 +3929,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W7" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X7" s="4">
         <v>0</v>
@@ -3563,7 +3951,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E8" s="4">
         <v>4</v>
@@ -3627,7 +4015,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W8" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X8" s="4">
         <v>0</v>
@@ -3656,7 +4044,7 @@
       </c>
       <c r="F9" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Juscelino</v>
+        <v>Wesley</v>
       </c>
       <c r="G9" s="10">
         <v>6077.29</v>
@@ -3713,7 +4101,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W9" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X9" s="4">
         <v>0</v>
@@ -3735,7 +4123,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E10" s="4">
         <v>1</v>
@@ -3799,7 +4187,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W10" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X10" s="4">
         <v>0</v>
@@ -3821,7 +4209,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E11" s="4">
         <v>1</v>
@@ -3885,7 +4273,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W11" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X11" s="4">
         <v>0</v>
@@ -3907,7 +4295,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E12" s="4">
         <v>11</v>
@@ -3971,7 +4359,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W12" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X12" s="4">
         <v>0</v>
@@ -3993,7 +4381,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" s="4">
         <v>2</v>
@@ -4057,7 +4445,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W13" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X13" s="4">
         <v>0</v>
@@ -4086,7 +4474,7 @@
       </c>
       <c r="F14" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Juscelino</v>
+        <v>Wesley</v>
       </c>
       <c r="G14" s="10">
         <v>15984.44</v>
@@ -4143,7 +4531,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W14" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X14" s="4">
         <v>0</v>
@@ -4165,7 +4553,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E15" s="4">
         <v>1</v>
@@ -4229,7 +4617,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W15" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X15" s="4">
         <v>0</v>
@@ -4251,7 +4639,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E16" s="4">
         <v>5</v>
@@ -4315,7 +4703,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W16" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X16" s="4">
         <v>0</v>
@@ -4337,7 +4725,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E17" s="4">
         <v>1</v>
@@ -4401,7 +4789,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W17" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X17" s="4">
         <v>0</v>
@@ -4423,14 +4811,14 @@
         <v>8</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E18" s="4">
         <v>3</v>
       </c>
       <c r="F18" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>William</v>
       </c>
       <c r="G18" s="10">
         <v>6579.78</v>
@@ -4487,7 +4875,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W18" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X18" s="4">
         <v>0</v>
@@ -4509,7 +4897,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E19" s="4">
         <v>1</v>
@@ -4573,7 +4961,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W19" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X19" s="4">
         <v>0</v>
@@ -4595,7 +4983,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E20" s="4">
         <v>1</v>
@@ -4659,7 +5047,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W20" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X20" s="4">
         <v>0</v>
@@ -4681,7 +5069,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E21" s="4">
         <v>1</v>
@@ -4745,7 +5133,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W21" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X21" s="4">
         <v>0</v>
@@ -4767,7 +5155,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E22" s="4">
         <v>2</v>
@@ -4831,7 +5219,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W22" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X22" s="4">
         <v>0</v>
@@ -4853,7 +5241,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E23" s="4">
         <v>1</v>
@@ -4917,7 +5305,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W23" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X23" s="4">
         <v>0</v>
@@ -4939,7 +5327,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E24" s="4">
         <v>11</v>
@@ -5003,7 +5391,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W24" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X24" s="4">
         <v>6</v>
@@ -5025,7 +5413,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E25" s="4">
         <v>1</v>
@@ -5089,7 +5477,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W25" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X25" s="4">
         <v>0</v>
@@ -5111,7 +5499,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E26" s="4">
         <v>2</v>
@@ -5175,7 +5563,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W26" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X26" s="4">
         <v>0</v>
@@ -5197,7 +5585,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E27" s="4">
         <v>1</v>
@@ -5261,7 +5649,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W27" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X27" s="4">
         <v>0</v>
@@ -5290,7 +5678,7 @@
       </c>
       <c r="F28" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Juscelino</v>
+        <v>Wesley</v>
       </c>
       <c r="G28" s="10">
         <v>10766.57</v>
@@ -5347,7 +5735,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W28" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X28" s="4">
         <v>0</v>
@@ -5369,14 +5757,14 @@
         <v>8</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E29" s="4">
         <v>3</v>
       </c>
       <c r="F29" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>William</v>
       </c>
       <c r="G29" s="10">
         <v>5479.41</v>
@@ -5433,7 +5821,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W29" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X29" s="4">
         <v>0</v>
@@ -5455,7 +5843,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E30" s="4">
         <v>1</v>
@@ -5519,7 +5907,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W30" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X30" s="4">
         <v>0</v>
@@ -5541,7 +5929,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E31" s="4">
         <v>1</v>
@@ -5605,7 +5993,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W31" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X31" s="4">
         <v>0</v>
@@ -5627,7 +6015,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E32" s="4">
         <v>11</v>
@@ -5691,7 +6079,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W32" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X32" s="4">
         <v>0</v>
@@ -5713,7 +6101,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E33" s="4">
         <v>1</v>
@@ -5777,7 +6165,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W33" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X33" s="4">
         <v>3</v>
@@ -5799,7 +6187,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E34" s="4">
         <v>1</v>
@@ -5863,7 +6251,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W34" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X34" s="4">
         <v>3</v>
@@ -5885,7 +6273,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E35" s="4">
         <v>1</v>
@@ -5949,7 +6337,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W35" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X35" s="4">
         <v>0</v>
@@ -5971,7 +6359,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E36" s="4">
         <v>11</v>
@@ -6035,7 +6423,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W36" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X36" s="4">
         <v>0</v>
@@ -6057,14 +6445,14 @@
         <v>8</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E37" s="4">
         <v>3</v>
       </c>
       <c r="F37" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>William</v>
       </c>
       <c r="G37" s="10">
         <v>5239.71</v>
@@ -6121,7 +6509,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W37" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X37" s="4">
         <v>0</v>
@@ -6143,7 +6531,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E38" s="4">
         <v>1</v>
@@ -6207,13 +6595,13 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W38" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X38" s="4">
         <v>2</v>
       </c>
       <c r="Y38" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.25">
@@ -6229,7 +6617,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E39" s="4">
         <v>5</v>
@@ -6293,7 +6681,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W39" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X39" s="4">
         <v>0</v>
@@ -6315,7 +6703,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E40" s="4">
         <v>1</v>
@@ -6379,7 +6767,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W40" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X40" s="4">
         <v>2</v>
@@ -6408,7 +6796,7 @@
       </c>
       <c r="F41" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Juscelino</v>
+        <v>Wesley</v>
       </c>
       <c r="G41" s="10">
         <v>10933.65</v>
@@ -6465,7 +6853,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W41" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X41" s="4">
         <v>0</v>
@@ -6487,7 +6875,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E42" s="4">
         <v>4</v>
@@ -6551,7 +6939,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W42" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X42" s="4">
         <v>1</v>
@@ -6573,7 +6961,7 @@
         <v>8</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E43" s="4">
         <v>2</v>
@@ -6637,7 +7025,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W43" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X43" s="4">
         <v>0</v>
@@ -6659,7 +7047,7 @@
         <v>8</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E44" s="4">
         <v>2</v>
@@ -6723,7 +7111,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W44" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X44" s="4">
         <v>0</v>
@@ -6745,7 +7133,7 @@
         <v>8</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E45" s="4">
         <v>1</v>
@@ -6809,7 +7197,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W45" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X45" s="4">
         <v>0</v>
@@ -6831,7 +7219,7 @@
         <v>8</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E46" s="4">
         <v>1</v>
@@ -6895,7 +7283,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W46" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X46" s="4">
         <v>0</v>
@@ -6917,7 +7305,7 @@
         <v>8</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E47" s="4">
         <v>3</v>
@@ -6981,13 +7369,13 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W47" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X47" s="4">
         <v>2</v>
       </c>
       <c r="Y47" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.25">
@@ -7010,7 +7398,7 @@
       </c>
       <c r="F48" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Juscelino</v>
+        <v>Wesley</v>
       </c>
       <c r="G48" s="10">
         <v>6699.26</v>
@@ -7067,7 +7455,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W48" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X48" s="4">
         <v>0</v>
@@ -7089,7 +7477,7 @@
         <v>8</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E49" s="4">
         <v>3</v>
@@ -7153,7 +7541,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W49" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X49" s="4">
         <v>0</v>
@@ -7175,7 +7563,7 @@
         <v>8</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E50" s="4">
         <v>5</v>
@@ -7239,13 +7627,13 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W50" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X50" s="4">
         <v>2</v>
       </c>
       <c r="Y50" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.25">
@@ -7261,7 +7649,7 @@
         <v>8</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E51" s="4">
         <v>11</v>
@@ -7325,7 +7713,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W51" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X51" s="4">
         <v>0</v>
@@ -7347,7 +7735,7 @@
         <v>8</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E52" s="4">
         <v>1</v>
@@ -7411,7 +7799,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W52" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X52" s="4">
         <v>0</v>
@@ -7433,7 +7821,7 @@
         <v>8</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E53" s="4">
         <v>1</v>
@@ -7497,7 +7885,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W53" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X53" s="4">
         <v>0</v>
@@ -7519,14 +7907,14 @@
         <v>8</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E54" s="4">
         <v>1</v>
       </c>
       <c r="F54" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>William</v>
       </c>
       <c r="G54" s="10">
         <v>13472.32</v>
@@ -7583,7 +7971,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W54" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X54" s="4">
         <v>0</v>
@@ -7605,7 +7993,7 @@
         <v>8</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E55" s="4">
         <v>1</v>
@@ -7669,7 +8057,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W55" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X55" s="4">
         <v>0</v>
@@ -7691,7 +8079,7 @@
         <v>8</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E56" s="4">
         <v>3</v>
@@ -7755,7 +8143,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W56" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X56" s="4">
         <v>0</v>
@@ -7777,7 +8165,7 @@
         <v>8</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E57" s="4">
         <v>1</v>
@@ -7841,7 +8229,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W57" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X57" s="4">
         <v>0</v>
@@ -7870,7 +8258,7 @@
       </c>
       <c r="F58" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Juscelino</v>
+        <v>Wesley</v>
       </c>
       <c r="G58" s="10">
         <v>5884.88</v>
@@ -7927,7 +8315,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W58" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X58" s="4">
         <v>0</v>
@@ -7949,7 +8337,7 @@
         <v>8</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E59" s="4">
         <v>1</v>
@@ -8013,7 +8401,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W59" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X59" s="4">
         <v>0</v>
@@ -8035,7 +8423,7 @@
         <v>8</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E60" s="4">
         <v>1</v>
@@ -8099,7 +8487,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W60" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X60" s="4">
         <v>0</v>
@@ -8121,7 +8509,7 @@
         <v>8</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E61" s="4">
         <v>5</v>
@@ -8185,7 +8573,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W61" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X61" s="4">
         <v>0</v>
@@ -8207,14 +8595,14 @@
         <v>8</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E62" s="4">
         <v>4</v>
       </c>
       <c r="F62" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>William</v>
       </c>
       <c r="G62" s="10">
         <v>13239.31</v>
@@ -8271,13 +8659,13 @@
         <v>Não Atendeu a Meta</v>
       </c>
       <c r="W62" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X62" s="4">
         <v>3</v>
       </c>
       <c r="Y62" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.25">
@@ -8293,7 +8681,7 @@
         <v>8</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E63" s="4">
         <v>11</v>
@@ -8357,7 +8745,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W63" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X63" s="4">
         <v>1</v>
@@ -8379,7 +8767,7 @@
         <v>8</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E64" s="4">
         <v>11</v>
@@ -8443,7 +8831,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W64" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X64" s="4">
         <v>0</v>
@@ -8465,7 +8853,7 @@
         <v>8</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E65" s="4">
         <v>11</v>
@@ -8529,7 +8917,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W65" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X65" s="4">
         <v>0</v>
@@ -8558,7 +8946,7 @@
       </c>
       <c r="F66" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Juscelino</v>
+        <v>Wesley</v>
       </c>
       <c r="G66" s="10">
         <v>12632.35</v>
@@ -8615,7 +9003,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W66" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X66" s="4">
         <v>0</v>
@@ -8637,7 +9025,7 @@
         <v>8</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E67" s="4">
         <v>11</v>
@@ -8701,7 +9089,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W67" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X67" s="4">
         <v>0</v>
@@ -8723,14 +9111,14 @@
         <v>8</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E68" s="4">
         <v>1</v>
       </c>
       <c r="F68" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>William</v>
       </c>
       <c r="G68" s="10">
         <v>4236.68</v>
@@ -8787,7 +9175,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W68" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X68" s="4">
         <v>0</v>
@@ -8809,7 +9197,7 @@
         <v>8</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E69" s="4">
         <v>1</v>
@@ -8873,7 +9261,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W69" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X69" s="4">
         <v>0</v>
@@ -8895,7 +9283,7 @@
         <v>8</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E70" s="4">
         <v>1</v>
@@ -8959,7 +9347,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W70" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X70" s="4">
         <v>0</v>
@@ -8981,7 +9369,7 @@
         <v>8</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E71" s="4">
         <v>11</v>
@@ -9045,7 +9433,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W71" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X71" s="4">
         <v>0</v>
@@ -9067,7 +9455,7 @@
         <v>8</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E72" s="4">
         <v>3</v>
@@ -9131,7 +9519,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W72" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X72" s="4">
         <v>0</v>
@@ -9153,7 +9541,7 @@
         <v>8</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E73" s="4">
         <v>5</v>
@@ -9217,7 +9605,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W73" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X73" s="4">
         <v>0</v>
@@ -9239,7 +9627,7 @@
         <v>8</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E74" s="4">
         <v>2</v>
@@ -9303,7 +9691,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W74" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X74" s="4">
         <v>0</v>
@@ -9325,7 +9713,7 @@
         <v>8</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E75" s="4">
         <v>3</v>
@@ -9389,7 +9777,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W75" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X75" s="4">
         <v>0</v>
@@ -9418,7 +9806,7 @@
       </c>
       <c r="F76" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Juscelino</v>
+        <v>Wesley</v>
       </c>
       <c r="G76" s="10">
         <v>10304.700000000001</v>
@@ -9475,7 +9863,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W76" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X76" s="4">
         <v>0</v>
@@ -9497,14 +9885,14 @@
         <v>8</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E77" s="4">
         <v>1</v>
       </c>
       <c r="F77" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>William</v>
       </c>
       <c r="G77" s="10">
         <v>5685.81</v>
@@ -9561,7 +9949,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W77" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X77" s="4">
         <v>0</v>
@@ -9583,7 +9971,7 @@
         <v>8</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E78" s="4">
         <v>3</v>
@@ -9647,7 +10035,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W78" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X78" s="4">
         <v>0</v>
@@ -9669,7 +10057,7 @@
         <v>8</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E79" s="4">
         <v>1</v>
@@ -9733,7 +10121,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W79" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X79" s="4">
         <v>0</v>
@@ -9755,7 +10143,7 @@
         <v>8</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E80" s="4">
         <v>1</v>
@@ -9819,7 +10207,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W80" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X80" s="4">
         <v>0</v>
@@ -9841,7 +10229,7 @@
         <v>8</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E81" s="4">
         <v>1</v>
@@ -9905,7 +10293,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W81" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X81" s="4">
         <v>0</v>
@@ -9927,7 +10315,7 @@
         <v>8</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E82" s="4">
         <v>5</v>
@@ -9991,7 +10379,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W82" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X82" s="4">
         <v>0</v>
@@ -10013,7 +10401,7 @@
         <v>8</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E83" s="4">
         <v>11</v>
@@ -10077,7 +10465,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W83" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X83" s="4">
         <v>4</v>
@@ -10099,14 +10487,14 @@
         <v>8</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E84" s="4">
         <v>11</v>
       </c>
       <c r="F84" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>William</v>
       </c>
       <c r="G84" s="10">
         <v>7378.67</v>
@@ -10163,7 +10551,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W84" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X84" s="4">
         <v>0</v>
@@ -10185,7 +10573,7 @@
         <v>8</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E85" s="4">
         <v>1</v>
@@ -10249,7 +10637,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W85" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X85" s="4">
         <v>0</v>
@@ -10271,7 +10659,7 @@
         <v>8</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E86" s="4">
         <v>3</v>
@@ -10335,7 +10723,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W86" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X86" s="4">
         <v>0</v>
@@ -10357,7 +10745,7 @@
         <v>8</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E87" s="4">
         <v>5</v>
@@ -10421,13 +10809,13 @@
         <v>Não Atendeu a Meta</v>
       </c>
       <c r="W87" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X87" s="4">
         <v>3</v>
       </c>
       <c r="Y87" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.25">
@@ -10450,7 +10838,7 @@
       </c>
       <c r="F88" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Juscelino</v>
+        <v>Wesley</v>
       </c>
       <c r="G88" s="10">
         <v>7158.89</v>
@@ -10507,7 +10895,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W88" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X88" s="4">
         <v>0</v>
@@ -10529,7 +10917,7 @@
         <v>8</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E89" s="4">
         <v>11</v>
@@ -10593,7 +10981,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W89" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X89" s="4">
         <v>0</v>
@@ -10615,7 +11003,7 @@
         <v>8</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E90" s="4">
         <v>1</v>
@@ -10679,7 +11067,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W90" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X90" s="4">
         <v>0</v>
@@ -10701,7 +11089,7 @@
         <v>8</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E91" s="4">
         <v>3</v>
@@ -10765,7 +11153,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W91" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X91" s="4">
         <v>1</v>
@@ -10787,7 +11175,7 @@
         <v>8</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E92" s="4">
         <v>1</v>
@@ -10851,7 +11239,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W92" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X92" s="4">
         <v>0</v>
@@ -10873,7 +11261,7 @@
         <v>8</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E93" s="4">
         <v>1</v>
@@ -10937,7 +11325,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W93" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X93" s="4">
         <v>0</v>
@@ -10959,7 +11347,7 @@
         <v>8</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E94" s="4">
         <v>1</v>
@@ -11023,7 +11411,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W94" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X94" s="4">
         <v>0</v>
@@ -11045,7 +11433,7 @@
         <v>8</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E95" s="4">
         <v>4</v>
@@ -11109,7 +11497,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W95" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X95" s="4">
         <v>0</v>
@@ -11131,7 +11519,7 @@
         <v>8</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E96" s="4">
         <v>1</v>
@@ -11195,7 +11583,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W96" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="X96" s="4">
         <v>0</v>
@@ -11217,7 +11605,7 @@
         <v>8</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E97" s="4">
         <v>1</v>
@@ -11281,7 +11669,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W97" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X97" s="4">
         <v>3</v>
@@ -11303,7 +11691,7 @@
         <v>8</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E98" s="4">
         <v>11</v>
@@ -11367,7 +11755,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W98" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X98" s="4">
         <v>0</v>
@@ -11389,7 +11777,7 @@
         <v>8</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E99" s="4">
         <v>1</v>
@@ -11453,7 +11841,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W99" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X99" s="4">
         <v>0</v>
@@ -11475,7 +11863,7 @@
         <v>8</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E100" s="4">
         <v>1</v>
@@ -11539,7 +11927,7 @@
         <v>Não Atendeu a Meta</v>
       </c>
       <c r="W100" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X100" s="4">
         <v>1</v>
@@ -11568,7 +11956,7 @@
       </c>
       <c r="F101" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Juscelino</v>
+        <v>Wesley</v>
       </c>
       <c r="G101" s="10">
         <v>7088.01</v>
@@ -11625,7 +12013,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W101" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X101" s="4">
         <v>0</v>
@@ -11647,7 +12035,7 @@
         <v>8</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E102" s="4">
         <v>5</v>
@@ -11711,7 +12099,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W102" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X102" s="4">
         <v>0</v>
@@ -11733,14 +12121,14 @@
         <v>8</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E103" s="4">
         <v>11</v>
       </c>
       <c r="F103" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>William</v>
       </c>
       <c r="G103" s="10">
         <v>8907.3799999999992</v>
@@ -11797,7 +12185,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W103" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X103" s="4">
         <v>0</v>
@@ -11819,7 +12207,7 @@
         <v>8</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E104" s="4">
         <v>1</v>
@@ -11883,7 +12271,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W104" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X104" s="4">
         <v>0</v>
@@ -11905,7 +12293,7 @@
         <v>8</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E105" s="4">
         <v>1</v>
@@ -11969,7 +12357,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W105" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X105" s="4">
         <v>0</v>
@@ -11991,7 +12379,7 @@
         <v>8</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E106" s="4">
         <v>11</v>
@@ -12055,7 +12443,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W106" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X106" s="4">
         <v>1</v>
@@ -12077,7 +12465,7 @@
         <v>8</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E107" s="4">
         <v>1</v>
@@ -12141,7 +12529,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W107" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X107" s="4">
         <v>2</v>
@@ -12163,14 +12551,14 @@
         <v>8</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E108" s="4">
         <v>4</v>
       </c>
       <c r="F108" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>William</v>
       </c>
       <c r="G108" s="10">
         <v>5003.6899999999996</v>
@@ -12227,7 +12615,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W108" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X108" s="4">
         <v>0</v>
@@ -12249,7 +12637,7 @@
         <v>8</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E109" s="4">
         <v>1</v>
@@ -12313,7 +12701,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W109" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X109" s="4">
         <v>0</v>
@@ -12342,7 +12730,7 @@
       </c>
       <c r="F110" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Juscelino</v>
+        <v>Wesley</v>
       </c>
       <c r="G110" s="10">
         <v>8968.25</v>
@@ -12399,7 +12787,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W110" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X110" s="4">
         <v>0</v>
@@ -12421,7 +12809,7 @@
         <v>8</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E111" s="4">
         <v>2</v>
@@ -12485,7 +12873,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W111" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X111" s="4">
         <v>2</v>
@@ -12507,7 +12895,7 @@
         <v>8</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E112" s="4">
         <v>11</v>
@@ -12571,7 +12959,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W112" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X112" s="4">
         <v>4</v>
@@ -12593,7 +12981,7 @@
         <v>8</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E113" s="4">
         <v>5</v>
@@ -12657,7 +13045,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W113" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X113" s="4">
         <v>0</v>
@@ -12679,7 +13067,7 @@
         <v>8</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E114" s="4">
         <v>1</v>
@@ -12743,7 +13131,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W114" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X114" s="4">
         <v>0</v>
@@ -12772,7 +13160,7 @@
       </c>
       <c r="F115" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Juscelino</v>
+        <v>Wesley</v>
       </c>
       <c r="G115" s="10">
         <v>6952.52</v>
@@ -12829,7 +13217,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W115" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X115" s="4">
         <v>0</v>
@@ -12851,7 +13239,7 @@
         <v>8</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E116" s="4">
         <v>1</v>
@@ -12915,7 +13303,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W116" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X116" s="4">
         <v>0</v>
@@ -12937,7 +13325,7 @@
         <v>8</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E117" s="4">
         <v>1</v>
@@ -13001,7 +13389,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W117" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X117" s="4">
         <v>0</v>
@@ -13023,14 +13411,14 @@
         <v>8</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E118" s="4">
         <v>5</v>
       </c>
       <c r="F118" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>William</v>
       </c>
       <c r="G118" s="10">
         <v>5043.58</v>
@@ -13087,7 +13475,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W118" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="X118" s="4">
         <v>0</v>
@@ -13109,7 +13497,7 @@
         <v>8</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E119" s="4">
         <v>5</v>
@@ -13173,7 +13561,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W119" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X119" s="4">
         <v>0</v>
@@ -13195,7 +13583,7 @@
         <v>8</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E120" s="4">
         <v>11</v>
@@ -13259,7 +13647,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W120" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X120" s="4">
         <v>0</v>
@@ -13281,7 +13669,7 @@
         <v>8</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E121" s="4">
         <v>1</v>
@@ -13345,7 +13733,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W121" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X121" s="4">
         <v>0</v>
@@ -13367,7 +13755,7 @@
         <v>8</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E122" s="4">
         <v>1</v>
@@ -13431,7 +13819,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W122" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X122" s="4">
         <v>0</v>
@@ -13453,7 +13841,7 @@
         <v>8</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E123" s="4">
         <v>1</v>
@@ -13517,7 +13905,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W123" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X123" s="4">
         <v>0</v>
@@ -13539,7 +13927,7 @@
         <v>8</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E124" s="4">
         <v>1</v>
@@ -13603,7 +13991,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W124" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X124" s="4">
         <v>0</v>
@@ -13625,7 +14013,7 @@
         <v>8</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E125" s="4">
         <v>2</v>
@@ -13689,7 +14077,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W125" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X125" s="4">
         <v>0</v>
@@ -13711,7 +14099,7 @@
         <v>8</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E126" s="4">
         <v>2</v>
@@ -13775,7 +14163,7 @@
         <v>Não Atendeu a Meta</v>
       </c>
       <c r="W126" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X126" s="4">
         <v>2</v>
@@ -13797,7 +14185,7 @@
         <v>8</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E127" s="4">
         <v>1</v>
@@ -13861,7 +14249,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W127" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="X127" s="4">
         <v>0</v>
@@ -13883,7 +14271,7 @@
         <v>8</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E128" s="4">
         <v>1</v>
@@ -13947,7 +14335,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W128" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X128" s="4">
         <v>0</v>
@@ -13969,14 +14357,14 @@
         <v>8</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E129" s="4">
         <v>1</v>
       </c>
       <c r="F129" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>William</v>
       </c>
       <c r="G129" s="10">
         <v>8081.76</v>
@@ -14033,7 +14421,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W129" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X129" s="4">
         <v>0</v>
@@ -14062,7 +14450,7 @@
       </c>
       <c r="F130" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Juscelino</v>
+        <v>Wesley</v>
       </c>
       <c r="G130" s="10">
         <v>6967.71</v>
@@ -14119,7 +14507,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W130" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X130" s="4">
         <v>0</v>
@@ -14141,7 +14529,7 @@
         <v>8</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E131" s="4">
         <v>11</v>
@@ -14205,7 +14593,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W131" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X131" s="4">
         <v>0</v>
@@ -14227,7 +14615,7 @@
         <v>8</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E132" s="4">
         <v>2</v>
@@ -14291,7 +14679,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W132" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X132" s="4">
         <v>0</v>
@@ -14313,7 +14701,7 @@
         <v>8</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E133" s="4">
         <v>1</v>
@@ -14377,7 +14765,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W133" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X133" s="4">
         <v>2</v>
@@ -14399,7 +14787,7 @@
         <v>8</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E134" s="4">
         <v>1</v>
@@ -14463,13 +14851,13 @@
         <v>Não Atendeu a Meta</v>
       </c>
       <c r="W134" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X134" s="4">
         <v>7</v>
       </c>
       <c r="Y134" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="135" spans="1:25" x14ac:dyDescent="0.25">
@@ -14485,7 +14873,7 @@
         <v>8</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E135" s="4">
         <v>5</v>
@@ -14549,13 +14937,13 @@
         <v>Não Atendeu a Meta</v>
       </c>
       <c r="W135" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X135" s="4">
         <v>3</v>
       </c>
       <c r="Y135" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="136" spans="1:25" x14ac:dyDescent="0.25">
@@ -14571,7 +14959,7 @@
         <v>8</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E136" s="4">
         <v>2</v>
@@ -14635,7 +15023,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W136" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X136" s="4">
         <v>3</v>
@@ -14657,7 +15045,7 @@
         <v>8</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E137" s="4">
         <v>2</v>
@@ -14721,7 +15109,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W137" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X137" s="4">
         <v>0</v>
@@ -14743,7 +15131,7 @@
         <v>8</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E138" s="4">
         <v>1</v>
@@ -14807,7 +15195,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W138" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X138" s="4">
         <v>0</v>
@@ -14829,7 +15217,7 @@
         <v>8</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E139" s="4">
         <v>4</v>
@@ -14893,7 +15281,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W139" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X139" s="4">
         <v>2</v>
@@ -14915,7 +15303,7 @@
         <v>8</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E140" s="4">
         <v>1</v>
@@ -14979,7 +15367,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W140" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X140" s="4">
         <v>0</v>
@@ -15001,7 +15389,7 @@
         <v>8</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E141" s="4">
         <v>5</v>
@@ -15065,7 +15453,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W141" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X141" s="4">
         <v>0</v>
@@ -15087,7 +15475,7 @@
         <v>8</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E142" s="4">
         <v>1</v>
@@ -15151,13 +15539,13 @@
         <v>Não Atendeu a Meta</v>
       </c>
       <c r="W142" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X142" s="4">
         <v>5</v>
       </c>
       <c r="Y142" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="143" spans="1:25" x14ac:dyDescent="0.25">
@@ -15173,7 +15561,7 @@
         <v>8</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E143" s="4">
         <v>1</v>
@@ -15237,7 +15625,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W143" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X143" s="4">
         <v>1</v>
@@ -15266,7 +15654,7 @@
       </c>
       <c r="F144" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Juscelino</v>
+        <v>Wesley</v>
       </c>
       <c r="G144" s="10">
         <v>12213.47</v>
@@ -15323,7 +15711,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W144" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X144" s="4">
         <v>0</v>
@@ -15345,7 +15733,7 @@
         <v>8</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E145" s="4">
         <v>1</v>
@@ -15409,7 +15797,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W145" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X145" s="4">
         <v>0</v>
@@ -15431,14 +15819,14 @@
         <v>8</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E146" s="4">
         <v>1</v>
       </c>
       <c r="F146" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>William</v>
       </c>
       <c r="G146" s="10">
         <v>11238.27</v>
@@ -15495,13 +15883,13 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W146" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X146" s="4">
         <v>3</v>
       </c>
       <c r="Y146" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="147" spans="1:25" x14ac:dyDescent="0.25">
@@ -15517,7 +15905,7 @@
         <v>8</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E147" s="4">
         <v>2</v>
@@ -15581,7 +15969,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W147" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X147" s="4">
         <v>0</v>
@@ -15603,7 +15991,7 @@
         <v>8</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E148" s="4">
         <v>1</v>
@@ -15667,7 +16055,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W148" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X148" s="4">
         <v>0</v>
@@ -15689,7 +16077,7 @@
         <v>8</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E149" s="4">
         <v>1</v>
@@ -15753,7 +16141,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W149" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X149" s="4">
         <v>0</v>
@@ -15775,7 +16163,7 @@
         <v>8</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E150" s="4">
         <v>2</v>
@@ -15839,7 +16227,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W150" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X150" s="4">
         <v>0</v>
@@ -15861,7 +16249,7 @@
         <v>8</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E151" s="4">
         <v>11</v>
@@ -15925,7 +16313,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W151" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X151" s="4">
         <v>0</v>
@@ -15947,7 +16335,7 @@
         <v>8</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E152" s="4">
         <v>1</v>
@@ -16011,7 +16399,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W152" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="X152" s="4">
         <v>0</v>
@@ -16033,7 +16421,7 @@
         <v>8</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E153" s="4">
         <v>1</v>
@@ -16097,7 +16485,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W153" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X153" s="4">
         <v>0</v>
@@ -16119,7 +16507,7 @@
         <v>8</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E154" s="4">
         <v>1</v>
@@ -16183,7 +16571,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W154" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X154" s="4">
         <v>0</v>
@@ -16205,7 +16593,7 @@
         <v>8</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E155" s="4">
         <v>3</v>
@@ -16269,7 +16657,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W155" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X155" s="4">
         <v>1</v>
@@ -16298,7 +16686,7 @@
       </c>
       <c r="F156" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Juscelino</v>
+        <v>Wesley</v>
       </c>
       <c r="G156" s="10">
         <v>4996.9399999999996</v>
@@ -16355,7 +16743,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W156" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X156" s="4">
         <v>0</v>
@@ -16377,7 +16765,7 @@
         <v>8</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E157" s="4">
         <v>3</v>
@@ -16441,7 +16829,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W157" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X157" s="4">
         <v>0</v>
@@ -16463,14 +16851,14 @@
         <v>8</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E158" s="4">
         <v>1</v>
       </c>
       <c r="F158" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>William</v>
       </c>
       <c r="G158" s="10">
         <v>6915.91</v>
@@ -16527,7 +16915,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W158" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X158" s="4">
         <v>0</v>
@@ -16549,7 +16937,7 @@
         <v>8</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E159" s="4">
         <v>11</v>
@@ -16613,7 +17001,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W159" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X159" s="4">
         <v>0</v>
@@ -16642,7 +17030,7 @@
       </c>
       <c r="F160" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Juscelino</v>
+        <v>Wesley</v>
       </c>
       <c r="G160" s="10">
         <v>4179.62</v>
@@ -16699,7 +17087,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W160" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X160" s="4">
         <v>0</v>
@@ -16721,7 +17109,7 @@
         <v>8</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E161" s="4">
         <v>3</v>
@@ -16785,13 +17173,13 @@
         <v>Não Atendeu a Meta</v>
       </c>
       <c r="W161" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X161" s="4">
         <v>3</v>
       </c>
       <c r="Y161" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="162" spans="1:25" x14ac:dyDescent="0.25">
@@ -16807,7 +17195,7 @@
         <v>8</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E162" s="4">
         <v>2</v>
@@ -16871,7 +17259,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W162" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X162" s="4">
         <v>0</v>
@@ -16893,14 +17281,14 @@
         <v>8</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E163" s="4">
         <v>4</v>
       </c>
       <c r="F163" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>William</v>
       </c>
       <c r="G163" s="10">
         <v>3983.6</v>
@@ -16957,7 +17345,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W163" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X163" s="4">
         <v>0</v>
@@ -16979,7 +17367,7 @@
         <v>8</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E164" s="4">
         <v>1</v>
@@ -17043,7 +17431,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W164" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X164" s="4">
         <v>0</v>
@@ -17065,7 +17453,7 @@
         <v>8</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E165" s="4">
         <v>1</v>
@@ -17129,7 +17517,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W165" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X165" s="4">
         <v>0</v>
@@ -17151,7 +17539,7 @@
         <v>8</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E166" s="4">
         <v>11</v>
@@ -17215,7 +17603,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W166" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X166" s="4">
         <v>0</v>
@@ -17237,7 +17625,7 @@
         <v>8</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E167" s="4">
         <v>1</v>
@@ -17301,7 +17689,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W167" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X167" s="4">
         <v>0</v>
@@ -17323,7 +17711,7 @@
         <v>8</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E168" s="4">
         <v>1</v>
@@ -17387,7 +17775,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W168" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X168" s="4">
         <v>0</v>
@@ -17409,7 +17797,7 @@
         <v>8</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E169" s="4">
         <v>1</v>
@@ -17473,7 +17861,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W169" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X169" s="4">
         <v>0</v>
@@ -17495,7 +17883,7 @@
         <v>8</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E170" s="4">
         <v>3</v>
@@ -17559,13 +17947,13 @@
         <v>Não Atendeu a Meta</v>
       </c>
       <c r="W170" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X170" s="4">
         <v>4</v>
       </c>
       <c r="Y170" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="171" spans="1:25" x14ac:dyDescent="0.25">
@@ -17581,7 +17969,7 @@
         <v>8</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E171" s="4">
         <v>5</v>
@@ -17645,7 +18033,7 @@
         <v>Não Atendeu a Meta</v>
       </c>
       <c r="W171" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X171" s="4">
         <v>1</v>
@@ -17667,7 +18055,7 @@
         <v>8</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E172" s="4">
         <v>11</v>
@@ -17731,7 +18119,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W172" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X172" s="4">
         <v>1</v>
@@ -17753,14 +18141,14 @@
         <v>8</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E173" s="4">
         <v>2</v>
       </c>
       <c r="F173" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>William</v>
       </c>
       <c r="G173" s="10">
         <v>11164.34</v>
@@ -17817,7 +18205,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W173" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X173" s="4">
         <v>0</v>
@@ -17846,7 +18234,7 @@
       </c>
       <c r="F174" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Juscelino</v>
+        <v>Wesley</v>
       </c>
       <c r="G174" s="10">
         <v>5030.4399999999996</v>
@@ -17903,7 +18291,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W174" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X174" s="4">
         <v>0</v>
@@ -17925,7 +18313,7 @@
         <v>8</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E175" s="4">
         <v>1</v>
@@ -17989,7 +18377,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W175" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X175" s="4">
         <v>0</v>
@@ -18011,7 +18399,7 @@
         <v>8</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E176" s="4">
         <v>2</v>
@@ -18075,7 +18463,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W176" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X176" s="4">
         <v>0</v>
@@ -18097,7 +18485,7 @@
         <v>8</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E177" s="4">
         <v>1</v>
@@ -18160,7 +18548,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W177" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X177" s="4">
         <v>0</v>
@@ -18182,7 +18570,7 @@
         <v>8</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E178" s="4">
         <v>1</v>
@@ -18246,7 +18634,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W178" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X178" s="4">
         <v>1</v>
@@ -18268,7 +18656,7 @@
         <v>8</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E179" s="4">
         <v>3</v>
@@ -18332,7 +18720,7 @@
         <v>Não Atendeu a Meta</v>
       </c>
       <c r="W179" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X179" s="4">
         <v>1</v>
@@ -18354,7 +18742,7 @@
         <v>8</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E180" s="4">
         <v>11</v>
@@ -18418,7 +18806,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W180" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X180" s="4">
         <v>0</v>
@@ -18440,7 +18828,7 @@
         <v>8</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E181" s="4">
         <v>1</v>
@@ -18504,7 +18892,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W181" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X181" s="4">
         <v>1</v>
@@ -18526,7 +18914,7 @@
         <v>8</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E182" s="4">
         <v>1</v>
@@ -18590,7 +18978,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W182" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X182" s="4">
         <v>1</v>
@@ -18612,7 +19000,7 @@
         <v>8</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E183" s="4">
         <v>1</v>
@@ -18676,7 +19064,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W183" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X183" s="4">
         <v>0</v>
@@ -18705,7 +19093,7 @@
       </c>
       <c r="F184" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Juscelino</v>
+        <v>Wesley</v>
       </c>
       <c r="G184" s="10">
         <v>4475.83</v>
@@ -18762,7 +19150,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W184" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X184" s="4">
         <v>0</v>
@@ -18784,14 +19172,14 @@
         <v>8</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E185" s="4">
         <v>0</v>
       </c>
       <c r="F185" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>William</v>
       </c>
       <c r="G185" s="10">
         <v>13667.92</v>
@@ -18848,7 +19236,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W185" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X185" s="4">
         <v>0</v>
@@ -18870,7 +19258,7 @@
         <v>8</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E186" s="4">
         <v>1</v>
@@ -18934,7 +19322,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W186" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X186" s="4">
         <v>0</v>
@@ -18956,7 +19344,7 @@
         <v>8</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E187" s="4">
         <v>2</v>
@@ -19020,7 +19408,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W187" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X187" s="4">
         <v>0</v>
@@ -19042,7 +19430,7 @@
         <v>8</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E188" s="4">
         <v>5</v>
@@ -19106,7 +19494,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W188" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X188" s="4">
         <v>0</v>
@@ -19128,7 +19516,7 @@
         <v>8</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E189" s="4">
         <v>4</v>
@@ -19192,7 +19580,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W189" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X189" s="4">
         <v>0</v>
@@ -19221,7 +19609,7 @@
       </c>
       <c r="F190" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Juscelino</v>
+        <v>Wesley</v>
       </c>
       <c r="G190" s="10">
         <v>5645.21</v>
@@ -19278,7 +19666,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W190" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X190" s="4">
         <v>0</v>
@@ -19300,7 +19688,7 @@
         <v>8</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E191" s="4">
         <v>11</v>
@@ -19364,7 +19752,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W191" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X191" s="4">
         <v>2</v>
@@ -19386,7 +19774,7 @@
         <v>8</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E192" s="4">
         <v>1</v>
@@ -19450,7 +19838,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W192" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X192" s="4">
         <v>1</v>
@@ -19472,7 +19860,7 @@
         <v>8</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E193" s="4">
         <v>1</v>
@@ -19536,7 +19924,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W193" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X193" s="4">
         <v>0</v>
@@ -19558,7 +19946,7 @@
         <v>8</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E194" s="4">
         <v>1</v>
@@ -19622,7 +20010,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W194" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X194" s="4">
         <v>1</v>
@@ -19644,14 +20032,14 @@
         <v>8</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E195" s="4">
         <v>4</v>
       </c>
       <c r="F195" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>William</v>
       </c>
       <c r="G195" s="10">
         <v>6956.26</v>
@@ -19708,7 +20096,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W195" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X195" s="4">
         <v>0</v>
@@ -19730,7 +20118,7 @@
         <v>8</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E196" s="4">
         <v>2</v>
@@ -19794,7 +20182,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W196" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X196" s="4">
         <v>1</v>
@@ -19816,7 +20204,7 @@
         <v>8</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E197" s="4">
         <v>3</v>
@@ -19880,7 +20268,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W197" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X197" s="4">
         <v>0</v>
@@ -19902,7 +20290,7 @@
         <v>8</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E198" s="4">
         <v>1</v>
@@ -19966,7 +20354,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W198" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X198" s="4">
         <v>0</v>
@@ -19988,7 +20376,7 @@
         <v>8</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E199" s="4">
         <v>1</v>
@@ -20052,13 +20440,13 @@
         <v>Não Atendeu a Meta</v>
       </c>
       <c r="W199" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X199" s="4">
         <v>14</v>
       </c>
       <c r="Y199" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="200" spans="1:25" x14ac:dyDescent="0.25">
@@ -20074,7 +20462,7 @@
         <v>8</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E200" s="4">
         <v>5</v>
@@ -20138,7 +20526,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W200" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X200" s="4">
         <v>0</v>
@@ -20160,7 +20548,7 @@
         <v>8</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E201" s="4">
         <v>1</v>
@@ -20224,7 +20612,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W201" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X201" s="4">
         <v>0</v>
@@ -20246,7 +20634,7 @@
         <v>8</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E202" s="4">
         <v>1</v>
@@ -20310,7 +20698,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W202" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X202" s="4">
         <v>0</v>
@@ -20332,7 +20720,7 @@
         <v>8</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E203" s="4">
         <v>4</v>
@@ -20396,7 +20784,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W203" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X203" s="4">
         <v>0</v>
@@ -20418,7 +20806,7 @@
         <v>8</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E204" s="4">
         <v>5</v>
@@ -20482,7 +20870,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W204" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X204" s="4">
         <v>0</v>
@@ -20504,7 +20892,7 @@
         <v>8</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E205" s="4">
         <v>11</v>
@@ -20568,7 +20956,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W205" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X205" s="4">
         <v>0</v>
@@ -20597,7 +20985,7 @@
       </c>
       <c r="F206" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Juscelino</v>
+        <v>Wesley</v>
       </c>
       <c r="G206" s="10">
         <v>10576.51</v>
@@ -20654,7 +21042,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W206" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X206" s="4">
         <v>0</v>
@@ -20676,7 +21064,7 @@
         <v>8</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E207" s="4">
         <v>5</v>
@@ -20740,7 +21128,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W207" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X207" s="4">
         <v>0</v>
@@ -20762,7 +21150,7 @@
         <v>8</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E208" s="4">
         <v>5</v>
@@ -20826,7 +21214,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W208" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X208" s="4">
         <v>0</v>
@@ -20848,7 +21236,7 @@
         <v>8</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E209" s="4">
         <v>3</v>
@@ -20912,7 +21300,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W209" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X209" s="4">
         <v>1</v>
@@ -20934,7 +21322,7 @@
         <v>8</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E210" s="4">
         <v>1</v>
@@ -20998,7 +21386,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W210" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X210" s="4">
         <v>0</v>
@@ -21020,14 +21408,14 @@
         <v>8</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E211" s="4">
         <v>1</v>
       </c>
       <c r="F211" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>William</v>
       </c>
       <c r="G211" s="10">
         <v>4864.74</v>
@@ -21084,7 +21472,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W211" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X211" s="4">
         <v>0</v>
@@ -21106,7 +21494,7 @@
         <v>8</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E212" s="4">
         <v>1</v>
@@ -21170,7 +21558,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W212" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X212" s="4">
         <v>0</v>
@@ -21192,7 +21580,7 @@
         <v>8</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E213" s="4">
         <v>1</v>
@@ -21256,7 +21644,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W213" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X213" s="4">
         <v>0</v>
@@ -21278,7 +21666,7 @@
         <v>9</v>
       </c>
       <c r="D214" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E214" s="4">
         <v>11</v>
@@ -21342,7 +21730,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W214" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X214" s="4">
         <v>0</v>
@@ -21364,7 +21752,7 @@
         <v>9</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E215" s="4">
         <v>1</v>
@@ -21428,7 +21816,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W215" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X215" s="4">
         <v>0</v>
@@ -21450,7 +21838,7 @@
         <v>9</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E216" s="4">
         <v>5</v>
@@ -21514,7 +21902,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W216" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X216" s="4">
         <v>0</v>
@@ -21536,7 +21924,7 @@
         <v>9</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E217" s="4">
         <v>1</v>
@@ -21600,7 +21988,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W217" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X217" s="4">
         <v>0</v>
@@ -21622,7 +22010,7 @@
         <v>9</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E218" s="4">
         <v>1</v>
@@ -21686,7 +22074,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W218" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X218" s="4">
         <v>0</v>
@@ -21715,7 +22103,7 @@
       </c>
       <c r="F219" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Juscelino</v>
+        <v>Wesley</v>
       </c>
       <c r="G219" s="10">
         <v>10475.75</v>
@@ -21772,7 +22160,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W219" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="X219" s="4">
         <v>0</v>
@@ -21794,7 +22182,7 @@
         <v>9</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E220" s="4">
         <v>1</v>
@@ -21858,7 +22246,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W220" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X220" s="4">
         <v>0</v>
@@ -21880,7 +22268,7 @@
         <v>9</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E221" s="4">
         <v>3</v>
@@ -21944,7 +22332,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W221" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X221" s="4">
         <v>1</v>
@@ -21966,7 +22354,7 @@
         <v>9</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E222" s="4">
         <v>1</v>
@@ -22030,7 +22418,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W222" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X222" s="4">
         <v>0</v>
@@ -22052,7 +22440,7 @@
         <v>9</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E223" s="4">
         <v>4</v>
@@ -22116,7 +22504,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W223" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X223" s="4">
         <v>0</v>
@@ -22138,7 +22526,7 @@
         <v>9</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E224" s="4">
         <v>2</v>
@@ -22202,7 +22590,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W224" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X224" s="4">
         <v>0</v>
@@ -22224,7 +22612,7 @@
         <v>9</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E225" s="4">
         <v>11</v>
@@ -22288,7 +22676,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W225" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X225" s="4">
         <v>0</v>
@@ -22310,7 +22698,7 @@
         <v>9</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E226" s="4">
         <v>5</v>
@@ -22374,7 +22762,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W226" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X226" s="4">
         <v>0</v>
@@ -22396,7 +22784,7 @@
         <v>9</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E227" s="4">
         <v>1</v>
@@ -22460,7 +22848,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W227" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="X227" s="4">
         <v>0</v>
@@ -22482,7 +22870,7 @@
         <v>9</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E228" s="4">
         <v>1</v>
@@ -22546,7 +22934,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W228" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="X228" s="4">
         <v>0</v>
@@ -22568,14 +22956,14 @@
         <v>9</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E229" s="4">
         <v>5</v>
       </c>
       <c r="F229" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>William</v>
       </c>
       <c r="G229" s="10">
         <v>13060.73</v>
@@ -22632,7 +23020,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W229" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X229" s="4">
         <v>1</v>
@@ -22654,7 +23042,7 @@
         <v>9</v>
       </c>
       <c r="D230" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E230" s="4">
         <v>1</v>
@@ -22718,7 +23106,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W230" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X230" s="4">
         <v>0</v>
@@ -22740,7 +23128,7 @@
         <v>9</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E231" s="4">
         <v>1</v>
@@ -22804,7 +23192,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W231" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X231" s="4">
         <v>0</v>
@@ -22826,7 +23214,7 @@
         <v>9</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E232" s="4">
         <v>2</v>
@@ -22890,7 +23278,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W232" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X232" s="4">
         <v>1</v>
@@ -22919,7 +23307,7 @@
       </c>
       <c r="F233" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Juscelino</v>
+        <v>Wesley</v>
       </c>
       <c r="G233" s="10">
         <v>10367.19</v>
@@ -22976,7 +23364,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W233" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X233" s="4">
         <v>0</v>
@@ -22998,7 +23386,7 @@
         <v>9</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E234" s="4">
         <v>1</v>
@@ -23062,7 +23450,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W234" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X234" s="4">
         <v>1</v>
@@ -23084,7 +23472,7 @@
         <v>9</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E235" s="4">
         <v>11</v>
@@ -23148,13 +23536,13 @@
         <v>Não Atendeu a Meta</v>
       </c>
       <c r="W235" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X235" s="4">
         <v>8</v>
       </c>
       <c r="Y235" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="236" spans="1:25" x14ac:dyDescent="0.25">
@@ -23177,7 +23565,7 @@
       </c>
       <c r="F236" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Juscelino</v>
+        <v>Wesley</v>
       </c>
       <c r="G236" s="10">
         <v>8185.35</v>
@@ -23234,7 +23622,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W236" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X236" s="4">
         <v>0</v>
@@ -23256,14 +23644,14 @@
         <v>9</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E237" s="4">
         <v>5</v>
       </c>
       <c r="F237" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>William</v>
       </c>
       <c r="G237" s="10">
         <v>7540.74</v>
@@ -23320,7 +23708,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W237" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X237" s="4">
         <v>0</v>
@@ -23342,7 +23730,7 @@
         <v>9</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E238" s="4">
         <v>1</v>
@@ -23406,7 +23794,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W238" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X238" s="4">
         <v>0</v>
@@ -23428,7 +23816,7 @@
         <v>9</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E239" s="4">
         <v>4</v>
@@ -23492,7 +23880,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W239" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X239" s="4">
         <v>0</v>
@@ -23514,7 +23902,7 @@
         <v>9</v>
       </c>
       <c r="D240" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E240" s="4">
         <v>2</v>
@@ -23578,7 +23966,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W240" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X240" s="4">
         <v>0</v>
@@ -23600,7 +23988,7 @@
         <v>9</v>
       </c>
       <c r="D241" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E241" s="4">
         <v>3</v>
@@ -23664,7 +24052,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W241" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X241" s="4">
         <v>0</v>
@@ -23686,7 +24074,7 @@
         <v>9</v>
       </c>
       <c r="D242" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E242" s="4">
         <v>1</v>
@@ -23750,7 +24138,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W242" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X242" s="4">
         <v>0</v>
@@ -23772,14 +24160,14 @@
         <v>9</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E243" s="4">
         <v>4</v>
       </c>
       <c r="F243" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>William</v>
       </c>
       <c r="G243" s="10">
         <v>6774.06</v>
@@ -23836,7 +24224,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W243" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X243" s="4">
         <v>0</v>
@@ -23858,7 +24246,7 @@
         <v>9</v>
       </c>
       <c r="D244" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E244" s="4">
         <v>1</v>
@@ -23922,7 +24310,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W244" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X244" s="4">
         <v>0</v>
@@ -23944,7 +24332,7 @@
         <v>9</v>
       </c>
       <c r="D245" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E245" s="4">
         <v>2</v>
@@ -24008,7 +24396,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W245" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X245" s="4">
         <v>0</v>
@@ -24030,7 +24418,7 @@
         <v>9</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E246" s="4">
         <v>5</v>
@@ -24094,7 +24482,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W246" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X246" s="4">
         <v>0</v>
@@ -24116,7 +24504,7 @@
         <v>9</v>
       </c>
       <c r="D247" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E247" s="4">
         <v>1</v>
@@ -24180,7 +24568,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W247" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X247" s="4">
         <v>0</v>
@@ -24202,7 +24590,7 @@
         <v>9</v>
       </c>
       <c r="D248" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E248" s="4">
         <v>1</v>
@@ -24266,7 +24654,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W248" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="X248" s="4">
         <v>0</v>
@@ -24288,7 +24676,7 @@
         <v>9</v>
       </c>
       <c r="D249" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E249" s="4">
         <v>1</v>
@@ -24352,7 +24740,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W249" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X249" s="4">
         <v>0</v>
@@ -24374,14 +24762,14 @@
         <v>9</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E250" s="4">
         <v>11</v>
       </c>
       <c r="F250" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>William</v>
       </c>
       <c r="G250" s="10">
         <v>13686.92</v>
@@ -24438,7 +24826,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W250" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X250" s="4">
         <v>0</v>
@@ -24460,7 +24848,7 @@
         <v>9</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E251" s="4">
         <v>5</v>
@@ -24524,7 +24912,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W251" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X251" s="4">
         <v>0</v>
@@ -24546,7 +24934,7 @@
         <v>9</v>
       </c>
       <c r="D252" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E252" s="4">
         <v>3</v>
@@ -24610,13 +24998,13 @@
         <v>Não Atendeu a Meta</v>
       </c>
       <c r="W252" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X252" s="4">
         <v>2</v>
       </c>
       <c r="Y252" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="253" spans="1:25" x14ac:dyDescent="0.25">
@@ -24632,7 +25020,7 @@
         <v>9</v>
       </c>
       <c r="D253" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E253" s="4">
         <v>11</v>
@@ -24696,7 +25084,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W253" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X253" s="4">
         <v>0</v>
@@ -24718,7 +25106,7 @@
         <v>9</v>
       </c>
       <c r="D254" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E254" s="4">
         <v>3</v>
@@ -24782,7 +25170,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W254" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X254" s="4">
         <v>0</v>
@@ -24804,7 +25192,7 @@
         <v>9</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E255" s="4">
         <v>11</v>
@@ -24868,13 +25256,13 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W255" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X255" s="4">
         <v>0</v>
       </c>
       <c r="Y255" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="256" spans="1:25" x14ac:dyDescent="0.25">
@@ -24890,7 +25278,7 @@
         <v>9</v>
       </c>
       <c r="D256" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E256" s="4">
         <v>5</v>
@@ -24954,13 +25342,13 @@
         <v>Não Atendeu a Meta</v>
       </c>
       <c r="W256" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X256" s="4">
         <v>9</v>
       </c>
       <c r="Y256" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="257" spans="1:25" x14ac:dyDescent="0.25">
@@ -24976,7 +25364,7 @@
         <v>9</v>
       </c>
       <c r="D257" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E257" s="4">
         <v>1</v>
@@ -25040,7 +25428,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W257" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X257" s="4">
         <v>0</v>
@@ -25062,7 +25450,7 @@
         <v>9</v>
       </c>
       <c r="D258" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E258" s="4">
         <v>2</v>
@@ -25126,7 +25514,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W258" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X258" s="4">
         <v>0</v>
@@ -25148,7 +25536,7 @@
         <v>9</v>
       </c>
       <c r="D259" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E259" s="4">
         <v>3</v>
@@ -25212,7 +25600,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W259" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X259" s="4">
         <v>1</v>
@@ -25241,7 +25629,7 @@
       </c>
       <c r="F260" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Juscelino</v>
+        <v>Wesley</v>
       </c>
       <c r="G260" s="10">
         <v>8483.69</v>
@@ -25298,7 +25686,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W260" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X260" s="4">
         <v>0</v>
@@ -25320,7 +25708,7 @@
         <v>9</v>
       </c>
       <c r="D261" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E261" s="4">
         <v>1</v>
@@ -25384,7 +25772,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W261" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X261" s="4">
         <v>0</v>
@@ -25406,7 +25794,7 @@
         <v>9</v>
       </c>
       <c r="D262" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E262" s="4">
         <v>1</v>
@@ -25470,7 +25858,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W262" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="X262" s="4">
         <v>0</v>
@@ -25492,7 +25880,7 @@
         <v>9</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E263" s="4">
         <v>1</v>
@@ -25556,7 +25944,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W263" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X263" s="4">
         <v>0</v>
@@ -25578,14 +25966,14 @@
         <v>9</v>
       </c>
       <c r="D264" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E264" s="4">
         <v>5</v>
       </c>
       <c r="F264" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>William</v>
       </c>
       <c r="G264" s="10">
         <v>15317.32</v>
@@ -25642,7 +26030,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W264" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X264" s="4">
         <v>0</v>
@@ -25664,7 +26052,7 @@
         <v>9</v>
       </c>
       <c r="D265" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E265" s="4">
         <v>2</v>
@@ -25728,49 +26116,1855 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W265" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X265" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y265" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A266" s="8">
+        <v>46274</v>
+      </c>
+      <c r="B266" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C266" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D266" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E266" s="4">
+        <v>3</v>
+      </c>
+      <c r="F266" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G266" s="10">
+        <v>6363.45</v>
+      </c>
+      <c r="H266" s="10">
+        <v>192714.53</v>
+      </c>
+      <c r="I266" s="4">
+        <v>1387</v>
+      </c>
+      <c r="J266" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.3020084162828825E-2</v>
+      </c>
+      <c r="K266" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L266" s="15">
+        <v>0.74305555555555558</v>
+      </c>
+      <c r="M266" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="N266" s="4">
+        <v>119633</v>
+      </c>
+      <c r="O266" s="4">
+        <v>119690</v>
+      </c>
+      <c r="P266" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>57</v>
+      </c>
+      <c r="Q266" s="4">
+        <v>316</v>
+      </c>
+      <c r="R266" s="4">
+        <v>16</v>
+      </c>
+      <c r="S266" s="4">
+        <v>16</v>
+      </c>
+      <c r="T266" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U266" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V266" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W266" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X266" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y266" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A267" s="8">
+        <v>46274</v>
+      </c>
+      <c r="B267" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C267" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D267" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E267" s="4">
+        <v>5</v>
+      </c>
+      <c r="F267" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G267" s="10">
+        <v>8630.99</v>
+      </c>
+      <c r="H267" s="10">
+        <v>188763.4</v>
+      </c>
+      <c r="I267" s="4">
+        <v>2529</v>
+      </c>
+      <c r="J267" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.5723853246974783E-2</v>
+      </c>
+      <c r="K267" s="11">
+        <v>0.30208333333333331</v>
+      </c>
+      <c r="L267" s="15">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M267" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="N267" s="4">
+        <v>280284</v>
+      </c>
+      <c r="O267" s="4">
+        <v>280306</v>
+      </c>
+      <c r="P267" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>22</v>
+      </c>
+      <c r="Q267" s="4">
+        <v>415</v>
+      </c>
+      <c r="R267" s="4">
+        <v>28</v>
+      </c>
+      <c r="S267" s="4">
+        <v>28</v>
+      </c>
+      <c r="T267" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U267" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V267" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W267" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X267" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y267" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A268" s="8">
+        <v>46274</v>
+      </c>
+      <c r="B268" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C268" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D268" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E268" s="4">
+        <v>11</v>
+      </c>
+      <c r="F268" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G268" s="10">
+        <v>23231.13</v>
+      </c>
+      <c r="H268" s="10">
+        <v>568767.07999999996</v>
+      </c>
+      <c r="I268" s="4">
+        <v>3937</v>
+      </c>
+      <c r="J268" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.0844716258894596E-2</v>
+      </c>
+      <c r="K268" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L268" s="15">
+        <v>0.79652777777777772</v>
+      </c>
+      <c r="M268" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.52569444444444446</v>
+      </c>
+      <c r="N268" s="4">
+        <v>105079</v>
+      </c>
+      <c r="O268" s="4">
+        <v>105230</v>
+      </c>
+      <c r="P268" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>151</v>
+      </c>
+      <c r="Q268" s="4">
+        <v>219</v>
+      </c>
+      <c r="R268" s="4">
+        <v>19</v>
+      </c>
+      <c r="S268" s="4">
+        <v>19</v>
+      </c>
+      <c r="T268" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U268" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V268" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W268" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X268" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y268" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A269" s="8">
+        <v>46274</v>
+      </c>
+      <c r="B269" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C269" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D269" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E269" s="4">
+        <v>5</v>
+      </c>
+      <c r="F269" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G269" s="10">
+        <v>6408.08</v>
+      </c>
+      <c r="H269" s="10">
+        <v>114752.32000000001</v>
+      </c>
+      <c r="I269" s="4">
+        <v>1427</v>
+      </c>
+      <c r="J269" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.5842705402383147E-2</v>
+      </c>
+      <c r="K269" s="11">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="L269" s="15">
+        <v>0.78125</v>
+      </c>
+      <c r="M269" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4826388888888889</v>
+      </c>
+      <c r="N269" s="4">
+        <v>13214</v>
+      </c>
+      <c r="O269" s="4">
+        <v>13253</v>
+      </c>
+      <c r="P269" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>39</v>
+      </c>
+      <c r="Q269" s="4">
+        <v>599</v>
+      </c>
+      <c r="R269" s="4">
+        <v>3</v>
+      </c>
+      <c r="S269" s="4">
+        <v>3</v>
+      </c>
+      <c r="T269" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U269" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V269" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W269" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X269" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y269" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A270" s="8">
+        <v>46274</v>
+      </c>
+      <c r="B270" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C270" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D270" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E270" s="4">
+        <v>1</v>
+      </c>
+      <c r="F270" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G270" s="10">
+        <v>12077</v>
+      </c>
+      <c r="H270" s="10">
+        <v>194565.5</v>
+      </c>
+      <c r="I270" s="4">
+        <v>2323</v>
+      </c>
+      <c r="J270" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.2071641683648954E-2</v>
+      </c>
+      <c r="K270" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L270" s="15">
+        <v>0.80763888888888891</v>
+      </c>
+      <c r="M270" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.51597222222222228</v>
+      </c>
+      <c r="N270" s="4">
+        <v>304242</v>
+      </c>
+      <c r="O270" s="4">
+        <v>304326</v>
+      </c>
+      <c r="P270" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>84</v>
+      </c>
+      <c r="Q270" s="4">
+        <v>229</v>
+      </c>
+      <c r="R270" s="4">
+        <v>41</v>
+      </c>
+      <c r="S270" s="4">
+        <v>41</v>
+      </c>
+      <c r="T270" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U270" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V270" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W270" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="X270" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y270" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A271" s="8">
+        <v>46274</v>
+      </c>
+      <c r="B271" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C271" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D271" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E271" s="4">
+        <v>1</v>
+      </c>
+      <c r="F271" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Manoel</v>
+      </c>
+      <c r="G271" s="10">
+        <v>512.91</v>
+      </c>
+      <c r="H271" s="10">
+        <v>4311.4799999999996</v>
+      </c>
+      <c r="I271" s="4">
+        <v>9.1</v>
+      </c>
+      <c r="J271" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.11896378969634558</v>
+      </c>
+      <c r="K271" s="11">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="L271" s="15">
+        <v>0.73124999999999996</v>
+      </c>
+      <c r="M271" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.22083333333333333</v>
+      </c>
+      <c r="N271" s="4">
+        <v>11930</v>
+      </c>
+      <c r="O271" s="4">
+        <v>11968</v>
+      </c>
+      <c r="P271" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>38</v>
+      </c>
+      <c r="Q271" s="4">
+        <v>10</v>
+      </c>
+      <c r="R271" s="4">
+        <v>1</v>
+      </c>
+      <c r="S271" s="4">
+        <v>1</v>
+      </c>
+      <c r="T271" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U271" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V271" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W271" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X271" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y271" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A272" s="8">
+        <v>46274</v>
+      </c>
+      <c r="B272" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C272" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D272" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E272" s="4">
+        <v>1</v>
+      </c>
+      <c r="F272" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G272" s="10">
+        <v>2603.98</v>
+      </c>
+      <c r="H272" s="10">
+        <v>52384.78</v>
+      </c>
+      <c r="I272" s="4">
+        <v>199</v>
+      </c>
+      <c r="J272" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.9708713103309779E-2</v>
+      </c>
+      <c r="K272" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L272" s="15">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="M272" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="N272" s="4">
+        <v>275543</v>
+      </c>
+      <c r="O272" s="4">
+        <v>275573</v>
+      </c>
+      <c r="P272" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>30</v>
+      </c>
+      <c r="Q272" s="4">
+        <v>47</v>
+      </c>
+      <c r="R272" s="4">
+        <v>2</v>
+      </c>
+      <c r="S272" s="4">
+        <v>2</v>
+      </c>
+      <c r="T272" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U272" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V272" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W272" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="X265" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y265" s="5">
+      <c r="X272" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y272" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A273" s="8">
+        <v>46274</v>
+      </c>
+      <c r="B273" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C273" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D273" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E273" s="4">
+        <v>1</v>
+      </c>
+      <c r="F273" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G273" s="10">
+        <v>692.88</v>
+      </c>
+      <c r="H273" s="10">
+        <v>7644</v>
+      </c>
+      <c r="I273" s="4">
+        <v>51</v>
+      </c>
+      <c r="J273" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>9.0643642072213496E-2</v>
+      </c>
+      <c r="K273" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L273" s="15">
+        <v>0.72777777777777775</v>
+      </c>
+      <c r="M273" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.43611111111111106</v>
+      </c>
+      <c r="N273" s="4">
+        <v>155216</v>
+      </c>
+      <c r="O273" s="4">
+        <v>155311</v>
+      </c>
+      <c r="P273" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>95</v>
+      </c>
+      <c r="Q273" s="4">
+        <v>1</v>
+      </c>
+      <c r="R273" s="4">
+        <v>1</v>
+      </c>
+      <c r="S273" s="4">
+        <v>1</v>
+      </c>
+      <c r="T273" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U273" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V273" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W273" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X273" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y273" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A274" s="8">
+        <v>46274</v>
+      </c>
+      <c r="B274" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C274" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D274" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E274" s="4">
+        <v>4</v>
+      </c>
+      <c r="F274" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G274" s="10">
+        <v>3712.6</v>
+      </c>
+      <c r="H274" s="10">
+        <v>97729.68</v>
+      </c>
+      <c r="I274" s="4">
+        <v>1241</v>
+      </c>
+      <c r="J274" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.7988459595897583E-2</v>
+      </c>
+      <c r="K274" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L274" s="15">
+        <v>0.73611111111111116</v>
+      </c>
+      <c r="M274" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44444444444444448</v>
+      </c>
+      <c r="N274" s="4">
+        <v>124972</v>
+      </c>
+      <c r="O274" s="4">
+        <v>125031</v>
+      </c>
+      <c r="P274" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>59</v>
+      </c>
+      <c r="Q274" s="4">
+        <v>227</v>
+      </c>
+      <c r="R274" s="4">
+        <v>11</v>
+      </c>
+      <c r="S274" s="4">
+        <v>11</v>
+      </c>
+      <c r="T274" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U274" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V274" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W274" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X274" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y274" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A275" s="8">
+        <v>46274</v>
+      </c>
+      <c r="B275" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C275" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D275" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E275" s="4">
+        <v>2</v>
+      </c>
+      <c r="F275" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G275" s="10">
+        <v>11696.65</v>
+      </c>
+      <c r="H275" s="10">
+        <v>239969.72</v>
+      </c>
+      <c r="I275" s="4">
+        <v>1889</v>
+      </c>
+      <c r="J275" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.8742191306469833E-2</v>
+      </c>
+      <c r="K275" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L275" s="15">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="M275" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.40624999999999994</v>
+      </c>
+      <c r="N275" s="4">
+        <v>142979</v>
+      </c>
+      <c r="O275" s="4">
+        <v>143039</v>
+      </c>
+      <c r="P275" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>60</v>
+      </c>
+      <c r="Q275" s="4">
+        <v>370</v>
+      </c>
+      <c r="R275" s="4">
+        <v>31</v>
+      </c>
+      <c r="S275" s="4">
+        <v>31</v>
+      </c>
+      <c r="T275" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U275" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V275" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W275" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X275" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y275" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A276" s="8">
+        <v>46274</v>
+      </c>
+      <c r="B276" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C276" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D276" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E276" s="4">
+        <v>2</v>
+      </c>
+      <c r="F276" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G276" s="10">
+        <v>7083.64</v>
+      </c>
+      <c r="H276" s="10">
+        <v>128076.66</v>
+      </c>
+      <c r="I276" s="4">
+        <v>2148</v>
+      </c>
+      <c r="J276" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.5307813304937843E-2</v>
+      </c>
+      <c r="K276" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L276" s="15">
+        <v>0.74305555555555558</v>
+      </c>
+      <c r="M276" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="N276" s="4">
+        <v>291172</v>
+      </c>
+      <c r="O276" s="4">
+        <v>291225</v>
+      </c>
+      <c r="P276" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>53</v>
+      </c>
+      <c r="Q276" s="4">
+        <v>468</v>
+      </c>
+      <c r="R276" s="4">
+        <v>26</v>
+      </c>
+      <c r="S276" s="4">
+        <v>26</v>
+      </c>
+      <c r="T276" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U276" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V276" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W276" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X276" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y276" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A277" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B277" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C277" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D277" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E277" s="4">
+        <v>5</v>
+      </c>
+      <c r="F277" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G277" s="10">
+        <v>11188.55</v>
+      </c>
+      <c r="H277" s="10">
+        <v>300110.93</v>
+      </c>
+      <c r="I277" s="4">
+        <v>2883</v>
+      </c>
+      <c r="J277" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.7281381254591427E-2</v>
+      </c>
+      <c r="K277" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L277" s="15">
+        <v>0.74652777777777779</v>
+      </c>
+      <c r="M277" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4548611111111111</v>
+      </c>
+      <c r="N277" s="4">
+        <v>280306</v>
+      </c>
+      <c r="O277" s="4">
+        <v>280434</v>
+      </c>
+      <c r="P277" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>128</v>
+      </c>
+      <c r="Q277" s="4">
+        <v>549</v>
+      </c>
+      <c r="R277" s="4">
+        <v>30</v>
+      </c>
+      <c r="S277" s="4">
+        <v>30</v>
+      </c>
+      <c r="T277" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U277" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V277" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W277" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X277" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y277" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A278" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B278" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C278" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D278" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E278" s="4">
+        <v>1</v>
+      </c>
+      <c r="F278" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G278" s="10">
+        <v>11866.81</v>
+      </c>
+      <c r="H278" s="10">
+        <v>161792.17000000001</v>
+      </c>
+      <c r="I278" s="4">
+        <v>2922</v>
+      </c>
+      <c r="J278" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.3346009266084991E-2</v>
+      </c>
+      <c r="K278" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L278" s="15">
+        <v>0.76388888888888884</v>
+      </c>
+      <c r="M278" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47222222222222215</v>
+      </c>
+      <c r="N278" s="4">
+        <v>304326</v>
+      </c>
+      <c r="O278" s="4">
+        <v>304416</v>
+      </c>
+      <c r="P278" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>90</v>
+      </c>
+      <c r="Q278" s="4">
+        <v>382</v>
+      </c>
+      <c r="R278" s="4">
+        <v>26</v>
+      </c>
+      <c r="S278" s="4">
+        <v>26</v>
+      </c>
+      <c r="T278" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U278" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V278" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W278" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="X278" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y278" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A279" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B279" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C279" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D279" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E279" s="4">
+        <v>11</v>
+      </c>
+      <c r="F279" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G279" s="10">
+        <v>15619.95</v>
+      </c>
+      <c r="H279" s="10">
+        <v>325047.38</v>
+      </c>
+      <c r="I279" s="4">
+        <v>2613</v>
+      </c>
+      <c r="J279" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.8054379026220735E-2</v>
+      </c>
+      <c r="K279" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L279" s="15">
+        <v>0.75763888888888886</v>
+      </c>
+      <c r="M279" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.48680555555555555</v>
+      </c>
+      <c r="N279" s="4">
+        <v>105230</v>
+      </c>
+      <c r="O279" s="4">
+        <v>105359</v>
+      </c>
+      <c r="P279" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>129</v>
+      </c>
+      <c r="Q279" s="4">
+        <v>315</v>
+      </c>
+      <c r="R279" s="4">
+        <v>37</v>
+      </c>
+      <c r="S279" s="4">
+        <v>37</v>
+      </c>
+      <c r="T279" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U279" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V279" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W279" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X279" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y279" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A280" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B280" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C280" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D280" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E280" s="4">
+        <v>11</v>
+      </c>
+      <c r="F280" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G280" s="10">
+        <v>11376.6</v>
+      </c>
+      <c r="H280" s="10">
+        <v>255027.26</v>
+      </c>
+      <c r="I280" s="4">
+        <v>2886</v>
+      </c>
+      <c r="J280" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.460934882020063E-2</v>
+      </c>
+      <c r="K280" s="11">
+        <v>0.27430555555555558</v>
+      </c>
+      <c r="L280" s="15">
+        <v>0.79374999999999996</v>
+      </c>
+      <c r="M280" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.51944444444444438</v>
+      </c>
+      <c r="N280" s="4">
+        <v>13253</v>
+      </c>
+      <c r="O280" s="4">
+        <v>13402</v>
+      </c>
+      <c r="P280" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>149</v>
+      </c>
+      <c r="Q280" s="4">
+        <v>298</v>
+      </c>
+      <c r="R280" s="4">
+        <v>20</v>
+      </c>
+      <c r="S280" s="4">
+        <v>20</v>
+      </c>
+      <c r="T280" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U280" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V280" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W280" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X280" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y280" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A281" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B281" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C281" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D281" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E281" s="4">
+        <v>2</v>
+      </c>
+      <c r="F281" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G281" s="10">
+        <v>6643.12</v>
+      </c>
+      <c r="H281" s="10">
+        <v>124444.41</v>
+      </c>
+      <c r="I281" s="4">
+        <v>2173</v>
+      </c>
+      <c r="J281" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.3382229061152683E-2</v>
+      </c>
+      <c r="K281" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L281" s="15">
+        <v>0.69444444444444442</v>
+      </c>
+      <c r="M281" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4236111111111111</v>
+      </c>
+      <c r="N281" s="4">
+        <v>143039</v>
+      </c>
+      <c r="O281" s="4">
+        <v>143088</v>
+      </c>
+      <c r="P281" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>49</v>
+      </c>
+      <c r="Q281" s="4">
+        <v>405</v>
+      </c>
+      <c r="R281" s="4">
+        <v>16</v>
+      </c>
+      <c r="S281" s="4">
+        <v>16</v>
+      </c>
+      <c r="T281" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U281" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V281" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W281" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X281" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y281" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A282" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B282" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C282" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D282" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E282" s="4">
+        <v>1</v>
+      </c>
+      <c r="F282" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G282" s="10">
+        <v>3912.33</v>
+      </c>
+      <c r="H282" s="10">
+        <v>99851.520000000004</v>
+      </c>
+      <c r="I282" s="4">
+        <v>796</v>
+      </c>
+      <c r="J282" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.9181476656539628E-2</v>
+      </c>
+      <c r="K282" s="11">
+        <v>0.49305555555555558</v>
+      </c>
+      <c r="L282" s="15">
+        <v>0.76111111111111107</v>
+      </c>
+      <c r="M282" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.26805555555555549</v>
+      </c>
+      <c r="N282" s="4">
+        <v>275543</v>
+      </c>
+      <c r="O282" s="4">
+        <v>275626</v>
+      </c>
+      <c r="P282" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>83</v>
+      </c>
+      <c r="Q282" s="4">
+        <v>9</v>
+      </c>
+      <c r="R282" s="4">
+        <v>4</v>
+      </c>
+      <c r="S282" s="4">
+        <v>4</v>
+      </c>
+      <c r="T282" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U282" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V282" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W282" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X282" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y282" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A283" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B283" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C283" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D283" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E283" s="4">
+        <v>1</v>
+      </c>
+      <c r="F283" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G283" s="10">
+        <v>3701.45</v>
+      </c>
+      <c r="H283" s="10">
+        <v>123607.77</v>
+      </c>
+      <c r="I283" s="4">
+        <v>168</v>
+      </c>
+      <c r="J283" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.9945123999890941E-2</v>
+      </c>
+      <c r="K283" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L283" s="15">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="M283" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="N283" s="4">
+        <v>291225</v>
+      </c>
+      <c r="O283" s="4">
+        <v>291267</v>
+      </c>
+      <c r="P283" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>42</v>
+      </c>
+      <c r="Q283" s="4">
+        <v>156</v>
+      </c>
+      <c r="R283" s="4">
+        <v>6</v>
+      </c>
+      <c r="S283" s="4">
+        <v>6</v>
+      </c>
+      <c r="T283" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U283" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V283" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W283" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X283" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y283" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A284" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B284" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C284" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D284" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E284" s="4">
+        <v>3</v>
+      </c>
+      <c r="F284" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G284" s="10">
+        <v>9120.92</v>
+      </c>
+      <c r="H284" s="10">
+        <v>202548.46</v>
+      </c>
+      <c r="I284" s="4">
+        <v>1212</v>
+      </c>
+      <c r="J284" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.5030803986364547E-2</v>
+      </c>
+      <c r="K284" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L284" s="15">
+        <v>0.6875</v>
+      </c>
+      <c r="M284" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="N284" s="4">
+        <v>119690</v>
+      </c>
+      <c r="O284" s="4">
+        <v>119739</v>
+      </c>
+      <c r="P284" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>49</v>
+      </c>
+      <c r="Q284" s="4">
+        <v>95</v>
+      </c>
+      <c r="R284" s="4">
+        <v>29</v>
+      </c>
+      <c r="S284" s="4">
+        <v>29</v>
+      </c>
+      <c r="T284" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U284" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V284" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W284" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X284" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y284" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A285" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B285" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C285" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D285" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E285" s="4">
+        <v>5</v>
+      </c>
+      <c r="F285" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G285" s="10">
+        <v>2961.64</v>
+      </c>
+      <c r="H285" s="10">
+        <v>20513.91</v>
+      </c>
+      <c r="I285" s="4">
+        <v>505</v>
+      </c>
+      <c r="J285" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.14437228202717084</v>
+      </c>
+      <c r="K285" s="11">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L285" s="15">
+        <v>0.69652777777777775</v>
+      </c>
+      <c r="M285" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.36319444444444443</v>
+      </c>
+      <c r="N285" s="4">
+        <v>155311</v>
+      </c>
+      <c r="O285" s="4">
+        <v>155347</v>
+      </c>
+      <c r="P285" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>36</v>
+      </c>
+      <c r="Q285" s="4">
+        <v>63</v>
+      </c>
+      <c r="R285" s="4">
+        <v>3</v>
+      </c>
+      <c r="S285" s="4">
+        <v>3</v>
+      </c>
+      <c r="T285" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U285" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V285" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W285" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X285" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y285" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A286" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B286" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C286" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D286" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E286" s="4">
+        <v>4</v>
+      </c>
+      <c r="F286" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G286" s="10">
+        <v>7116.05</v>
+      </c>
+      <c r="H286" s="10">
+        <v>161134.03</v>
+      </c>
+      <c r="I286" s="4">
+        <v>1216</v>
+      </c>
+      <c r="J286" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.4162303890742383E-2</v>
+      </c>
+      <c r="K286" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L286" s="15">
+        <v>0.71527777777777779</v>
+      </c>
+      <c r="M286" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4236111111111111</v>
+      </c>
+      <c r="N286" s="4">
+        <v>125031</v>
+      </c>
+      <c r="O286" s="4">
+        <v>125105</v>
+      </c>
+      <c r="P286" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>74</v>
+      </c>
+      <c r="Q286" s="4">
+        <v>177</v>
+      </c>
+      <c r="R286" s="4">
+        <v>37</v>
+      </c>
+      <c r="S286" s="4">
+        <v>37</v>
+      </c>
+      <c r="T286" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U286" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V286" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W286" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X286" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y286" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J265">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="J2:J286">
+    <cfRule type="cellIs" dxfId="65" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="64" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U265">
-    <cfRule type="cellIs" dxfId="8" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="U2:U286">
+    <cfRule type="cellIs" dxfId="63" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="62" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="61" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="60" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="59" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="57" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V265">
-    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="V2:V286">
+    <cfRule type="expression" dxfId="56" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -25779,7 +27973,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25795,7 +27989,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D265</xm:sqref>
+          <xm:sqref>D2:D286</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755360BE-6166-49E8-A0AD-13075DCCC61D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA6118C5-8001-46D7-A07F-FB0B582E525F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="81">
   <si>
     <t>Data</t>
   </si>
@@ -284,6 +284,9 @@
   <si>
     <t>William</t>
   </si>
+  <si>
+    <t>5,5,8,8</t>
+  </si>
 </sst>
 </file>
 
@@ -486,7 +489,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -560,6 +563,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -569,7 +575,84 @@
     <cellStyle name="Normal 2 2 2" xfId="3" xr:uid="{F6D7429B-6BC2-41D1-B818-FB0128371036}"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="134">
+  <dxfs count="145">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -2084,94 +2167,94 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V10" totalsRowShown="0" headerRowDxfId="133" dataDxfId="131" headerRowBorderDxfId="132" tableBorderDxfId="130" totalsRowBorderDxfId="129" headerRowCellStyle="Normal 2 2 2">
-  <autoFilter ref="A1:V10" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V11" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
+  <autoFilter ref="A1:V11" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="128"/>
-    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="127"/>
-    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="126"/>
-    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="125"/>
-    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="124" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="123" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="122"/>
-    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="121" dataCellStyle="Porcentagem">
+    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="139"/>
+    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="138"/>
+    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="137"/>
+    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="136"/>
+    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="135" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="134" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="133"/>
+    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="132" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="120"/>
-    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="119"/>
-    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="118">
+    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="131"/>
+    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="130"/>
+    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="129">
       <calculatedColumnFormula>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="117" dataCellStyle="Moeda"/>
-    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="116" dataCellStyle="Porcentagem">
+    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="128" dataCellStyle="Moeda"/>
+    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="127" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="115"/>
-    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="114"/>
-    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="113"/>
-    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="112">
+    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="126"/>
+    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="125"/>
+    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="124"/>
+    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="123">
       <calculatedColumnFormula>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="111" dataCellStyle="Moeda 2 2">
+    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="122" dataCellStyle="Moeda 2 2">
       <calculatedColumnFormula>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="110" dataCellStyle="Moeda 3">
+    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="121" dataCellStyle="Moeda 3">
       <calculatedColumnFormula>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="109"/>
-    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="108"/>
-    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="107"/>
+    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="120"/>
+    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="119"/>
+    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="118"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y286" totalsRowShown="0" headerRowDxfId="106" dataDxfId="104" headerRowBorderDxfId="105" tableBorderDxfId="103" totalsRowBorderDxfId="102">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y300" totalsRowShown="0" headerRowDxfId="117" dataDxfId="115" headerRowBorderDxfId="116" tableBorderDxfId="114" totalsRowBorderDxfId="113">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="101"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="100">
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="112"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="111">
       <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="99">
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="110">
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="98"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="97"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="96">
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="109"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="108"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="107">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="95" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="94" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="93"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="92" dataCellStyle="Normal 2 2 2">
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="106" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="105" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="104"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="103" dataCellStyle="Normal 2 2 2">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="91"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="90"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="89">
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="102"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="101"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="100">
       <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="88"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="87"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="86">
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="99"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="98"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="97">
       <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="85"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="84"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="83"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="82">
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="96"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="95"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="94"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="93">
       <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="81" dataCellStyle="Moeda">
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="92" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="80">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="91">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="79"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="78"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="77"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="90"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="89"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="88"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2600,7 +2683,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A050DE7D-8F3F-47CF-9E37-B95AFD2ED76A}">
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="23" bestFit="1" customWidth="1"/>
@@ -3262,40 +3345,96 @@
       <c r="U10" s="4"/>
       <c r="V10" s="5"/>
     </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="27">
+        <v>4224.17</v>
+      </c>
+      <c r="F11" s="27">
+        <v>96676.42</v>
+      </c>
+      <c r="G11" s="4">
+        <v>879</v>
+      </c>
+      <c r="H11" s="9">
+        <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
+        <v>4.3693901780806531E-2</v>
+      </c>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4">
+        <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="10">
+        <v>500</v>
+      </c>
+      <c r="M11" s="9">
+        <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
+        <v>0.11836644832002499</v>
+      </c>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="12">
+        <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="R11" s="13" t="e">
+        <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S11" s="14" t="e">
+        <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
+      <c r="V11" s="5"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H10">
-    <cfRule type="cellIs" dxfId="76" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="H2:H11">
+    <cfRule type="cellIs" dxfId="87" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="86" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R10">
-    <cfRule type="cellIs" dxfId="74" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="R2:R11">
+    <cfRule type="cellIs" dxfId="85" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="84" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="83" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="82" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="81" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="80" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="79" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S10">
-    <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="S2:S11">
+    <cfRule type="expression" dxfId="78" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -3304,7 +3443,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3318,7 +3457,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y286"/>
+  <dimension ref="A1:Y300"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -26129,11 +26268,11 @@
       <c r="A266" s="8">
         <v>46274</v>
       </c>
-      <c r="B266" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C266" s="26">
+      <c r="B266" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C266" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -26215,11 +26354,11 @@
       <c r="A267" s="8">
         <v>46274</v>
       </c>
-      <c r="B267" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C267" s="26">
+      <c r="B267" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C267" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -26301,11 +26440,11 @@
       <c r="A268" s="8">
         <v>46274</v>
       </c>
-      <c r="B268" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C268" s="26">
+      <c r="B268" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C268" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -26387,11 +26526,11 @@
       <c r="A269" s="8">
         <v>46274</v>
       </c>
-      <c r="B269" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C269" s="26">
+      <c r="B269" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C269" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -26473,11 +26612,11 @@
       <c r="A270" s="8">
         <v>46274</v>
       </c>
-      <c r="B270" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C270" s="26">
+      <c r="B270" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C270" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -26559,11 +26698,11 @@
       <c r="A271" s="8">
         <v>46274</v>
       </c>
-      <c r="B271" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C271" s="26">
+      <c r="B271" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C271" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -26645,11 +26784,11 @@
       <c r="A272" s="8">
         <v>46274</v>
       </c>
-      <c r="B272" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C272" s="26">
+      <c r="B272" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C272" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -26731,11 +26870,11 @@
       <c r="A273" s="8">
         <v>46274</v>
       </c>
-      <c r="B273" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C273" s="26">
+      <c r="B273" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C273" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -26817,11 +26956,11 @@
       <c r="A274" s="8">
         <v>46274</v>
       </c>
-      <c r="B274" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C274" s="26">
+      <c r="B274" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C274" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -26903,11 +27042,11 @@
       <c r="A275" s="8">
         <v>46274</v>
       </c>
-      <c r="B275" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C275" s="26">
+      <c r="B275" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C275" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -26989,11 +27128,11 @@
       <c r="A276" s="8">
         <v>46274</v>
       </c>
-      <c r="B276" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C276" s="26">
+      <c r="B276" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C276" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -27075,11 +27214,11 @@
       <c r="A277" s="8">
         <v>46275</v>
       </c>
-      <c r="B277" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C277" s="26">
+      <c r="B277" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C277" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -27161,11 +27300,11 @@
       <c r="A278" s="8">
         <v>46275</v>
       </c>
-      <c r="B278" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C278" s="26">
+      <c r="B278" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C278" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -27247,11 +27386,11 @@
       <c r="A279" s="8">
         <v>46275</v>
       </c>
-      <c r="B279" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C279" s="26">
+      <c r="B279" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C279" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -27333,11 +27472,11 @@
       <c r="A280" s="8">
         <v>46275</v>
       </c>
-      <c r="B280" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C280" s="26">
+      <c r="B280" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C280" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -27419,11 +27558,11 @@
       <c r="A281" s="8">
         <v>46275</v>
       </c>
-      <c r="B281" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C281" s="26">
+      <c r="B281" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C281" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -27505,11 +27644,11 @@
       <c r="A282" s="8">
         <v>46275</v>
       </c>
-      <c r="B282" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C282" s="26">
+      <c r="B282" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C282" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -27591,11 +27730,11 @@
       <c r="A283" s="8">
         <v>46275</v>
       </c>
-      <c r="B283" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C283" s="26">
+      <c r="B283" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C283" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -27677,11 +27816,11 @@
       <c r="A284" s="8">
         <v>46275</v>
       </c>
-      <c r="B284" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C284" s="26">
+      <c r="B284" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C284" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -27763,11 +27902,11 @@
       <c r="A285" s="8">
         <v>46275</v>
       </c>
-      <c r="B285" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C285" s="26">
+      <c r="B285" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C285" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -27849,11 +27988,11 @@
       <c r="A286" s="8">
         <v>46275</v>
       </c>
-      <c r="B286" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C286" s="26">
+      <c r="B286" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C286" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -27931,40 +28070,1242 @@
         <v>0</v>
       </c>
     </row>
+    <row r="287" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A287" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B287" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C287" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D287" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E287" s="4">
+        <v>5</v>
+      </c>
+      <c r="F287" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G287" s="10">
+        <v>5637.02</v>
+      </c>
+      <c r="H287" s="10">
+        <v>109511.97</v>
+      </c>
+      <c r="I287" s="4">
+        <v>1052</v>
+      </c>
+      <c r="J287" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.1474007818506057E-2</v>
+      </c>
+      <c r="K287" s="11">
+        <v>0.32013888888888886</v>
+      </c>
+      <c r="L287" s="15">
+        <v>0.75416666666666665</v>
+      </c>
+      <c r="M287" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.43402777777777779</v>
+      </c>
+      <c r="N287" s="4">
+        <v>280434</v>
+      </c>
+      <c r="O287" s="4">
+        <v>280521</v>
+      </c>
+      <c r="P287" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>87</v>
+      </c>
+      <c r="Q287" s="4">
+        <v>106</v>
+      </c>
+      <c r="R287" s="4">
+        <v>23</v>
+      </c>
+      <c r="S287" s="4">
+        <v>23</v>
+      </c>
+      <c r="T287" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U287" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V287" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W287" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X287" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y287" s="5"/>
+    </row>
+    <row r="288" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A288" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B288" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C288" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D288" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E288" s="4">
+        <v>11</v>
+      </c>
+      <c r="F288" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G288" s="10">
+        <v>13396.57</v>
+      </c>
+      <c r="H288" s="10">
+        <v>234333.57</v>
+      </c>
+      <c r="I288" s="4">
+        <v>1775</v>
+      </c>
+      <c r="J288" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.7168804281861961E-2</v>
+      </c>
+      <c r="K288" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L288" s="15">
+        <v>0.80555555555555558</v>
+      </c>
+      <c r="M288" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.53472222222222232</v>
+      </c>
+      <c r="N288" s="4">
+        <v>105359</v>
+      </c>
+      <c r="O288" s="4">
+        <v>105497</v>
+      </c>
+      <c r="P288" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>138</v>
+      </c>
+      <c r="Q288" s="4">
+        <v>211</v>
+      </c>
+      <c r="R288" s="4">
+        <v>42</v>
+      </c>
+      <c r="S288" s="4">
+        <v>42</v>
+      </c>
+      <c r="T288" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U288" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V288" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W288" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X288" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y288" s="5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="289" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A289" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B289" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C289" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D289" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E289" s="4">
+        <v>1</v>
+      </c>
+      <c r="F289" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G289" s="10">
+        <v>2741.07</v>
+      </c>
+      <c r="H289" s="10">
+        <v>48246.09</v>
+      </c>
+      <c r="I289" s="4">
+        <v>402</v>
+      </c>
+      <c r="J289" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.6814344955207777E-2</v>
+      </c>
+      <c r="K289" s="11">
+        <v>0.68055555555555558</v>
+      </c>
+      <c r="L289" s="15">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="M289" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>1.7361111111111049E-2</v>
+      </c>
+      <c r="N289" s="4">
+        <v>275645</v>
+      </c>
+      <c r="O289" s="4">
+        <v>275646</v>
+      </c>
+      <c r="P289" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>1</v>
+      </c>
+      <c r="Q289" s="4">
+        <v>2</v>
+      </c>
+      <c r="R289" s="4">
+        <v>1</v>
+      </c>
+      <c r="S289" s="4">
+        <v>1</v>
+      </c>
+      <c r="T289" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U289" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V289" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W289" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="X289" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y289" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A290" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B290" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C290" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D290" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E290" s="4">
+        <v>5</v>
+      </c>
+      <c r="F290" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Geber</v>
+      </c>
+      <c r="G290" s="10">
+        <v>26771.97</v>
+      </c>
+      <c r="H290" s="10">
+        <v>623236.66</v>
+      </c>
+      <c r="I290" s="4">
+        <v>4429</v>
+      </c>
+      <c r="J290" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.2956346630828805E-2</v>
+      </c>
+      <c r="K290" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L290" s="15">
+        <v>0.77222222222222225</v>
+      </c>
+      <c r="M290" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.48055555555555557</v>
+      </c>
+      <c r="N290" s="4">
+        <v>365685</v>
+      </c>
+      <c r="O290" s="4">
+        <v>365734</v>
+      </c>
+      <c r="P290" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>49</v>
+      </c>
+      <c r="Q290" s="4">
+        <v>353</v>
+      </c>
+      <c r="R290" s="4">
+        <v>12</v>
+      </c>
+      <c r="S290" s="4">
+        <v>12</v>
+      </c>
+      <c r="T290" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U290" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V290" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W290" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X290" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y290" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A291" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B291" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C291" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D291" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E291" s="4">
+        <v>2</v>
+      </c>
+      <c r="F291" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G291" s="10">
+        <v>10981.94</v>
+      </c>
+      <c r="H291" s="10">
+        <v>205579.85</v>
+      </c>
+      <c r="I291" s="4">
+        <v>2298</v>
+      </c>
+      <c r="J291" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.3419340465517412E-2</v>
+      </c>
+      <c r="K291" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L291" s="15">
+        <v>0.71666666666666667</v>
+      </c>
+      <c r="M291" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44583333333333336</v>
+      </c>
+      <c r="N291" s="4">
+        <v>143088</v>
+      </c>
+      <c r="O291" s="4">
+        <v>143143</v>
+      </c>
+      <c r="P291" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>55</v>
+      </c>
+      <c r="Q291" s="4">
+        <v>269</v>
+      </c>
+      <c r="R291" s="4">
+        <v>29</v>
+      </c>
+      <c r="S291" s="4">
+        <v>29</v>
+      </c>
+      <c r="T291" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U291" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V291" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W291" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X291" s="4">
+        <v>4</v>
+      </c>
+      <c r="Y291" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="292" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A292" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B292" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C292" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D292" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E292" s="4">
+        <v>4</v>
+      </c>
+      <c r="F292" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G292" s="10">
+        <v>7240.24</v>
+      </c>
+      <c r="H292" s="10">
+        <v>85925</v>
+      </c>
+      <c r="I292" s="4">
+        <v>1276</v>
+      </c>
+      <c r="J292" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.4262321792260689E-2</v>
+      </c>
+      <c r="K292" s="11">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="L292" s="15">
+        <v>0.76736111111111116</v>
+      </c>
+      <c r="M292" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.48958333333333337</v>
+      </c>
+      <c r="N292" s="4">
+        <v>13402</v>
+      </c>
+      <c r="O292" s="4">
+        <v>13471</v>
+      </c>
+      <c r="P292" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>69</v>
+      </c>
+      <c r="Q292" s="4">
+        <v>212</v>
+      </c>
+      <c r="R292" s="4">
+        <v>13</v>
+      </c>
+      <c r="S292" s="4">
+        <v>13</v>
+      </c>
+      <c r="T292" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U292" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V292" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W292" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X292" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y292" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="293" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A293" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B293" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C293" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D293" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E293" s="4">
+        <v>3</v>
+      </c>
+      <c r="F293" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G293" s="10">
+        <v>13353.33</v>
+      </c>
+      <c r="H293" s="10">
+        <v>191629.74</v>
+      </c>
+      <c r="I293" s="4">
+        <v>4000</v>
+      </c>
+      <c r="J293" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.9682973008260624E-2</v>
+      </c>
+      <c r="K293" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L293" s="15">
+        <v>0.73611111111111116</v>
+      </c>
+      <c r="M293" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44444444444444448</v>
+      </c>
+      <c r="N293" s="4">
+        <v>119739</v>
+      </c>
+      <c r="O293" s="4">
+        <v>119789</v>
+      </c>
+      <c r="P293" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>50</v>
+      </c>
+      <c r="Q293" s="4">
+        <v>442</v>
+      </c>
+      <c r="R293" s="4">
+        <v>17</v>
+      </c>
+      <c r="S293" s="4">
+        <v>17</v>
+      </c>
+      <c r="T293" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U293" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V293" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W293" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X293" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y293" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A294" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B294" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C294" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D294" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E294" s="4">
+        <v>1</v>
+      </c>
+      <c r="F294" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G294" s="10">
+        <v>6797.35</v>
+      </c>
+      <c r="H294" s="10">
+        <v>97639.01</v>
+      </c>
+      <c r="I294" s="4">
+        <v>1365</v>
+      </c>
+      <c r="J294" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.9617154045293991E-2</v>
+      </c>
+      <c r="K294" s="11">
+        <v>0.30208333333333331</v>
+      </c>
+      <c r="L294" s="15">
+        <v>0.6875</v>
+      </c>
+      <c r="M294" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="N294" s="4">
+        <v>304416</v>
+      </c>
+      <c r="O294" s="4">
+        <v>304453</v>
+      </c>
+      <c r="P294" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>37</v>
+      </c>
+      <c r="Q294" s="4">
+        <v>206</v>
+      </c>
+      <c r="R294" s="4">
+        <v>8</v>
+      </c>
+      <c r="S294" s="4">
+        <v>8</v>
+      </c>
+      <c r="T294" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U294" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V294" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W294" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="X294" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y294" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A295" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B295" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C295" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D295" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E295" s="4">
+        <v>1</v>
+      </c>
+      <c r="F295" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G295" s="10">
+        <v>4372.7700000000004</v>
+      </c>
+      <c r="H295" s="10">
+        <v>11638.94</v>
+      </c>
+      <c r="I295" s="4">
+        <v>275</v>
+      </c>
+      <c r="J295" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.37570173916181371</v>
+      </c>
+      <c r="K295" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L295" s="15">
+        <v>0.70486111111111116</v>
+      </c>
+      <c r="M295" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.41319444444444448</v>
+      </c>
+      <c r="N295" s="4">
+        <v>155357</v>
+      </c>
+      <c r="O295" s="4">
+        <v>155383</v>
+      </c>
+      <c r="P295" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>26</v>
+      </c>
+      <c r="Q295" s="4">
+        <v>136</v>
+      </c>
+      <c r="R295" s="4">
+        <v>1</v>
+      </c>
+      <c r="S295" s="4">
+        <v>1</v>
+      </c>
+      <c r="T295" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U295" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V295" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W295" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X295" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y295" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A296" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B296" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C296" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D296" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E296" s="4">
+        <v>1</v>
+      </c>
+      <c r="F296" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G296" s="10">
+        <v>3879.13</v>
+      </c>
+      <c r="H296" s="10">
+        <v>110429.15</v>
+      </c>
+      <c r="I296" s="4">
+        <v>825</v>
+      </c>
+      <c r="J296" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.51277719696294E-2</v>
+      </c>
+      <c r="K296" s="11">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L296" s="15">
+        <v>0.72569444444444442</v>
+      </c>
+      <c r="M296" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="N296" s="4">
+        <v>125105</v>
+      </c>
+      <c r="O296" s="4">
+        <v>125135</v>
+      </c>
+      <c r="P296" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>30</v>
+      </c>
+      <c r="Q296" s="4">
+        <v>2</v>
+      </c>
+      <c r="R296" s="4">
+        <v>1</v>
+      </c>
+      <c r="S296" s="4">
+        <v>1</v>
+      </c>
+      <c r="T296" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U296" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V296" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W296" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X296" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y296" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A297" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B297" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C297" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D297" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E297" s="4">
+        <v>1</v>
+      </c>
+      <c r="F297" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G297" s="10">
+        <v>6947.78</v>
+      </c>
+      <c r="H297" s="10">
+        <v>96422.18</v>
+      </c>
+      <c r="I297" s="4">
+        <v>882</v>
+      </c>
+      <c r="J297" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.2055827818869059E-2</v>
+      </c>
+      <c r="K297" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L297" s="15">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="M297" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="N297" s="4">
+        <v>291267</v>
+      </c>
+      <c r="O297" s="4">
+        <v>291352</v>
+      </c>
+      <c r="P297" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>85</v>
+      </c>
+      <c r="Q297" s="4">
+        <v>156</v>
+      </c>
+      <c r="R297" s="4">
+        <v>22</v>
+      </c>
+      <c r="S297" s="4">
+        <v>22</v>
+      </c>
+      <c r="T297" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U297" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V297" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W297" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="X297" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y297" s="5">
+        <v>38.380000000000003</v>
+      </c>
+    </row>
+    <row r="298" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A298" s="8">
+        <v>46277</v>
+      </c>
+      <c r="B298" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C298" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D298" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E298" s="4">
+        <v>1</v>
+      </c>
+      <c r="F298" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G298" s="10">
+        <v>5227.76</v>
+      </c>
+      <c r="H298" s="10">
+        <v>58650.09</v>
+      </c>
+      <c r="I298" s="4">
+        <v>563</v>
+      </c>
+      <c r="J298" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.9134731080549076E-2</v>
+      </c>
+      <c r="K298" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L298" s="15">
+        <v>0.46875</v>
+      </c>
+      <c r="M298" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.17708333333333331</v>
+      </c>
+      <c r="N298" s="4">
+        <v>304453</v>
+      </c>
+      <c r="O298" s="4">
+        <v>304578</v>
+      </c>
+      <c r="P298" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>125</v>
+      </c>
+      <c r="Q298" s="4">
+        <v>79</v>
+      </c>
+      <c r="R298" s="4">
+        <v>22</v>
+      </c>
+      <c r="S298" s="4">
+        <v>22</v>
+      </c>
+      <c r="T298" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U298" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V298" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W298" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X298" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y298" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A299" s="8">
+        <v>46277</v>
+      </c>
+      <c r="B299" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C299" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D299" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E299" s="4">
+        <v>11</v>
+      </c>
+      <c r="F299" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G299" s="10">
+        <v>7173.91</v>
+      </c>
+      <c r="H299" s="10">
+        <v>99979.49</v>
+      </c>
+      <c r="I299" s="4">
+        <v>853</v>
+      </c>
+      <c r="J299" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.175381670780677E-2</v>
+      </c>
+      <c r="K299" s="11">
+        <v>0.28125</v>
+      </c>
+      <c r="L299" s="15">
+        <v>0.59861111111111109</v>
+      </c>
+      <c r="M299" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.31736111111111109</v>
+      </c>
+      <c r="N299" s="4">
+        <v>13471</v>
+      </c>
+      <c r="O299" s="4">
+        <v>13592</v>
+      </c>
+      <c r="P299" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>121</v>
+      </c>
+      <c r="Q299" s="4">
+        <v>134</v>
+      </c>
+      <c r="R299" s="4">
+        <v>28</v>
+      </c>
+      <c r="S299" s="4">
+        <v>28</v>
+      </c>
+      <c r="T299" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U299" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V299" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W299" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X299" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y299" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A300" s="8">
+        <v>46277</v>
+      </c>
+      <c r="B300" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C300" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D300" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E300" s="4">
+        <v>3</v>
+      </c>
+      <c r="F300" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G300" s="10">
+        <v>6590.53</v>
+      </c>
+      <c r="H300" s="10">
+        <v>108858.17</v>
+      </c>
+      <c r="I300" s="4">
+        <v>1101</v>
+      </c>
+      <c r="J300" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.0542355249955056E-2</v>
+      </c>
+      <c r="K300" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L300" s="15">
+        <v>0.47222222222222221</v>
+      </c>
+      <c r="M300" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.18055555555555552</v>
+      </c>
+      <c r="N300" s="4">
+        <v>119790</v>
+      </c>
+      <c r="O300" s="4">
+        <v>119831</v>
+      </c>
+      <c r="P300" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>41</v>
+      </c>
+      <c r="Q300" s="4">
+        <v>152</v>
+      </c>
+      <c r="R300" s="4">
+        <v>7</v>
+      </c>
+      <c r="S300" s="4">
+        <v>7</v>
+      </c>
+      <c r="T300" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U300" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V300" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W300" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X300" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y300" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J286">
-    <cfRule type="cellIs" dxfId="65" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="J2:J300">
+    <cfRule type="cellIs" dxfId="76" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="75" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U286">
-    <cfRule type="cellIs" dxfId="63" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="U2:U300">
+    <cfRule type="cellIs" dxfId="74" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="73" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="72" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="71" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="70" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="69" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="68" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V286">
-    <cfRule type="expression" dxfId="56" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="V2:V300">
+    <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -27973,7 +29314,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27989,7 +29330,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D286</xm:sqref>
+          <xm:sqref>D2:D300</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA6118C5-8001-46D7-A07F-FB0B582E525F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39428DC2-861B-42DC-99E1-AA97B008F0D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="82">
   <si>
     <t>Data</t>
   </si>
@@ -287,6 +287,9 @@
   <si>
     <t>5,5,8,8</t>
   </si>
+  <si>
+    <t>13,27,27,27</t>
+  </si>
 </sst>
 </file>
 
@@ -489,7 +492,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -561,9 +564,6 @@
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -652,6 +652,509 @@
         <i val="0"/>
         <color rgb="FFFF0000"/>
       </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[h]:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[h]:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0070C0"/>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1355,509 +1858,6 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[h]:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[h]:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="25" formatCode="hh:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0070C0"/>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -2210,51 +2210,51 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y300" totalsRowShown="0" headerRowDxfId="117" dataDxfId="115" headerRowBorderDxfId="116" tableBorderDxfId="114" totalsRowBorderDxfId="113">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y312" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39" headerRowBorderDxfId="37" tableBorderDxfId="38" totalsRowBorderDxfId="36">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="112"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="111">
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="35"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="34">
       <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="110">
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="33">
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="109"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="108"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="107">
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="30">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="106" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="105" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="104"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="103" dataCellStyle="Normal 2 2 2">
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="29" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="28" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="27"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="26" dataCellStyle="Normal 2 2 2">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="102"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="101"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="100">
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="25"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="24"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="23">
       <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="99"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="98"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="97">
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="22"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="21"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="20">
       <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="96"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="95"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="94"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="93">
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="19"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="18"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="17"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="16">
       <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="92" dataCellStyle="Moeda">
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="15" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="91">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="14">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="90"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="89"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="88"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="13"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="12"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3356,10 +3356,10 @@
       <c r="D11" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="10">
         <v>4224.17</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="10">
         <v>96676.42</v>
       </c>
       <c r="G11" s="4">
@@ -3403,38 +3403,38 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H11">
-    <cfRule type="cellIs" dxfId="87" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="117" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="116" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R11">
-    <cfRule type="cellIs" dxfId="85" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="115" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="114" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="113" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="112" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="111" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="110" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="109" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S11">
-    <cfRule type="expression" dxfId="78" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="108" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -3443,7 +3443,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="107" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3457,7 +3457,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y300"/>
+  <dimension ref="A1:Y312"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -28074,11 +28074,11 @@
       <c r="A287" s="8">
         <v>46276</v>
       </c>
-      <c r="B287" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C287" s="26">
+      <c r="B287" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C287" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -28158,11 +28158,11 @@
       <c r="A288" s="8">
         <v>46276</v>
       </c>
-      <c r="B288" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C288" s="26">
+      <c r="B288" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C288" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -28244,11 +28244,11 @@
       <c r="A289" s="8">
         <v>46276</v>
       </c>
-      <c r="B289" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C289" s="26">
+      <c r="B289" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C289" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -28330,11 +28330,11 @@
       <c r="A290" s="8">
         <v>46276</v>
       </c>
-      <c r="B290" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C290" s="26">
+      <c r="B290" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C290" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -28416,11 +28416,11 @@
       <c r="A291" s="8">
         <v>46276</v>
       </c>
-      <c r="B291" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C291" s="26">
+      <c r="B291" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C291" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -28502,11 +28502,11 @@
       <c r="A292" s="8">
         <v>46276</v>
       </c>
-      <c r="B292" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C292" s="26">
+      <c r="B292" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C292" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -28588,11 +28588,11 @@
       <c r="A293" s="8">
         <v>46276</v>
       </c>
-      <c r="B293" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C293" s="26">
+      <c r="B293" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C293" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -28674,11 +28674,11 @@
       <c r="A294" s="8">
         <v>46276</v>
       </c>
-      <c r="B294" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C294" s="26">
+      <c r="B294" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C294" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -28760,11 +28760,11 @@
       <c r="A295" s="8">
         <v>46276</v>
       </c>
-      <c r="B295" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C295" s="26">
+      <c r="B295" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C295" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -28846,11 +28846,11 @@
       <c r="A296" s="8">
         <v>46276</v>
       </c>
-      <c r="B296" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C296" s="26">
+      <c r="B296" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C296" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -28932,11 +28932,11 @@
       <c r="A297" s="8">
         <v>46276</v>
       </c>
-      <c r="B297" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C297" s="26">
+      <c r="B297" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C297" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -29018,11 +29018,11 @@
       <c r="A298" s="8">
         <v>46277</v>
       </c>
-      <c r="B298" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C298" s="26">
+      <c r="B298" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C298" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -29104,11 +29104,11 @@
       <c r="A299" s="8">
         <v>46277</v>
       </c>
-      <c r="B299" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C299" s="26">
+      <c r="B299" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C299" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -29190,11 +29190,11 @@
       <c r="A300" s="8">
         <v>46277</v>
       </c>
-      <c r="B300" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C300" s="26">
+      <c r="B300" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C300" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -29272,40 +29272,1072 @@
         <v>0</v>
       </c>
     </row>
+    <row r="301" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A301" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B301" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C301" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D301" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E301" s="4">
+        <v>1</v>
+      </c>
+      <c r="F301" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G301" s="10">
+        <v>12518.28</v>
+      </c>
+      <c r="H301" s="10">
+        <v>157704.44</v>
+      </c>
+      <c r="I301" s="4">
+        <v>1771</v>
+      </c>
+      <c r="J301" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.9378107553598365E-2</v>
+      </c>
+      <c r="K301" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L301" s="15">
+        <v>0.78472222222222221</v>
+      </c>
+      <c r="M301" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.49305555555555552</v>
+      </c>
+      <c r="N301" s="4">
+        <v>125135</v>
+      </c>
+      <c r="O301" s="4">
+        <v>125211</v>
+      </c>
+      <c r="P301" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>76</v>
+      </c>
+      <c r="Q301" s="4">
+        <v>196</v>
+      </c>
+      <c r="R301" s="4">
+        <v>21</v>
+      </c>
+      <c r="S301" s="4">
+        <v>19</v>
+      </c>
+      <c r="T301" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>2</v>
+      </c>
+      <c r="U301" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.90476190476190477</v>
+      </c>
+      <c r="V301" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W301" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="X301" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y301" s="5">
+        <v>13.13</v>
+      </c>
+    </row>
+    <row r="302" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A302" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B302" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C302" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D302" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E302" s="4">
+        <v>1</v>
+      </c>
+      <c r="F302" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G302" s="10">
+        <v>497.84</v>
+      </c>
+      <c r="H302" s="10">
+        <v>4219.17</v>
+      </c>
+      <c r="I302" s="4">
+        <v>9</v>
+      </c>
+      <c r="J302" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.11799477148349082</v>
+      </c>
+      <c r="K302" s="11">
+        <v>0.29583333333333334</v>
+      </c>
+      <c r="L302" s="15">
+        <v>0.41388888888888886</v>
+      </c>
+      <c r="M302" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.11805555555555552</v>
+      </c>
+      <c r="N302" s="4">
+        <v>155395</v>
+      </c>
+      <c r="O302" s="4">
+        <v>155427</v>
+      </c>
+      <c r="P302" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>32</v>
+      </c>
+      <c r="Q302" s="4">
+        <v>4</v>
+      </c>
+      <c r="R302" s="4">
+        <v>1</v>
+      </c>
+      <c r="S302" s="4">
+        <v>1</v>
+      </c>
+      <c r="T302" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U302" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V302" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W302" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X302" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y302" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A303" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B303" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C303" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D303" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E303" s="4">
+        <v>3</v>
+      </c>
+      <c r="F303" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G303" s="10">
+        <v>12651.35</v>
+      </c>
+      <c r="H303" s="10">
+        <v>173270.99</v>
+      </c>
+      <c r="I303" s="4">
+        <v>2366</v>
+      </c>
+      <c r="J303" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.3014819156974872E-2</v>
+      </c>
+      <c r="K303" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L303" s="15">
+        <v>0.77430555555555558</v>
+      </c>
+      <c r="M303" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4826388888888889</v>
+      </c>
+      <c r="N303" s="4">
+        <v>143154</v>
+      </c>
+      <c r="O303" s="4">
+        <v>143202</v>
+      </c>
+      <c r="P303" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>48</v>
+      </c>
+      <c r="Q303" s="4">
+        <v>143</v>
+      </c>
+      <c r="R303" s="4">
+        <v>17</v>
+      </c>
+      <c r="S303" s="4">
+        <v>17</v>
+      </c>
+      <c r="T303" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U303" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V303" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W303" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X303" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y303" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A304" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B304" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C304" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D304" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E304" s="4">
+        <v>4</v>
+      </c>
+      <c r="F304" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G304" s="10">
+        <v>10896.53</v>
+      </c>
+      <c r="H304" s="10">
+        <v>203436.34</v>
+      </c>
+      <c r="I304" s="4">
+        <v>1849</v>
+      </c>
+      <c r="J304" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.3562357639741265E-2</v>
+      </c>
+      <c r="K304" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L304" s="15">
+        <v>0.8125</v>
+      </c>
+      <c r="M304" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.52083333333333326</v>
+      </c>
+      <c r="N304" s="4">
+        <v>291352</v>
+      </c>
+      <c r="O304" s="4">
+        <v>291428</v>
+      </c>
+      <c r="P304" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>76</v>
+      </c>
+      <c r="Q304" s="4">
+        <v>288</v>
+      </c>
+      <c r="R304" s="4">
+        <v>29</v>
+      </c>
+      <c r="S304" s="4">
+        <v>29</v>
+      </c>
+      <c r="T304" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U304" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V304" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W304" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X304" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y304" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A305" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B305" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C305" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D305" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E305" s="4">
+        <v>5</v>
+      </c>
+      <c r="F305" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G305" s="10">
+        <v>8298.8700000000008</v>
+      </c>
+      <c r="H305" s="10">
+        <v>141119.21</v>
+      </c>
+      <c r="I305" s="4">
+        <v>1323</v>
+      </c>
+      <c r="J305" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.8807514582883517E-2</v>
+      </c>
+      <c r="K305" s="11">
+        <v>0.31944444444444442</v>
+      </c>
+      <c r="L305" s="15">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M305" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="N305" s="4">
+        <v>119831</v>
+      </c>
+      <c r="O305" s="4">
+        <v>119898</v>
+      </c>
+      <c r="P305" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>67</v>
+      </c>
+      <c r="Q305" s="4">
+        <v>388</v>
+      </c>
+      <c r="R305" s="4">
+        <v>25</v>
+      </c>
+      <c r="S305" s="4">
+        <v>25</v>
+      </c>
+      <c r="T305" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U305" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V305" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W305" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X305" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y305" s="5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="306" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A306" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B306" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C306" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D306" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E306" s="4">
+        <v>1</v>
+      </c>
+      <c r="F306" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G306" s="10">
+        <v>8146.99</v>
+      </c>
+      <c r="H306" s="10">
+        <v>172796.79999999999</v>
+      </c>
+      <c r="I306" s="4">
+        <v>1415</v>
+      </c>
+      <c r="J306" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.7147805977888479E-2</v>
+      </c>
+      <c r="K306" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L306" s="15">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="M306" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45833333333333337</v>
+      </c>
+      <c r="N306" s="4">
+        <v>275645</v>
+      </c>
+      <c r="O306" s="4">
+        <v>275727</v>
+      </c>
+      <c r="P306" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>82</v>
+      </c>
+      <c r="Q306" s="4">
+        <v>312</v>
+      </c>
+      <c r="R306" s="4">
+        <v>21</v>
+      </c>
+      <c r="S306" s="4">
+        <v>21</v>
+      </c>
+      <c r="T306" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U306" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V306" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W306" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="X306" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y306" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="307" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A307" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B307" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C307" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D307" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E307" s="4">
+        <v>5</v>
+      </c>
+      <c r="F307" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G307" s="10">
+        <v>2898.57</v>
+      </c>
+      <c r="H307" s="10">
+        <v>18467.22</v>
+      </c>
+      <c r="I307" s="4">
+        <v>420</v>
+      </c>
+      <c r="J307" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.15695757130743013</v>
+      </c>
+      <c r="K307" s="11">
+        <v>0.30555555555555558</v>
+      </c>
+      <c r="L307" s="15">
+        <v>0.75138888888888888</v>
+      </c>
+      <c r="M307" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4458333333333333</v>
+      </c>
+      <c r="N307" s="4">
+        <v>280521</v>
+      </c>
+      <c r="O307" s="4">
+        <v>280560</v>
+      </c>
+      <c r="P307" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>39</v>
+      </c>
+      <c r="Q307" s="4">
+        <v>66</v>
+      </c>
+      <c r="R307" s="4">
+        <v>4</v>
+      </c>
+      <c r="S307" s="4">
+        <v>3</v>
+      </c>
+      <c r="T307" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>1</v>
+      </c>
+      <c r="U307" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.75</v>
+      </c>
+      <c r="V307" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W307" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X307" s="4">
+        <v>4</v>
+      </c>
+      <c r="Y307" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="308" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A308" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B308" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C308" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D308" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E308" s="4">
+        <v>1</v>
+      </c>
+      <c r="F308" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G308" s="10">
+        <v>2801.01</v>
+      </c>
+      <c r="H308" s="10">
+        <v>44016.45</v>
+      </c>
+      <c r="I308" s="4">
+        <v>305</v>
+      </c>
+      <c r="J308" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.363552717222766E-2</v>
+      </c>
+      <c r="K308" s="11">
+        <v>0.4826388888888889</v>
+      </c>
+      <c r="L308" s="15">
+        <v>0.74791666666666667</v>
+      </c>
+      <c r="M308" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.26527777777777778</v>
+      </c>
+      <c r="N308" s="4">
+        <v>155427</v>
+      </c>
+      <c r="O308" s="4">
+        <v>155512</v>
+      </c>
+      <c r="P308" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>85</v>
+      </c>
+      <c r="Q308" s="4">
+        <v>60</v>
+      </c>
+      <c r="R308" s="4">
+        <v>16</v>
+      </c>
+      <c r="S308" s="4">
+        <v>16</v>
+      </c>
+      <c r="T308" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U308" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V308" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W308" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X308" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y308" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A309" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B309" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C309" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D309" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E309" s="4">
+        <v>5</v>
+      </c>
+      <c r="F309" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G309" s="10">
+        <v>4334.04</v>
+      </c>
+      <c r="H309" s="10">
+        <v>70129.5</v>
+      </c>
+      <c r="I309" s="4">
+        <v>1552</v>
+      </c>
+      <c r="J309" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.1800526169443669E-2</v>
+      </c>
+      <c r="K309" s="11">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="L309" s="15">
+        <v>0.74097222222222225</v>
+      </c>
+      <c r="M309" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44236111111111115</v>
+      </c>
+      <c r="N309" s="4">
+        <v>13592</v>
+      </c>
+      <c r="O309" s="4">
+        <v>13659</v>
+      </c>
+      <c r="P309" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>67</v>
+      </c>
+      <c r="Q309" s="4">
+        <v>169</v>
+      </c>
+      <c r="R309" s="4">
+        <v>14</v>
+      </c>
+      <c r="S309" s="4">
+        <v>14</v>
+      </c>
+      <c r="T309" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U309" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V309" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W309" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X309" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y309" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A310" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B310" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C310" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D310" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E310" s="4">
+        <v>11</v>
+      </c>
+      <c r="F310" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G310" s="10">
+        <v>15187.44</v>
+      </c>
+      <c r="H310" s="10">
+        <v>223919.01</v>
+      </c>
+      <c r="I310" s="4">
+        <v>2397</v>
+      </c>
+      <c r="J310" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.7825594620126273E-2</v>
+      </c>
+      <c r="K310" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L310" s="15">
+        <v>0.77638888888888891</v>
+      </c>
+      <c r="M310" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.50555555555555554</v>
+      </c>
+      <c r="N310" s="4">
+        <v>105497</v>
+      </c>
+      <c r="O310" s="4">
+        <v>105634</v>
+      </c>
+      <c r="P310" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>137</v>
+      </c>
+      <c r="Q310" s="4">
+        <v>253</v>
+      </c>
+      <c r="R310" s="4">
+        <v>40</v>
+      </c>
+      <c r="S310" s="4">
+        <v>40</v>
+      </c>
+      <c r="T310" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U310" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V310" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W310" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X310" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y310" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A311" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B311" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C311" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D311" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E311" s="4">
+        <v>2</v>
+      </c>
+      <c r="F311" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G311" s="10">
+        <v>7035.69</v>
+      </c>
+      <c r="H311" s="10">
+        <v>162106.54</v>
+      </c>
+      <c r="I311" s="4">
+        <v>1233</v>
+      </c>
+      <c r="J311" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.3401641907846525E-2</v>
+      </c>
+      <c r="K311" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L311" s="15">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="M311" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.43750000000000006</v>
+      </c>
+      <c r="N311" s="4">
+        <v>304578</v>
+      </c>
+      <c r="O311" s="4">
+        <v>304633</v>
+      </c>
+      <c r="P311" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>55</v>
+      </c>
+      <c r="Q311" s="4">
+        <v>152</v>
+      </c>
+      <c r="R311" s="4">
+        <v>28</v>
+      </c>
+      <c r="S311" s="4">
+        <v>28</v>
+      </c>
+      <c r="T311" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U311" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V311" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W311" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X311" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y311" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A312" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B312" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C312" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D312" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E312" s="4">
+        <v>5</v>
+      </c>
+      <c r="F312" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Geber</v>
+      </c>
+      <c r="G312" s="10">
+        <v>43098.8</v>
+      </c>
+      <c r="H312" s="10">
+        <v>995354.17</v>
+      </c>
+      <c r="I312" s="4">
+        <v>8352</v>
+      </c>
+      <c r="J312" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.3299964273018521E-2</v>
+      </c>
+      <c r="K312" s="11">
+        <v>0.2673611111111111</v>
+      </c>
+      <c r="L312" s="15">
+        <v>0.77430555555555558</v>
+      </c>
+      <c r="M312" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="N312" s="4">
+        <v>365871</v>
+      </c>
+      <c r="O312" s="4">
+        <v>365909</v>
+      </c>
+      <c r="P312" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>38</v>
+      </c>
+      <c r="Q312" s="4">
+        <v>312</v>
+      </c>
+      <c r="R312" s="4">
+        <v>29</v>
+      </c>
+      <c r="S312" s="4">
+        <v>29</v>
+      </c>
+      <c r="T312" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U312" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V312" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W312" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X312" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y312" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J300">
-    <cfRule type="cellIs" dxfId="76" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="J2:J312">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U300">
-    <cfRule type="cellIs" dxfId="74" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="U2:U312">
+    <cfRule type="cellIs" dxfId="8" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="7" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="6" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V300">
-    <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="V2:V312">
+    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -29314,7 +30346,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -29330,7 +30362,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D300</xm:sqref>
+          <xm:sqref>D2:D312</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39428DC2-861B-42DC-99E1-AA97B008F0D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04F9096-A050-4214-B9CC-547E8E8F1983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="82">
   <si>
     <t>Data</t>
   </si>
@@ -492,7 +492,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -566,6 +566,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -575,7 +578,101 @@
     <cellStyle name="Normal 2 2 2" xfId="3" xr:uid="{F6D7429B-6BC2-41D1-B818-FB0128371036}"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="145">
+  <dxfs count="134">
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1542,160 +1639,6 @@
       </font>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -1859,23 +1802,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -2167,94 +2093,94 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V11" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
-  <autoFilter ref="A1:V11" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V12" totalsRowShown="0" headerRowDxfId="133" dataDxfId="131" headerRowBorderDxfId="132" tableBorderDxfId="130" totalsRowBorderDxfId="129" headerRowCellStyle="Normal 2 2 2">
+  <autoFilter ref="A1:V12" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="139"/>
-    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="138"/>
-    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="137"/>
-    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="136"/>
-    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="135" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="134" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="133"/>
-    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="132" dataCellStyle="Porcentagem">
+    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="128"/>
+    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="127"/>
+    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="126"/>
+    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="125"/>
+    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="124" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="123" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="122"/>
+    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="121" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="131"/>
-    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="130"/>
-    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="129">
+    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="120"/>
+    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="119"/>
+    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="0">
       <calculatedColumnFormula>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="128" dataCellStyle="Moeda"/>
-    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="127" dataCellStyle="Porcentagem">
+    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="118" dataCellStyle="Moeda"/>
+    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="117" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="126"/>
-    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="125"/>
-    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="124"/>
-    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="123">
+    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="116"/>
+    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="115"/>
+    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="114"/>
+    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="113">
       <calculatedColumnFormula>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="122" dataCellStyle="Moeda 2 2">
+    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="112" dataCellStyle="Moeda 2 2">
       <calculatedColumnFormula>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="121" dataCellStyle="Moeda 3">
+    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="111" dataCellStyle="Moeda 3">
       <calculatedColumnFormula>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="120"/>
-    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="119"/>
-    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="118"/>
+    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="110"/>
+    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="109"/>
+    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="108"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y312" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39" headerRowBorderDxfId="37" tableBorderDxfId="38" totalsRowBorderDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y322" totalsRowShown="0" headerRowDxfId="52" dataDxfId="51" headerRowBorderDxfId="49" tableBorderDxfId="50" totalsRowBorderDxfId="48">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="35"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="34">
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="47"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="46">
       <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="33">
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="45">
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="30">
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="42">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="29" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="28" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="27"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="26" dataCellStyle="Normal 2 2 2">
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="41" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="40" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="39"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="38" dataCellStyle="Normal 2 2 2">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="25"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="24"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="23">
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="37"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="36"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="35">
       <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="22"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="21"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="20">
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="34"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="33"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="32">
       <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="19"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="18"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="17"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="16">
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="31"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="30"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="29"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="28">
       <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="15" dataCellStyle="Moeda">
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="27" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="14">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="26">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="13"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="12"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="11"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="25"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="24"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2683,7 +2609,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A050DE7D-8F3F-47CF-9E37-B95AFD2ED76A}">
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="23" bestFit="1" customWidth="1"/>
@@ -2801,15 +2727,11 @@
         <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
         <v>5.5516736244924467E-2</v>
       </c>
-      <c r="I2" s="11">
-        <v>0.25</v>
-      </c>
-      <c r="J2" s="11">
-        <v>0.77083333333333337</v>
-      </c>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
       <c r="K2" s="11">
         <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
-        <v>0.52083333333333337</v>
+        <v>0</v>
       </c>
       <c r="L2" s="10">
         <v>500</v>
@@ -3401,40 +3323,94 @@
       <c r="U11" s="4"/>
       <c r="V11" s="5"/>
     </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="27">
+        <v>3592.03</v>
+      </c>
+      <c r="F12" s="27">
+        <v>44758.63</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="9">
+        <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
+        <v>8.0253350024341683E-2</v>
+      </c>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4">
+        <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="10">
+        <v>500</v>
+      </c>
+      <c r="M12" s="9">
+        <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
+        <v>0.13919705570387775</v>
+      </c>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="12">
+        <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="R12" s="13" t="e">
+        <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S12" s="14" t="e">
+        <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T12" s="4"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="5"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H11">
-    <cfRule type="cellIs" dxfId="117" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="H2:H12">
+    <cfRule type="cellIs" dxfId="107" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="116" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="106" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R11">
-    <cfRule type="cellIs" dxfId="115" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="R2:R12">
+    <cfRule type="cellIs" dxfId="105" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="104" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="103" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="102" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="101" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="100" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="99" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S11">
-    <cfRule type="expression" dxfId="108" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="S2:S12">
+    <cfRule type="expression" dxfId="98" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -3443,7 +3419,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="107" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="97" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3457,7 +3433,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y312"/>
+  <dimension ref="A1:Y322"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -29276,11 +29252,11 @@
       <c r="A301" s="8">
         <v>46279</v>
       </c>
-      <c r="B301" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C301" s="26">
+      <c r="B301" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C301" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -29362,11 +29338,11 @@
       <c r="A302" s="8">
         <v>46279</v>
       </c>
-      <c r="B302" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C302" s="26">
+      <c r="B302" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C302" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -29448,11 +29424,11 @@
       <c r="A303" s="8">
         <v>46279</v>
       </c>
-      <c r="B303" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C303" s="26">
+      <c r="B303" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C303" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -29534,11 +29510,11 @@
       <c r="A304" s="8">
         <v>46279</v>
       </c>
-      <c r="B304" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C304" s="26">
+      <c r="B304" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C304" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -29620,11 +29596,11 @@
       <c r="A305" s="8">
         <v>46279</v>
       </c>
-      <c r="B305" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C305" s="26">
+      <c r="B305" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C305" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -29706,11 +29682,11 @@
       <c r="A306" s="8">
         <v>46279</v>
       </c>
-      <c r="B306" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C306" s="26">
+      <c r="B306" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C306" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -29792,11 +29768,11 @@
       <c r="A307" s="8">
         <v>46279</v>
       </c>
-      <c r="B307" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C307" s="26">
+      <c r="B307" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C307" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -29878,11 +29854,11 @@
       <c r="A308" s="8">
         <v>46279</v>
       </c>
-      <c r="B308" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C308" s="26">
+      <c r="B308" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C308" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -29964,11 +29940,11 @@
       <c r="A309" s="8">
         <v>46279</v>
       </c>
-      <c r="B309" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C309" s="26">
+      <c r="B309" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C309" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -30050,11 +30026,11 @@
       <c r="A310" s="8">
         <v>46279</v>
       </c>
-      <c r="B310" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C310" s="26">
+      <c r="B310" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C310" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -30136,11 +30112,11 @@
       <c r="A311" s="8">
         <v>46279</v>
       </c>
-      <c r="B311" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C311" s="26">
+      <c r="B311" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C311" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -30222,11 +30198,11 @@
       <c r="A312" s="8">
         <v>46279</v>
       </c>
-      <c r="B312" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C312" s="26">
+      <c r="B312" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C312" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -30304,40 +30280,900 @@
         <v>0</v>
       </c>
     </row>
+    <row r="313" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A313" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B313" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C313" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D313" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E313" s="4">
+        <v>5</v>
+      </c>
+      <c r="F313" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G313" s="10">
+        <v>18853.400000000001</v>
+      </c>
+      <c r="H313" s="10">
+        <v>324836.46999999997</v>
+      </c>
+      <c r="I313" s="4">
+        <v>2903</v>
+      </c>
+      <c r="J313" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.8039665312210796E-2</v>
+      </c>
+      <c r="K313" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L313" s="15">
+        <v>0.76180555555555551</v>
+      </c>
+      <c r="M313" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4909722222222222</v>
+      </c>
+      <c r="N313" s="4">
+        <v>105634</v>
+      </c>
+      <c r="O313" s="4">
+        <v>105668</v>
+      </c>
+      <c r="P313" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>34</v>
+      </c>
+      <c r="Q313" s="4">
+        <v>1169</v>
+      </c>
+      <c r="R313" s="4">
+        <v>11</v>
+      </c>
+      <c r="S313" s="4">
+        <v>11</v>
+      </c>
+      <c r="T313" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U313" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V313" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W313" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X313" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y313" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A314" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B314" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C314" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D314" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E314" s="4">
+        <v>3</v>
+      </c>
+      <c r="F314" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G314" s="10">
+        <v>7393.87</v>
+      </c>
+      <c r="H314" s="10">
+        <v>125117.98</v>
+      </c>
+      <c r="I314" s="4">
+        <v>1597</v>
+      </c>
+      <c r="J314" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.9095183601909178E-2</v>
+      </c>
+      <c r="K314" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L314" s="15">
+        <v>0.6875</v>
+      </c>
+      <c r="M314" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="N314" s="4">
+        <v>143202</v>
+      </c>
+      <c r="O314" s="4">
+        <v>143264</v>
+      </c>
+      <c r="P314" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>62</v>
+      </c>
+      <c r="Q314" s="4">
+        <v>282</v>
+      </c>
+      <c r="R314" s="4">
+        <v>17</v>
+      </c>
+      <c r="S314" s="4">
+        <v>17</v>
+      </c>
+      <c r="T314" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U314" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V314" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W314" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X314" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y314" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A315" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B315" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C315" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D315" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E315" s="4">
+        <v>11</v>
+      </c>
+      <c r="F315" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G315" s="10">
+        <v>15059.51</v>
+      </c>
+      <c r="H315" s="10">
+        <v>244376.56</v>
+      </c>
+      <c r="I315" s="4">
+        <v>1768</v>
+      </c>
+      <c r="J315" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.1624199964186423E-2</v>
+      </c>
+      <c r="K315" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L315" s="15">
+        <v>0.7993055555555556</v>
+      </c>
+      <c r="M315" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.52847222222222223</v>
+      </c>
+      <c r="N315" s="4">
+        <v>304633</v>
+      </c>
+      <c r="O315" s="4">
+        <v>304774</v>
+      </c>
+      <c r="P315" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>141</v>
+      </c>
+      <c r="Q315" s="4">
+        <v>325</v>
+      </c>
+      <c r="R315" s="4">
+        <v>51</v>
+      </c>
+      <c r="S315" s="4">
+        <v>51</v>
+      </c>
+      <c r="T315" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U315" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V315" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W315" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X315" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y315" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A316" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B316" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C316" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D316" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E316" s="4">
+        <v>2</v>
+      </c>
+      <c r="F316" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G316" s="10">
+        <v>9399.57</v>
+      </c>
+      <c r="H316" s="10">
+        <v>152021.64000000001</v>
+      </c>
+      <c r="I316" s="4">
+        <v>2125</v>
+      </c>
+      <c r="J316" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.1830473608888832E-2</v>
+      </c>
+      <c r="K316" s="11">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="L316" s="15">
+        <v>0.79861111111111116</v>
+      </c>
+      <c r="M316" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="N316" s="4">
+        <v>13659</v>
+      </c>
+      <c r="O316" s="4">
+        <v>13713</v>
+      </c>
+      <c r="P316" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>54</v>
+      </c>
+      <c r="Q316" s="4">
+        <v>300</v>
+      </c>
+      <c r="R316" s="4">
+        <v>37</v>
+      </c>
+      <c r="S316" s="4">
+        <v>37</v>
+      </c>
+      <c r="T316" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U316" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V316" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W316" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X316" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y316" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A317" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B317" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C317" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D317" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E317" s="4">
+        <v>1</v>
+      </c>
+      <c r="F317" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G317" s="10">
+        <v>4610.2</v>
+      </c>
+      <c r="H317" s="10">
+        <v>62316.29</v>
+      </c>
+      <c r="I317" s="4">
+        <v>454</v>
+      </c>
+      <c r="J317" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.3980655780374605E-2</v>
+      </c>
+      <c r="K317" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L317" s="15">
+        <v>0.62847222222222221</v>
+      </c>
+      <c r="M317" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.33680555555555552</v>
+      </c>
+      <c r="N317" s="4">
+        <v>275727</v>
+      </c>
+      <c r="O317" s="4">
+        <v>275769</v>
+      </c>
+      <c r="P317" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>42</v>
+      </c>
+      <c r="Q317" s="4">
+        <v>128</v>
+      </c>
+      <c r="R317" s="4">
+        <v>4</v>
+      </c>
+      <c r="S317" s="4">
+        <v>4</v>
+      </c>
+      <c r="T317" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U317" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V317" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W317" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X317" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y317" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A318" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B318" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C318" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D318" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E318" s="4">
+        <v>1</v>
+      </c>
+      <c r="F318" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G318" s="10">
+        <v>9051.34</v>
+      </c>
+      <c r="H318" s="10">
+        <v>88336.69</v>
+      </c>
+      <c r="I318" s="4">
+        <v>1831</v>
+      </c>
+      <c r="J318" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.10246410636395817</v>
+      </c>
+      <c r="K318" s="11">
+        <v>0.30555555555555558</v>
+      </c>
+      <c r="L318" s="15">
+        <v>0.65625</v>
+      </c>
+      <c r="M318" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.35069444444444442</v>
+      </c>
+      <c r="N318" s="4">
+        <v>280560</v>
+      </c>
+      <c r="O318" s="4">
+        <v>280603</v>
+      </c>
+      <c r="P318" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>43</v>
+      </c>
+      <c r="Q318" s="4">
+        <v>285</v>
+      </c>
+      <c r="R318" s="4">
+        <v>12</v>
+      </c>
+      <c r="S318" s="4">
+        <v>11</v>
+      </c>
+      <c r="T318" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>1</v>
+      </c>
+      <c r="U318" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="V318" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W318" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X318" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y318" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="319" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A319" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B319" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C319" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D319" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E319" s="4">
+        <v>1</v>
+      </c>
+      <c r="F319" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G319" s="10">
+        <v>12937.47</v>
+      </c>
+      <c r="H319" s="10">
+        <v>193243.18</v>
+      </c>
+      <c r="I319" s="4">
+        <v>2257</v>
+      </c>
+      <c r="J319" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.6949167365182041E-2</v>
+      </c>
+      <c r="K319" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L319" s="15">
+        <v>0.76736111111111116</v>
+      </c>
+      <c r="M319" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47569444444444448</v>
+      </c>
+      <c r="N319" s="4">
+        <v>125211</v>
+      </c>
+      <c r="O319" s="4">
+        <v>125287</v>
+      </c>
+      <c r="P319" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>76</v>
+      </c>
+      <c r="Q319" s="4">
+        <v>280</v>
+      </c>
+      <c r="R319" s="4">
+        <v>20</v>
+      </c>
+      <c r="S319" s="4">
+        <v>17</v>
+      </c>
+      <c r="T319" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>3</v>
+      </c>
+      <c r="U319" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.85</v>
+      </c>
+      <c r="V319" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W319" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="X319" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y319" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="320" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A320" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B320" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C320" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D320" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E320" s="4">
+        <v>1</v>
+      </c>
+      <c r="F320" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G320" s="10">
+        <v>1832.2</v>
+      </c>
+      <c r="H320" s="10">
+        <v>85862.29</v>
+      </c>
+      <c r="I320" s="4">
+        <v>282</v>
+      </c>
+      <c r="J320" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.1338820569542231E-2</v>
+      </c>
+      <c r="K320" s="11">
+        <v>0.29791666666666666</v>
+      </c>
+      <c r="L320" s="15">
+        <v>0.70625000000000004</v>
+      </c>
+      <c r="M320" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.40833333333333338</v>
+      </c>
+      <c r="N320" s="4">
+        <v>155512</v>
+      </c>
+      <c r="O320" s="4">
+        <v>155574</v>
+      </c>
+      <c r="P320" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>62</v>
+      </c>
+      <c r="Q320" s="4">
+        <v>145</v>
+      </c>
+      <c r="R320" s="4">
+        <v>2</v>
+      </c>
+      <c r="S320" s="4">
+        <v>2</v>
+      </c>
+      <c r="T320" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U320" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V320" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W320" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X320" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y320" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A321" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B321" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C321" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D321" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E321" s="4">
+        <v>4</v>
+      </c>
+      <c r="F321" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G321" s="10">
+        <v>7881.64</v>
+      </c>
+      <c r="H321" s="10">
+        <v>137881.19</v>
+      </c>
+      <c r="I321" s="4">
+        <v>1468</v>
+      </c>
+      <c r="J321" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.7162546972505821E-2</v>
+      </c>
+      <c r="K321" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L321" s="15">
+        <v>0.7416666666666667</v>
+      </c>
+      <c r="M321" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45</v>
+      </c>
+      <c r="N321" s="4">
+        <v>291428</v>
+      </c>
+      <c r="O321" s="4">
+        <v>291495</v>
+      </c>
+      <c r="P321" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>67</v>
+      </c>
+      <c r="Q321" s="4">
+        <v>299</v>
+      </c>
+      <c r="R321" s="4">
+        <v>27</v>
+      </c>
+      <c r="S321" s="4">
+        <v>27</v>
+      </c>
+      <c r="T321" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U321" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V321" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W321" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X321" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y321" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A322" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B322" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C322" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D322" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E322" s="4">
+        <v>5</v>
+      </c>
+      <c r="F322" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G322" s="10">
+        <v>7095.1</v>
+      </c>
+      <c r="H322" s="10">
+        <v>90277.26</v>
+      </c>
+      <c r="I322" s="4">
+        <v>998</v>
+      </c>
+      <c r="J322" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.8592327680303997E-2</v>
+      </c>
+      <c r="K322" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L322" s="15">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="M322" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.43055555555555552</v>
+      </c>
+      <c r="N322" s="4">
+        <v>119898</v>
+      </c>
+      <c r="O322" s="4">
+        <v>119995</v>
+      </c>
+      <c r="P322" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>97</v>
+      </c>
+      <c r="Q322" s="4">
+        <v>203</v>
+      </c>
+      <c r="R322" s="4">
+        <v>21</v>
+      </c>
+      <c r="S322" s="4">
+        <v>21</v>
+      </c>
+      <c r="T322" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U322" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V322" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W322" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X322" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y322" s="5">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J312">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="J2:J322">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U312">
-    <cfRule type="cellIs" dxfId="8" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="U2:U322">
+    <cfRule type="cellIs" dxfId="20" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="19" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="18" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V312">
-    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="V2:V322">
+    <cfRule type="expression" dxfId="13" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -30346,7 +31182,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30362,7 +31198,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D312</xm:sqref>
+          <xm:sqref>D2:D322</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04F9096-A050-4214-B9CC-547E8E8F1983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023D07C9-F984-4223-B37B-9D54316CCDBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="82">
   <si>
     <t>Data</t>
   </si>
@@ -171,9 +171,6 @@
     <t>Castanhal</t>
   </si>
   <si>
-    <t>Geber</t>
-  </si>
-  <si>
     <t>Vols</t>
   </si>
   <si>
@@ -289,6 +286,9 @@
   </si>
   <si>
     <t>13,27,27,27</t>
+  </si>
+  <si>
+    <t>Heremilton</t>
   </si>
 </sst>
 </file>
@@ -578,23 +578,468 @@
     <cellStyle name="Normal 2 2 2" xfId="3" xr:uid="{F6D7429B-6BC2-41D1-B818-FB0128371036}"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="134">
+  <dxfs count="145">
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1193,13 +1638,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1217,6 +1655,13 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1252,391 +1697,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
     </dxf>
     <dxf>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1802,6 +1862,23 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -2093,94 +2170,94 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V12" totalsRowShown="0" headerRowDxfId="133" dataDxfId="131" headerRowBorderDxfId="132" tableBorderDxfId="130" totalsRowBorderDxfId="129" headerRowCellStyle="Normal 2 2 2">
-  <autoFilter ref="A1:V12" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V13" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
+  <autoFilter ref="A1:V13" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="128"/>
-    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="127"/>
-    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="126"/>
-    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="125"/>
-    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="124" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="123" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="122"/>
-    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="121" dataCellStyle="Porcentagem">
+    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="139"/>
+    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="138"/>
+    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="137"/>
+    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="136"/>
+    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="135" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="134" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="133"/>
+    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="132" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="120"/>
-    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="119"/>
-    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="0">
+    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="131"/>
+    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="130"/>
+    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="129">
       <calculatedColumnFormula>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="118" dataCellStyle="Moeda"/>
-    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="117" dataCellStyle="Porcentagem">
+    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="128" dataCellStyle="Moeda"/>
+    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="127" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="116"/>
-    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="115"/>
-    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="114"/>
-    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="113">
+    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="126"/>
+    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="125"/>
+    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="124"/>
+    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="123">
       <calculatedColumnFormula>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="112" dataCellStyle="Moeda 2 2">
+    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="122" dataCellStyle="Moeda 2 2">
       <calculatedColumnFormula>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="111" dataCellStyle="Moeda 3">
+    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="121" dataCellStyle="Moeda 3">
       <calculatedColumnFormula>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="110"/>
-    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="109"/>
-    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="108"/>
+    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="120"/>
+    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="119"/>
+    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="118"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y322" totalsRowShown="0" headerRowDxfId="52" dataDxfId="51" headerRowBorderDxfId="49" tableBorderDxfId="50" totalsRowBorderDxfId="48">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y332" totalsRowShown="0" headerRowDxfId="117" dataDxfId="115" headerRowBorderDxfId="116" tableBorderDxfId="114" totalsRowBorderDxfId="113">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="47"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="46">
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="112"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="111">
       <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="45">
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="110">
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="42">
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="109"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="108"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="107">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="41" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="40" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="39"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="38" dataCellStyle="Normal 2 2 2">
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="106" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="105" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="104"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="103" dataCellStyle="Normal 2 2 2">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="37"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="36"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="35">
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="102"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="101"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="100">
       <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="34"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="33"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="32">
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="99"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="98"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="97">
       <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="31"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="30"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="29"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="28">
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="96"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="95"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="94"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="93">
       <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="27" dataCellStyle="Moeda">
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="92" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="26">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="91">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="25"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="24"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="23"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="90"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="89"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="88"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2511,7 +2588,7 @@
         <v>22</v>
       </c>
       <c r="B1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -2519,7 +2596,7 @@
         <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2535,7 +2612,7 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2543,7 +2620,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2575,7 +2652,7 @@
         <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -2583,7 +2660,7 @@
         <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -2596,7 +2673,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
         <v>24</v>
@@ -2609,7 +2686,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A050DE7D-8F3F-47CF-9E37-B95AFD2ED76A}">
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="23" bestFit="1" customWidth="1"/>
@@ -2670,13 +2747,13 @@
         <v>10</v>
       </c>
       <c r="L1" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="N1" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>14</v>
@@ -2708,11 +2785,11 @@
         <v>46027</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E2" s="10">
         <v>4275.3</v>
@@ -2776,11 +2853,11 @@
         <v>46238</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E3" s="10">
         <v>7461.93</v>
@@ -2830,11 +2907,11 @@
         <v>46241</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E4" s="10">
         <v>4770.58</v>
@@ -2898,11 +2975,11 @@
         <v>46245</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E5" s="10">
         <v>7701.21</v>
@@ -2952,7 +3029,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="U5" s="4"/>
       <c r="V5" s="5"/>
@@ -2962,11 +3039,11 @@
         <v>46247</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E6" s="10">
         <v>5668.48</v>
@@ -3030,11 +3107,11 @@
         <v>46252</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E7" s="10">
         <v>8639.84</v>
@@ -3084,7 +3161,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="U7" s="4">
         <v>1</v>
@@ -3098,11 +3175,11 @@
         <v>46253</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E8" s="10">
         <v>8971</v>
@@ -3160,11 +3237,11 @@
         <v>46268</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E9" s="10">
         <v>5954.82</v>
@@ -3216,11 +3293,11 @@
         <v>46269</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E10" s="10">
         <v>24238.02</v>
@@ -3272,11 +3349,11 @@
         <v>46276</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E11" s="10">
         <v>4224.17</v>
@@ -3328,16 +3405,16 @@
         <v>46280</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="27">
+        <v>45</v>
+      </c>
+      <c r="E12" s="10">
         <v>3592.03</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="10">
         <v>44758.63</v>
       </c>
       <c r="G12" s="4"/>
@@ -3377,40 +3454,94 @@
       <c r="U12" s="4"/>
       <c r="V12" s="5"/>
     </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="27">
+        <v>4998.43</v>
+      </c>
+      <c r="F13" s="27">
+        <v>82581.279999999999</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="9">
+        <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
+        <v>6.0527397976878054E-2</v>
+      </c>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4">
+        <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="10">
+        <v>500</v>
+      </c>
+      <c r="M13" s="9">
+        <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
+        <v>0.10003140986269689</v>
+      </c>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="12">
+        <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="R13" s="13" t="e">
+        <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S13" s="14" t="e">
+        <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T13" s="4"/>
+      <c r="U13" s="4"/>
+      <c r="V13" s="5"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H12">
-    <cfRule type="cellIs" dxfId="107" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="H2:H13">
+    <cfRule type="cellIs" dxfId="87" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="86" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R12">
-    <cfRule type="cellIs" dxfId="105" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="R2:R13">
+    <cfRule type="cellIs" dxfId="85" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="104" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="84" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="83" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="82" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="81" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="80" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="79" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S12">
-    <cfRule type="expression" dxfId="98" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="S2:S13">
+    <cfRule type="expression" dxfId="78" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -3419,7 +3550,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3433,7 +3564,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y322"/>
+  <dimension ref="A1:Y332"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -3465,16 +3596,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -3510,13 +3641,13 @@
         <v>13</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="R1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="S1" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>16</v>
@@ -3534,7 +3665,7 @@
         <v>20</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
@@ -3722,7 +3853,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E4" s="4">
         <v>1</v>
@@ -4044,7 +4175,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W7" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X7" s="4">
         <v>0</v>
@@ -4245,7 +4376,7 @@
       </c>
       <c r="F10" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Geber</v>
+        <v>Heremilton</v>
       </c>
       <c r="G10" s="10">
         <v>32724.35</v>
@@ -4668,7 +4799,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E15" s="4">
         <v>1</v>
@@ -5248,7 +5379,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W21" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X21" s="4">
         <v>0</v>
@@ -5592,7 +5723,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W25" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X25" s="4">
         <v>0</v>
@@ -5958,7 +6089,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E30" s="4">
         <v>1</v>
@@ -6280,7 +6411,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W33" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X33" s="4">
         <v>3</v>
@@ -6366,7 +6497,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W34" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X34" s="4">
         <v>3</v>
@@ -6710,13 +6841,13 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W38" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X38" s="4">
         <v>2</v>
       </c>
       <c r="Y38" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.25">
@@ -6882,7 +7013,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W40" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X40" s="4">
         <v>2</v>
@@ -6990,7 +7121,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E42" s="4">
         <v>4</v>
@@ -7398,7 +7529,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W46" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X46" s="4">
         <v>0</v>
@@ -7484,13 +7615,13 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W47" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X47" s="4">
         <v>2</v>
       </c>
       <c r="Y47" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.25">
@@ -7592,7 +7723,7 @@
         <v>8</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E49" s="4">
         <v>3</v>
@@ -7748,7 +7879,7 @@
         <v>2</v>
       </c>
       <c r="Y50" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.25">
@@ -8086,7 +8217,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W54" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X54" s="4">
         <v>0</v>
@@ -8115,7 +8246,7 @@
       </c>
       <c r="F55" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Geber</v>
+        <v>Heremilton</v>
       </c>
       <c r="G55" s="10">
         <v>23271.119999999999</v>
@@ -8194,7 +8325,7 @@
         <v>8</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E56" s="4">
         <v>3</v>
@@ -8780,7 +8911,7 @@
         <v>3</v>
       </c>
       <c r="Y62" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.25">
@@ -9376,7 +9507,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W69" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X69" s="4">
         <v>0</v>
@@ -9462,7 +9593,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W70" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X70" s="4">
         <v>0</v>
@@ -9570,7 +9701,7 @@
         <v>8</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E72" s="4">
         <v>3</v>
@@ -9806,7 +9937,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W74" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X74" s="4">
         <v>0</v>
@@ -10516,7 +10647,7 @@
         <v>8</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E83" s="4">
         <v>11</v>
@@ -10752,7 +10883,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W85" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X85" s="4">
         <v>0</v>
@@ -10930,7 +11061,7 @@
         <v>3</v>
       </c>
       <c r="Y87" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.25">
@@ -11032,7 +11163,7 @@
         <v>8</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E89" s="4">
         <v>11</v>
@@ -11548,7 +11679,7 @@
         <v>8</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E95" s="4">
         <v>4</v>
@@ -11698,7 +11829,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W96" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X96" s="4">
         <v>0</v>
@@ -11784,7 +11915,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W97" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X97" s="4">
         <v>3</v>
@@ -12042,7 +12173,7 @@
         <v>Não Atendeu a Meta</v>
       </c>
       <c r="W100" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X100" s="4">
         <v>1</v>
@@ -12924,7 +13055,7 @@
         <v>8</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E111" s="4">
         <v>2</v>
@@ -13246,7 +13377,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W114" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X114" s="4">
         <v>0</v>
@@ -13590,7 +13721,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W118" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X118" s="4">
         <v>0</v>
@@ -13963,7 +14094,7 @@
       </c>
       <c r="F123" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Geber</v>
+        <v>Heremilton</v>
       </c>
       <c r="G123" s="10">
         <v>46053.04</v>
@@ -14192,7 +14323,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W125" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X125" s="4">
         <v>0</v>
@@ -14214,7 +14345,7 @@
         <v>8</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E126" s="4">
         <v>2</v>
@@ -14364,7 +14495,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W127" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="X127" s="4">
         <v>0</v>
@@ -14880,7 +15011,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W133" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X133" s="4">
         <v>2</v>
@@ -14966,13 +15097,13 @@
         <v>Não Atendeu a Meta</v>
       </c>
       <c r="W134" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X134" s="4">
         <v>7</v>
       </c>
       <c r="Y134" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="135" spans="1:25" x14ac:dyDescent="0.25">
@@ -15058,7 +15189,7 @@
         <v>3</v>
       </c>
       <c r="Y135" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="136" spans="1:25" x14ac:dyDescent="0.25">
@@ -15074,7 +15205,7 @@
         <v>8</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E136" s="4">
         <v>2</v>
@@ -15332,7 +15463,7 @@
         <v>8</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E139" s="4">
         <v>4</v>
@@ -15654,13 +15785,13 @@
         <v>Não Atendeu a Meta</v>
       </c>
       <c r="W142" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X142" s="4">
         <v>5</v>
       </c>
       <c r="Y142" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="143" spans="1:25" x14ac:dyDescent="0.25">
@@ -15998,13 +16129,13 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W146" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X146" s="4">
         <v>3</v>
       </c>
       <c r="Y146" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="147" spans="1:25" x14ac:dyDescent="0.25">
@@ -16514,7 +16645,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W152" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X152" s="4">
         <v>0</v>
@@ -16708,7 +16839,7 @@
         <v>8</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E155" s="4">
         <v>3</v>
@@ -16944,7 +17075,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W157" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X157" s="4">
         <v>0</v>
@@ -17030,7 +17161,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W158" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X158" s="4">
         <v>0</v>
@@ -17224,7 +17355,7 @@
         <v>8</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E161" s="4">
         <v>3</v>
@@ -17294,7 +17425,7 @@
         <v>3</v>
       </c>
       <c r="Y161" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="162" spans="1:25" x14ac:dyDescent="0.25">
@@ -17632,7 +17763,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W165" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X165" s="4">
         <v>0</v>
@@ -17804,7 +17935,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W167" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X167" s="4">
         <v>0</v>
@@ -17976,7 +18107,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W169" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X169" s="4">
         <v>0</v>
@@ -17998,7 +18129,7 @@
         <v>8</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E170" s="4">
         <v>3</v>
@@ -18068,7 +18199,7 @@
         <v>4</v>
       </c>
       <c r="Y170" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="171" spans="1:25" x14ac:dyDescent="0.25">
@@ -18663,7 +18794,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W177" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X177" s="4">
         <v>0</v>
@@ -18749,7 +18880,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W178" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X178" s="4">
         <v>1</v>
@@ -18771,7 +18902,7 @@
         <v>8</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E179" s="4">
         <v>3</v>
@@ -19007,7 +19138,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W181" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X181" s="4">
         <v>1</v>
@@ -19093,7 +19224,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W182" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X182" s="4">
         <v>1</v>
@@ -19695,7 +19826,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W189" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X189" s="4">
         <v>0</v>
@@ -19953,7 +20084,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W192" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X192" s="4">
         <v>1</v>
@@ -20125,7 +20256,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W194" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X194" s="4">
         <v>1</v>
@@ -20319,7 +20450,7 @@
         <v>8</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E197" s="4">
         <v>3</v>
@@ -20469,7 +20600,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W198" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X198" s="4">
         <v>0</v>
@@ -20555,13 +20686,13 @@
         <v>Não Atendeu a Meta</v>
       </c>
       <c r="W199" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X199" s="4">
         <v>14</v>
       </c>
       <c r="Y199" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="200" spans="1:25" x14ac:dyDescent="0.25">
@@ -21157,7 +21288,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W206" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X206" s="4">
         <v>0</v>
@@ -21587,7 +21718,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W211" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X211" s="4">
         <v>0</v>
@@ -21695,7 +21826,7 @@
         <v>8</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E213" s="4">
         <v>1</v>
@@ -21953,7 +22084,7 @@
         <v>9</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E216" s="4">
         <v>5</v>
@@ -22189,7 +22320,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W218" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X218" s="4">
         <v>0</v>
@@ -22275,7 +22406,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W219" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X219" s="4">
         <v>0</v>
@@ -22963,7 +23094,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W227" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="X227" s="4">
         <v>0</v>
@@ -23049,7 +23180,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W228" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="X228" s="4">
         <v>0</v>
@@ -23307,7 +23438,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W231" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X231" s="4">
         <v>0</v>
@@ -23479,7 +23610,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W233" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X233" s="4">
         <v>0</v>
@@ -23565,7 +23696,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W234" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X234" s="4">
         <v>1</v>
@@ -23657,7 +23788,7 @@
         <v>8</v>
       </c>
       <c r="Y235" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="236" spans="1:25" x14ac:dyDescent="0.25">
@@ -24425,7 +24556,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W244" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X244" s="4">
         <v>0</v>
@@ -24533,7 +24664,7 @@
         <v>9</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E246" s="4">
         <v>5</v>
@@ -24683,7 +24814,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W247" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X247" s="4">
         <v>0</v>
@@ -24769,7 +24900,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W248" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X248" s="4">
         <v>0</v>
@@ -25119,7 +25250,7 @@
         <v>2</v>
       </c>
       <c r="Y252" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="253" spans="1:25" x14ac:dyDescent="0.25">
@@ -25221,7 +25352,7 @@
         <v>9</v>
       </c>
       <c r="D254" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E254" s="4">
         <v>3</v>
@@ -25377,7 +25508,7 @@
         <v>0</v>
       </c>
       <c r="Y255" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="256" spans="1:25" x14ac:dyDescent="0.25">
@@ -25463,7 +25594,7 @@
         <v>9</v>
       </c>
       <c r="Y256" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="257" spans="1:25" x14ac:dyDescent="0.25">
@@ -25801,7 +25932,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W260" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X260" s="4">
         <v>0</v>
@@ -25823,7 +25954,7 @@
         <v>9</v>
       </c>
       <c r="D261" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E261" s="4">
         <v>1</v>
@@ -25973,7 +26104,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W262" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X262" s="4">
         <v>0</v>
@@ -26511,7 +26642,7 @@
         <v>9</v>
       </c>
       <c r="D269" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E269" s="4">
         <v>5</v>
@@ -26661,7 +26792,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W270" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X270" s="4">
         <v>0</v>
@@ -27349,7 +27480,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W278" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X278" s="4">
         <v>0</v>
@@ -27457,7 +27588,7 @@
         <v>9</v>
       </c>
       <c r="D280" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E280" s="4">
         <v>11</v>
@@ -28293,7 +28424,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W289" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X289" s="4">
         <v>0</v>
@@ -28322,7 +28453,7 @@
       </c>
       <c r="F290" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Geber</v>
+        <v>Heremilton</v>
       </c>
       <c r="G290" s="10">
         <v>26771.97</v>
@@ -28471,7 +28602,7 @@
         <v>4</v>
       </c>
       <c r="Y291" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="292" spans="1:25" x14ac:dyDescent="0.25">
@@ -28487,7 +28618,7 @@
         <v>9</v>
       </c>
       <c r="D292" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E292" s="4">
         <v>4</v>
@@ -28723,7 +28854,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W294" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X294" s="4">
         <v>0</v>
@@ -28981,7 +29112,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W297" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X297" s="4">
         <v>0</v>
@@ -29089,7 +29220,7 @@
         <v>9</v>
       </c>
       <c r="D299" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E299" s="4">
         <v>11</v>
@@ -29325,7 +29456,7 @@
         <v>Não Atendeu a Meta</v>
       </c>
       <c r="W301" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X301" s="4">
         <v>2</v>
@@ -29755,7 +29886,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W306" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X306" s="4">
         <v>1</v>
@@ -29847,7 +29978,7 @@
         <v>4</v>
       </c>
       <c r="Y307" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="308" spans="1:25" x14ac:dyDescent="0.25">
@@ -29949,7 +30080,7 @@
         <v>9</v>
       </c>
       <c r="D309" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E309" s="4">
         <v>5</v>
@@ -30214,7 +30345,7 @@
       </c>
       <c r="F312" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Geber</v>
+        <v>Heremilton</v>
       </c>
       <c r="G312" s="10">
         <v>43098.8</v>
@@ -30284,11 +30415,11 @@
       <c r="A313" s="8">
         <v>46280</v>
       </c>
-      <c r="B313" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C313" s="26">
+      <c r="B313" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C313" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -30370,11 +30501,11 @@
       <c r="A314" s="8">
         <v>46280</v>
       </c>
-      <c r="B314" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C314" s="26">
+      <c r="B314" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C314" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -30456,11 +30587,11 @@
       <c r="A315" s="8">
         <v>46280</v>
       </c>
-      <c r="B315" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C315" s="26">
+      <c r="B315" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C315" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -30542,16 +30673,16 @@
       <c r="A316" s="8">
         <v>46280</v>
       </c>
-      <c r="B316" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C316" s="26">
+      <c r="B316" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C316" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
       <c r="D316" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E316" s="4">
         <v>2</v>
@@ -30628,11 +30759,11 @@
       <c r="A317" s="8">
         <v>46280</v>
       </c>
-      <c r="B317" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C317" s="26">
+      <c r="B317" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C317" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -30714,11 +30845,11 @@
       <c r="A318" s="8">
         <v>46280</v>
       </c>
-      <c r="B318" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C318" s="26">
+      <c r="B318" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C318" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -30800,11 +30931,11 @@
       <c r="A319" s="8">
         <v>46280</v>
       </c>
-      <c r="B319" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C319" s="26">
+      <c r="B319" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C319" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -30873,24 +31004,24 @@
         <v>Não Atendeu a Meta</v>
       </c>
       <c r="W319" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X319" s="4">
         <v>3</v>
       </c>
       <c r="Y319" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="320" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A320" s="8">
         <v>46280</v>
       </c>
-      <c r="B320" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C320" s="26">
+      <c r="B320" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C320" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -30972,11 +31103,11 @@
       <c r="A321" s="8">
         <v>46280</v>
       </c>
-      <c r="B321" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C321" s="26">
+      <c r="B321" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C321" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -31058,11 +31189,11 @@
       <c r="A322" s="8">
         <v>46280</v>
       </c>
-      <c r="B322" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C322" s="26">
+      <c r="B322" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C322" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -31140,40 +31271,900 @@
         <v>38</v>
       </c>
     </row>
+    <row r="323" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A323" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B323" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C323" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D323" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E323" s="4">
+        <v>5</v>
+      </c>
+      <c r="F323" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Heremilton</v>
+      </c>
+      <c r="G323" s="10">
+        <v>5872.06</v>
+      </c>
+      <c r="H323" s="10">
+        <v>201220.86</v>
+      </c>
+      <c r="I323" s="4">
+        <v>1865</v>
+      </c>
+      <c r="J323" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.9182163320443023E-2</v>
+      </c>
+      <c r="K323" s="11">
+        <v>0.27638888888888891</v>
+      </c>
+      <c r="L323" s="15">
+        <v>0.75694444444444442</v>
+      </c>
+      <c r="M323" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.48055555555555551</v>
+      </c>
+      <c r="N323" s="4">
+        <v>365909</v>
+      </c>
+      <c r="O323" s="4">
+        <v>366023</v>
+      </c>
+      <c r="P323" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>114</v>
+      </c>
+      <c r="Q323" s="4">
+        <v>406</v>
+      </c>
+      <c r="R323" s="4">
+        <v>18</v>
+      </c>
+      <c r="S323" s="4">
+        <v>18</v>
+      </c>
+      <c r="T323" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U323" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V323" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W323" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X323" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y323" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A324" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B324" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C324" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D324" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E324" s="4">
+        <v>11</v>
+      </c>
+      <c r="F324" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G324" s="10">
+        <v>13839.81</v>
+      </c>
+      <c r="H324" s="10">
+        <v>263221.28999999998</v>
+      </c>
+      <c r="I324" s="4">
+        <v>1370</v>
+      </c>
+      <c r="J324" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.2578611707282494E-2</v>
+      </c>
+      <c r="K324" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L324" s="15">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="M324" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.53125</v>
+      </c>
+      <c r="N324" s="4">
+        <v>304775</v>
+      </c>
+      <c r="O324" s="4">
+        <v>304927</v>
+      </c>
+      <c r="P324" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>152</v>
+      </c>
+      <c r="Q324" s="4">
+        <v>336</v>
+      </c>
+      <c r="R324" s="4">
+        <v>18</v>
+      </c>
+      <c r="S324" s="4">
+        <v>18</v>
+      </c>
+      <c r="T324" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U324" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V324" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W324" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X324" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y324" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A325" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B325" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C325" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D325" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E325" s="4">
+        <v>3</v>
+      </c>
+      <c r="F325" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G325" s="10">
+        <v>15170.57</v>
+      </c>
+      <c r="H325" s="10">
+        <v>176953.19</v>
+      </c>
+      <c r="I325" s="4">
+        <v>3551</v>
+      </c>
+      <c r="J325" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.573210802246628E-2</v>
+      </c>
+      <c r="K325" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L325" s="15">
+        <v>0.78125</v>
+      </c>
+      <c r="M325" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="N325" s="4">
+        <v>143264</v>
+      </c>
+      <c r="O325" s="4">
+        <v>143327</v>
+      </c>
+      <c r="P325" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>63</v>
+      </c>
+      <c r="Q325" s="4">
+        <v>258</v>
+      </c>
+      <c r="R325" s="4">
+        <v>17</v>
+      </c>
+      <c r="S325" s="4">
+        <v>17</v>
+      </c>
+      <c r="T325" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U325" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V325" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W325" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X325" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y325" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A326" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B326" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C326" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D326" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E326" s="4">
+        <v>2</v>
+      </c>
+      <c r="F326" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G326" s="10">
+        <v>7020.05</v>
+      </c>
+      <c r="H326" s="10">
+        <v>117163.06</v>
+      </c>
+      <c r="I326" s="4">
+        <v>1515</v>
+      </c>
+      <c r="J326" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.9916922620491475E-2</v>
+      </c>
+      <c r="K326" s="11">
+        <v>0.28472222222222221</v>
+      </c>
+      <c r="L326" s="15">
+        <v>0.81597222222222221</v>
+      </c>
+      <c r="M326" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.53125</v>
+      </c>
+      <c r="N326" s="4">
+        <v>13713</v>
+      </c>
+      <c r="O326" s="4">
+        <v>13778</v>
+      </c>
+      <c r="P326" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>65</v>
+      </c>
+      <c r="Q326" s="4">
+        <v>253</v>
+      </c>
+      <c r="R326" s="4">
+        <v>18</v>
+      </c>
+      <c r="S326" s="4">
+        <v>18</v>
+      </c>
+      <c r="T326" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U326" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V326" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W326" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X326" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y326" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A327" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B327" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C327" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D327" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E327" s="4">
+        <v>1</v>
+      </c>
+      <c r="F327" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G327" s="10">
+        <v>8636.98</v>
+      </c>
+      <c r="H327" s="10">
+        <v>106331.64</v>
+      </c>
+      <c r="I327" s="4">
+        <v>1392</v>
+      </c>
+      <c r="J327" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.1226810759243429E-2</v>
+      </c>
+      <c r="K327" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L327" s="15">
+        <v>0.78819444444444442</v>
+      </c>
+      <c r="M327" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.49652777777777773</v>
+      </c>
+      <c r="N327" s="4">
+        <v>125387</v>
+      </c>
+      <c r="O327" s="4">
+        <v>125456</v>
+      </c>
+      <c r="P327" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>69</v>
+      </c>
+      <c r="Q327" s="4">
+        <v>220</v>
+      </c>
+      <c r="R327" s="4">
+        <v>21</v>
+      </c>
+      <c r="S327" s="4">
+        <v>21</v>
+      </c>
+      <c r="T327" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U327" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V327" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W327" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X327" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y327" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A328" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B328" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C328" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D328" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E328" s="4">
+        <v>1</v>
+      </c>
+      <c r="F328" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G328" s="10">
+        <v>4901</v>
+      </c>
+      <c r="H328" s="10">
+        <v>81792.149999999994</v>
+      </c>
+      <c r="I328" s="4">
+        <v>1711</v>
+      </c>
+      <c r="J328" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.9920175713684021E-2</v>
+      </c>
+      <c r="K328" s="11">
+        <v>0.32291666666666669</v>
+      </c>
+      <c r="L328" s="15">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="M328" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.43749999999999994</v>
+      </c>
+      <c r="N328" s="4">
+        <v>280603</v>
+      </c>
+      <c r="O328" s="4">
+        <v>280628</v>
+      </c>
+      <c r="P328" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>25</v>
+      </c>
+      <c r="Q328" s="4">
+        <v>322</v>
+      </c>
+      <c r="R328" s="4">
+        <v>5</v>
+      </c>
+      <c r="S328" s="4">
+        <v>5</v>
+      </c>
+      <c r="T328" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U328" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V328" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W328" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X328" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y328" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A329" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B329" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C329" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D329" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E329" s="4">
+        <v>1</v>
+      </c>
+      <c r="F329" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G329" s="10">
+        <v>524.25</v>
+      </c>
+      <c r="H329" s="10">
+        <v>6389.52</v>
+      </c>
+      <c r="I329" s="4">
+        <v>13</v>
+      </c>
+      <c r="J329" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.2048416782481301E-2</v>
+      </c>
+      <c r="K329" s="11">
+        <v>0.29305555555555557</v>
+      </c>
+      <c r="L329" s="15">
+        <v>0.57986111111111116</v>
+      </c>
+      <c r="M329" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.28680555555555559</v>
+      </c>
+      <c r="N329" s="4">
+        <v>155574</v>
+      </c>
+      <c r="O329" s="4">
+        <v>155604</v>
+      </c>
+      <c r="P329" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>30</v>
+      </c>
+      <c r="Q329" s="4">
+        <v>6</v>
+      </c>
+      <c r="R329" s="4">
+        <v>1</v>
+      </c>
+      <c r="S329" s="4">
+        <v>1</v>
+      </c>
+      <c r="T329" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U329" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V329" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W329" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X329" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y329" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A330" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B330" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C330" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D330" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E330" s="4">
+        <v>3</v>
+      </c>
+      <c r="F330" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G330" s="10">
+        <v>16100.79</v>
+      </c>
+      <c r="H330" s="10">
+        <v>48925.7</v>
+      </c>
+      <c r="I330" s="4">
+        <v>7239</v>
+      </c>
+      <c r="J330" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.32908655369264012</v>
+      </c>
+      <c r="K330" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L330" s="15">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="M330" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.37499999999999994</v>
+      </c>
+      <c r="N330" s="4">
+        <v>105668</v>
+      </c>
+      <c r="O330" s="4">
+        <v>105705</v>
+      </c>
+      <c r="P330" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>37</v>
+      </c>
+      <c r="Q330" s="4">
+        <v>122</v>
+      </c>
+      <c r="R330" s="4">
+        <v>3</v>
+      </c>
+      <c r="S330" s="4">
+        <v>3</v>
+      </c>
+      <c r="T330" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U330" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V330" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W330" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X330" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y330" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A331" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B331" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C331" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D331" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E331" s="4">
+        <v>5</v>
+      </c>
+      <c r="F331" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G331" s="10">
+        <v>5277.99</v>
+      </c>
+      <c r="H331" s="10">
+        <v>140605.03</v>
+      </c>
+      <c r="I331" s="4">
+        <v>853</v>
+      </c>
+      <c r="J331" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.7537704020972791E-2</v>
+      </c>
+      <c r="K331" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L331" s="15">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="M331" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="N331" s="4">
+        <v>119995</v>
+      </c>
+      <c r="O331" s="4">
+        <v>120091</v>
+      </c>
+      <c r="P331" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>96</v>
+      </c>
+      <c r="Q331" s="4">
+        <v>181</v>
+      </c>
+      <c r="R331" s="4">
+        <v>18</v>
+      </c>
+      <c r="S331" s="4">
+        <v>18</v>
+      </c>
+      <c r="T331" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U331" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V331" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W331" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X331" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y331" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A332" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B332" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C332" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D332" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E332" s="4">
+        <v>1</v>
+      </c>
+      <c r="F332" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G332" s="10">
+        <v>2603.98</v>
+      </c>
+      <c r="H332" s="10">
+        <v>52384.78</v>
+      </c>
+      <c r="I332" s="4">
+        <v>199</v>
+      </c>
+      <c r="J332" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.9708713103309779E-2</v>
+      </c>
+      <c r="K332" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L332" s="15">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="M332" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="N332" s="4">
+        <v>275769</v>
+      </c>
+      <c r="O332" s="4">
+        <v>275868</v>
+      </c>
+      <c r="P332" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>99</v>
+      </c>
+      <c r="Q332" s="4">
+        <v>47</v>
+      </c>
+      <c r="R332" s="4">
+        <v>2</v>
+      </c>
+      <c r="S332" s="4">
+        <v>2</v>
+      </c>
+      <c r="T332" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U332" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V332" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W332" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X332" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y332" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J322">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="J2:J332">
+    <cfRule type="cellIs" dxfId="76" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="75" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U322">
-    <cfRule type="cellIs" dxfId="20" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="U2:U332">
+    <cfRule type="cellIs" dxfId="74" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="73" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="72" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="71" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="70" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="69" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="68" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V322">
-    <cfRule type="expression" dxfId="13" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="V2:V332">
+    <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -31182,7 +32173,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -31198,7 +32189,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D322</xm:sqref>
+          <xm:sqref>D2:D332</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023D07C9-F984-4223-B37B-9D54316CCDBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9362CC88-EB69-4442-9F52-DD16819DC512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="83">
   <si>
     <t>Data</t>
   </si>
@@ -289,6 +289,9 @@
   </si>
   <si>
     <t>Heremilton</t>
+  </si>
+  <si>
+    <t>38,38,38</t>
   </si>
 </sst>
 </file>
@@ -732,6 +735,509 @@
         <i val="0"/>
         <color rgb="FFFF0000"/>
       </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[h]:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[h]:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0070C0"/>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1358,509 +1864,6 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[h]:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[h]:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="25" formatCode="hh:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0070C0"/>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -2170,8 +2173,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V13" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
-  <autoFilter ref="A1:V13" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V14" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
+  <autoFilter ref="A1:V14" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="139"/>
     <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="138"/>
@@ -2213,51 +2216,51 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y332" totalsRowShown="0" headerRowDxfId="117" dataDxfId="115" headerRowBorderDxfId="116" tableBorderDxfId="114" totalsRowBorderDxfId="113">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y343" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50" headerRowBorderDxfId="48" tableBorderDxfId="49" totalsRowBorderDxfId="47">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="112"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="111">
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="46"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="45">
       <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="110">
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="44">
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="109"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="108"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="107">
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="41">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="106" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="105" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="104"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="103" dataCellStyle="Normal 2 2 2">
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="40" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="39" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="38"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="37" dataCellStyle="Normal 2 2 2">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="102"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="101"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="100">
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="36"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="35"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="34">
       <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="99"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="98"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="97">
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="33"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="32"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="31">
       <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="96"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="95"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="94"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="93">
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="30"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="29"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="28"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="27">
       <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="92" dataCellStyle="Moeda">
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="26" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="91">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="25">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="90"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="89"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="88"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="24"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="23"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2686,7 +2689,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A050DE7D-8F3F-47CF-9E37-B95AFD2ED76A}">
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="23" bestFit="1" customWidth="1"/>
@@ -3465,10 +3468,10 @@
       <c r="D13" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="10">
         <v>4998.43</v>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="10">
         <v>82581.279999999999</v>
       </c>
       <c r="G13" s="4"/>
@@ -3508,40 +3511,104 @@
       <c r="U13" s="4"/>
       <c r="V13" s="5"/>
     </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="27">
+        <v>3850.15</v>
+      </c>
+      <c r="F14" s="27">
+        <v>59193.01</v>
+      </c>
+      <c r="G14" s="4">
+        <v>537</v>
+      </c>
+      <c r="H14" s="9">
+        <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
+        <v>6.5043997593634786E-2</v>
+      </c>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4">
+        <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="10">
+        <v>500</v>
+      </c>
+      <c r="M14" s="9">
+        <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
+        <v>0.12986507019207044</v>
+      </c>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4">
+        <v>16</v>
+      </c>
+      <c r="P14" s="4">
+        <v>14</v>
+      </c>
+      <c r="Q14" s="12">
+        <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
+        <v>2</v>
+      </c>
+      <c r="R14" s="13">
+        <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
+        <v>0.875</v>
+      </c>
+      <c r="S14" s="14" t="str">
+        <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="T14" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="U14" s="4">
+        <v>2</v>
+      </c>
+      <c r="V14" s="5"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H13">
-    <cfRule type="cellIs" dxfId="87" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="H2:H14">
+    <cfRule type="cellIs" dxfId="117" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="116" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R13">
-    <cfRule type="cellIs" dxfId="85" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="R2:R14">
+    <cfRule type="cellIs" dxfId="115" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="114" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="113" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="112" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="111" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="110" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="109" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S13">
-    <cfRule type="expression" dxfId="78" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="S2:S14">
+    <cfRule type="expression" dxfId="108" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -3550,7 +3617,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="107" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3564,7 +3631,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y332"/>
+  <dimension ref="A1:Y343"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -31275,11 +31342,11 @@
       <c r="A323" s="8">
         <v>46281</v>
       </c>
-      <c r="B323" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C323" s="26">
+      <c r="B323" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C323" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -31361,11 +31428,11 @@
       <c r="A324" s="8">
         <v>46281</v>
       </c>
-      <c r="B324" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C324" s="26">
+      <c r="B324" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C324" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -31447,11 +31514,11 @@
       <c r="A325" s="8">
         <v>46281</v>
       </c>
-      <c r="B325" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C325" s="26">
+      <c r="B325" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C325" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -31533,11 +31600,11 @@
       <c r="A326" s="8">
         <v>46281</v>
       </c>
-      <c r="B326" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C326" s="26">
+      <c r="B326" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C326" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -31619,11 +31686,11 @@
       <c r="A327" s="8">
         <v>46281</v>
       </c>
-      <c r="B327" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C327" s="26">
+      <c r="B327" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C327" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -31705,11 +31772,11 @@
       <c r="A328" s="8">
         <v>46281</v>
       </c>
-      <c r="B328" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C328" s="26">
+      <c r="B328" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C328" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -31791,11 +31858,11 @@
       <c r="A329" s="8">
         <v>46281</v>
       </c>
-      <c r="B329" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C329" s="26">
+      <c r="B329" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C329" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -31877,11 +31944,11 @@
       <c r="A330" s="8">
         <v>46281</v>
       </c>
-      <c r="B330" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C330" s="26">
+      <c r="B330" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C330" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -31963,11 +32030,11 @@
       <c r="A331" s="8">
         <v>46281</v>
       </c>
-      <c r="B331" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C331" s="26">
+      <c r="B331" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C331" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -32049,11 +32116,11 @@
       <c r="A332" s="8">
         <v>46281</v>
       </c>
-      <c r="B332" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C332" s="26">
+      <c r="B332" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C332" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -32131,40 +32198,986 @@
         <v>0</v>
       </c>
     </row>
+    <row r="333" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A333" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B333" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C333" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D333" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E333" s="4">
+        <v>1</v>
+      </c>
+      <c r="F333" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G333" s="10">
+        <v>5521.26</v>
+      </c>
+      <c r="H333" s="10">
+        <v>129596.87</v>
+      </c>
+      <c r="I333" s="4">
+        <v>1034</v>
+      </c>
+      <c r="J333" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.2603343738162817E-2</v>
+      </c>
+      <c r="K333" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L333" s="15">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="M333" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="N333" s="4">
+        <v>125456</v>
+      </c>
+      <c r="O333" s="4">
+        <v>125509</v>
+      </c>
+      <c r="P333" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>53</v>
+      </c>
+      <c r="Q333" s="4">
+        <v>343</v>
+      </c>
+      <c r="R333" s="4">
+        <v>6</v>
+      </c>
+      <c r="S333" s="4">
+        <v>6</v>
+      </c>
+      <c r="T333" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U333" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V333" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W333" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X333" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y333" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A334" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B334" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C334" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D334" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E334" s="4">
+        <v>11</v>
+      </c>
+      <c r="F334" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G334" s="10">
+        <v>12275.41</v>
+      </c>
+      <c r="H334" s="10">
+        <v>140685.51</v>
+      </c>
+      <c r="I334" s="4">
+        <v>1206</v>
+      </c>
+      <c r="J334" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.725425951826879E-2</v>
+      </c>
+      <c r="K334" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L334" s="15">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="M334" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.5</v>
+      </c>
+      <c r="N334" s="4">
+        <v>304927</v>
+      </c>
+      <c r="O334" s="4">
+        <v>305081</v>
+      </c>
+      <c r="P334" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>154</v>
+      </c>
+      <c r="Q334" s="4">
+        <v>296</v>
+      </c>
+      <c r="R334" s="4">
+        <v>34</v>
+      </c>
+      <c r="S334" s="4">
+        <v>34</v>
+      </c>
+      <c r="T334" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U334" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V334" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W334" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X334" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y334" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A335" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B335" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C335" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D335" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E335" s="4">
+        <v>5</v>
+      </c>
+      <c r="F335" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G335" s="10">
+        <v>8076.38</v>
+      </c>
+      <c r="H335" s="10">
+        <v>293775.09999999998</v>
+      </c>
+      <c r="I335" s="4">
+        <v>2323</v>
+      </c>
+      <c r="J335" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.7491710495545746E-2</v>
+      </c>
+      <c r="K335" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L335" s="15">
+        <v>0.67013888888888884</v>
+      </c>
+      <c r="M335" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.37847222222222215</v>
+      </c>
+      <c r="N335" s="4">
+        <v>120091</v>
+      </c>
+      <c r="O335" s="4">
+        <v>120139</v>
+      </c>
+      <c r="P335" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>48</v>
+      </c>
+      <c r="Q335" s="4">
+        <v>349</v>
+      </c>
+      <c r="R335" s="4">
+        <v>3</v>
+      </c>
+      <c r="S335" s="4">
+        <v>3</v>
+      </c>
+      <c r="T335" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U335" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V335" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W335" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X335" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y335" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A336" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B336" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C336" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D336" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E336" s="4">
+        <v>1</v>
+      </c>
+      <c r="F336" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Manoel</v>
+      </c>
+      <c r="G336" s="10">
+        <v>358.18</v>
+      </c>
+      <c r="H336" s="10">
+        <v>2455.2399999999998</v>
+      </c>
+      <c r="I336" s="4">
+        <v>25</v>
+      </c>
+      <c r="J336" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.14588390544305244</v>
+      </c>
+      <c r="K336" s="11">
+        <v>0.375</v>
+      </c>
+      <c r="L336" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="M336" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.125</v>
+      </c>
+      <c r="N336" s="4">
+        <v>12285</v>
+      </c>
+      <c r="O336" s="4">
+        <v>12305</v>
+      </c>
+      <c r="P336" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>20</v>
+      </c>
+      <c r="Q336" s="4">
+        <v>1</v>
+      </c>
+      <c r="R336" s="4">
+        <v>1</v>
+      </c>
+      <c r="S336" s="4">
+        <v>1</v>
+      </c>
+      <c r="T336" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U336" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V336" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W336" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X336" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y336" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A337" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B337" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C337" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D337" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E337" s="4">
+        <v>3</v>
+      </c>
+      <c r="F337" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G337" s="10">
+        <v>8813.31</v>
+      </c>
+      <c r="H337" s="10">
+        <v>242834.71</v>
+      </c>
+      <c r="I337" s="4">
+        <v>32</v>
+      </c>
+      <c r="J337" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.6293452447551666E-2</v>
+      </c>
+      <c r="K337" s="11">
+        <v>0.30555555555555558</v>
+      </c>
+      <c r="L337" s="15">
+        <v>0.72638888888888886</v>
+      </c>
+      <c r="M337" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.42083333333333328</v>
+      </c>
+      <c r="N337" s="4">
+        <v>143337</v>
+      </c>
+      <c r="O337" s="4">
+        <v>143392</v>
+      </c>
+      <c r="P337" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>55</v>
+      </c>
+      <c r="Q337" s="4">
+        <v>233</v>
+      </c>
+      <c r="R337" s="4">
+        <v>32</v>
+      </c>
+      <c r="S337" s="4">
+        <v>31</v>
+      </c>
+      <c r="T337" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>1</v>
+      </c>
+      <c r="U337" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.96875</v>
+      </c>
+      <c r="V337" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W337" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X337" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y337" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="338" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A338" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B338" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C338" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D338" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E338" s="4">
+        <v>5</v>
+      </c>
+      <c r="F338" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G338" s="10">
+        <v>16075.23</v>
+      </c>
+      <c r="H338" s="10">
+        <v>107067.52</v>
+      </c>
+      <c r="I338" s="4">
+        <v>7073</v>
+      </c>
+      <c r="J338" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.15014105117966681</v>
+      </c>
+      <c r="K338" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L338" s="15">
+        <v>0.66180555555555554</v>
+      </c>
+      <c r="M338" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.39097222222222222</v>
+      </c>
+      <c r="N338" s="4">
+        <v>105705</v>
+      </c>
+      <c r="O338" s="4">
+        <v>105750</v>
+      </c>
+      <c r="P338" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>45</v>
+      </c>
+      <c r="Q338" s="4">
+        <v>543</v>
+      </c>
+      <c r="R338" s="4">
+        <v>3</v>
+      </c>
+      <c r="S338" s="4">
+        <v>3</v>
+      </c>
+      <c r="T338" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U338" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V338" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W338" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X338" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y338" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="339" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A339" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B339" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C339" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D339" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E339" s="4">
+        <v>2</v>
+      </c>
+      <c r="F339" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G339" s="10">
+        <v>10916.48</v>
+      </c>
+      <c r="H339" s="10">
+        <v>227108.77</v>
+      </c>
+      <c r="I339" s="4">
+        <v>1530</v>
+      </c>
+      <c r="J339" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.8067188246407218E-2</v>
+      </c>
+      <c r="K339" s="11">
+        <v>0.28125</v>
+      </c>
+      <c r="L339" s="15">
+        <v>0.83680555555555558</v>
+      </c>
+      <c r="M339" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="N339" s="4">
+        <v>13778</v>
+      </c>
+      <c r="O339" s="4">
+        <v>13855</v>
+      </c>
+      <c r="P339" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>77</v>
+      </c>
+      <c r="Q339" s="4">
+        <v>254</v>
+      </c>
+      <c r="R339" s="4">
+        <v>40</v>
+      </c>
+      <c r="S339" s="4">
+        <v>40</v>
+      </c>
+      <c r="T339" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U339" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V339" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W339" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X339" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y339" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="340" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A340" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B340" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C340" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D340" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E340" s="4">
+        <v>1</v>
+      </c>
+      <c r="F340" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G340" s="10">
+        <v>1935.41</v>
+      </c>
+      <c r="H340" s="10">
+        <v>95702.02</v>
+      </c>
+      <c r="I340" s="4">
+        <v>207</v>
+      </c>
+      <c r="J340" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.0223293092455102E-2</v>
+      </c>
+      <c r="K340" s="11">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="L340" s="15">
+        <v>0.62986111111111109</v>
+      </c>
+      <c r="M340" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.33124999999999999</v>
+      </c>
+      <c r="N340" s="4">
+        <v>280628</v>
+      </c>
+      <c r="O340" s="4">
+        <v>280667</v>
+      </c>
+      <c r="P340" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>39</v>
+      </c>
+      <c r="Q340" s="4">
+        <v>1</v>
+      </c>
+      <c r="R340" s="4">
+        <v>1</v>
+      </c>
+      <c r="S340" s="4">
+        <v>1</v>
+      </c>
+      <c r="T340" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U340" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V340" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W340" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X340" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y340" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A341" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B341" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C341" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D341" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E341" s="4">
+        <v>1</v>
+      </c>
+      <c r="F341" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G341" s="10">
+        <v>2190.85</v>
+      </c>
+      <c r="H341" s="10">
+        <v>64848.55</v>
+      </c>
+      <c r="I341" s="4">
+        <v>423</v>
+      </c>
+      <c r="J341" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.3784101572047483E-2</v>
+      </c>
+      <c r="K341" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L341" s="15">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="M341" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.43055555555555552</v>
+      </c>
+      <c r="N341" s="4">
+        <v>275868</v>
+      </c>
+      <c r="O341" s="4">
+        <v>275910</v>
+      </c>
+      <c r="P341" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>42</v>
+      </c>
+      <c r="Q341" s="4">
+        <v>54</v>
+      </c>
+      <c r="R341" s="4">
+        <v>1</v>
+      </c>
+      <c r="S341" s="4">
+        <v>1</v>
+      </c>
+      <c r="T341" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U341" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V341" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W341" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X341" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y341" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A342" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B342" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C342" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D342" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E342" s="4">
+        <v>1</v>
+      </c>
+      <c r="F342" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Heremilton</v>
+      </c>
+      <c r="G342" s="10">
+        <v>11172.61</v>
+      </c>
+      <c r="H342" s="10">
+        <v>867848.53</v>
+      </c>
+      <c r="I342" s="4">
+        <v>1787</v>
+      </c>
+      <c r="J342" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>1.2873917064767051E-2</v>
+      </c>
+      <c r="K342" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L342" s="15">
+        <v>0.75347222222222221</v>
+      </c>
+      <c r="M342" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4826388888888889</v>
+      </c>
+      <c r="N342" s="4">
+        <v>366023</v>
+      </c>
+      <c r="O342" s="4">
+        <v>366117</v>
+      </c>
+      <c r="P342" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>94</v>
+      </c>
+      <c r="Q342" s="4">
+        <v>861</v>
+      </c>
+      <c r="R342" s="4">
+        <v>7</v>
+      </c>
+      <c r="S342" s="4">
+        <v>7</v>
+      </c>
+      <c r="T342" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U342" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V342" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W342" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X342" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y342" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A343" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B343" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C343" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D343" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E343" s="4">
+        <v>5</v>
+      </c>
+      <c r="F343" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G343" s="10">
+        <v>2661.82</v>
+      </c>
+      <c r="H343" s="10">
+        <v>203325.31</v>
+      </c>
+      <c r="I343" s="4">
+        <v>450</v>
+      </c>
+      <c r="J343" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>1.3091434607919695E-2</v>
+      </c>
+      <c r="K343" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L343" s="15">
+        <v>0.74583333333333335</v>
+      </c>
+      <c r="M343" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45416666666666666</v>
+      </c>
+      <c r="N343" s="4">
+        <v>155638</v>
+      </c>
+      <c r="O343" s="4">
+        <v>155669</v>
+      </c>
+      <c r="P343" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>31</v>
+      </c>
+      <c r="Q343" s="4">
+        <v>269</v>
+      </c>
+      <c r="R343" s="4">
+        <v>3</v>
+      </c>
+      <c r="S343" s="4">
+        <v>3</v>
+      </c>
+      <c r="T343" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U343" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V343" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W343" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X343" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y343" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J332">
-    <cfRule type="cellIs" dxfId="76" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="J2:J343">
+    <cfRule type="cellIs" dxfId="21" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="20" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U332">
-    <cfRule type="cellIs" dxfId="74" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="U2:U343">
+    <cfRule type="cellIs" dxfId="19" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="18" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="17" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V332">
-    <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="V2:V343">
+    <cfRule type="expression" dxfId="12" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -32173,7 +33186,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -32189,7 +33202,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D332</xm:sqref>
+          <xm:sqref>D2:D343</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9362CC88-EB69-4442-9F52-DD16819DC512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35E3A36-029A-4526-8687-E4811A365637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha2" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="84">
   <si>
     <t>Data</t>
   </si>
@@ -292,6 +292,9 @@
   </si>
   <si>
     <t>38,38,38</t>
+  </si>
+  <si>
+    <t>42,10,13,13</t>
   </si>
 </sst>
 </file>
@@ -2173,8 +2176,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V14" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
-  <autoFilter ref="A1:V14" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V15" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
+  <autoFilter ref="A1:V15" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="139"/>
     <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="138"/>
@@ -2216,7 +2219,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y343" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50" headerRowBorderDxfId="48" tableBorderDxfId="49" totalsRowBorderDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y354" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50" headerRowBorderDxfId="48" tableBorderDxfId="49" totalsRowBorderDxfId="47">
   <tableColumns count="25">
     <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="46"/>
     <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="45">
@@ -2689,7 +2692,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A050DE7D-8F3F-47CF-9E37-B95AFD2ED76A}">
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="23" bestFit="1" customWidth="1"/>
@@ -3522,10 +3525,10 @@
       <c r="D14" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="10">
         <v>3850.15</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="10">
         <v>59193.01</v>
       </c>
       <c r="G14" s="4">
@@ -3575,8 +3578,64 @@
       </c>
       <c r="V14" s="5"/>
     </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" s="8">
+        <v>46283</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="27">
+        <v>6994.8</v>
+      </c>
+      <c r="F15" s="27">
+        <v>202752.86</v>
+      </c>
+      <c r="G15" s="4">
+        <v>1833</v>
+      </c>
+      <c r="H15" s="9">
+        <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
+        <v>3.4499143439949503E-2</v>
+      </c>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4">
+        <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="10">
+        <v>500</v>
+      </c>
+      <c r="M15" s="9">
+        <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
+        <v>7.1481672099273738E-2</v>
+      </c>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="12">
+        <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="R15" s="13" t="e">
+        <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S15" s="14" t="e">
+        <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T15" s="4"/>
+      <c r="U15" s="4"/>
+      <c r="V15" s="5"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H14">
+  <conditionalFormatting sqref="H2:H15">
     <cfRule type="cellIs" dxfId="117" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
@@ -3584,7 +3643,7 @@
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R14">
+  <conditionalFormatting sqref="R2:R15">
     <cfRule type="cellIs" dxfId="115" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
@@ -3607,7 +3666,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S14">
+  <conditionalFormatting sqref="S2:S15">
     <cfRule type="expression" dxfId="108" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
@@ -3631,7 +3690,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y343"/>
+  <dimension ref="A1:Y354"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -32202,11 +32261,11 @@
       <c r="A333" s="8">
         <v>46282</v>
       </c>
-      <c r="B333" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C333" s="26">
+      <c r="B333" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C333" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -32288,11 +32347,11 @@
       <c r="A334" s="8">
         <v>46282</v>
       </c>
-      <c r="B334" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C334" s="26">
+      <c r="B334" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C334" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -32374,11 +32433,11 @@
       <c r="A335" s="8">
         <v>46282</v>
       </c>
-      <c r="B335" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C335" s="26">
+      <c r="B335" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C335" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -32460,11 +32519,11 @@
       <c r="A336" s="8">
         <v>46282</v>
       </c>
-      <c r="B336" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C336" s="26">
+      <c r="B336" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C336" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -32546,11 +32605,11 @@
       <c r="A337" s="8">
         <v>46282</v>
       </c>
-      <c r="B337" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C337" s="26">
+      <c r="B337" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C337" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -32632,11 +32691,11 @@
       <c r="A338" s="8">
         <v>46282</v>
       </c>
-      <c r="B338" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C338" s="26">
+      <c r="B338" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C338" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -32718,11 +32777,11 @@
       <c r="A339" s="8">
         <v>46282</v>
       </c>
-      <c r="B339" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C339" s="26">
+      <c r="B339" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C339" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -32804,11 +32863,11 @@
       <c r="A340" s="8">
         <v>46282</v>
       </c>
-      <c r="B340" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C340" s="26">
+      <c r="B340" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C340" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -32890,11 +32949,11 @@
       <c r="A341" s="8">
         <v>46282</v>
       </c>
-      <c r="B341" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C341" s="26">
+      <c r="B341" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C341" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -32976,11 +33035,11 @@
       <c r="A342" s="8">
         <v>46282</v>
       </c>
-      <c r="B342" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C342" s="26">
+      <c r="B342" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C342" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -33062,11 +33121,11 @@
       <c r="A343" s="8">
         <v>46282</v>
       </c>
-      <c r="B343" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C343" s="26">
+      <c r="B343" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C343" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -33144,8 +33203,954 @@
         <v>0</v>
       </c>
     </row>
+    <row r="344" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A344" s="8">
+        <v>46283</v>
+      </c>
+      <c r="B344" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C344" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D344" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E344" s="4">
+        <v>4</v>
+      </c>
+      <c r="F344" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Manoel</v>
+      </c>
+      <c r="G344" s="10">
+        <v>127.39</v>
+      </c>
+      <c r="H344" s="10">
+        <v>3141.84</v>
+      </c>
+      <c r="I344" s="4">
+        <v>95</v>
+      </c>
+      <c r="J344" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.0546304076592057E-2</v>
+      </c>
+      <c r="K344" s="11">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="L344" s="15">
+        <v>0.75</v>
+      </c>
+      <c r="M344" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.16666666666666663</v>
+      </c>
+      <c r="N344" s="4">
+        <v>12334</v>
+      </c>
+      <c r="O344" s="4">
+        <v>12372</v>
+      </c>
+      <c r="P344" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>38</v>
+      </c>
+      <c r="Q344" s="4">
+        <v>23</v>
+      </c>
+      <c r="R344" s="4">
+        <v>1</v>
+      </c>
+      <c r="S344" s="4">
+        <v>1</v>
+      </c>
+      <c r="T344" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U344" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V344" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W344" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X344" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y344" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="345" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A345" s="8">
+        <v>46283</v>
+      </c>
+      <c r="B345" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C345" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D345" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E345" s="4">
+        <v>1</v>
+      </c>
+      <c r="F345" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G345" s="10">
+        <v>1727.4</v>
+      </c>
+      <c r="H345" s="10">
+        <v>8066.11</v>
+      </c>
+      <c r="I345" s="4">
+        <v>99</v>
+      </c>
+      <c r="J345" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.21415527435157716</v>
+      </c>
+      <c r="K345" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L345" s="15">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="M345" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.34374999999999994</v>
+      </c>
+      <c r="N345" s="4">
+        <v>155669</v>
+      </c>
+      <c r="O345" s="4">
+        <v>155756</v>
+      </c>
+      <c r="P345" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>87</v>
+      </c>
+      <c r="Q345" s="4">
+        <v>94</v>
+      </c>
+      <c r="R345" s="4">
+        <v>1</v>
+      </c>
+      <c r="S345" s="4">
+        <v>1</v>
+      </c>
+      <c r="T345" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U345" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V345" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W345" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="X345" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y345" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A346" s="8">
+        <v>46283</v>
+      </c>
+      <c r="B346" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C346" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D346" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E346" s="4">
+        <v>11</v>
+      </c>
+      <c r="F346" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G346" s="10">
+        <v>13968.57</v>
+      </c>
+      <c r="H346" s="10">
+        <v>268279.21999999997</v>
+      </c>
+      <c r="I346" s="4">
+        <v>2757</v>
+      </c>
+      <c r="J346" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.2067282736247708E-2</v>
+      </c>
+      <c r="K346" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L346" s="15">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="M346" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="N346" s="4">
+        <v>105750</v>
+      </c>
+      <c r="O346" s="4">
+        <v>105897</v>
+      </c>
+      <c r="P346" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>147</v>
+      </c>
+      <c r="Q346" s="4">
+        <v>317</v>
+      </c>
+      <c r="R346" s="4">
+        <v>32</v>
+      </c>
+      <c r="S346" s="4">
+        <v>32</v>
+      </c>
+      <c r="T346" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U346" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V346" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W346" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X346" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y346" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A347" s="8">
+        <v>46283</v>
+      </c>
+      <c r="B347" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C347" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D347" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E347" s="4">
+        <v>1</v>
+      </c>
+      <c r="F347" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G347" s="10">
+        <v>752.68</v>
+      </c>
+      <c r="H347" s="10">
+        <v>12536.17</v>
+      </c>
+      <c r="I347" s="4">
+        <v>62</v>
+      </c>
+      <c r="J347" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.0040666327913543E-2</v>
+      </c>
+      <c r="K347" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L347" s="15">
+        <v>0.49444444444444446</v>
+      </c>
+      <c r="M347" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.20277777777777778</v>
+      </c>
+      <c r="N347" s="4">
+        <v>275910</v>
+      </c>
+      <c r="O347" s="4">
+        <v>275974</v>
+      </c>
+      <c r="P347" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>64</v>
+      </c>
+      <c r="Q347" s="4">
+        <v>38</v>
+      </c>
+      <c r="R347" s="4">
+        <v>1</v>
+      </c>
+      <c r="S347" s="4">
+        <v>1</v>
+      </c>
+      <c r="T347" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U347" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V347" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W347" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X347" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y347" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A348" s="8">
+        <v>46283</v>
+      </c>
+      <c r="B348" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C348" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D348" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E348" s="4">
+        <v>5</v>
+      </c>
+      <c r="F348" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G348" s="10">
+        <v>6548.52</v>
+      </c>
+      <c r="H348" s="10">
+        <v>109020.64</v>
+      </c>
+      <c r="I348" s="4">
+        <v>1746</v>
+      </c>
+      <c r="J348" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.0066791022323852E-2</v>
+      </c>
+      <c r="K348" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L348" s="15">
+        <v>0.75694444444444442</v>
+      </c>
+      <c r="M348" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.46527777777777773</v>
+      </c>
+      <c r="N348" s="4">
+        <v>291510</v>
+      </c>
+      <c r="O348" s="4">
+        <v>291597</v>
+      </c>
+      <c r="P348" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>87</v>
+      </c>
+      <c r="Q348" s="4">
+        <v>215</v>
+      </c>
+      <c r="R348" s="4">
+        <v>18</v>
+      </c>
+      <c r="S348" s="4">
+        <v>17</v>
+      </c>
+      <c r="T348" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>1</v>
+      </c>
+      <c r="U348" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="V348" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W348" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X348" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y348" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="349" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A349" s="8">
+        <v>46283</v>
+      </c>
+      <c r="B349" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C349" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D349" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E349" s="4">
+        <v>3</v>
+      </c>
+      <c r="F349" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G349" s="10">
+        <v>10577.38</v>
+      </c>
+      <c r="H349" s="10">
+        <v>209246.11</v>
+      </c>
+      <c r="I349" s="4">
+        <v>2665</v>
+      </c>
+      <c r="J349" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.0549948097004048E-2</v>
+      </c>
+      <c r="K349" s="11">
+        <v>0.30555555555555558</v>
+      </c>
+      <c r="L349" s="15">
+        <v>0.69861111111111107</v>
+      </c>
+      <c r="M349" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.39305555555555549</v>
+      </c>
+      <c r="N349" s="4">
+        <v>143392</v>
+      </c>
+      <c r="O349" s="4">
+        <v>143445</v>
+      </c>
+      <c r="P349" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>53</v>
+      </c>
+      <c r="Q349" s="4">
+        <v>269</v>
+      </c>
+      <c r="R349" s="4">
+        <v>20</v>
+      </c>
+      <c r="S349" s="4">
+        <v>20</v>
+      </c>
+      <c r="T349" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U349" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V349" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W349" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X349" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y349" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A350" s="8">
+        <v>46283</v>
+      </c>
+      <c r="B350" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C350" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D350" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E350" s="4">
+        <v>4</v>
+      </c>
+      <c r="F350" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G350" s="10">
+        <v>8358.3700000000008</v>
+      </c>
+      <c r="H350" s="10">
+        <v>204550.14</v>
+      </c>
+      <c r="I350" s="4">
+        <v>2464</v>
+      </c>
+      <c r="J350" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.0862206205285412E-2</v>
+      </c>
+      <c r="K350" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L350" s="15">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="M350" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.49999999999999994</v>
+      </c>
+      <c r="N350" s="4">
+        <v>13855</v>
+      </c>
+      <c r="O350" s="4">
+        <v>13918</v>
+      </c>
+      <c r="P350" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>63</v>
+      </c>
+      <c r="Q350" s="4">
+        <v>535</v>
+      </c>
+      <c r="R350" s="4">
+        <v>19</v>
+      </c>
+      <c r="S350" s="4">
+        <v>19</v>
+      </c>
+      <c r="T350" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U350" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V350" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W350" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X350" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y350" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A351" s="8">
+        <v>46283</v>
+      </c>
+      <c r="B351" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C351" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D351" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E351" s="4">
+        <v>5</v>
+      </c>
+      <c r="F351" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Heremilton</v>
+      </c>
+      <c r="G351" s="10">
+        <v>53283.21</v>
+      </c>
+      <c r="H351" s="10">
+        <v>1088532.82</v>
+      </c>
+      <c r="I351" s="4">
+        <v>9913</v>
+      </c>
+      <c r="J351" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.8949566812326338E-2</v>
+      </c>
+      <c r="K351" s="11">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="L351" s="15">
+        <v>0.82361111111111107</v>
+      </c>
+      <c r="M351" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.54583333333333328</v>
+      </c>
+      <c r="N351" s="4">
+        <v>366162</v>
+      </c>
+      <c r="O351" s="4">
+        <v>366198</v>
+      </c>
+      <c r="P351" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>36</v>
+      </c>
+      <c r="Q351" s="4">
+        <v>2043</v>
+      </c>
+      <c r="R351" s="4">
+        <v>24</v>
+      </c>
+      <c r="S351" s="4">
+        <v>24</v>
+      </c>
+      <c r="T351" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U351" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V351" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W351" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X351" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y351" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A352" s="8">
+        <v>46283</v>
+      </c>
+      <c r="B352" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C352" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D352" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E352" s="4">
+        <v>1</v>
+      </c>
+      <c r="F352" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G352" s="10">
+        <v>5252.08</v>
+      </c>
+      <c r="H352" s="10">
+        <v>96048.94</v>
+      </c>
+      <c r="I352" s="4">
+        <v>1159</v>
+      </c>
+      <c r="J352" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.4681290600396004E-2</v>
+      </c>
+      <c r="K352" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L352" s="15">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M352" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.43749999999999994</v>
+      </c>
+      <c r="N352" s="4">
+        <v>125509</v>
+      </c>
+      <c r="O352" s="4">
+        <v>125582</v>
+      </c>
+      <c r="P352" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>73</v>
+      </c>
+      <c r="Q352" s="4">
+        <v>168</v>
+      </c>
+      <c r="R352" s="4">
+        <v>13</v>
+      </c>
+      <c r="S352" s="4">
+        <v>13</v>
+      </c>
+      <c r="T352" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U352" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V352" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W352" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X352" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y352" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A353" s="8">
+        <v>46283</v>
+      </c>
+      <c r="B353" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C353" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D353" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E353" s="4">
+        <v>2</v>
+      </c>
+      <c r="F353" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G353" s="10">
+        <v>11713.19</v>
+      </c>
+      <c r="H353" s="10">
+        <v>212269.7</v>
+      </c>
+      <c r="I353" s="4">
+        <v>598</v>
+      </c>
+      <c r="J353" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.5180697009511954E-2</v>
+      </c>
+      <c r="K353" s="11">
+        <v>0.27291666666666664</v>
+      </c>
+      <c r="L353" s="15">
+        <v>0.81597222222222221</v>
+      </c>
+      <c r="M353" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.54305555555555562</v>
+      </c>
+      <c r="N353" s="4">
+        <v>305081</v>
+      </c>
+      <c r="O353" s="4">
+        <v>305140</v>
+      </c>
+      <c r="P353" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>59</v>
+      </c>
+      <c r="Q353" s="4">
+        <v>317</v>
+      </c>
+      <c r="R353" s="4">
+        <v>16</v>
+      </c>
+      <c r="S353" s="4">
+        <v>16</v>
+      </c>
+      <c r="T353" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U353" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V353" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W353" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X353" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y353" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A354" s="8">
+        <v>46283</v>
+      </c>
+      <c r="B354" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C354" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D354" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E354" s="4">
+        <v>1</v>
+      </c>
+      <c r="F354" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G354" s="10">
+        <v>7384.41</v>
+      </c>
+      <c r="H354" s="10">
+        <v>185284.08</v>
+      </c>
+      <c r="I354" s="4">
+        <v>1375</v>
+      </c>
+      <c r="J354" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.9854530405418538E-2</v>
+      </c>
+      <c r="K354" s="11">
+        <v>0.2951388888888889</v>
+      </c>
+      <c r="L354" s="15">
+        <v>0.74305555555555558</v>
+      </c>
+      <c r="M354" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="N354" s="4">
+        <v>280667</v>
+      </c>
+      <c r="O354" s="4">
+        <v>280716</v>
+      </c>
+      <c r="P354" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>49</v>
+      </c>
+      <c r="Q354" s="4">
+        <v>195</v>
+      </c>
+      <c r="R354" s="4">
+        <v>30</v>
+      </c>
+      <c r="S354" s="4">
+        <v>28</v>
+      </c>
+      <c r="T354" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>2</v>
+      </c>
+      <c r="U354" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="V354" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W354" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X354" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y354" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J343">
+  <conditionalFormatting sqref="J2:J354">
     <cfRule type="cellIs" dxfId="21" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
@@ -33153,7 +34158,7 @@
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U343">
+  <conditionalFormatting sqref="U2:U354">
     <cfRule type="cellIs" dxfId="19" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
@@ -33176,7 +34181,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V343">
+  <conditionalFormatting sqref="V2:V354">
     <cfRule type="expression" dxfId="12" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
@@ -33202,7 +34207,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D343</xm:sqref>
+          <xm:sqref>D2:D354</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35E3A36-029A-4526-8687-E4811A365637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2247549D-6947-4ED8-8E71-80B19CF679E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha2" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="89">
   <si>
     <t>Data</t>
   </si>
@@ -295,6 +295,21 @@
   </si>
   <si>
     <t>42,10,13,13</t>
+  </si>
+  <si>
+    <t>42,9,9</t>
+  </si>
+  <si>
+    <t>38,38,38,9,13,13,13</t>
+  </si>
+  <si>
+    <t>10,9,42,9</t>
+  </si>
+  <si>
+    <t>13,13,13,13,9</t>
+  </si>
+  <si>
+    <t>27,27,27,27</t>
   </si>
 </sst>
 </file>
@@ -738,509 +753,6 @@
         <i val="0"/>
         <color rgb="FFFF0000"/>
       </font>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[h]:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[h]:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="25" formatCode="hh:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0070C0"/>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1867,6 +1379,509 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[h]:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[h]:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0070C0"/>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -2176,8 +2191,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V15" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
-  <autoFilter ref="A1:V15" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V19" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
+  <autoFilter ref="A1:V19" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="139"/>
     <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="138"/>
@@ -2219,51 +2234,51 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y354" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50" headerRowBorderDxfId="48" tableBorderDxfId="49" totalsRowBorderDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y402" totalsRowShown="0" headerRowDxfId="117" dataDxfId="115" headerRowBorderDxfId="116" tableBorderDxfId="114" totalsRowBorderDxfId="113">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="46"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="45">
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="112"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="111">
       <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="44">
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="110">
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="41">
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="109"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="108"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="107">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="40" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="39" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="38"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="37" dataCellStyle="Normal 2 2 2">
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="106" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="105" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="104"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="103" dataCellStyle="Normal 2 2 2">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="36"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="35"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="34">
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="102"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="101"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="100">
       <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="33"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="32"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="31">
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="99"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="98"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="97">
       <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="30"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="29"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="28"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="27">
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="96"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="95"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="94"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="93">
       <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="26" dataCellStyle="Moeda">
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="92" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="25">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="91">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="24"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="23"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="22"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="90"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="89"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="88"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2692,7 +2707,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A050DE7D-8F3F-47CF-9E37-B95AFD2ED76A}">
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="23" bestFit="1" customWidth="1"/>
@@ -3589,10 +3604,10 @@
       <c r="D15" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="10">
         <v>6994.8</v>
       </c>
-      <c r="F15" s="27">
+      <c r="F15" s="10">
         <v>202752.86</v>
       </c>
       <c r="G15" s="4">
@@ -3634,40 +3649,284 @@
       <c r="U15" s="4"/>
       <c r="V15" s="5"/>
     </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="8">
+        <v>46287</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="27">
+        <v>6537.08</v>
+      </c>
+      <c r="F16" s="27">
+        <v>70656.17</v>
+      </c>
+      <c r="G16" s="4">
+        <v>2255</v>
+      </c>
+      <c r="H16" s="9">
+        <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
+        <v>9.2519591707277651E-2</v>
+      </c>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4">
+        <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="10">
+        <v>500</v>
+      </c>
+      <c r="M16" s="9">
+        <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
+        <v>7.6486749435527787E-2</v>
+      </c>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4">
+        <v>11</v>
+      </c>
+      <c r="P16" s="4">
+        <v>11</v>
+      </c>
+      <c r="Q16" s="12">
+        <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="R16" s="13">
+        <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="S16" s="14" t="str">
+        <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4"/>
+      <c r="V16" s="5"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" s="8">
+        <v>46287</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" s="27">
+        <v>4118.54</v>
+      </c>
+      <c r="F17" s="27">
+        <v>62885.27</v>
+      </c>
+      <c r="G17" s="4">
+        <v>632</v>
+      </c>
+      <c r="H17" s="9">
+        <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
+        <v>6.5492920679198804E-2</v>
+      </c>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4">
+        <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="10">
+        <v>500</v>
+      </c>
+      <c r="M17" s="9">
+        <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
+        <v>0.12140224448469604</v>
+      </c>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4">
+        <v>5</v>
+      </c>
+      <c r="P17" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="12">
+        <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="R17" s="13">
+        <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="S17" s="14" t="str">
+        <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="5"/>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" s="8">
+        <v>46288</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="27">
+        <v>4151.1400000000003</v>
+      </c>
+      <c r="F18" s="27">
+        <v>51812.79</v>
+      </c>
+      <c r="G18" s="4">
+        <v>631</v>
+      </c>
+      <c r="H18" s="9">
+        <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
+        <v>8.0118055792787843E-2</v>
+      </c>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4">
+        <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="10">
+        <v>500</v>
+      </c>
+      <c r="M18" s="9">
+        <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
+        <v>0.12044884055946077</v>
+      </c>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4">
+        <v>11</v>
+      </c>
+      <c r="P18" s="4">
+        <v>11</v>
+      </c>
+      <c r="Q18" s="12">
+        <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="R18" s="13">
+        <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="S18" s="14" t="str">
+        <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="T18" s="4"/>
+      <c r="U18" s="4"/>
+      <c r="V18" s="5"/>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" s="8">
+        <v>46289</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="27">
+        <v>3779.58</v>
+      </c>
+      <c r="F19" s="27">
+        <v>77696.94</v>
+      </c>
+      <c r="G19" s="4">
+        <v>718</v>
+      </c>
+      <c r="H19" s="9">
+        <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
+        <v>4.864515899853971E-2</v>
+      </c>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4">
+        <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="10">
+        <v>500</v>
+      </c>
+      <c r="M19" s="9">
+        <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
+        <v>0.13228983114525952</v>
+      </c>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4">
+        <v>14</v>
+      </c>
+      <c r="P19" s="4">
+        <v>14</v>
+      </c>
+      <c r="Q19" s="12">
+        <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="R19" s="13">
+        <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="S19" s="14" t="str">
+        <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="T19" s="4">
+        <v>0</v>
+      </c>
+      <c r="U19" s="4">
+        <v>38</v>
+      </c>
+      <c r="V19" s="5"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H15">
-    <cfRule type="cellIs" dxfId="117" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="H2:H19">
+    <cfRule type="cellIs" dxfId="87" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="116" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="86" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R15">
-    <cfRule type="cellIs" dxfId="115" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="R2:R19">
+    <cfRule type="cellIs" dxfId="85" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="84" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="83" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="82" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="81" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="80" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="79" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S15">
-    <cfRule type="expression" dxfId="108" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="S2:S19">
+    <cfRule type="expression" dxfId="78" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -3676,7 +3935,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="107" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3690,7 +3949,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y354"/>
+  <dimension ref="A1:Y402"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -33207,11 +33466,11 @@
       <c r="A344" s="8">
         <v>46283</v>
       </c>
-      <c r="B344" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C344" s="26">
+      <c r="B344" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C344" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -33293,11 +33552,11 @@
       <c r="A345" s="8">
         <v>46283</v>
       </c>
-      <c r="B345" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C345" s="26">
+      <c r="B345" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C345" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -33379,11 +33638,11 @@
       <c r="A346" s="8">
         <v>46283</v>
       </c>
-      <c r="B346" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C346" s="26">
+      <c r="B346" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C346" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -33465,11 +33724,11 @@
       <c r="A347" s="8">
         <v>46283</v>
       </c>
-      <c r="B347" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C347" s="26">
+      <c r="B347" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C347" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -33551,11 +33810,11 @@
       <c r="A348" s="8">
         <v>46283</v>
       </c>
-      <c r="B348" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C348" s="26">
+      <c r="B348" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C348" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -33637,11 +33896,11 @@
       <c r="A349" s="8">
         <v>46283</v>
       </c>
-      <c r="B349" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C349" s="26">
+      <c r="B349" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C349" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -33723,11 +33982,11 @@
       <c r="A350" s="8">
         <v>46283</v>
       </c>
-      <c r="B350" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C350" s="26">
+      <c r="B350" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C350" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -33809,11 +34068,11 @@
       <c r="A351" s="8">
         <v>46283</v>
       </c>
-      <c r="B351" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C351" s="26">
+      <c r="B351" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C351" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -33895,11 +34154,11 @@
       <c r="A352" s="8">
         <v>46283</v>
       </c>
-      <c r="B352" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C352" s="26">
+      <c r="B352" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C352" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -33981,11 +34240,11 @@
       <c r="A353" s="8">
         <v>46283</v>
       </c>
-      <c r="B353" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C353" s="26">
+      <c r="B353" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C353" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -34067,11 +34326,11 @@
       <c r="A354" s="8">
         <v>46283</v>
       </c>
-      <c r="B354" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C354" s="26">
+      <c r="B354" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C354" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -34149,40 +34408,4168 @@
         <v>83</v>
       </c>
     </row>
+    <row r="355" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A355" s="8">
+        <v>46286</v>
+      </c>
+      <c r="B355" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C355" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D355" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E355" s="4">
+        <v>3</v>
+      </c>
+      <c r="F355" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G355" s="10">
+        <v>7669.01</v>
+      </c>
+      <c r="H355" s="10">
+        <v>109425.94</v>
+      </c>
+      <c r="I355" s="4">
+        <v>2407</v>
+      </c>
+      <c r="J355" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.008402212491846E-2</v>
+      </c>
+      <c r="K355" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L355" s="15">
+        <v>0.75694444444444442</v>
+      </c>
+      <c r="M355" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.46527777777777773</v>
+      </c>
+      <c r="N355" s="4">
+        <v>13919</v>
+      </c>
+      <c r="O355" s="4">
+        <v>13972</v>
+      </c>
+      <c r="P355" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>53</v>
+      </c>
+      <c r="Q355" s="4">
+        <v>240</v>
+      </c>
+      <c r="R355" s="4">
+        <v>13</v>
+      </c>
+      <c r="S355" s="4">
+        <v>13</v>
+      </c>
+      <c r="T355" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U355" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V355" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W355" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X355" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y355" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="356" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A356" s="8">
+        <v>46286</v>
+      </c>
+      <c r="B356" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C356" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D356" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E356" s="4">
+        <v>5</v>
+      </c>
+      <c r="F356" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G356" s="10">
+        <v>5167.83</v>
+      </c>
+      <c r="H356" s="10">
+        <v>46740.68</v>
+      </c>
+      <c r="I356" s="4">
+        <v>567</v>
+      </c>
+      <c r="J356" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.11056386000374833</v>
+      </c>
+      <c r="K356" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L356" s="15">
+        <v>0.67152777777777772</v>
+      </c>
+      <c r="M356" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.35902777777777772</v>
+      </c>
+      <c r="N356" s="4">
+        <v>143494</v>
+      </c>
+      <c r="O356" s="4">
+        <v>143560</v>
+      </c>
+      <c r="P356" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>66</v>
+      </c>
+      <c r="Q356" s="4">
+        <v>73</v>
+      </c>
+      <c r="R356" s="4">
+        <v>7</v>
+      </c>
+      <c r="S356" s="4">
+        <v>7</v>
+      </c>
+      <c r="T356" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U356" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V356" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W356" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X356" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y356" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A357" s="8">
+        <v>46286</v>
+      </c>
+      <c r="B357" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C357" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D357" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E357" s="4">
+        <v>11</v>
+      </c>
+      <c r="F357" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G357" s="10">
+        <v>11465.64</v>
+      </c>
+      <c r="H357" s="10">
+        <v>273006.78999999998</v>
+      </c>
+      <c r="I357" s="4">
+        <v>1599</v>
+      </c>
+      <c r="J357" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.1997636762074672E-2</v>
+      </c>
+      <c r="K357" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L357" s="15">
+        <v>0.8125</v>
+      </c>
+      <c r="M357" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.54166666666666674</v>
+      </c>
+      <c r="N357" s="4">
+        <v>125582</v>
+      </c>
+      <c r="O357" s="4">
+        <v>125748</v>
+      </c>
+      <c r="P357" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>166</v>
+      </c>
+      <c r="Q357" s="4">
+        <v>313</v>
+      </c>
+      <c r="R357" s="4">
+        <v>28</v>
+      </c>
+      <c r="S357" s="4">
+        <v>28</v>
+      </c>
+      <c r="T357" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U357" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V357" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W357" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X357" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y357" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="358" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A358" s="8">
+        <v>46286</v>
+      </c>
+      <c r="B358" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C358" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D358" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E358" s="4">
+        <v>2</v>
+      </c>
+      <c r="F358" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G358" s="10">
+        <v>7236.81</v>
+      </c>
+      <c r="H358" s="10">
+        <v>173289.63</v>
+      </c>
+      <c r="I358" s="4">
+        <v>1096</v>
+      </c>
+      <c r="J358" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.1761356406612445E-2</v>
+      </c>
+      <c r="K358" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L358" s="15">
+        <v>0.66319444444444442</v>
+      </c>
+      <c r="M358" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="N358" s="4">
+        <v>305258</v>
+      </c>
+      <c r="O358" s="4">
+        <v>305309</v>
+      </c>
+      <c r="P358" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>51</v>
+      </c>
+      <c r="Q358" s="4">
+        <v>183</v>
+      </c>
+      <c r="R358" s="4">
+        <v>26</v>
+      </c>
+      <c r="S358" s="4">
+        <v>26</v>
+      </c>
+      <c r="T358" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U358" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V358" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W358" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X358" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y358" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A359" s="8">
+        <v>46286</v>
+      </c>
+      <c r="B359" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C359" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D359" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E359" s="4">
+        <v>1</v>
+      </c>
+      <c r="F359" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G359" s="10">
+        <v>2929.13</v>
+      </c>
+      <c r="H359" s="10">
+        <v>35646.160000000003</v>
+      </c>
+      <c r="I359" s="4">
+        <v>226</v>
+      </c>
+      <c r="J359" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.2172385468729306E-2</v>
+      </c>
+      <c r="K359" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L359" s="15">
+        <v>0.70416666666666672</v>
+      </c>
+      <c r="M359" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.41250000000000003</v>
+      </c>
+      <c r="N359" s="4">
+        <v>155786</v>
+      </c>
+      <c r="O359" s="4">
+        <v>155935</v>
+      </c>
+      <c r="P359" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>149</v>
+      </c>
+      <c r="Q359" s="4">
+        <v>42</v>
+      </c>
+      <c r="R359" s="4">
+        <v>14</v>
+      </c>
+      <c r="S359" s="4">
+        <v>14</v>
+      </c>
+      <c r="T359" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U359" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V359" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W359" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X359" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y359" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A360" s="8">
+        <v>46286</v>
+      </c>
+      <c r="B360" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C360" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D360" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E360" s="4">
+        <v>3</v>
+      </c>
+      <c r="F360" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Manoel</v>
+      </c>
+      <c r="G360" s="10">
+        <v>795.97</v>
+      </c>
+      <c r="H360" s="10">
+        <v>15740.97</v>
+      </c>
+      <c r="I360" s="4">
+        <v>13</v>
+      </c>
+      <c r="J360" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.056676939222933E-2</v>
+      </c>
+      <c r="K360" s="11">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="L360" s="15">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="M360" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.125</v>
+      </c>
+      <c r="N360" s="4">
+        <v>12395</v>
+      </c>
+      <c r="O360" s="4">
+        <v>12437</v>
+      </c>
+      <c r="P360" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>42</v>
+      </c>
+      <c r="Q360" s="4">
+        <v>13</v>
+      </c>
+      <c r="R360" s="4">
+        <v>2</v>
+      </c>
+      <c r="S360" s="4">
+        <v>2</v>
+      </c>
+      <c r="T360" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U360" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V360" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W360" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X360" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y360" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A361" s="8">
+        <v>46286</v>
+      </c>
+      <c r="B361" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C361" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D361" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E361" s="4">
+        <v>1</v>
+      </c>
+      <c r="F361" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G361" s="10">
+        <v>7949.91</v>
+      </c>
+      <c r="H361" s="10">
+        <v>124108.67</v>
+      </c>
+      <c r="I361" s="4">
+        <v>1127</v>
+      </c>
+      <c r="J361" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.405604056509509E-2</v>
+      </c>
+      <c r="K361" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L361" s="15">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="M361" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.39583333333333337</v>
+      </c>
+      <c r="N361" s="4">
+        <v>120142</v>
+      </c>
+      <c r="O361" s="4">
+        <v>120182</v>
+      </c>
+      <c r="P361" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>40</v>
+      </c>
+      <c r="Q361" s="4">
+        <v>155</v>
+      </c>
+      <c r="R361" s="4">
+        <v>26</v>
+      </c>
+      <c r="S361" s="4">
+        <v>23</v>
+      </c>
+      <c r="T361" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>3</v>
+      </c>
+      <c r="U361" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.88461538461538458</v>
+      </c>
+      <c r="V361" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W361" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X361" s="4">
+        <v>4</v>
+      </c>
+      <c r="Y361" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="362" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A362" s="8">
+        <v>46286</v>
+      </c>
+      <c r="B362" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C362" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D362" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E362" s="4">
+        <v>5</v>
+      </c>
+      <c r="F362" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G362" s="10">
+        <v>5549.43</v>
+      </c>
+      <c r="H362" s="10">
+        <v>94435.31</v>
+      </c>
+      <c r="I362" s="4">
+        <v>541</v>
+      </c>
+      <c r="J362" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.8764354138298489E-2</v>
+      </c>
+      <c r="K362" s="11">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L362" s="15">
+        <v>0.71666666666666667</v>
+      </c>
+      <c r="M362" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.38333333333333336</v>
+      </c>
+      <c r="N362" s="4">
+        <v>280717</v>
+      </c>
+      <c r="O362" s="4">
+        <v>280801</v>
+      </c>
+      <c r="P362" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>84</v>
+      </c>
+      <c r="Q362" s="4">
+        <v>108</v>
+      </c>
+      <c r="R362" s="4">
+        <v>31</v>
+      </c>
+      <c r="S362" s="4">
+        <v>31</v>
+      </c>
+      <c r="T362" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U362" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V362" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W362" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X362" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y362" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="363" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A363" s="8">
+        <v>46286</v>
+      </c>
+      <c r="B363" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C363" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D363" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E363" s="4">
+        <v>1</v>
+      </c>
+      <c r="F363" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G363" s="10">
+        <v>29994.17</v>
+      </c>
+      <c r="H363" s="10">
+        <v>232856.46</v>
+      </c>
+      <c r="I363" s="4">
+        <v>3895</v>
+      </c>
+      <c r="J363" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.12880969675481624</v>
+      </c>
+      <c r="K363" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L363" s="15">
+        <v>0.75</v>
+      </c>
+      <c r="M363" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="N363" s="4">
+        <v>105897</v>
+      </c>
+      <c r="O363" s="4">
+        <v>105931</v>
+      </c>
+      <c r="P363" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>34</v>
+      </c>
+      <c r="Q363" s="4">
+        <v>1187</v>
+      </c>
+      <c r="R363" s="4">
+        <v>1</v>
+      </c>
+      <c r="S363" s="4">
+        <v>1</v>
+      </c>
+      <c r="T363" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U363" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V363" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W363" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X363" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y363" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A364" s="8">
+        <v>46286</v>
+      </c>
+      <c r="B364" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C364" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D364" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E364" s="4">
+        <v>4</v>
+      </c>
+      <c r="F364" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G364" s="10">
+        <v>8805.2099999999991</v>
+      </c>
+      <c r="H364" s="10">
+        <v>200874.32</v>
+      </c>
+      <c r="I364" s="4">
+        <v>1306</v>
+      </c>
+      <c r="J364" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.3834423434513672E-2</v>
+      </c>
+      <c r="K364" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L364" s="15">
+        <v>0.75208333333333333</v>
+      </c>
+      <c r="M364" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.46041666666666664</v>
+      </c>
+      <c r="N364" s="4">
+        <v>291597</v>
+      </c>
+      <c r="O364" s="4">
+        <v>291668</v>
+      </c>
+      <c r="P364" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>71</v>
+      </c>
+      <c r="Q364" s="4">
+        <v>185</v>
+      </c>
+      <c r="R364" s="4">
+        <v>30</v>
+      </c>
+      <c r="S364" s="4">
+        <v>30</v>
+      </c>
+      <c r="T364" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U364" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V364" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W364" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X364" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y364" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A365" s="8">
+        <v>46286</v>
+      </c>
+      <c r="B365" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C365" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D365" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E365" s="4">
+        <v>1</v>
+      </c>
+      <c r="F365" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G365" s="10">
+        <v>3409.79</v>
+      </c>
+      <c r="H365" s="10">
+        <v>67607.839999999997</v>
+      </c>
+      <c r="I365" s="4">
+        <v>478</v>
+      </c>
+      <c r="J365" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.0434831226674304E-2</v>
+      </c>
+      <c r="K365" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L365" s="15">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="M365" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.46874999999999994</v>
+      </c>
+      <c r="N365" s="4">
+        <v>275923</v>
+      </c>
+      <c r="O365" s="4">
+        <v>276025</v>
+      </c>
+      <c r="P365" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>102</v>
+      </c>
+      <c r="Q365" s="4">
+        <v>103</v>
+      </c>
+      <c r="R365" s="4">
+        <v>10</v>
+      </c>
+      <c r="S365" s="4">
+        <v>10</v>
+      </c>
+      <c r="T365" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U365" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V365" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W365" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X365" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y365" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A366" s="8">
+        <v>46284</v>
+      </c>
+      <c r="B366" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C366" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D366" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E366" s="4">
+        <v>11</v>
+      </c>
+      <c r="F366" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G366" s="10">
+        <v>9000.1200000000008</v>
+      </c>
+      <c r="H366" s="10">
+        <v>133683.42000000001</v>
+      </c>
+      <c r="I366" s="4">
+        <v>1122</v>
+      </c>
+      <c r="J366" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.7324130397023049E-2</v>
+      </c>
+      <c r="K366" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L366" s="15">
+        <v>0.48333333333333334</v>
+      </c>
+      <c r="M366" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.21250000000000002</v>
+      </c>
+      <c r="N366" s="4">
+        <v>305140</v>
+      </c>
+      <c r="O366" s="4">
+        <v>305258</v>
+      </c>
+      <c r="P366" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>118</v>
+      </c>
+      <c r="Q366" s="4">
+        <v>164</v>
+      </c>
+      <c r="R366" s="4">
+        <v>37</v>
+      </c>
+      <c r="S366" s="4">
+        <v>37</v>
+      </c>
+      <c r="T366" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U366" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V366" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W366" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X366" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y366" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A367" s="8">
+        <v>46284</v>
+      </c>
+      <c r="B367" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C367" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D367" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E367" s="4">
+        <v>3</v>
+      </c>
+      <c r="F367" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G367" s="10">
+        <v>4098.82</v>
+      </c>
+      <c r="H367" s="10">
+        <v>104510.87</v>
+      </c>
+      <c r="I367" s="4">
+        <v>726</v>
+      </c>
+      <c r="J367" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.9219078359983034E-2</v>
+      </c>
+      <c r="K367" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L367" s="15">
+        <v>0.50416666666666665</v>
+      </c>
+      <c r="M367" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.19166666666666665</v>
+      </c>
+      <c r="N367" s="4">
+        <v>143445</v>
+      </c>
+      <c r="O367" s="4">
+        <v>143494</v>
+      </c>
+      <c r="P367" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>49</v>
+      </c>
+      <c r="Q367" s="4">
+        <v>137</v>
+      </c>
+      <c r="R367" s="4">
+        <v>7</v>
+      </c>
+      <c r="S367" s="4">
+        <v>7</v>
+      </c>
+      <c r="T367" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U367" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V367" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W367" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X367" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y367" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A368" s="8">
+        <v>46284</v>
+      </c>
+      <c r="B368" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C368" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D368" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E368" s="4">
+        <v>1</v>
+      </c>
+      <c r="F368" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G368" s="10">
+        <v>512.66999999999996</v>
+      </c>
+      <c r="H368" s="10">
+        <v>31213</v>
+      </c>
+      <c r="I368" s="4">
+        <v>62</v>
+      </c>
+      <c r="J368" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>1.6424887066286482E-2</v>
+      </c>
+      <c r="K368" s="11">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L368" s="15">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="M368" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.125</v>
+      </c>
+      <c r="N368" s="4">
+        <v>155756</v>
+      </c>
+      <c r="O368" s="4">
+        <v>155786</v>
+      </c>
+      <c r="P368" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>30</v>
+      </c>
+      <c r="Q368" s="4">
+        <v>20</v>
+      </c>
+      <c r="R368" s="4">
+        <v>1</v>
+      </c>
+      <c r="S368" s="4">
+        <v>1</v>
+      </c>
+      <c r="T368" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U368" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V368" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W368" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X368" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y368" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A369" s="8">
+        <v>46287</v>
+      </c>
+      <c r="B369" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C369" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D369" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E369" s="4">
+        <v>5</v>
+      </c>
+      <c r="F369" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G369" s="10">
+        <v>4644.68</v>
+      </c>
+      <c r="H369" s="10">
+        <v>94224.9</v>
+      </c>
+      <c r="I369" s="4">
+        <v>913</v>
+      </c>
+      <c r="J369" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.929355191674388E-2</v>
+      </c>
+      <c r="K369" s="11">
+        <v>0.30208333333333331</v>
+      </c>
+      <c r="L369" s="15">
+        <v>0.75</v>
+      </c>
+      <c r="M369" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="N369" s="4">
+        <v>280801</v>
+      </c>
+      <c r="O369" s="4">
+        <v>280890</v>
+      </c>
+      <c r="P369" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>89</v>
+      </c>
+      <c r="Q369" s="4">
+        <v>201</v>
+      </c>
+      <c r="R369" s="4">
+        <v>13</v>
+      </c>
+      <c r="S369" s="4">
+        <v>13</v>
+      </c>
+      <c r="T369" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U369" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V369" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W369" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X369" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y369" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A370" s="8">
+        <v>46287</v>
+      </c>
+      <c r="B370" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C370" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D370" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E370" s="4">
+        <v>3</v>
+      </c>
+      <c r="F370" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G370" s="10">
+        <v>7506.49</v>
+      </c>
+      <c r="H370" s="10">
+        <v>202005.7</v>
+      </c>
+      <c r="I370" s="4">
+        <v>1611</v>
+      </c>
+      <c r="J370" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.7159793015741634E-2</v>
+      </c>
+      <c r="K370" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L370" s="15">
+        <v>0.80902777777777779</v>
+      </c>
+      <c r="M370" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.51736111111111116</v>
+      </c>
+      <c r="N370" s="4">
+        <v>276025</v>
+      </c>
+      <c r="O370" s="4">
+        <v>276067</v>
+      </c>
+      <c r="P370" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>42</v>
+      </c>
+      <c r="Q370" s="4">
+        <v>3</v>
+      </c>
+      <c r="R370" s="4">
+        <v>1</v>
+      </c>
+      <c r="S370" s="4">
+        <v>1</v>
+      </c>
+      <c r="T370" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U370" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V370" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W370" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X370" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y370" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A371" s="8">
+        <v>46287</v>
+      </c>
+      <c r="B371" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C371" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D371" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E371" s="4">
+        <v>1</v>
+      </c>
+      <c r="F371" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G371" s="10">
+        <v>4164.1000000000004</v>
+      </c>
+      <c r="H371" s="10">
+        <v>43167.4</v>
+      </c>
+      <c r="I371" s="4">
+        <v>778</v>
+      </c>
+      <c r="J371" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>9.6463998295009665E-2</v>
+      </c>
+      <c r="K371" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L371" s="15">
+        <v>0.66388888888888886</v>
+      </c>
+      <c r="M371" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.37222222222222218</v>
+      </c>
+      <c r="N371" s="4">
+        <v>291668</v>
+      </c>
+      <c r="O371" s="4">
+        <v>291707</v>
+      </c>
+      <c r="P371" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>39</v>
+      </c>
+      <c r="Q371" s="4">
+        <v>155</v>
+      </c>
+      <c r="R371" s="4">
+        <v>6</v>
+      </c>
+      <c r="S371" s="4">
+        <v>6</v>
+      </c>
+      <c r="T371" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U371" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V371" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W371" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X371" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y371" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A372" s="8">
+        <v>46287</v>
+      </c>
+      <c r="B372" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C372" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D372" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E372" s="4">
+        <v>1</v>
+      </c>
+      <c r="F372" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G372" s="10">
+        <v>6513.12</v>
+      </c>
+      <c r="H372" s="10">
+        <v>54219.19</v>
+      </c>
+      <c r="I372" s="4">
+        <v>229</v>
+      </c>
+      <c r="J372" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.12012573408049806</v>
+      </c>
+      <c r="K372" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L372" s="15">
+        <v>0.71666666666666667</v>
+      </c>
+      <c r="M372" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="N372" s="4">
+        <v>143560</v>
+      </c>
+      <c r="O372" s="4">
+        <v>143701</v>
+      </c>
+      <c r="P372" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>141</v>
+      </c>
+      <c r="Q372" s="4">
+        <v>229</v>
+      </c>
+      <c r="R372" s="4">
+        <v>10</v>
+      </c>
+      <c r="S372" s="4">
+        <v>10</v>
+      </c>
+      <c r="T372" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U372" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V372" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W372" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X372" s="4">
+        <v>4</v>
+      </c>
+      <c r="Y372" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="373" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A373" s="8">
+        <v>46287</v>
+      </c>
+      <c r="B373" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C373" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D373" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E373" s="4">
+        <v>3</v>
+      </c>
+      <c r="F373" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G373" s="10">
+        <v>503.65</v>
+      </c>
+      <c r="H373" s="10">
+        <v>7881.12</v>
+      </c>
+      <c r="I373" s="4">
+        <v>28</v>
+      </c>
+      <c r="J373" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.3905891548409366E-2</v>
+      </c>
+      <c r="K373" s="11">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="L373" s="15">
+        <v>0.53125</v>
+      </c>
+      <c r="M373" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.11458333333333331</v>
+      </c>
+      <c r="N373" s="4">
+        <v>120182</v>
+      </c>
+      <c r="O373" s="4">
+        <v>120198</v>
+      </c>
+      <c r="P373" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>16</v>
+      </c>
+      <c r="Q373" s="4">
+        <v>4</v>
+      </c>
+      <c r="R373" s="4">
+        <v>2</v>
+      </c>
+      <c r="S373" s="4">
+        <v>2</v>
+      </c>
+      <c r="T373" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U373" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V373" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W373" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X373" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y373" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A374" s="8">
+        <v>46287</v>
+      </c>
+      <c r="B374" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C374" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D374" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E374" s="4">
+        <v>5</v>
+      </c>
+      <c r="F374" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Heremilton</v>
+      </c>
+      <c r="G374" s="10">
+        <v>34255.589999999997</v>
+      </c>
+      <c r="H374" s="10">
+        <v>676663.59</v>
+      </c>
+      <c r="I374" s="4">
+        <v>8307</v>
+      </c>
+      <c r="J374" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.0624254808803879E-2</v>
+      </c>
+      <c r="K374" s="11">
+        <v>0.27569444444444446</v>
+      </c>
+      <c r="L374" s="15">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="M374" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.37013888888888891</v>
+      </c>
+      <c r="N374" s="4">
+        <v>366295</v>
+      </c>
+      <c r="O374" s="4">
+        <v>366330</v>
+      </c>
+      <c r="P374" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>35</v>
+      </c>
+      <c r="Q374" s="4">
+        <v>1640</v>
+      </c>
+      <c r="R374" s="4">
+        <v>10</v>
+      </c>
+      <c r="S374" s="4">
+        <v>10</v>
+      </c>
+      <c r="T374" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U374" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V374" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W374" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X374" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y374" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A375" s="8">
+        <v>46287</v>
+      </c>
+      <c r="B375" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C375" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D375" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E375" s="4">
+        <v>1</v>
+      </c>
+      <c r="F375" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G375" s="10">
+        <v>6596.24</v>
+      </c>
+      <c r="H375" s="10">
+        <v>24651.56</v>
+      </c>
+      <c r="I375" s="4">
+        <v>743</v>
+      </c>
+      <c r="J375" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.2675790091986065</v>
+      </c>
+      <c r="K375" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L375" s="15">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M375" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.41666666666666663</v>
+      </c>
+      <c r="N375" s="4">
+        <v>125748</v>
+      </c>
+      <c r="O375" s="4">
+        <v>125778</v>
+      </c>
+      <c r="P375" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>30</v>
+      </c>
+      <c r="Q375" s="4">
+        <v>366</v>
+      </c>
+      <c r="R375" s="4">
+        <v>1</v>
+      </c>
+      <c r="S375" s="4">
+        <v>1</v>
+      </c>
+      <c r="T375" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U375" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V375" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W375" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X375" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y375" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A376" s="8">
+        <v>46287</v>
+      </c>
+      <c r="B376" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C376" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D376" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E376" s="4">
+        <v>1</v>
+      </c>
+      <c r="F376" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G376" s="10">
+        <v>1974.29</v>
+      </c>
+      <c r="H376" s="10">
+        <v>76472.990000000005</v>
+      </c>
+      <c r="I376" s="4">
+        <v>195</v>
+      </c>
+      <c r="J376" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.5816827614560379E-2</v>
+      </c>
+      <c r="K376" s="11">
+        <v>0.29583333333333334</v>
+      </c>
+      <c r="L376" s="15">
+        <v>0.5625</v>
+      </c>
+      <c r="M376" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.26666666666666666</v>
+      </c>
+      <c r="N376" s="4">
+        <v>155978</v>
+      </c>
+      <c r="O376" s="4">
+        <v>156013</v>
+      </c>
+      <c r="P376" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>35</v>
+      </c>
+      <c r="Q376" s="4">
+        <v>63</v>
+      </c>
+      <c r="R376" s="4">
+        <v>3</v>
+      </c>
+      <c r="S376" s="4">
+        <v>3</v>
+      </c>
+      <c r="T376" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U376" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V376" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W376" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X376" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y376" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A377" s="8">
+        <v>46287</v>
+      </c>
+      <c r="B377" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C377" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D377" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E377" s="4">
+        <v>3</v>
+      </c>
+      <c r="F377" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G377" s="10">
+        <v>7055.93</v>
+      </c>
+      <c r="H377" s="10">
+        <v>114579.97</v>
+      </c>
+      <c r="I377" s="4">
+        <v>1549</v>
+      </c>
+      <c r="J377" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.158083301994232E-2</v>
+      </c>
+      <c r="K377" s="11">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="L377" s="15">
+        <v>0.81805555555555554</v>
+      </c>
+      <c r="M377" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.51944444444444438</v>
+      </c>
+      <c r="N377" s="4">
+        <v>13972</v>
+      </c>
+      <c r="O377" s="4">
+        <v>14008</v>
+      </c>
+      <c r="P377" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>36</v>
+      </c>
+      <c r="Q377" s="4">
+        <v>301</v>
+      </c>
+      <c r="R377" s="4">
+        <v>22</v>
+      </c>
+      <c r="S377" s="4">
+        <v>18</v>
+      </c>
+      <c r="T377" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>4</v>
+      </c>
+      <c r="U377" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="V377" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W377" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X377" s="4">
+        <v>5</v>
+      </c>
+      <c r="Y377" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="378" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A378" s="8">
+        <v>46287</v>
+      </c>
+      <c r="B378" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C378" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D378" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E378" s="4">
+        <v>11</v>
+      </c>
+      <c r="F378" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G378" s="10">
+        <v>30371.46</v>
+      </c>
+      <c r="H378" s="10">
+        <v>407002.73</v>
+      </c>
+      <c r="I378" s="4">
+        <v>6712</v>
+      </c>
+      <c r="J378" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.4622251305292223E-2</v>
+      </c>
+      <c r="K378" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L378" s="15">
+        <v>0.82430555555555551</v>
+      </c>
+      <c r="M378" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.55347222222222214</v>
+      </c>
+      <c r="N378" s="4">
+        <v>105897</v>
+      </c>
+      <c r="O378" s="4">
+        <v>106073</v>
+      </c>
+      <c r="P378" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>176</v>
+      </c>
+      <c r="Q378" s="4">
+        <v>951</v>
+      </c>
+      <c r="R378" s="4">
+        <v>23</v>
+      </c>
+      <c r="S378" s="4">
+        <v>23</v>
+      </c>
+      <c r="T378" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U378" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V378" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W378" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X378" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y378" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A379" s="8">
+        <v>46287</v>
+      </c>
+      <c r="B379" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C379" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D379" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E379" s="4">
+        <v>1</v>
+      </c>
+      <c r="F379" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G379" s="10">
+        <v>1536.76</v>
+      </c>
+      <c r="H379" s="10">
+        <v>27858.75</v>
+      </c>
+      <c r="I379" s="4">
+        <v>286</v>
+      </c>
+      <c r="J379" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.5162561134293533E-2</v>
+      </c>
+      <c r="K379" s="11">
+        <v>0.59375</v>
+      </c>
+      <c r="L379" s="15">
+        <v>0.72569444444444442</v>
+      </c>
+      <c r="M379" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.13194444444444442</v>
+      </c>
+      <c r="N379" s="4">
+        <v>156013</v>
+      </c>
+      <c r="O379" s="4">
+        <v>156044</v>
+      </c>
+      <c r="P379" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>31</v>
+      </c>
+      <c r="Q379" s="4">
+        <v>32</v>
+      </c>
+      <c r="R379" s="4">
+        <v>6</v>
+      </c>
+      <c r="S379" s="4">
+        <v>6</v>
+      </c>
+      <c r="T379" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U379" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V379" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W379" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X379" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y379" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A380" s="8">
+        <v>46287</v>
+      </c>
+      <c r="B380" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C380" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D380" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E380" s="4">
+        <v>2</v>
+      </c>
+      <c r="F380" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G380" s="10">
+        <v>8171.1</v>
+      </c>
+      <c r="H380" s="10">
+        <v>181524.78</v>
+      </c>
+      <c r="I380" s="4">
+        <v>1715</v>
+      </c>
+      <c r="J380" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.5013689040140969E-2</v>
+      </c>
+      <c r="K380" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L380" s="15">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="M380" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.43750000000000006</v>
+      </c>
+      <c r="N380" s="4">
+        <v>305309</v>
+      </c>
+      <c r="O380" s="4">
+        <v>305368</v>
+      </c>
+      <c r="P380" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>59</v>
+      </c>
+      <c r="Q380" s="4">
+        <v>299</v>
+      </c>
+      <c r="R380" s="4">
+        <v>27</v>
+      </c>
+      <c r="S380" s="4">
+        <v>27</v>
+      </c>
+      <c r="T380" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U380" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V380" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W380" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X380" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y380" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A381" s="8">
+        <v>46288</v>
+      </c>
+      <c r="B381" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C381" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D381" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E381" s="4">
+        <v>1</v>
+      </c>
+      <c r="F381" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G381" s="10">
+        <v>11813.92</v>
+      </c>
+      <c r="H381" s="10">
+        <v>564102.5</v>
+      </c>
+      <c r="I381" s="4">
+        <v>1127</v>
+      </c>
+      <c r="J381" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.09428605616887E-2</v>
+      </c>
+      <c r="K381" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L381" s="15">
+        <v>0.73611111111111116</v>
+      </c>
+      <c r="M381" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44444444444444448</v>
+      </c>
+      <c r="N381" s="4">
+        <v>291707</v>
+      </c>
+      <c r="O381" s="4">
+        <v>291751</v>
+      </c>
+      <c r="P381" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>44</v>
+      </c>
+      <c r="Q381" s="4">
+        <v>5</v>
+      </c>
+      <c r="R381" s="4">
+        <v>1</v>
+      </c>
+      <c r="S381" s="4">
+        <v>1</v>
+      </c>
+      <c r="T381" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U381" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V381" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W381" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X381" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y381" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A382" s="8">
+        <v>46288</v>
+      </c>
+      <c r="B382" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C382" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D382" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E382" s="4">
+        <v>1</v>
+      </c>
+      <c r="F382" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G382" s="10">
+        <v>2738.5</v>
+      </c>
+      <c r="H382" s="10">
+        <v>132086.92000000001</v>
+      </c>
+      <c r="I382" s="4">
+        <v>411</v>
+      </c>
+      <c r="J382" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.073256004455248E-2</v>
+      </c>
+      <c r="K382" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L382" s="15">
+        <v>0.46736111111111112</v>
+      </c>
+      <c r="M382" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.17569444444444443</v>
+      </c>
+      <c r="N382" s="4">
+        <v>143702</v>
+      </c>
+      <c r="O382" s="4">
+        <v>143739</v>
+      </c>
+      <c r="P382" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>37</v>
+      </c>
+      <c r="Q382" s="4">
+        <v>136</v>
+      </c>
+      <c r="R382" s="4">
+        <v>3</v>
+      </c>
+      <c r="S382" s="4">
+        <v>3</v>
+      </c>
+      <c r="T382" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U382" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V382" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W382" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X382" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y382" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A383" s="8">
+        <v>46288</v>
+      </c>
+      <c r="B383" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C383" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D383" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E383" s="4">
+        <v>1</v>
+      </c>
+      <c r="F383" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G383" s="10">
+        <v>2511.91</v>
+      </c>
+      <c r="H383" s="10">
+        <v>27293.42</v>
+      </c>
+      <c r="I383" s="4">
+        <v>344</v>
+      </c>
+      <c r="J383" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>9.203353775378828E-2</v>
+      </c>
+      <c r="K383" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L383" s="15">
+        <v>0.61111111111111116</v>
+      </c>
+      <c r="M383" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.31944444444444448</v>
+      </c>
+      <c r="N383" s="4">
+        <v>276067</v>
+      </c>
+      <c r="O383" s="4">
+        <v>276205</v>
+      </c>
+      <c r="P383" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>138</v>
+      </c>
+      <c r="Q383" s="4">
+        <v>71</v>
+      </c>
+      <c r="R383" s="4">
+        <v>5</v>
+      </c>
+      <c r="S383" s="4">
+        <v>5</v>
+      </c>
+      <c r="T383" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U383" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V383" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W383" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X383" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y383" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A384" s="8">
+        <v>46288</v>
+      </c>
+      <c r="B384" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C384" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D384" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E384" s="4">
+        <v>11</v>
+      </c>
+      <c r="F384" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G384" s="10">
+        <v>9796.26</v>
+      </c>
+      <c r="H384" s="10">
+        <v>171667.59</v>
+      </c>
+      <c r="I384" s="4">
+        <v>1400</v>
+      </c>
+      <c r="J384" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.7065285299339269E-2</v>
+      </c>
+      <c r="K384" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L384" s="15">
+        <v>0.76388888888888884</v>
+      </c>
+      <c r="M384" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47222222222222215</v>
+      </c>
+      <c r="N384" s="4">
+        <v>125779</v>
+      </c>
+      <c r="O384" s="4">
+        <v>125926</v>
+      </c>
+      <c r="P384" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>147</v>
+      </c>
+      <c r="Q384" s="4">
+        <v>217</v>
+      </c>
+      <c r="R384" s="4">
+        <v>26</v>
+      </c>
+      <c r="S384" s="4">
+        <v>26</v>
+      </c>
+      <c r="T384" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U384" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V384" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W384" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X384" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y384" s="5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="385" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A385" s="8">
+        <v>46288</v>
+      </c>
+      <c r="B385" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C385" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D385" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E385" s="4">
+        <v>1</v>
+      </c>
+      <c r="F385" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G385" s="10">
+        <v>849.66</v>
+      </c>
+      <c r="H385" s="10">
+        <v>16194.12</v>
+      </c>
+      <c r="I385" s="4">
+        <v>510</v>
+      </c>
+      <c r="J385" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.2467191795540602E-2</v>
+      </c>
+      <c r="K385" s="11">
+        <v>0.47638888888888886</v>
+      </c>
+      <c r="L385" s="15">
+        <v>0.72291666666666665</v>
+      </c>
+      <c r="M385" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.24652777777777779</v>
+      </c>
+      <c r="N385" s="4">
+        <v>143739</v>
+      </c>
+      <c r="O385" s="4">
+        <v>143759</v>
+      </c>
+      <c r="P385" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>20</v>
+      </c>
+      <c r="Q385" s="4">
+        <v>109</v>
+      </c>
+      <c r="R385" s="4">
+        <v>4</v>
+      </c>
+      <c r="S385" s="4">
+        <v>4</v>
+      </c>
+      <c r="T385" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U385" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V385" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W385" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X385" s="4">
+        <v>4</v>
+      </c>
+      <c r="Y385" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="386" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A386" s="8">
+        <v>46288</v>
+      </c>
+      <c r="B386" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C386" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D386" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E386" s="4">
+        <v>1</v>
+      </c>
+      <c r="F386" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G386" s="10">
+        <v>4931.01</v>
+      </c>
+      <c r="H386" s="10">
+        <v>78148.53</v>
+      </c>
+      <c r="I386" s="4">
+        <v>1048</v>
+      </c>
+      <c r="J386" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.3097923914883627E-2</v>
+      </c>
+      <c r="K386" s="11">
+        <v>0.30902777777777779</v>
+      </c>
+      <c r="L386" s="15">
+        <v>0.77916666666666667</v>
+      </c>
+      <c r="M386" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47013888888888888</v>
+      </c>
+      <c r="N386" s="4">
+        <v>280891</v>
+      </c>
+      <c r="O386" s="4">
+        <v>280977</v>
+      </c>
+      <c r="P386" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>86</v>
+      </c>
+      <c r="Q386" s="4">
+        <v>94</v>
+      </c>
+      <c r="R386" s="4">
+        <v>18</v>
+      </c>
+      <c r="S386" s="4">
+        <v>18</v>
+      </c>
+      <c r="T386" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U386" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V386" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W386" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X386" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y386" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A387" s="8">
+        <v>46288</v>
+      </c>
+      <c r="B387" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C387" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D387" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E387" s="4">
+        <v>3</v>
+      </c>
+      <c r="F387" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G387" s="10">
+        <v>14040.59</v>
+      </c>
+      <c r="H387" s="10">
+        <v>84411.99</v>
+      </c>
+      <c r="I387" s="4">
+        <v>5971</v>
+      </c>
+      <c r="J387" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.16633407173554371</v>
+      </c>
+      <c r="K387" s="11">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="L387" s="15">
+        <v>0.77916666666666667</v>
+      </c>
+      <c r="M387" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.48055555555555557</v>
+      </c>
+      <c r="N387" s="4">
+        <v>14020</v>
+      </c>
+      <c r="O387" s="4">
+        <v>14057</v>
+      </c>
+      <c r="P387" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>37</v>
+      </c>
+      <c r="Q387" s="4">
+        <v>400</v>
+      </c>
+      <c r="R387" s="4">
+        <v>6</v>
+      </c>
+      <c r="S387" s="4">
+        <v>6</v>
+      </c>
+      <c r="T387" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U387" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V387" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W387" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X387" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y387" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A388" s="8">
+        <v>46288</v>
+      </c>
+      <c r="B388" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C388" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D388" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E388" s="4">
+        <v>1</v>
+      </c>
+      <c r="F388" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G388" s="10">
+        <v>1754.16</v>
+      </c>
+      <c r="H388" s="10">
+        <v>22404.55</v>
+      </c>
+      <c r="I388" s="4">
+        <v>652</v>
+      </c>
+      <c r="J388" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.8294810652300539E-2</v>
+      </c>
+      <c r="K388" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L388" s="15">
+        <v>0.69097222222222221</v>
+      </c>
+      <c r="M388" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.39930555555555552</v>
+      </c>
+      <c r="N388" s="4">
+        <v>156044</v>
+      </c>
+      <c r="O388" s="4">
+        <v>156095</v>
+      </c>
+      <c r="P388" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>51</v>
+      </c>
+      <c r="Q388" s="4">
+        <v>90</v>
+      </c>
+      <c r="R388" s="4">
+        <v>5</v>
+      </c>
+      <c r="S388" s="4">
+        <v>5</v>
+      </c>
+      <c r="T388" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U388" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V388" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W388" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="X388" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y388" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A389" s="8">
+        <v>46288</v>
+      </c>
+      <c r="B389" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C389" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D389" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E389" s="4">
+        <v>4</v>
+      </c>
+      <c r="F389" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G389" s="10">
+        <v>12520.8</v>
+      </c>
+      <c r="H389" s="10">
+        <v>192147.28</v>
+      </c>
+      <c r="I389" s="4">
+        <v>3036</v>
+      </c>
+      <c r="J389" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.5162514920846126E-2</v>
+      </c>
+      <c r="K389" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L389" s="15">
+        <v>0.84652777777777777</v>
+      </c>
+      <c r="M389" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.57569444444444451</v>
+      </c>
+      <c r="N389" s="4">
+        <v>305368</v>
+      </c>
+      <c r="O389" s="4">
+        <v>305441</v>
+      </c>
+      <c r="P389" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>73</v>
+      </c>
+      <c r="Q389" s="4">
+        <v>487</v>
+      </c>
+      <c r="R389" s="4">
+        <v>31</v>
+      </c>
+      <c r="S389" s="4">
+        <v>31</v>
+      </c>
+      <c r="T389" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U389" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V389" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W389" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X389" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y389" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A390" s="8">
+        <v>46288</v>
+      </c>
+      <c r="B390" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C390" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D390" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E390" s="4">
+        <v>1</v>
+      </c>
+      <c r="F390" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G390" s="10">
+        <v>8679.9500000000007</v>
+      </c>
+      <c r="H390" s="10">
+        <v>126902.55</v>
+      </c>
+      <c r="I390" s="4">
+        <v>1112</v>
+      </c>
+      <c r="J390" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.8398546758910675E-2</v>
+      </c>
+      <c r="K390" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L390" s="15">
+        <v>0.71250000000000002</v>
+      </c>
+      <c r="M390" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4</v>
+      </c>
+      <c r="N390" s="4">
+        <v>120223</v>
+      </c>
+      <c r="O390" s="4">
+        <v>120289</v>
+      </c>
+      <c r="P390" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>66</v>
+      </c>
+      <c r="Q390" s="4">
+        <v>210</v>
+      </c>
+      <c r="R390" s="4">
+        <v>21</v>
+      </c>
+      <c r="S390" s="4">
+        <v>21</v>
+      </c>
+      <c r="T390" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U390" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V390" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W390" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X390" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y390" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A391" s="8">
+        <v>46288</v>
+      </c>
+      <c r="B391" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C391" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D391" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E391" s="4">
+        <v>5</v>
+      </c>
+      <c r="F391" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G391" s="10">
+        <v>29666.37</v>
+      </c>
+      <c r="H391" s="10">
+        <v>541276.69999999995</v>
+      </c>
+      <c r="I391" s="4">
+        <v>4074</v>
+      </c>
+      <c r="J391" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.4808141566041919E-2</v>
+      </c>
+      <c r="K391" s="11">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="L391" s="15">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="M391" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.38888888888888884</v>
+      </c>
+      <c r="N391" s="4">
+        <v>106073</v>
+      </c>
+      <c r="O391" s="4">
+        <v>106119</v>
+      </c>
+      <c r="P391" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>46</v>
+      </c>
+      <c r="Q391" s="4">
+        <v>327</v>
+      </c>
+      <c r="R391" s="4">
+        <v>5</v>
+      </c>
+      <c r="S391" s="4">
+        <v>5</v>
+      </c>
+      <c r="T391" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U391" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V391" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W391" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X391" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y391" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A392" s="8">
+        <v>46289</v>
+      </c>
+      <c r="B392" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C392" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D392" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E392" s="4">
+        <v>5</v>
+      </c>
+      <c r="F392" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G392" s="10">
+        <v>849.66</v>
+      </c>
+      <c r="H392" s="10">
+        <v>16194.12</v>
+      </c>
+      <c r="I392" s="4">
+        <v>510</v>
+      </c>
+      <c r="J392" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.2467191795540602E-2</v>
+      </c>
+      <c r="K392" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L392" s="15">
+        <v>0.72638888888888886</v>
+      </c>
+      <c r="M392" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.41388888888888886</v>
+      </c>
+      <c r="N392" s="4">
+        <v>143759</v>
+      </c>
+      <c r="O392" s="4">
+        <v>143780</v>
+      </c>
+      <c r="P392" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>21</v>
+      </c>
+      <c r="Q392" s="4">
+        <v>109</v>
+      </c>
+      <c r="R392" s="4">
+        <v>4</v>
+      </c>
+      <c r="S392" s="4">
+        <v>4</v>
+      </c>
+      <c r="T392" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U392" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V392" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W392" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X392" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y392" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A393" s="8">
+        <v>46289</v>
+      </c>
+      <c r="B393" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C393" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D393" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E393" s="4">
+        <v>2</v>
+      </c>
+      <c r="F393" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G393" s="10">
+        <v>9266.7900000000009</v>
+      </c>
+      <c r="H393" s="10">
+        <v>143510.03</v>
+      </c>
+      <c r="I393" s="4">
+        <v>1967</v>
+      </c>
+      <c r="J393" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.4572420478206299E-2</v>
+      </c>
+      <c r="K393" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L393" s="15">
+        <v>0.75277777777777777</v>
+      </c>
+      <c r="M393" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.48194444444444445</v>
+      </c>
+      <c r="N393" s="4">
+        <v>305448</v>
+      </c>
+      <c r="O393" s="4">
+        <v>305511</v>
+      </c>
+      <c r="P393" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>63</v>
+      </c>
+      <c r="Q393" s="4">
+        <v>326</v>
+      </c>
+      <c r="R393" s="4">
+        <v>36</v>
+      </c>
+      <c r="S393" s="4">
+        <v>36</v>
+      </c>
+      <c r="T393" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U393" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V393" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W393" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X393" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y393" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A394" s="8">
+        <v>46289</v>
+      </c>
+      <c r="B394" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C394" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D394" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E394" s="4">
+        <v>1</v>
+      </c>
+      <c r="F394" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G394" s="10">
+        <v>3913.35</v>
+      </c>
+      <c r="H394" s="10">
+        <v>79617.289999999994</v>
+      </c>
+      <c r="I394" s="4">
+        <v>568</v>
+      </c>
+      <c r="J394" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.9152012081797813E-2</v>
+      </c>
+      <c r="K394" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L394" s="15">
+        <v>0.63888888888888884</v>
+      </c>
+      <c r="M394" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.34722222222222215</v>
+      </c>
+      <c r="N394" s="4">
+        <v>291751</v>
+      </c>
+      <c r="O394" s="4">
+        <v>291803</v>
+      </c>
+      <c r="P394" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>52</v>
+      </c>
+      <c r="Q394" s="4">
+        <v>568</v>
+      </c>
+      <c r="R394" s="4">
+        <v>3</v>
+      </c>
+      <c r="S394" s="4">
+        <v>3</v>
+      </c>
+      <c r="T394" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U394" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V394" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W394" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X394" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y394" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A395" s="8">
+        <v>46289</v>
+      </c>
+      <c r="B395" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C395" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D395" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E395" s="4">
+        <v>1</v>
+      </c>
+      <c r="F395" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G395" s="10">
+        <v>1138.6099999999999</v>
+      </c>
+      <c r="H395" s="10">
+        <v>12566.7</v>
+      </c>
+      <c r="I395" s="4">
+        <v>131</v>
+      </c>
+      <c r="J395" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>9.0605329959336969E-2</v>
+      </c>
+      <c r="K395" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L395" s="15">
+        <v>0.48958333333333331</v>
+      </c>
+      <c r="M395" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.19791666666666663</v>
+      </c>
+      <c r="N395" s="4">
+        <v>156095</v>
+      </c>
+      <c r="O395" s="4">
+        <v>156124</v>
+      </c>
+      <c r="P395" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>29</v>
+      </c>
+      <c r="Q395" s="4">
+        <v>73</v>
+      </c>
+      <c r="R395" s="4">
+        <v>1</v>
+      </c>
+      <c r="S395" s="4">
+        <v>1</v>
+      </c>
+      <c r="T395" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U395" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V395" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W395" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X395" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y395" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A396" s="8">
+        <v>46289</v>
+      </c>
+      <c r="B396" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C396" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D396" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E396" s="4">
+        <v>11</v>
+      </c>
+      <c r="F396" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G396" s="10">
+        <v>13182.61</v>
+      </c>
+      <c r="H396" s="10">
+        <v>220347.32</v>
+      </c>
+      <c r="I396" s="4">
+        <v>2205</v>
+      </c>
+      <c r="J396" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.9826504810677979E-2</v>
+      </c>
+      <c r="K396" s="11">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="L396" s="15">
+        <v>0.77430555555555558</v>
+      </c>
+      <c r="M396" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.49652777777777779</v>
+      </c>
+      <c r="N396" s="4">
+        <v>106119</v>
+      </c>
+      <c r="O396" s="4">
+        <v>106267</v>
+      </c>
+      <c r="P396" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>148</v>
+      </c>
+      <c r="Q396" s="4">
+        <v>383</v>
+      </c>
+      <c r="R396" s="4">
+        <v>42</v>
+      </c>
+      <c r="S396" s="4">
+        <v>42</v>
+      </c>
+      <c r="T396" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U396" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V396" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W396" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X396" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y396" s="5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="397" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A397" s="8">
+        <v>46289</v>
+      </c>
+      <c r="B397" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C397" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D397" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E397" s="4">
+        <v>3</v>
+      </c>
+      <c r="F397" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G397" s="10">
+        <v>10875.33</v>
+      </c>
+      <c r="H397" s="10">
+        <v>98740.479999999996</v>
+      </c>
+      <c r="I397" s="4">
+        <v>1510</v>
+      </c>
+      <c r="J397" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.11014054215657045</v>
+      </c>
+      <c r="K397" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L397" s="15">
+        <v>0.75694444444444442</v>
+      </c>
+      <c r="M397" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="N397" s="4">
+        <v>14057</v>
+      </c>
+      <c r="O397" s="4">
+        <v>14111</v>
+      </c>
+      <c r="P397" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>54</v>
+      </c>
+      <c r="Q397" s="4">
+        <v>276</v>
+      </c>
+      <c r="R397" s="4">
+        <v>18</v>
+      </c>
+      <c r="S397" s="4">
+        <v>18</v>
+      </c>
+      <c r="T397" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U397" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V397" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W397" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X397" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y397" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="398" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A398" s="8">
+        <v>46289</v>
+      </c>
+      <c r="B398" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C398" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D398" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E398" s="4">
+        <v>1</v>
+      </c>
+      <c r="F398" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G398" s="10">
+        <v>8404.52</v>
+      </c>
+      <c r="H398" s="10">
+        <v>128824.18</v>
+      </c>
+      <c r="I398" s="4">
+        <v>1771</v>
+      </c>
+      <c r="J398" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.5240236731955142E-2</v>
+      </c>
+      <c r="K398" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L398" s="15">
+        <v>0.71527777777777779</v>
+      </c>
+      <c r="M398" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.40277777777777779</v>
+      </c>
+      <c r="N398" s="4">
+        <v>120289</v>
+      </c>
+      <c r="O398" s="4">
+        <v>120351</v>
+      </c>
+      <c r="P398" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>62</v>
+      </c>
+      <c r="Q398" s="4">
+        <v>238</v>
+      </c>
+      <c r="R398" s="4">
+        <v>21</v>
+      </c>
+      <c r="S398" s="4">
+        <v>21</v>
+      </c>
+      <c r="T398" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U398" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V398" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W398" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X398" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y398" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A399" s="8">
+        <v>46289</v>
+      </c>
+      <c r="B399" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C399" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D399" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E399" s="4">
+        <v>11</v>
+      </c>
+      <c r="F399" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G399" s="10">
+        <v>6979.52</v>
+      </c>
+      <c r="H399" s="10">
+        <v>102383.03999999999</v>
+      </c>
+      <c r="I399" s="4">
+        <v>1176</v>
+      </c>
+      <c r="J399" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.8170665766517591E-2</v>
+      </c>
+      <c r="K399" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L399" s="15">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="M399" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.54166666666666674</v>
+      </c>
+      <c r="N399" s="4">
+        <v>125926</v>
+      </c>
+      <c r="O399" s="4">
+        <v>126093</v>
+      </c>
+      <c r="P399" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>167</v>
+      </c>
+      <c r="Q399" s="4">
+        <v>188</v>
+      </c>
+      <c r="R399" s="4">
+        <v>16</v>
+      </c>
+      <c r="S399" s="4">
+        <v>16</v>
+      </c>
+      <c r="T399" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U399" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V399" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W399" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X399" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y399" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A400" s="8">
+        <v>46289</v>
+      </c>
+      <c r="B400" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C400" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D400" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E400" s="4">
+        <v>1</v>
+      </c>
+      <c r="F400" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G400" s="10">
+        <v>2100.86</v>
+      </c>
+      <c r="H400" s="10">
+        <v>76062.289999999994</v>
+      </c>
+      <c r="I400" s="4">
+        <v>189</v>
+      </c>
+      <c r="J400" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.7620257028811521E-2</v>
+      </c>
+      <c r="K400" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L400" s="15">
+        <v>0.69097222222222221</v>
+      </c>
+      <c r="M400" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.39930555555555552</v>
+      </c>
+      <c r="N400" s="4">
+        <v>276205</v>
+      </c>
+      <c r="O400" s="4">
+        <v>276245</v>
+      </c>
+      <c r="P400" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>40</v>
+      </c>
+      <c r="Q400" s="4">
+        <v>99</v>
+      </c>
+      <c r="R400" s="4">
+        <v>3</v>
+      </c>
+      <c r="S400" s="4">
+        <v>3</v>
+      </c>
+      <c r="T400" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U400" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V400" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W400" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X400" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y400" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A401" s="8">
+        <v>46289</v>
+      </c>
+      <c r="B401" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C401" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D401" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E401" s="4">
+        <v>1</v>
+      </c>
+      <c r="F401" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G401" s="10">
+        <v>4045.1</v>
+      </c>
+      <c r="H401" s="10">
+        <v>55543.93</v>
+      </c>
+      <c r="I401" s="4">
+        <v>87</v>
+      </c>
+      <c r="J401" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.2827039786345693E-2</v>
+      </c>
+      <c r="K401" s="11">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="L401" s="15">
+        <v>0.71944444444444444</v>
+      </c>
+      <c r="M401" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.13611111111111107</v>
+      </c>
+      <c r="N401" s="4">
+        <v>156124</v>
+      </c>
+      <c r="O401" s="4">
+        <v>156143</v>
+      </c>
+      <c r="P401" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>19</v>
+      </c>
+      <c r="Q401" s="4">
+        <v>87</v>
+      </c>
+      <c r="R401" s="4">
+        <v>7</v>
+      </c>
+      <c r="S401" s="4">
+        <v>7</v>
+      </c>
+      <c r="T401" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U401" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V401" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W401" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X401" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y401" s="5">
+        <v>38.380000000000003</v>
+      </c>
+    </row>
+    <row r="402" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A402" s="8">
+        <v>46289</v>
+      </c>
+      <c r="B402" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C402" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D402" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E402" s="4">
+        <v>5</v>
+      </c>
+      <c r="F402" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G402" s="10">
+        <v>13121.13</v>
+      </c>
+      <c r="H402" s="10">
+        <v>404814.06</v>
+      </c>
+      <c r="I402" s="4">
+        <v>3870</v>
+      </c>
+      <c r="J402" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.2412732897666642E-2</v>
+      </c>
+      <c r="K402" s="11">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L402" s="15">
+        <v>0.75</v>
+      </c>
+      <c r="M402" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="N402" s="4">
+        <v>280977</v>
+      </c>
+      <c r="O402" s="4">
+        <v>281008</v>
+      </c>
+      <c r="P402" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>31</v>
+      </c>
+      <c r="Q402" s="4">
+        <v>685</v>
+      </c>
+      <c r="R402" s="4">
+        <v>9</v>
+      </c>
+      <c r="S402" s="4">
+        <v>9</v>
+      </c>
+      <c r="T402" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U402" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V402" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W402" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X402" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y402" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J354">
-    <cfRule type="cellIs" dxfId="21" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="J2:J402">
+    <cfRule type="cellIs" dxfId="76" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="75" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U354">
-    <cfRule type="cellIs" dxfId="19" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="U2:U402">
+    <cfRule type="cellIs" dxfId="74" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="73" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="72" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="71" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="70" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="69" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="68" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V354">
-    <cfRule type="expression" dxfId="12" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="V2:V402">
+    <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -34191,7 +38578,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34207,7 +38594,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D354</xm:sqref>
+          <xm:sqref>D2:D402</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2247549D-6947-4ED8-8E71-80B19CF679E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3BC813E-DA5A-4ECA-9F9B-34FDAE50A797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha2" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="90">
   <si>
     <t>Data</t>
   </si>
@@ -310,6 +310,9 @@
   </si>
   <si>
     <t>27,27,27,27</t>
+  </si>
+  <si>
+    <t>38,38,38,38</t>
   </si>
 </sst>
 </file>
@@ -2191,8 +2194,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V19" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
-  <autoFilter ref="A1:V19" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V20" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
+  <autoFilter ref="A1:V20" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="139"/>
     <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="138"/>
@@ -2234,7 +2237,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y402" totalsRowShown="0" headerRowDxfId="117" dataDxfId="115" headerRowBorderDxfId="116" tableBorderDxfId="114" totalsRowBorderDxfId="113">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y413" totalsRowShown="0" headerRowDxfId="117" dataDxfId="115" headerRowBorderDxfId="116" tableBorderDxfId="114" totalsRowBorderDxfId="113">
   <tableColumns count="25">
     <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="112"/>
     <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="111">
@@ -2707,7 +2710,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A050DE7D-8F3F-47CF-9E37-B95AFD2ED76A}">
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="23" bestFit="1" customWidth="1"/>
@@ -3660,10 +3663,10 @@
       <c r="D16" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="10">
         <v>6537.08</v>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="10">
         <v>70656.17</v>
       </c>
       <c r="G16" s="4">
@@ -3720,10 +3723,10 @@
       <c r="D17" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="10">
         <v>4118.54</v>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="10">
         <v>62885.27</v>
       </c>
       <c r="G17" s="4">
@@ -3780,10 +3783,10 @@
       <c r="D18" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="10">
         <v>4151.1400000000003</v>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="10">
         <v>51812.79</v>
       </c>
       <c r="G18" s="4">
@@ -3840,10 +3843,10 @@
       <c r="D19" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="10">
         <v>3779.58</v>
       </c>
-      <c r="F19" s="27">
+      <c r="F19" s="10">
         <v>77696.94</v>
       </c>
       <c r="G19" s="4">
@@ -3893,8 +3896,72 @@
       </c>
       <c r="V19" s="5"/>
     </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" s="27">
+        <v>10761.38</v>
+      </c>
+      <c r="F20" s="27">
+        <v>181084.37</v>
+      </c>
+      <c r="G20" s="4">
+        <v>2461</v>
+      </c>
+      <c r="H20" s="9">
+        <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
+        <v>5.9427437055997706E-2</v>
+      </c>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4">
+        <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="10">
+        <v>500</v>
+      </c>
+      <c r="M20" s="9">
+        <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
+        <v>4.646244254918979E-2</v>
+      </c>
+      <c r="N20" s="4"/>
+      <c r="O20" s="4">
+        <v>28</v>
+      </c>
+      <c r="P20" s="4">
+        <v>28</v>
+      </c>
+      <c r="Q20" s="12">
+        <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="R20" s="13">
+        <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="S20" s="14" t="str">
+        <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="T20" s="4">
+        <v>0</v>
+      </c>
+      <c r="U20" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="V20" s="5"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H19">
+  <conditionalFormatting sqref="H2:H20">
     <cfRule type="cellIs" dxfId="87" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
@@ -3902,7 +3969,7 @@
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R19">
+  <conditionalFormatting sqref="R2:R20">
     <cfRule type="cellIs" dxfId="85" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
@@ -3925,7 +3992,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S19">
+  <conditionalFormatting sqref="S2:S20">
     <cfRule type="expression" dxfId="78" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
@@ -3949,7 +4016,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y402"/>
+  <dimension ref="A1:Y413"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -35702,11 +35769,11 @@
       <c r="A370" s="8">
         <v>46287</v>
       </c>
-      <c r="B370" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C370" s="26">
+      <c r="B370" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C370" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -35788,11 +35855,11 @@
       <c r="A371" s="8">
         <v>46287</v>
       </c>
-      <c r="B371" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C371" s="26">
+      <c r="B371" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C371" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -35874,11 +35941,11 @@
       <c r="A372" s="8">
         <v>46287</v>
       </c>
-      <c r="B372" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C372" s="26">
+      <c r="B372" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C372" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -35960,11 +36027,11 @@
       <c r="A373" s="8">
         <v>46287</v>
       </c>
-      <c r="B373" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C373" s="26">
+      <c r="B373" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C373" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -36046,11 +36113,11 @@
       <c r="A374" s="8">
         <v>46287</v>
       </c>
-      <c r="B374" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C374" s="26">
+      <c r="B374" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C374" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -36132,11 +36199,11 @@
       <c r="A375" s="8">
         <v>46287</v>
       </c>
-      <c r="B375" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C375" s="26">
+      <c r="B375" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C375" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -36218,11 +36285,11 @@
       <c r="A376" s="8">
         <v>46287</v>
       </c>
-      <c r="B376" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C376" s="26">
+      <c r="B376" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C376" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -36304,11 +36371,11 @@
       <c r="A377" s="8">
         <v>46287</v>
       </c>
-      <c r="B377" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C377" s="26">
+      <c r="B377" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C377" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -36390,11 +36457,11 @@
       <c r="A378" s="8">
         <v>46287</v>
       </c>
-      <c r="B378" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C378" s="26">
+      <c r="B378" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C378" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -36476,11 +36543,11 @@
       <c r="A379" s="8">
         <v>46287</v>
       </c>
-      <c r="B379" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C379" s="26">
+      <c r="B379" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C379" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -36562,11 +36629,11 @@
       <c r="A380" s="8">
         <v>46287</v>
       </c>
-      <c r="B380" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C380" s="26">
+      <c r="B380" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C380" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -36648,11 +36715,11 @@
       <c r="A381" s="8">
         <v>46288</v>
       </c>
-      <c r="B381" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C381" s="26">
+      <c r="B381" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C381" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -36734,11 +36801,11 @@
       <c r="A382" s="8">
         <v>46288</v>
       </c>
-      <c r="B382" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C382" s="26">
+      <c r="B382" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C382" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -36820,11 +36887,11 @@
       <c r="A383" s="8">
         <v>46288</v>
       </c>
-      <c r="B383" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C383" s="26">
+      <c r="B383" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C383" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -36906,11 +36973,11 @@
       <c r="A384" s="8">
         <v>46288</v>
       </c>
-      <c r="B384" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C384" s="26">
+      <c r="B384" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C384" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -36992,11 +37059,11 @@
       <c r="A385" s="8">
         <v>46288</v>
       </c>
-      <c r="B385" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C385" s="26">
+      <c r="B385" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C385" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -37078,11 +37145,11 @@
       <c r="A386" s="8">
         <v>46288</v>
       </c>
-      <c r="B386" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C386" s="26">
+      <c r="B386" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C386" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -37164,11 +37231,11 @@
       <c r="A387" s="8">
         <v>46288</v>
       </c>
-      <c r="B387" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C387" s="26">
+      <c r="B387" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C387" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -37250,11 +37317,11 @@
       <c r="A388" s="8">
         <v>46288</v>
       </c>
-      <c r="B388" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C388" s="26">
+      <c r="B388" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C388" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -37336,11 +37403,11 @@
       <c r="A389" s="8">
         <v>46288</v>
       </c>
-      <c r="B389" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C389" s="26">
+      <c r="B389" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C389" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -37422,11 +37489,11 @@
       <c r="A390" s="8">
         <v>46288</v>
       </c>
-      <c r="B390" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C390" s="26">
+      <c r="B390" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C390" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -37508,11 +37575,11 @@
       <c r="A391" s="8">
         <v>46288</v>
       </c>
-      <c r="B391" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C391" s="26">
+      <c r="B391" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C391" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -37594,11 +37661,11 @@
       <c r="A392" s="8">
         <v>46289</v>
       </c>
-      <c r="B392" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C392" s="26">
+      <c r="B392" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C392" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -37680,11 +37747,11 @@
       <c r="A393" s="8">
         <v>46289</v>
       </c>
-      <c r="B393" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C393" s="26">
+      <c r="B393" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C393" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -37766,11 +37833,11 @@
       <c r="A394" s="8">
         <v>46289</v>
       </c>
-      <c r="B394" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C394" s="26">
+      <c r="B394" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C394" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -37852,11 +37919,11 @@
       <c r="A395" s="8">
         <v>46289</v>
       </c>
-      <c r="B395" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C395" s="26">
+      <c r="B395" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C395" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -37938,11 +38005,11 @@
       <c r="A396" s="8">
         <v>46289</v>
       </c>
-      <c r="B396" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C396" s="26">
+      <c r="B396" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C396" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -38024,11 +38091,11 @@
       <c r="A397" s="8">
         <v>46289</v>
       </c>
-      <c r="B397" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C397" s="26">
+      <c r="B397" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C397" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -38110,11 +38177,11 @@
       <c r="A398" s="8">
         <v>46289</v>
       </c>
-      <c r="B398" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C398" s="26">
+      <c r="B398" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C398" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -38196,11 +38263,11 @@
       <c r="A399" s="8">
         <v>46289</v>
       </c>
-      <c r="B399" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C399" s="26">
+      <c r="B399" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C399" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -38282,11 +38349,11 @@
       <c r="A400" s="8">
         <v>46289</v>
       </c>
-      <c r="B400" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C400" s="26">
+      <c r="B400" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C400" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -38368,11 +38435,11 @@
       <c r="A401" s="8">
         <v>46289</v>
       </c>
-      <c r="B401" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C401" s="26">
+      <c r="B401" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C401" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -38454,11 +38521,11 @@
       <c r="A402" s="8">
         <v>46289</v>
       </c>
-      <c r="B402" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C402" s="26">
+      <c r="B402" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C402" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -38536,8 +38603,954 @@
         <v>0</v>
       </c>
     </row>
+    <row r="403" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A403" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B403" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C403" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D403" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E403" s="4">
+        <v>1</v>
+      </c>
+      <c r="F403" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G403" s="10">
+        <v>1400.31</v>
+      </c>
+      <c r="H403" s="10">
+        <v>7221.36</v>
+      </c>
+      <c r="I403" s="4">
+        <v>105</v>
+      </c>
+      <c r="J403" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.19391222705972283</v>
+      </c>
+      <c r="K403" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L403" s="15">
+        <v>0.50416666666666665</v>
+      </c>
+      <c r="M403" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.21249999999999997</v>
+      </c>
+      <c r="N403" s="4">
+        <v>156143</v>
+      </c>
+      <c r="O403" s="4">
+        <v>156190</v>
+      </c>
+      <c r="P403" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>47</v>
+      </c>
+      <c r="Q403" s="4">
+        <v>38</v>
+      </c>
+      <c r="R403" s="4">
+        <v>1</v>
+      </c>
+      <c r="S403" s="4">
+        <v>1</v>
+      </c>
+      <c r="T403" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U403" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V403" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W403" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X403" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y403" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A404" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B404" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C404" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D404" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E404" s="4">
+        <v>5</v>
+      </c>
+      <c r="F404" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G404" s="10">
+        <v>11508.77</v>
+      </c>
+      <c r="H404" s="10">
+        <v>507702.82</v>
+      </c>
+      <c r="I404" s="4">
+        <v>2305</v>
+      </c>
+      <c r="J404" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.2668320022331174E-2</v>
+      </c>
+      <c r="K404" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L404" s="15">
+        <v>0.77430555555555558</v>
+      </c>
+      <c r="M404" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4826388888888889</v>
+      </c>
+      <c r="N404" s="4">
+        <v>126093</v>
+      </c>
+      <c r="O404" s="4">
+        <v>126124</v>
+      </c>
+      <c r="P404" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>31</v>
+      </c>
+      <c r="Q404" s="4">
+        <v>352</v>
+      </c>
+      <c r="R404" s="4">
+        <v>10</v>
+      </c>
+      <c r="S404" s="4">
+        <v>10</v>
+      </c>
+      <c r="T404" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U404" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V404" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W404" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X404" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y404" s="5">
+        <v>21.21</v>
+      </c>
+    </row>
+    <row r="405" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A405" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B405" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C405" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D405" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E405" s="4">
+        <v>11</v>
+      </c>
+      <c r="F405" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Heremilton</v>
+      </c>
+      <c r="G405" s="10">
+        <v>25255.55</v>
+      </c>
+      <c r="H405" s="10">
+        <v>552525.32999999996</v>
+      </c>
+      <c r="I405" s="4">
+        <v>4094</v>
+      </c>
+      <c r="J405" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.5709307119005747E-2</v>
+      </c>
+      <c r="K405" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L405" s="15">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="M405" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.5</v>
+      </c>
+      <c r="N405" s="4">
+        <v>366659</v>
+      </c>
+      <c r="O405" s="4">
+        <v>366793</v>
+      </c>
+      <c r="P405" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>134</v>
+      </c>
+      <c r="Q405" s="4">
+        <v>52</v>
+      </c>
+      <c r="R405" s="4">
+        <v>4</v>
+      </c>
+      <c r="S405" s="4">
+        <v>4</v>
+      </c>
+      <c r="T405" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U405" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V405" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W405" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X405" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y405" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="406" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A406" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B406" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C406" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D406" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E406" s="4">
+        <v>1</v>
+      </c>
+      <c r="F406" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G406" s="10">
+        <v>4236.0200000000004</v>
+      </c>
+      <c r="H406" s="10">
+        <v>57103.57</v>
+      </c>
+      <c r="I406" s="4">
+        <v>642</v>
+      </c>
+      <c r="J406" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.4181351533713219E-2</v>
+      </c>
+      <c r="K406" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L406" s="15">
+        <v>0.75069444444444444</v>
+      </c>
+      <c r="M406" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45902777777777776</v>
+      </c>
+      <c r="N406" s="4">
+        <v>291751</v>
+      </c>
+      <c r="O406" s="4">
+        <v>291858</v>
+      </c>
+      <c r="P406" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>107</v>
+      </c>
+      <c r="Q406" s="4">
+        <v>103</v>
+      </c>
+      <c r="R406" s="4">
+        <v>11</v>
+      </c>
+      <c r="S406" s="4">
+        <v>11</v>
+      </c>
+      <c r="T406" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U406" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V406" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W406" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X406" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y406" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A407" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B407" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C407" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D407" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E407" s="4">
+        <v>5</v>
+      </c>
+      <c r="F407" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G407" s="10">
+        <v>5918.1</v>
+      </c>
+      <c r="H407" s="10">
+        <v>83496.66</v>
+      </c>
+      <c r="I407" s="4">
+        <v>1627</v>
+      </c>
+      <c r="J407" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.0878284233165736E-2</v>
+      </c>
+      <c r="K407" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L407" s="15">
+        <v>0.79861111111111116</v>
+      </c>
+      <c r="M407" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="N407" s="4">
+        <v>281008</v>
+      </c>
+      <c r="O407" s="4">
+        <v>281099</v>
+      </c>
+      <c r="P407" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>91</v>
+      </c>
+      <c r="Q407" s="4">
+        <v>123</v>
+      </c>
+      <c r="R407" s="4">
+        <v>19</v>
+      </c>
+      <c r="S407" s="4">
+        <v>19</v>
+      </c>
+      <c r="T407" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U407" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V407" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W407" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X407" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y407" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A408" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B408" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C408" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D408" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E408" s="4">
+        <v>1</v>
+      </c>
+      <c r="F408" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G408" s="10">
+        <v>6735.3</v>
+      </c>
+      <c r="H408" s="10">
+        <v>111500.64</v>
+      </c>
+      <c r="I408" s="4">
+        <v>2337</v>
+      </c>
+      <c r="J408" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.0405931302277727E-2</v>
+      </c>
+      <c r="K408" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L408" s="15">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="M408" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.54166666666666674</v>
+      </c>
+      <c r="N408" s="4">
+        <v>106227</v>
+      </c>
+      <c r="O408" s="4">
+        <v>106302</v>
+      </c>
+      <c r="P408" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>75</v>
+      </c>
+      <c r="Q408" s="4">
+        <v>19</v>
+      </c>
+      <c r="R408" s="4">
+        <v>19</v>
+      </c>
+      <c r="S408" s="4">
+        <v>19</v>
+      </c>
+      <c r="T408" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U408" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V408" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W408" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X408" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y408" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A409" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B409" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C409" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D409" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E409" s="4">
+        <v>2</v>
+      </c>
+      <c r="F409" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G409" s="10">
+        <v>9289.91</v>
+      </c>
+      <c r="H409" s="10">
+        <v>164673.81</v>
+      </c>
+      <c r="I409" s="4">
+        <v>1816</v>
+      </c>
+      <c r="J409" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.6414010218139729E-2</v>
+      </c>
+      <c r="K409" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L409" s="15">
+        <v>0.7729166666666667</v>
+      </c>
+      <c r="M409" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.50208333333333344</v>
+      </c>
+      <c r="N409" s="4">
+        <v>305511</v>
+      </c>
+      <c r="O409" s="4">
+        <v>305567</v>
+      </c>
+      <c r="P409" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>56</v>
+      </c>
+      <c r="Q409" s="4">
+        <v>272</v>
+      </c>
+      <c r="R409" s="4">
+        <v>27</v>
+      </c>
+      <c r="S409" s="4">
+        <v>27</v>
+      </c>
+      <c r="T409" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U409" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V409" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W409" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X409" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y409" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A410" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B410" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C410" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D410" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E410" s="4">
+        <v>3</v>
+      </c>
+      <c r="F410" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G410" s="10">
+        <v>11040.71</v>
+      </c>
+      <c r="H410" s="10">
+        <v>199413.43</v>
+      </c>
+      <c r="I410" s="4">
+        <v>2635</v>
+      </c>
+      <c r="J410" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.5365929967705785E-2</v>
+      </c>
+      <c r="K410" s="11">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="L410" s="15">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="M410" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44097222222222227</v>
+      </c>
+      <c r="N410" s="4">
+        <v>14111</v>
+      </c>
+      <c r="O410" s="4">
+        <v>14170</v>
+      </c>
+      <c r="P410" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>59</v>
+      </c>
+      <c r="Q410" s="4">
+        <v>204</v>
+      </c>
+      <c r="R410" s="4">
+        <v>23</v>
+      </c>
+      <c r="S410" s="4">
+        <v>23</v>
+      </c>
+      <c r="T410" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U410" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V410" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W410" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X410" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y410" s="5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="411" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A411" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B411" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C411" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D411" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E411" s="4">
+        <v>1</v>
+      </c>
+      <c r="F411" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G411" s="10">
+        <v>4396.1099999999997</v>
+      </c>
+      <c r="H411" s="10">
+        <v>244440.09</v>
+      </c>
+      <c r="I411" s="4">
+        <v>333</v>
+      </c>
+      <c r="J411" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>1.7984406731318091E-2</v>
+      </c>
+      <c r="K411" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L411" s="15">
+        <v>0.85347222222222219</v>
+      </c>
+      <c r="M411" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.56180555555555545</v>
+      </c>
+      <c r="N411" s="4">
+        <v>276245</v>
+      </c>
+      <c r="O411" s="4">
+        <v>276281</v>
+      </c>
+      <c r="P411" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>36</v>
+      </c>
+      <c r="Q411" s="4">
+        <v>199</v>
+      </c>
+      <c r="R411" s="4">
+        <v>5</v>
+      </c>
+      <c r="S411" s="4">
+        <v>5</v>
+      </c>
+      <c r="T411" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U411" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V411" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W411" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X411" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y411" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A412" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B412" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C412" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D412" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E412" s="4">
+        <v>1</v>
+      </c>
+      <c r="F412" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G412" s="10">
+        <v>14980.47</v>
+      </c>
+      <c r="H412" s="10">
+        <v>140701.66</v>
+      </c>
+      <c r="I412" s="4">
+        <v>5351</v>
+      </c>
+      <c r="J412" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.10646974598593932</v>
+      </c>
+      <c r="K412" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L412" s="15">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="M412" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.38541666666666663</v>
+      </c>
+      <c r="N412" s="4">
+        <v>120351</v>
+      </c>
+      <c r="O412" s="4">
+        <v>120398</v>
+      </c>
+      <c r="P412" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>47</v>
+      </c>
+      <c r="Q412" s="4">
+        <v>424</v>
+      </c>
+      <c r="R412" s="4">
+        <v>12</v>
+      </c>
+      <c r="S412" s="4">
+        <v>12</v>
+      </c>
+      <c r="T412" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U412" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V412" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W412" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X412" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y412" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A413" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B413" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C413" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D413" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E413" s="4">
+        <v>1</v>
+      </c>
+      <c r="F413" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G413" s="10">
+        <v>4004.13</v>
+      </c>
+      <c r="H413" s="10">
+        <v>51763.71</v>
+      </c>
+      <c r="I413" s="4">
+        <v>523</v>
+      </c>
+      <c r="J413" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.7353999549104963E-2</v>
+      </c>
+      <c r="K413" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L413" s="15">
+        <v>0.68958333333333333</v>
+      </c>
+      <c r="M413" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.37708333333333333</v>
+      </c>
+      <c r="N413" s="4">
+        <v>143760</v>
+      </c>
+      <c r="O413" s="4">
+        <v>143838</v>
+      </c>
+      <c r="P413" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>78</v>
+      </c>
+      <c r="Q413" s="4">
+        <v>105</v>
+      </c>
+      <c r="R413" s="4">
+        <v>17</v>
+      </c>
+      <c r="S413" s="4">
+        <v>17</v>
+      </c>
+      <c r="T413" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U413" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V413" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W413" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X413" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y413" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J402">
+  <conditionalFormatting sqref="J2:J413">
     <cfRule type="cellIs" dxfId="76" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
@@ -38545,7 +39558,7 @@
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U402">
+  <conditionalFormatting sqref="U2:U413">
     <cfRule type="cellIs" dxfId="74" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
@@ -38568,7 +39581,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V402">
+  <conditionalFormatting sqref="V2:V413">
     <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
@@ -38594,7 +39607,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D402</xm:sqref>
+          <xm:sqref>D2:D413</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3BC813E-DA5A-4ECA-9F9B-34FDAE50A797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A84D5F88-6696-4EAA-9CBD-E186FB780031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha2" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="991" uniqueCount="92">
   <si>
     <t>Data</t>
   </si>
@@ -314,6 +314,12 @@
   <si>
     <t>38,38,38,38</t>
   </si>
+  <si>
+    <t>13,13,8</t>
+  </si>
+  <si>
+    <t>Mosqueiro</t>
+  </si>
 </sst>
 </file>
 
@@ -516,7 +522,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -590,9 +596,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -602,84 +605,7 @@
     <cellStyle name="Normal 2 2 2" xfId="3" xr:uid="{F6D7429B-6BC2-41D1-B818-FB0128371036}"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="145">
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="134">
     <dxf>
       <font>
         <b/>
@@ -2194,94 +2120,94 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V20" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V20" totalsRowShown="0" headerRowDxfId="133" dataDxfId="131" headerRowBorderDxfId="132" tableBorderDxfId="130" totalsRowBorderDxfId="129" headerRowCellStyle="Normal 2 2 2">
   <autoFilter ref="A1:V20" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="139"/>
-    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="138"/>
-    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="137"/>
-    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="136"/>
-    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="135" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="134" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="133"/>
-    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="132" dataCellStyle="Porcentagem">
+    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="128"/>
+    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="127"/>
+    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="126"/>
+    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="125"/>
+    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="124" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="123" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="122"/>
+    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="121" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="131"/>
-    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="130"/>
-    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="129">
+    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="120"/>
+    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="119"/>
+    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="118">
       <calculatedColumnFormula>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="128" dataCellStyle="Moeda"/>
-    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="127" dataCellStyle="Porcentagem">
+    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="117" dataCellStyle="Moeda"/>
+    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="116" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="126"/>
-    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="125"/>
-    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="124"/>
-    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="123">
+    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="115"/>
+    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="114"/>
+    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="113"/>
+    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="112">
       <calculatedColumnFormula>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="122" dataCellStyle="Moeda 2 2">
+    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="111" dataCellStyle="Moeda 2 2">
       <calculatedColumnFormula>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="121" dataCellStyle="Moeda 3">
+    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="110" dataCellStyle="Moeda 3">
       <calculatedColumnFormula>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="120"/>
-    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="119"/>
-    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="118"/>
+    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="109"/>
+    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="108"/>
+    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="107"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y413" totalsRowShown="0" headerRowDxfId="117" dataDxfId="115" headerRowBorderDxfId="116" tableBorderDxfId="114" totalsRowBorderDxfId="113">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y424" totalsRowShown="0" headerRowDxfId="106" dataDxfId="104" headerRowBorderDxfId="105" tableBorderDxfId="103" totalsRowBorderDxfId="102">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="112"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="111">
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="101"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="100">
       <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="110">
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="99">
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="109"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="108"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="107">
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="98"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="97"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="96">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="106" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="105" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="104"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="103" dataCellStyle="Normal 2 2 2">
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="95" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="94" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="93"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="92" dataCellStyle="Normal 2 2 2">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="102"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="101"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="100">
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="91"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="90"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="89">
       <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="99"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="98"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="97">
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="88"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="87"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="86">
       <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="96"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="95"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="94"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="93">
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="85"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="84"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="83"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="82">
       <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="92" dataCellStyle="Moeda">
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="81" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="91">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="80">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="90"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="89"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="88"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="79"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="78"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="77"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3907,10 +3833,10 @@
       <c r="D20" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="10">
         <v>10761.38</v>
       </c>
-      <c r="F20" s="27">
+      <c r="F20" s="10">
         <v>181084.37</v>
       </c>
       <c r="G20" s="4">
@@ -3962,38 +3888,38 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H20">
-    <cfRule type="cellIs" dxfId="87" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="76" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="75" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R20">
-    <cfRule type="cellIs" dxfId="85" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="74" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="73" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="72" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="71" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="70" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="69" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="68" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S20">
-    <cfRule type="expression" dxfId="78" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -4002,7 +3928,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4016,7 +3942,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y413"/>
+  <dimension ref="A1:Y424"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -38607,11 +38533,11 @@
       <c r="A403" s="8">
         <v>46290</v>
       </c>
-      <c r="B403" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C403" s="26">
+      <c r="B403" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C403" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -38693,11 +38619,11 @@
       <c r="A404" s="8">
         <v>46290</v>
       </c>
-      <c r="B404" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C404" s="26">
+      <c r="B404" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C404" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -38779,11 +38705,11 @@
       <c r="A405" s="8">
         <v>46290</v>
       </c>
-      <c r="B405" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C405" s="26">
+      <c r="B405" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C405" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -38865,11 +38791,11 @@
       <c r="A406" s="8">
         <v>46290</v>
       </c>
-      <c r="B406" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C406" s="26">
+      <c r="B406" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C406" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -38951,11 +38877,11 @@
       <c r="A407" s="8">
         <v>46290</v>
       </c>
-      <c r="B407" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C407" s="26">
+      <c r="B407" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C407" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -39037,11 +38963,11 @@
       <c r="A408" s="8">
         <v>46290</v>
       </c>
-      <c r="B408" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C408" s="26">
+      <c r="B408" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C408" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -39123,11 +39049,11 @@
       <c r="A409" s="8">
         <v>46290</v>
       </c>
-      <c r="B409" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C409" s="26">
+      <c r="B409" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C409" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -39209,11 +39135,11 @@
       <c r="A410" s="8">
         <v>46290</v>
       </c>
-      <c r="B410" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C410" s="26">
+      <c r="B410" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C410" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -39295,11 +39221,11 @@
       <c r="A411" s="8">
         <v>46290</v>
       </c>
-      <c r="B411" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C411" s="26">
+      <c r="B411" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C411" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -39381,11 +39307,11 @@
       <c r="A412" s="8">
         <v>46290</v>
       </c>
-      <c r="B412" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C412" s="26">
+      <c r="B412" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C412" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -39467,11 +39393,11 @@
       <c r="A413" s="8">
         <v>46290</v>
       </c>
-      <c r="B413" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C413" s="26">
+      <c r="B413" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C413" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -39549,40 +39475,986 @@
         <v>0</v>
       </c>
     </row>
+    <row r="414" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A414" s="8">
+        <v>46293</v>
+      </c>
+      <c r="B414" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C414" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D414" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E414" s="4">
+        <v>11</v>
+      </c>
+      <c r="F414" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G414" s="10">
+        <v>21693.67</v>
+      </c>
+      <c r="H414" s="10">
+        <v>354040.34</v>
+      </c>
+      <c r="I414" s="4">
+        <v>4005</v>
+      </c>
+      <c r="J414" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.1274571140678483E-2</v>
+      </c>
+      <c r="K414" s="11">
+        <v>0.27430555555555558</v>
+      </c>
+      <c r="L414" s="15">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="M414" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.52777777777777779</v>
+      </c>
+      <c r="N414" s="4">
+        <v>106302</v>
+      </c>
+      <c r="O414" s="4">
+        <v>106433</v>
+      </c>
+      <c r="P414" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>131</v>
+      </c>
+      <c r="Q414" s="4">
+        <v>737</v>
+      </c>
+      <c r="R414" s="4">
+        <v>21</v>
+      </c>
+      <c r="S414" s="4">
+        <v>21</v>
+      </c>
+      <c r="T414" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U414" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V414" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W414" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X414" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y414" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A415" s="8">
+        <v>46293</v>
+      </c>
+      <c r="B415" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C415" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D415" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E415" s="4">
+        <v>1</v>
+      </c>
+      <c r="F415" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G415" s="10">
+        <v>2973.41</v>
+      </c>
+      <c r="H415" s="10">
+        <v>9200.4500000000007</v>
+      </c>
+      <c r="I415" s="4">
+        <v>177</v>
+      </c>
+      <c r="J415" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.32318093136748743</v>
+      </c>
+      <c r="K415" s="11">
+        <v>0.26319444444444445</v>
+      </c>
+      <c r="L415" s="15">
+        <v>0.49791666666666667</v>
+      </c>
+      <c r="M415" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.23472222222222222</v>
+      </c>
+      <c r="N415" s="4">
+        <v>156247</v>
+      </c>
+      <c r="O415" s="4">
+        <v>156302</v>
+      </c>
+      <c r="P415" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>55</v>
+      </c>
+      <c r="Q415" s="4">
+        <v>27</v>
+      </c>
+      <c r="R415" s="4">
+        <v>1</v>
+      </c>
+      <c r="S415" s="4">
+        <v>1</v>
+      </c>
+      <c r="T415" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U415" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V415" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W415" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X415" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y415" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A416" s="8">
+        <v>46293</v>
+      </c>
+      <c r="B416" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C416" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D416" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E416" s="4">
+        <v>3</v>
+      </c>
+      <c r="F416" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G416" s="10">
+        <v>9218.99</v>
+      </c>
+      <c r="H416" s="10">
+        <v>251213.41</v>
+      </c>
+      <c r="I416" s="4">
+        <v>2045</v>
+      </c>
+      <c r="J416" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.669784188670501E-2</v>
+      </c>
+      <c r="K416" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L416" s="15">
+        <v>0.76388888888888884</v>
+      </c>
+      <c r="M416" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47222222222222215</v>
+      </c>
+      <c r="N416" s="4">
+        <v>305567</v>
+      </c>
+      <c r="O416" s="4">
+        <v>305630</v>
+      </c>
+      <c r="P416" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>63</v>
+      </c>
+      <c r="Q416" s="4">
+        <v>262</v>
+      </c>
+      <c r="R416" s="4">
+        <v>23</v>
+      </c>
+      <c r="S416" s="4">
+        <v>21</v>
+      </c>
+      <c r="T416" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>2</v>
+      </c>
+      <c r="U416" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.91304347826086951</v>
+      </c>
+      <c r="V416" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W416" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X416" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y416" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="417" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A417" s="8">
+        <v>46293</v>
+      </c>
+      <c r="B417" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C417" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D417" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E417" s="4">
+        <v>2</v>
+      </c>
+      <c r="F417" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G417" s="10">
+        <v>9319.57</v>
+      </c>
+      <c r="H417" s="10">
+        <v>206129.93</v>
+      </c>
+      <c r="I417" s="4">
+        <v>1859</v>
+      </c>
+      <c r="J417" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.5212114514374499E-2</v>
+      </c>
+      <c r="K417" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L417" s="15">
+        <v>0.80555555555555558</v>
+      </c>
+      <c r="M417" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.53472222222222232</v>
+      </c>
+      <c r="N417" s="4">
+        <v>126246</v>
+      </c>
+      <c r="O417" s="4">
+        <v>126325</v>
+      </c>
+      <c r="P417" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>79</v>
+      </c>
+      <c r="Q417" s="4">
+        <v>267</v>
+      </c>
+      <c r="R417" s="4">
+        <v>32</v>
+      </c>
+      <c r="S417" s="4">
+        <v>32</v>
+      </c>
+      <c r="T417" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U417" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V417" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W417" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X417" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y417" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A418" s="8">
+        <v>46293</v>
+      </c>
+      <c r="B418" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C418" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D418" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E418" s="4">
+        <v>1</v>
+      </c>
+      <c r="F418" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G418" s="10">
+        <v>9333.08</v>
+      </c>
+      <c r="H418" s="10">
+        <v>290605.62</v>
+      </c>
+      <c r="I418" s="4">
+        <v>1402</v>
+      </c>
+      <c r="J418" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.2115965272798232E-2</v>
+      </c>
+      <c r="K418" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L418" s="15">
+        <v>0.78263888888888888</v>
+      </c>
+      <c r="M418" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4909722222222222</v>
+      </c>
+      <c r="N418" s="4">
+        <v>291859</v>
+      </c>
+      <c r="O418" s="4">
+        <v>291912</v>
+      </c>
+      <c r="P418" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>53</v>
+      </c>
+      <c r="Q418" s="4">
+        <v>143</v>
+      </c>
+      <c r="R418" s="4">
+        <v>5</v>
+      </c>
+      <c r="S418" s="4">
+        <v>5</v>
+      </c>
+      <c r="T418" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U418" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V418" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W418" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X418" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y418" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A419" s="8">
+        <v>46293</v>
+      </c>
+      <c r="B419" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C419" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D419" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E419" s="4">
+        <v>5</v>
+      </c>
+      <c r="F419" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G419" s="10">
+        <v>23684.07</v>
+      </c>
+      <c r="H419" s="10">
+        <v>464001.72</v>
+      </c>
+      <c r="I419" s="4">
+        <v>3729</v>
+      </c>
+      <c r="J419" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.1043065098982827E-2</v>
+      </c>
+      <c r="K419" s="11">
+        <v>0.29375000000000001</v>
+      </c>
+      <c r="L419" s="15">
+        <v>0.78055555555555556</v>
+      </c>
+      <c r="M419" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.48680555555555555</v>
+      </c>
+      <c r="N419" s="4">
+        <v>14171</v>
+      </c>
+      <c r="O419" s="4">
+        <v>14237</v>
+      </c>
+      <c r="P419" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>66</v>
+      </c>
+      <c r="Q419" s="4">
+        <v>274</v>
+      </c>
+      <c r="R419" s="4">
+        <v>21</v>
+      </c>
+      <c r="S419" s="4">
+        <v>21</v>
+      </c>
+      <c r="T419" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U419" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V419" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W419" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X419" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y419" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="420" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A420" s="8">
+        <v>46293</v>
+      </c>
+      <c r="B420" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C420" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D420" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E420" s="4">
+        <v>1</v>
+      </c>
+      <c r="F420" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G420" s="10">
+        <v>3368.44</v>
+      </c>
+      <c r="H420" s="10">
+        <v>39299.07</v>
+      </c>
+      <c r="I420" s="4">
+        <v>126</v>
+      </c>
+      <c r="J420" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.5712969798013031E-2</v>
+      </c>
+      <c r="K420" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L420" s="15">
+        <v>0.73263888888888884</v>
+      </c>
+      <c r="M420" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44097222222222215</v>
+      </c>
+      <c r="N420" s="4">
+        <v>276287</v>
+      </c>
+      <c r="O420" s="4">
+        <v>276329</v>
+      </c>
+      <c r="P420" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>42</v>
+      </c>
+      <c r="Q420" s="4">
+        <v>34</v>
+      </c>
+      <c r="R420" s="4">
+        <v>5</v>
+      </c>
+      <c r="S420" s="4">
+        <v>5</v>
+      </c>
+      <c r="T420" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U420" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V420" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W420" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X420" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y420" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A421" s="8">
+        <v>46293</v>
+      </c>
+      <c r="B421" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C421" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D421" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E421" s="4">
+        <v>1</v>
+      </c>
+      <c r="F421" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G421" s="10">
+        <v>4705.49</v>
+      </c>
+      <c r="H421" s="10">
+        <v>42953.85</v>
+      </c>
+      <c r="I421" s="4">
+        <v>769</v>
+      </c>
+      <c r="J421" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.10954757256916435</v>
+      </c>
+      <c r="K421" s="11">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="L421" s="15">
+        <v>0.85277777777777775</v>
+      </c>
+      <c r="M421" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.5541666666666667</v>
+      </c>
+      <c r="N421" s="4">
+        <v>281059</v>
+      </c>
+      <c r="O421" s="4">
+        <v>281247</v>
+      </c>
+      <c r="P421" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>188</v>
+      </c>
+      <c r="Q421" s="4">
+        <v>108</v>
+      </c>
+      <c r="R421" s="4">
+        <v>16</v>
+      </c>
+      <c r="S421" s="4">
+        <v>15</v>
+      </c>
+      <c r="T421" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>1</v>
+      </c>
+      <c r="U421" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.9375</v>
+      </c>
+      <c r="V421" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W421" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="X421" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y421" s="5">
+        <v>13.42</v>
+      </c>
+    </row>
+    <row r="422" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A422" s="8">
+        <v>46293</v>
+      </c>
+      <c r="B422" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C422" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D422" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E422" s="4">
+        <v>5</v>
+      </c>
+      <c r="F422" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Heremilton</v>
+      </c>
+      <c r="G422" s="10">
+        <v>12922.53</v>
+      </c>
+      <c r="H422" s="10">
+        <v>364913.29</v>
+      </c>
+      <c r="I422" s="4">
+        <v>2323</v>
+      </c>
+      <c r="J422" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.5412604457349312E-2</v>
+      </c>
+      <c r="K422" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L422" s="15">
+        <v>0.76388888888888884</v>
+      </c>
+      <c r="M422" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.49305555555555552</v>
+      </c>
+      <c r="N422" s="4">
+        <v>367044</v>
+      </c>
+      <c r="O422" s="4">
+        <v>367081</v>
+      </c>
+      <c r="P422" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>37</v>
+      </c>
+      <c r="Q422" s="4">
+        <v>576</v>
+      </c>
+      <c r="R422" s="4">
+        <v>12</v>
+      </c>
+      <c r="S422" s="4">
+        <v>12</v>
+      </c>
+      <c r="T422" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U422" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V422" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W422" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X422" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y422" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A423" s="8">
+        <v>46293</v>
+      </c>
+      <c r="B423" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C423" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D423" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E423" s="4">
+        <v>5</v>
+      </c>
+      <c r="F423" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G423" s="10">
+        <v>11215.28</v>
+      </c>
+      <c r="H423" s="10">
+        <v>148653.44</v>
+      </c>
+      <c r="I423" s="4">
+        <v>2785</v>
+      </c>
+      <c r="J423" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.5445815448334064E-2</v>
+      </c>
+      <c r="K423" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L423" s="15">
+        <v>0.73541666666666672</v>
+      </c>
+      <c r="M423" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44375000000000003</v>
+      </c>
+      <c r="N423" s="4">
+        <v>120399</v>
+      </c>
+      <c r="O423" s="4">
+        <v>120461</v>
+      </c>
+      <c r="P423" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>62</v>
+      </c>
+      <c r="Q423" s="4">
+        <v>302</v>
+      </c>
+      <c r="R423" s="4">
+        <v>11</v>
+      </c>
+      <c r="S423" s="4">
+        <v>10</v>
+      </c>
+      <c r="T423" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>1</v>
+      </c>
+      <c r="U423" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="V423" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W423" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X423" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y423" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="424" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A424" s="8">
+        <v>46293</v>
+      </c>
+      <c r="B424" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C424" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D424" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E424" s="4">
+        <v>1</v>
+      </c>
+      <c r="F424" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G424" s="10">
+        <v>9273.92</v>
+      </c>
+      <c r="H424" s="10">
+        <v>193715.08</v>
+      </c>
+      <c r="I424" s="4">
+        <v>1758</v>
+      </c>
+      <c r="J424" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.7874021991473253E-2</v>
+      </c>
+      <c r="K424" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L424" s="15">
+        <v>0.7583333333333333</v>
+      </c>
+      <c r="M424" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.46666666666666662</v>
+      </c>
+      <c r="N424" s="4">
+        <v>143838</v>
+      </c>
+      <c r="O424" s="4">
+        <v>143896</v>
+      </c>
+      <c r="P424" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>58</v>
+      </c>
+      <c r="Q424" s="4">
+        <v>163</v>
+      </c>
+      <c r="R424" s="4">
+        <v>20</v>
+      </c>
+      <c r="S424" s="4">
+        <v>20</v>
+      </c>
+      <c r="T424" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U424" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V424" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W424" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X424" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y424" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J413">
-    <cfRule type="cellIs" dxfId="76" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="J2:J424">
+    <cfRule type="cellIs" dxfId="65" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="64" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U413">
-    <cfRule type="cellIs" dxfId="74" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="U2:U424">
+    <cfRule type="cellIs" dxfId="63" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="62" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="61" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="60" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="59" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="57" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V413">
-    <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="V2:V424">
+    <cfRule type="expression" dxfId="56" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -39591,7 +40463,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39607,7 +40479,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D413</xm:sqref>
+          <xm:sqref>D2:D424</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A84D5F88-6696-4EAA-9CBD-E186FB780031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504AB399-B1DA-45C1-A9EE-A66C452343CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha2" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="991" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="92">
   <si>
     <t>Data</t>
   </si>
@@ -522,7 +522,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -596,6 +596,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -605,7 +608,7 @@
     <cellStyle name="Normal 2 2 2" xfId="3" xr:uid="{F6D7429B-6BC2-41D1-B818-FB0128371036}"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="134">
+  <dxfs count="145">
     <dxf>
       <font>
         <b/>
@@ -682,6 +685,586 @@
         <i val="0"/>
         <color rgb="FFFF0000"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[h]:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[h]:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0070C0"/>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1308,509 +1891,6 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[h]:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[h]:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="25" formatCode="hh:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0070C0"/>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -2120,94 +2200,94 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V20" totalsRowShown="0" headerRowDxfId="133" dataDxfId="131" headerRowBorderDxfId="132" tableBorderDxfId="130" totalsRowBorderDxfId="129" headerRowCellStyle="Normal 2 2 2">
-  <autoFilter ref="A1:V20" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V21" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
+  <autoFilter ref="A1:V21" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="128"/>
-    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="127"/>
-    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="126"/>
-    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="125"/>
-    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="124" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="123" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="122"/>
-    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="121" dataCellStyle="Porcentagem">
+    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="139"/>
+    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="138"/>
+    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="137"/>
+    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="136"/>
+    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="135" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="134" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="133"/>
+    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="132" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="120"/>
-    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="119"/>
-    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="118">
+    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="131"/>
+    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="130"/>
+    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="129">
       <calculatedColumnFormula>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="117" dataCellStyle="Moeda"/>
-    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="116" dataCellStyle="Porcentagem">
+    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="128" dataCellStyle="Moeda"/>
+    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="127" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="115"/>
-    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="114"/>
-    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="113"/>
-    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="112">
+    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="126"/>
+    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="125"/>
+    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="124"/>
+    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="123">
       <calculatedColumnFormula>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="111" dataCellStyle="Moeda 2 2">
+    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="122" dataCellStyle="Moeda 2 2">
       <calculatedColumnFormula>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="110" dataCellStyle="Moeda 3">
+    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="121" dataCellStyle="Moeda 3">
       <calculatedColumnFormula>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="109"/>
-    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="108"/>
-    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="107"/>
+    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="120"/>
+    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="119"/>
+    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="118"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y424" totalsRowShown="0" headerRowDxfId="106" dataDxfId="104" headerRowBorderDxfId="105" tableBorderDxfId="103" totalsRowBorderDxfId="102">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y434" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50" headerRowBorderDxfId="48" tableBorderDxfId="49" totalsRowBorderDxfId="47">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="101"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="100">
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="46"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="45">
       <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="99">
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="44">
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="98"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="97"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="96">
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="41">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="95" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="94" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="93"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="92" dataCellStyle="Normal 2 2 2">
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="40" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="39" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="38"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="37" dataCellStyle="Normal 2 2 2">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="91"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="90"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="89">
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="36"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="35"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="34">
       <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="88"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="87"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="86">
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="33"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="32"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="31">
       <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="85"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="84"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="83"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="82">
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="30"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="29"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="28"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="27">
       <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="81" dataCellStyle="Moeda">
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="26" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="80">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="25">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="79"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="78"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="77"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="24"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="23"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2636,7 +2716,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A050DE7D-8F3F-47CF-9E37-B95AFD2ED76A}">
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="23" bestFit="1" customWidth="1"/>
@@ -3886,40 +3966,88 @@
       </c>
       <c r="V20" s="5"/>
     </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" s="8">
+        <v>46294</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="9" t="e">
+        <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4">
+        <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="10"/>
+      <c r="M21" s="9" t="e">
+        <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="12">
+        <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="R21" s="13" t="e">
+        <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S21" s="14" t="e">
+        <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T21" s="4"/>
+      <c r="U21" s="4"/>
+      <c r="V21" s="5"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H20">
-    <cfRule type="cellIs" dxfId="76" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="H2:H21">
+    <cfRule type="cellIs" dxfId="117" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="116" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R20">
-    <cfRule type="cellIs" dxfId="74" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="R2:R21">
+    <cfRule type="cellIs" dxfId="115" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="114" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="113" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="112" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="111" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="110" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="109" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S20">
-    <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="S2:S21">
+    <cfRule type="expression" dxfId="108" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -3928,7 +4056,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="107" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3942,7 +4070,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y424"/>
+  <dimension ref="A1:Y434"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -39479,11 +39607,11 @@
       <c r="A414" s="8">
         <v>46293</v>
       </c>
-      <c r="B414" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C414" s="26">
+      <c r="B414" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C414" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -39565,11 +39693,11 @@
       <c r="A415" s="8">
         <v>46293</v>
       </c>
-      <c r="B415" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C415" s="26">
+      <c r="B415" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C415" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -39651,11 +39779,11 @@
       <c r="A416" s="8">
         <v>46293</v>
       </c>
-      <c r="B416" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C416" s="26">
+      <c r="B416" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C416" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -39737,11 +39865,11 @@
       <c r="A417" s="8">
         <v>46293</v>
       </c>
-      <c r="B417" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C417" s="26">
+      <c r="B417" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C417" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -39823,11 +39951,11 @@
       <c r="A418" s="8">
         <v>46293</v>
       </c>
-      <c r="B418" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C418" s="26">
+      <c r="B418" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C418" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -39909,11 +40037,11 @@
       <c r="A419" s="8">
         <v>46293</v>
       </c>
-      <c r="B419" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C419" s="26">
+      <c r="B419" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C419" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -39995,11 +40123,11 @@
       <c r="A420" s="8">
         <v>46293</v>
       </c>
-      <c r="B420" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C420" s="26">
+      <c r="B420" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C420" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -40081,11 +40209,11 @@
       <c r="A421" s="8">
         <v>46293</v>
       </c>
-      <c r="B421" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C421" s="26">
+      <c r="B421" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C421" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -40167,11 +40295,11 @@
       <c r="A422" s="8">
         <v>46293</v>
       </c>
-      <c r="B422" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C422" s="26">
+      <c r="B422" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C422" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -40253,11 +40381,11 @@
       <c r="A423" s="8">
         <v>46293</v>
       </c>
-      <c r="B423" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C423" s="26">
+      <c r="B423" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C423" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -40339,11 +40467,11 @@
       <c r="A424" s="8">
         <v>46293</v>
       </c>
-      <c r="B424" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C424" s="26">
+      <c r="B424" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C424" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -40421,40 +40549,900 @@
         <v>0</v>
       </c>
     </row>
+    <row r="425" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A425" s="8">
+        <v>46294</v>
+      </c>
+      <c r="B425" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C425" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D425" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E425" s="4">
+        <v>11</v>
+      </c>
+      <c r="F425" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G425" s="10">
+        <v>22617.07</v>
+      </c>
+      <c r="H425" s="10">
+        <v>281785.12</v>
+      </c>
+      <c r="I425" s="4">
+        <v>6226</v>
+      </c>
+      <c r="J425" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.0263535562133309E-2</v>
+      </c>
+      <c r="K425" s="11">
+        <v>0.27430555555555558</v>
+      </c>
+      <c r="L425" s="15">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="M425" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.51736111111111105</v>
+      </c>
+      <c r="N425" s="4">
+        <v>106433</v>
+      </c>
+      <c r="O425" s="4">
+        <v>106579</v>
+      </c>
+      <c r="P425" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>146</v>
+      </c>
+      <c r="Q425" s="4">
+        <v>755</v>
+      </c>
+      <c r="R425" s="4">
+        <v>37</v>
+      </c>
+      <c r="S425" s="4">
+        <v>37</v>
+      </c>
+      <c r="T425" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U425" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V425" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W425" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X425" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y425" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="426" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A426" s="8">
+        <v>46294</v>
+      </c>
+      <c r="B426" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C426" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D426" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E426" s="4">
+        <v>1</v>
+      </c>
+      <c r="F426" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G426" s="10">
+        <v>1113.4100000000001</v>
+      </c>
+      <c r="H426" s="10">
+        <v>12324</v>
+      </c>
+      <c r="I426" s="4">
+        <v>211</v>
+      </c>
+      <c r="J426" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>9.034485556637456E-2</v>
+      </c>
+      <c r="K426" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L426" s="15">
+        <v>0.625</v>
+      </c>
+      <c r="M426" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="N426" s="4">
+        <v>156302</v>
+      </c>
+      <c r="O426" s="4">
+        <v>156370</v>
+      </c>
+      <c r="P426" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>68</v>
+      </c>
+      <c r="Q426" s="4">
+        <v>20</v>
+      </c>
+      <c r="R426" s="4">
+        <v>1</v>
+      </c>
+      <c r="S426" s="4">
+        <v>1</v>
+      </c>
+      <c r="T426" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U426" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V426" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W426" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X426" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y426" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A427" s="8">
+        <v>46294</v>
+      </c>
+      <c r="B427" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C427" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D427" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E427" s="4">
+        <v>2</v>
+      </c>
+      <c r="F427" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G427" s="10">
+        <v>7509.04</v>
+      </c>
+      <c r="H427" s="10">
+        <v>133454.82999999999</v>
+      </c>
+      <c r="I427" s="4">
+        <v>1515</v>
+      </c>
+      <c r="J427" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.6266528532537941E-2</v>
+      </c>
+      <c r="K427" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L427" s="15">
+        <v>0.74305555555555558</v>
+      </c>
+      <c r="M427" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="N427" s="4">
+        <v>126325</v>
+      </c>
+      <c r="O427" s="4">
+        <v>126381</v>
+      </c>
+      <c r="P427" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>56</v>
+      </c>
+      <c r="Q427" s="4">
+        <v>190</v>
+      </c>
+      <c r="R427" s="4">
+        <v>26</v>
+      </c>
+      <c r="S427" s="4">
+        <v>26</v>
+      </c>
+      <c r="T427" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U427" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V427" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W427" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X427" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y427" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A428" s="8">
+        <v>46294</v>
+      </c>
+      <c r="B428" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C428" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D428" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E428" s="4">
+        <v>5</v>
+      </c>
+      <c r="F428" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G428" s="10">
+        <v>5011.5600000000004</v>
+      </c>
+      <c r="H428" s="10">
+        <v>90003.41</v>
+      </c>
+      <c r="I428" s="4">
+        <v>808</v>
+      </c>
+      <c r="J428" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.5681890275046247E-2</v>
+      </c>
+      <c r="K428" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L428" s="15">
+        <v>0.71527777777777779</v>
+      </c>
+      <c r="M428" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.40277777777777779</v>
+      </c>
+      <c r="N428" s="4">
+        <v>120461</v>
+      </c>
+      <c r="O428" s="4">
+        <v>120547</v>
+      </c>
+      <c r="P428" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>86</v>
+      </c>
+      <c r="Q428" s="4">
+        <v>119</v>
+      </c>
+      <c r="R428" s="4">
+        <v>18</v>
+      </c>
+      <c r="S428" s="4">
+        <v>18</v>
+      </c>
+      <c r="T428" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U428" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V428" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W428" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X428" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y428" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="429" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A429" s="8">
+        <v>46294</v>
+      </c>
+      <c r="B429" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C429" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D429" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E429" s="4">
+        <v>1</v>
+      </c>
+      <c r="F429" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G429" s="10">
+        <v>8326.7800000000007</v>
+      </c>
+      <c r="H429" s="10">
+        <v>93407.54</v>
+      </c>
+      <c r="I429" s="4">
+        <v>885</v>
+      </c>
+      <c r="J429" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.9144623656719796E-2</v>
+      </c>
+      <c r="K429" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L429" s="15">
+        <v>0.76111111111111107</v>
+      </c>
+      <c r="M429" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44861111111111107</v>
+      </c>
+      <c r="N429" s="4">
+        <v>143896</v>
+      </c>
+      <c r="O429" s="4">
+        <v>143967</v>
+      </c>
+      <c r="P429" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>71</v>
+      </c>
+      <c r="Q429" s="4">
+        <v>133</v>
+      </c>
+      <c r="R429" s="4">
+        <v>22</v>
+      </c>
+      <c r="S429" s="4">
+        <v>22</v>
+      </c>
+      <c r="T429" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U429" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V429" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W429" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X429" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y429" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A430" s="8">
+        <v>46294</v>
+      </c>
+      <c r="B430" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C430" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D430" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E430" s="4">
+        <v>3</v>
+      </c>
+      <c r="F430" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G430" s="10">
+        <v>10745.4</v>
+      </c>
+      <c r="H430" s="10">
+        <v>56053.61</v>
+      </c>
+      <c r="I430" s="4">
+        <v>3980</v>
+      </c>
+      <c r="J430" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.19169862565497564</v>
+      </c>
+      <c r="K430" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L430" s="15">
+        <v>0.71805555555555556</v>
+      </c>
+      <c r="M430" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.40555555555555556</v>
+      </c>
+      <c r="N430" s="4">
+        <v>276321</v>
+      </c>
+      <c r="O430" s="4">
+        <v>276371</v>
+      </c>
+      <c r="P430" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>50</v>
+      </c>
+      <c r="Q430" s="4">
+        <v>265</v>
+      </c>
+      <c r="R430" s="4">
+        <v>6</v>
+      </c>
+      <c r="S430" s="4">
+        <v>6</v>
+      </c>
+      <c r="T430" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U430" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V430" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W430" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X430" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y430" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A431" s="8">
+        <v>46294</v>
+      </c>
+      <c r="B431" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C431" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D431" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E431" s="4">
+        <v>5</v>
+      </c>
+      <c r="F431" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G431" s="10">
+        <v>2067.41</v>
+      </c>
+      <c r="H431" s="10">
+        <v>40528.410000000003</v>
+      </c>
+      <c r="I431" s="4">
+        <v>437</v>
+      </c>
+      <c r="J431" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.101137695754656E-2</v>
+      </c>
+      <c r="K431" s="11">
+        <v>0.3215277777777778</v>
+      </c>
+      <c r="L431" s="15">
+        <v>0.70486111111111116</v>
+      </c>
+      <c r="M431" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.38333333333333336</v>
+      </c>
+      <c r="N431" s="4">
+        <v>14237</v>
+      </c>
+      <c r="O431" s="4">
+        <v>14293</v>
+      </c>
+      <c r="P431" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>56</v>
+      </c>
+      <c r="Q431" s="4">
+        <v>87</v>
+      </c>
+      <c r="R431" s="4">
+        <v>8</v>
+      </c>
+      <c r="S431" s="4">
+        <v>8</v>
+      </c>
+      <c r="T431" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U431" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V431" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W431" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X431" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y431" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A432" s="8">
+        <v>46294</v>
+      </c>
+      <c r="B432" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C432" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D432" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E432" s="4">
+        <v>1</v>
+      </c>
+      <c r="F432" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G432" s="10">
+        <v>5478.94</v>
+      </c>
+      <c r="H432" s="10">
+        <v>119535.11</v>
+      </c>
+      <c r="I432" s="4">
+        <v>254</v>
+      </c>
+      <c r="J432" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.5835403506133049E-2</v>
+      </c>
+      <c r="K432" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L432" s="15">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="M432" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.41249999999999998</v>
+      </c>
+      <c r="N432" s="4">
+        <v>291912</v>
+      </c>
+      <c r="O432" s="4">
+        <v>292074</v>
+      </c>
+      <c r="P432" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>162</v>
+      </c>
+      <c r="Q432" s="4">
+        <v>254</v>
+      </c>
+      <c r="R432" s="4">
+        <v>10</v>
+      </c>
+      <c r="S432" s="4">
+        <v>10</v>
+      </c>
+      <c r="T432" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U432" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V432" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W432" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X432" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y432" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A433" s="8">
+        <v>46294</v>
+      </c>
+      <c r="B433" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C433" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D433" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E433" s="4">
+        <v>3</v>
+      </c>
+      <c r="F433" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G433" s="10">
+        <v>8588.69</v>
+      </c>
+      <c r="H433" s="10">
+        <v>124979.38</v>
+      </c>
+      <c r="I433" s="4">
+        <v>1375</v>
+      </c>
+      <c r="J433" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.8720856192437507E-2</v>
+      </c>
+      <c r="K433" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L433" s="15">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="M433" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.43333333333333329</v>
+      </c>
+      <c r="N433" s="4">
+        <v>305630</v>
+      </c>
+      <c r="O433" s="4">
+        <v>305683</v>
+      </c>
+      <c r="P433" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>53</v>
+      </c>
+      <c r="Q433" s="4">
+        <v>185</v>
+      </c>
+      <c r="R433" s="4">
+        <v>17</v>
+      </c>
+      <c r="S433" s="4">
+        <v>17</v>
+      </c>
+      <c r="T433" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U433" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V433" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W433" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X433" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y433" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A434" s="8">
+        <v>46294</v>
+      </c>
+      <c r="B434" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C434" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D434" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E434" s="4">
+        <v>4</v>
+      </c>
+      <c r="F434" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G434" s="10">
+        <v>12998.65</v>
+      </c>
+      <c r="H434" s="10">
+        <v>189947.66</v>
+      </c>
+      <c r="I434" s="4">
+        <v>2689</v>
+      </c>
+      <c r="J434" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.843279880362832E-2</v>
+      </c>
+      <c r="K434" s="11">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L434" s="15">
+        <v>0.73472222222222228</v>
+      </c>
+      <c r="M434" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.40138888888888896</v>
+      </c>
+      <c r="N434" s="4">
+        <v>281247</v>
+      </c>
+      <c r="O434" s="4">
+        <v>281328</v>
+      </c>
+      <c r="P434" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>81</v>
+      </c>
+      <c r="Q434" s="4">
+        <v>406</v>
+      </c>
+      <c r="R434" s="4">
+        <v>20</v>
+      </c>
+      <c r="S434" s="4">
+        <v>20</v>
+      </c>
+      <c r="T434" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U434" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V434" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W434" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X434" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y434" s="5">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J424">
-    <cfRule type="cellIs" dxfId="65" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="J2:J434">
+    <cfRule type="cellIs" dxfId="21" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="20" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U424">
-    <cfRule type="cellIs" dxfId="63" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="U2:U434">
+    <cfRule type="cellIs" dxfId="19" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="18" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="17" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V424">
-    <cfRule type="expression" dxfId="56" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="V2:V434">
+    <cfRule type="expression" dxfId="12" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -40463,7 +41451,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -40479,7 +41467,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D424</xm:sqref>
+          <xm:sqref>D2:D434</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504AB399-B1DA-45C1-A9EE-A66C452343CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4AB1C7D-9A07-4607-BA36-335858D4AE90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha2" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="92">
   <si>
     <t>Data</t>
   </si>
@@ -2200,8 +2200,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V21" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
-  <autoFilter ref="A1:V21" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V22" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
+  <autoFilter ref="A1:V22" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="139"/>
     <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="138"/>
@@ -2243,7 +2243,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y434" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50" headerRowBorderDxfId="48" tableBorderDxfId="49" totalsRowBorderDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y444" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50" headerRowBorderDxfId="48" tableBorderDxfId="49" totalsRowBorderDxfId="47">
   <tableColumns count="25">
     <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="46"/>
     <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="45">
@@ -2716,7 +2716,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A050DE7D-8F3F-47CF-9E37-B95AFD2ED76A}">
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="23" bestFit="1" customWidth="1"/>
@@ -3977,8 +3977,8 @@
       <c r="D21" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
       <c r="G21" s="4"/>
       <c r="H21" s="9" t="e">
         <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
@@ -4014,8 +4014,56 @@
       <c r="U21" s="4"/>
       <c r="V21" s="5"/>
     </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" s="8">
+        <v>46295</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="9" t="e">
+        <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4">
+        <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="10"/>
+      <c r="M22" s="9" t="e">
+        <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N22" s="4"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="12">
+        <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="R22" s="13" t="e">
+        <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S22" s="14" t="e">
+        <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T22" s="4"/>
+      <c r="U22" s="4"/>
+      <c r="V22" s="5"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H21">
+  <conditionalFormatting sqref="H2:H22">
     <cfRule type="cellIs" dxfId="117" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
@@ -4023,7 +4071,7 @@
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R21">
+  <conditionalFormatting sqref="R2:R22">
     <cfRule type="cellIs" dxfId="115" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
@@ -4046,7 +4094,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S21">
+  <conditionalFormatting sqref="S2:S22">
     <cfRule type="expression" dxfId="108" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
@@ -4070,7 +4118,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y434"/>
+  <dimension ref="A1:Y444"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -40553,11 +40601,11 @@
       <c r="A425" s="8">
         <v>46294</v>
       </c>
-      <c r="B425" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C425" s="26">
+      <c r="B425" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C425" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -40639,11 +40687,11 @@
       <c r="A426" s="8">
         <v>46294</v>
       </c>
-      <c r="B426" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C426" s="26">
+      <c r="B426" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C426" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -40725,11 +40773,11 @@
       <c r="A427" s="8">
         <v>46294</v>
       </c>
-      <c r="B427" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C427" s="26">
+      <c r="B427" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C427" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -40811,11 +40859,11 @@
       <c r="A428" s="8">
         <v>46294</v>
       </c>
-      <c r="B428" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C428" s="26">
+      <c r="B428" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C428" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -40897,11 +40945,11 @@
       <c r="A429" s="8">
         <v>46294</v>
       </c>
-      <c r="B429" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C429" s="26">
+      <c r="B429" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C429" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -40983,11 +41031,11 @@
       <c r="A430" s="8">
         <v>46294</v>
       </c>
-      <c r="B430" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C430" s="26">
+      <c r="B430" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C430" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -41069,11 +41117,11 @@
       <c r="A431" s="8">
         <v>46294</v>
       </c>
-      <c r="B431" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C431" s="26">
+      <c r="B431" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C431" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -41155,11 +41203,11 @@
       <c r="A432" s="8">
         <v>46294</v>
       </c>
-      <c r="B432" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C432" s="26">
+      <c r="B432" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C432" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -41241,11 +41289,11 @@
       <c r="A433" s="8">
         <v>46294</v>
       </c>
-      <c r="B433" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C433" s="26">
+      <c r="B433" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C433" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -41327,11 +41375,11 @@
       <c r="A434" s="8">
         <v>46294</v>
       </c>
-      <c r="B434" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C434" s="26">
+      <c r="B434" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C434" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -41409,8 +41457,868 @@
         <v>10</v>
       </c>
     </row>
+    <row r="435" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A435" s="8">
+        <v>46295</v>
+      </c>
+      <c r="B435" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C435" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D435" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E435" s="4">
+        <v>1</v>
+      </c>
+      <c r="F435" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G435" s="10">
+        <v>4335.72</v>
+      </c>
+      <c r="H435" s="10">
+        <v>230277.65</v>
+      </c>
+      <c r="I435" s="4">
+        <v>402</v>
+      </c>
+      <c r="J435" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>1.8828227576579839E-2</v>
+      </c>
+      <c r="K435" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L435" s="15">
+        <v>0.69097222222222221</v>
+      </c>
+      <c r="M435" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.39930555555555552</v>
+      </c>
+      <c r="N435" s="4">
+        <v>276371</v>
+      </c>
+      <c r="O435" s="4">
+        <v>276439</v>
+      </c>
+      <c r="P435" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>68</v>
+      </c>
+      <c r="Q435" s="4">
+        <v>370</v>
+      </c>
+      <c r="R435" s="4">
+        <v>11</v>
+      </c>
+      <c r="S435" s="4">
+        <v>11</v>
+      </c>
+      <c r="T435" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U435" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V435" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W435" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X435" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y435" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A436" s="8">
+        <v>46295</v>
+      </c>
+      <c r="B436" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C436" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D436" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E436" s="4">
+        <v>3</v>
+      </c>
+      <c r="F436" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G436" s="10">
+        <v>5957.62</v>
+      </c>
+      <c r="H436" s="10">
+        <v>67258.740000000005</v>
+      </c>
+      <c r="I436" s="4">
+        <v>611</v>
+      </c>
+      <c r="J436" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.8577633181947793E-2</v>
+      </c>
+      <c r="K436" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L436" s="15">
+        <v>0.72083333333333333</v>
+      </c>
+      <c r="M436" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.42916666666666664</v>
+      </c>
+      <c r="N436" s="4">
+        <v>305683</v>
+      </c>
+      <c r="O436" s="4">
+        <v>305745</v>
+      </c>
+      <c r="P436" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>62</v>
+      </c>
+      <c r="Q436" s="4">
+        <v>611</v>
+      </c>
+      <c r="R436" s="4">
+        <v>17</v>
+      </c>
+      <c r="S436" s="4">
+        <v>17</v>
+      </c>
+      <c r="T436" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U436" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V436" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W436" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X436" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y436" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A437" s="8">
+        <v>46295</v>
+      </c>
+      <c r="B437" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C437" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D437" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E437" s="4">
+        <v>1</v>
+      </c>
+      <c r="F437" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G437" s="10">
+        <v>4387.9399999999996</v>
+      </c>
+      <c r="H437" s="10">
+        <v>185606.16</v>
+      </c>
+      <c r="I437" s="4">
+        <v>485</v>
+      </c>
+      <c r="J437" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.3641133462380771E-2</v>
+      </c>
+      <c r="K437" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L437" s="15">
+        <v>0.44236111111111109</v>
+      </c>
+      <c r="M437" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.15069444444444441</v>
+      </c>
+      <c r="N437" s="4">
+        <v>292074</v>
+      </c>
+      <c r="O437" s="4">
+        <v>292110</v>
+      </c>
+      <c r="P437" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>36</v>
+      </c>
+      <c r="Q437" s="4">
+        <v>18</v>
+      </c>
+      <c r="R437" s="4">
+        <v>2</v>
+      </c>
+      <c r="S437" s="4">
+        <v>2</v>
+      </c>
+      <c r="T437" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U437" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V437" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W437" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X437" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y437" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A438" s="8">
+        <v>46295</v>
+      </c>
+      <c r="B438" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C438" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D438" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E438" s="4">
+        <v>1</v>
+      </c>
+      <c r="F438" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G438" s="10">
+        <v>2210.2199999999998</v>
+      </c>
+      <c r="H438" s="10">
+        <v>38816.51</v>
+      </c>
+      <c r="I438" s="4">
+        <v>293</v>
+      </c>
+      <c r="J438" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.6940204052347822E-2</v>
+      </c>
+      <c r="K438" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L438" s="15">
+        <v>0.7270833333333333</v>
+      </c>
+      <c r="M438" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45624999999999999</v>
+      </c>
+      <c r="N438" s="4">
+        <v>156370</v>
+      </c>
+      <c r="O438" s="4">
+        <v>156531</v>
+      </c>
+      <c r="P438" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>161</v>
+      </c>
+      <c r="Q438" s="4">
+        <v>59</v>
+      </c>
+      <c r="R438" s="4">
+        <v>10</v>
+      </c>
+      <c r="S438" s="4">
+        <v>10</v>
+      </c>
+      <c r="T438" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U438" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V438" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W438" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="X438" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y438" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A439" s="8">
+        <v>46295</v>
+      </c>
+      <c r="B439" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C439" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D439" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E439" s="4">
+        <v>2</v>
+      </c>
+      <c r="F439" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G439" s="10">
+        <v>5686</v>
+      </c>
+      <c r="H439" s="10">
+        <v>130464.87</v>
+      </c>
+      <c r="I439" s="4">
+        <v>854</v>
+      </c>
+      <c r="J439" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.3582613465218648E-2</v>
+      </c>
+      <c r="K439" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L439" s="15">
+        <v>0.76736111111111116</v>
+      </c>
+      <c r="M439" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47569444444444448</v>
+      </c>
+      <c r="N439" s="4">
+        <v>126381</v>
+      </c>
+      <c r="O439" s="4">
+        <v>126467</v>
+      </c>
+      <c r="P439" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>86</v>
+      </c>
+      <c r="Q439" s="4">
+        <v>171</v>
+      </c>
+      <c r="R439" s="4">
+        <v>29</v>
+      </c>
+      <c r="S439" s="4">
+        <v>29</v>
+      </c>
+      <c r="T439" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U439" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V439" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W439" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X439" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y439" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A440" s="8">
+        <v>46295</v>
+      </c>
+      <c r="B440" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C440" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D440" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E440" s="4">
+        <v>5</v>
+      </c>
+      <c r="F440" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G440" s="10">
+        <v>5528.24</v>
+      </c>
+      <c r="H440" s="10">
+        <v>167798.9</v>
+      </c>
+      <c r="I440" s="4">
+        <v>937</v>
+      </c>
+      <c r="J440" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.2945627176340253E-2</v>
+      </c>
+      <c r="K440" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L440" s="15">
+        <v>0.79861111111111116</v>
+      </c>
+      <c r="M440" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.48611111111111116</v>
+      </c>
+      <c r="N440" s="4">
+        <v>143967</v>
+      </c>
+      <c r="O440" s="4">
+        <v>144011</v>
+      </c>
+      <c r="P440" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>44</v>
+      </c>
+      <c r="Q440" s="4">
+        <v>294</v>
+      </c>
+      <c r="R440" s="4">
+        <v>11</v>
+      </c>
+      <c r="S440" s="4">
+        <v>11</v>
+      </c>
+      <c r="T440" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U440" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V440" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W440" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X440" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y440" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A441" s="8">
+        <v>46295</v>
+      </c>
+      <c r="B441" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C441" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D441" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E441" s="4">
+        <v>11</v>
+      </c>
+      <c r="F441" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G441" s="10">
+        <v>18788.560000000001</v>
+      </c>
+      <c r="H441" s="10">
+        <v>430956.89</v>
+      </c>
+      <c r="I441" s="4">
+        <v>3167</v>
+      </c>
+      <c r="J441" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.3597307378007114E-2</v>
+      </c>
+      <c r="K441" s="11">
+        <v>0.27430555555555558</v>
+      </c>
+      <c r="L441" s="15">
+        <v>0.79861111111111116</v>
+      </c>
+      <c r="M441" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.52430555555555558</v>
+      </c>
+      <c r="N441" s="4">
+        <v>281328</v>
+      </c>
+      <c r="O441" s="4">
+        <v>281467</v>
+      </c>
+      <c r="P441" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>139</v>
+      </c>
+      <c r="Q441" s="4">
+        <v>209</v>
+      </c>
+      <c r="R441" s="4">
+        <v>41</v>
+      </c>
+      <c r="S441" s="4">
+        <v>41</v>
+      </c>
+      <c r="T441" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U441" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V441" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W441" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X441" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y441" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A442" s="8">
+        <v>46295</v>
+      </c>
+      <c r="B442" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C442" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D442" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E442" s="4">
+        <v>5</v>
+      </c>
+      <c r="F442" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G442" s="10">
+        <v>9128.23</v>
+      </c>
+      <c r="H442" s="10">
+        <v>139821.72</v>
+      </c>
+      <c r="I442" s="4">
+        <v>1480</v>
+      </c>
+      <c r="J442" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.5284778359184822E-2</v>
+      </c>
+      <c r="K442" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L442" s="15">
+        <v>0.78472222222222221</v>
+      </c>
+      <c r="M442" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.49305555555555552</v>
+      </c>
+      <c r="N442" s="4">
+        <v>14293</v>
+      </c>
+      <c r="O442" s="4">
+        <v>14374</v>
+      </c>
+      <c r="P442" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>81</v>
+      </c>
+      <c r="Q442" s="4">
+        <v>205</v>
+      </c>
+      <c r="R442" s="4">
+        <v>19</v>
+      </c>
+      <c r="S442" s="4">
+        <v>19</v>
+      </c>
+      <c r="T442" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U442" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V442" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W442" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X442" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y442" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="443" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A443" s="8">
+        <v>46295</v>
+      </c>
+      <c r="B443" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C443" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D443" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E443" s="4">
+        <v>1</v>
+      </c>
+      <c r="F443" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G443" s="10">
+        <v>7688.66</v>
+      </c>
+      <c r="H443" s="10">
+        <v>179365.1</v>
+      </c>
+      <c r="I443" s="4">
+        <v>1406</v>
+      </c>
+      <c r="J443" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.2865975599489528E-2</v>
+      </c>
+      <c r="K443" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L443" s="15">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="M443" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.39583333333333337</v>
+      </c>
+      <c r="N443" s="4">
+        <v>120547</v>
+      </c>
+      <c r="O443" s="4">
+        <v>120577</v>
+      </c>
+      <c r="P443" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>30</v>
+      </c>
+      <c r="Q443" s="4">
+        <v>223</v>
+      </c>
+      <c r="R443" s="4">
+        <v>14</v>
+      </c>
+      <c r="S443" s="4">
+        <v>14</v>
+      </c>
+      <c r="T443" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U443" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V443" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W443" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X443" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y443" s="5">
+        <v>38.380000000000003</v>
+      </c>
+    </row>
+    <row r="444" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A444" s="8">
+        <v>46295</v>
+      </c>
+      <c r="B444" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C444" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>9</v>
+      </c>
+      <c r="D444" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E444" s="4">
+        <v>1</v>
+      </c>
+      <c r="F444" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G444" s="10">
+        <v>16471</v>
+      </c>
+      <c r="H444" s="10">
+        <v>145619.81</v>
+      </c>
+      <c r="I444" s="4">
+        <v>3858</v>
+      </c>
+      <c r="J444" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.11310961056740838</v>
+      </c>
+      <c r="K444" s="11">
+        <v>0.28472222222222221</v>
+      </c>
+      <c r="L444" s="15">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="M444" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.42361111111111116</v>
+      </c>
+      <c r="N444" s="4">
+        <v>106579</v>
+      </c>
+      <c r="O444" s="4">
+        <v>106612</v>
+      </c>
+      <c r="P444" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>33</v>
+      </c>
+      <c r="Q444" s="4">
+        <v>1158</v>
+      </c>
+      <c r="R444" s="4">
+        <v>4</v>
+      </c>
+      <c r="S444" s="4">
+        <v>4</v>
+      </c>
+      <c r="T444" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U444" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V444" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W444" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X444" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y444" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J434">
+  <conditionalFormatting sqref="J2:J444">
     <cfRule type="cellIs" dxfId="21" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
@@ -41418,7 +42326,7 @@
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U434">
+  <conditionalFormatting sqref="U2:U444">
     <cfRule type="cellIs" dxfId="19" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
@@ -41441,7 +42349,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V434">
+  <conditionalFormatting sqref="V2:V444">
     <cfRule type="expression" dxfId="12" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
@@ -41467,7 +42375,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D434</xm:sqref>
+          <xm:sqref>D2:D444</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4AB1C7D-9A07-4607-BA36-335858D4AE90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3CCC392-19F8-4D78-B9AB-0D49E4430756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="93">
   <si>
     <t>Data</t>
   </si>
@@ -319,6 +319,9 @@
   </si>
   <si>
     <t>Mosqueiro</t>
+  </si>
+  <si>
+    <t>38,38,38,8</t>
   </si>
 </sst>
 </file>
@@ -2200,8 +2203,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V22" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
-  <autoFilter ref="A1:V22" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V23" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
+  <autoFilter ref="A1:V23" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="139"/>
     <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="138"/>
@@ -2243,7 +2246,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y444" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50" headerRowBorderDxfId="48" tableBorderDxfId="49" totalsRowBorderDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y455" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50" headerRowBorderDxfId="48" tableBorderDxfId="49" totalsRowBorderDxfId="47">
   <tableColumns count="25">
     <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="46"/>
     <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="45">
@@ -2716,7 +2719,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A050DE7D-8F3F-47CF-9E37-B95AFD2ED76A}">
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="23" bestFit="1" customWidth="1"/>
@@ -4025,8 +4028,8 @@
       <c r="D22" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
       <c r="G22" s="4"/>
       <c r="H22" s="9" t="e">
         <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
@@ -4062,8 +4065,64 @@
       <c r="U22" s="4"/>
       <c r="V22" s="5"/>
     </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23" s="8">
+        <v>46296</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23" s="27">
+        <v>9007.2099999999991</v>
+      </c>
+      <c r="F23" s="27">
+        <v>179512.59</v>
+      </c>
+      <c r="G23" s="4">
+        <v>2015</v>
+      </c>
+      <c r="H23" s="9">
+        <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
+        <v>5.0175923593994157E-2</v>
+      </c>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4">
+        <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
+        <v>0</v>
+      </c>
+      <c r="L23" s="10">
+        <v>500</v>
+      </c>
+      <c r="M23" s="9">
+        <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
+        <v>5.5511085008565365E-2</v>
+      </c>
+      <c r="N23" s="4"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="12">
+        <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="R23" s="13" t="e">
+        <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S23" s="14" t="e">
+        <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T23" s="4"/>
+      <c r="U23" s="4"/>
+      <c r="V23" s="5"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H22">
+  <conditionalFormatting sqref="H2:H23">
     <cfRule type="cellIs" dxfId="117" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
@@ -4071,7 +4130,7 @@
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R22">
+  <conditionalFormatting sqref="R2:R23">
     <cfRule type="cellIs" dxfId="115" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
@@ -4094,7 +4153,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S22">
+  <conditionalFormatting sqref="S2:S23">
     <cfRule type="expression" dxfId="108" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
@@ -4118,7 +4177,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y444"/>
+  <dimension ref="A1:Y455"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -41461,11 +41520,11 @@
       <c r="A435" s="8">
         <v>46295</v>
       </c>
-      <c r="B435" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C435" s="26">
+      <c r="B435" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C435" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -41547,11 +41606,11 @@
       <c r="A436" s="8">
         <v>46295</v>
       </c>
-      <c r="B436" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C436" s="26">
+      <c r="B436" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C436" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -41633,11 +41692,11 @@
       <c r="A437" s="8">
         <v>46295</v>
       </c>
-      <c r="B437" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C437" s="26">
+      <c r="B437" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C437" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -41719,11 +41778,11 @@
       <c r="A438" s="8">
         <v>46295</v>
       </c>
-      <c r="B438" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C438" s="26">
+      <c r="B438" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C438" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -41805,11 +41864,11 @@
       <c r="A439" s="8">
         <v>46295</v>
       </c>
-      <c r="B439" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C439" s="26">
+      <c r="B439" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C439" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -41891,11 +41950,11 @@
       <c r="A440" s="8">
         <v>46295</v>
       </c>
-      <c r="B440" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C440" s="26">
+      <c r="B440" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C440" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -41977,11 +42036,11 @@
       <c r="A441" s="8">
         <v>46295</v>
       </c>
-      <c r="B441" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C441" s="26">
+      <c r="B441" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C441" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -42063,11 +42122,11 @@
       <c r="A442" s="8">
         <v>46295</v>
       </c>
-      <c r="B442" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C442" s="26">
+      <c r="B442" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C442" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -42149,11 +42208,11 @@
       <c r="A443" s="8">
         <v>46295</v>
       </c>
-      <c r="B443" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C443" s="26">
+      <c r="B443" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C443" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -42235,11 +42294,11 @@
       <c r="A444" s="8">
         <v>46295</v>
       </c>
-      <c r="B444" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C444" s="26">
+      <c r="B444" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C444" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>9</v>
       </c>
@@ -42317,8 +42376,954 @@
         <v>0</v>
       </c>
     </row>
+    <row r="445" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A445" s="8">
+        <v>46296</v>
+      </c>
+      <c r="B445" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C445" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D445" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E445" s="4">
+        <v>1</v>
+      </c>
+      <c r="F445" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G445" s="10">
+        <v>13166.64</v>
+      </c>
+      <c r="H445" s="10">
+        <v>173949.2</v>
+      </c>
+      <c r="I445" s="4">
+        <v>3519</v>
+      </c>
+      <c r="J445" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.5692443540987822E-2</v>
+      </c>
+      <c r="K445" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L445" s="15">
+        <v>0.69444444444444442</v>
+      </c>
+      <c r="M445" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="N445" s="4">
+        <v>120577</v>
+      </c>
+      <c r="O445" s="4">
+        <v>120652</v>
+      </c>
+      <c r="P445" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>75</v>
+      </c>
+      <c r="Q445" s="4">
+        <v>353</v>
+      </c>
+      <c r="R445" s="4">
+        <v>26</v>
+      </c>
+      <c r="S445" s="4">
+        <v>26</v>
+      </c>
+      <c r="T445" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U445" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V445" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W445" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X445" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y445" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A446" s="8">
+        <v>46296</v>
+      </c>
+      <c r="B446" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C446" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D446" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E446" s="4">
+        <v>3</v>
+      </c>
+      <c r="F446" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G446" s="10">
+        <v>5728.99</v>
+      </c>
+      <c r="H446" s="10">
+        <v>138851.32999999999</v>
+      </c>
+      <c r="I446" s="4">
+        <v>1010</v>
+      </c>
+      <c r="J446" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.1259885663320617E-2</v>
+      </c>
+      <c r="K446" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L446" s="15">
+        <v>0.69444444444444442</v>
+      </c>
+      <c r="M446" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.40277777777777773</v>
+      </c>
+      <c r="N446" s="4">
+        <v>305745</v>
+      </c>
+      <c r="O446" s="4">
+        <v>305801</v>
+      </c>
+      <c r="P446" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>56</v>
+      </c>
+      <c r="Q446" s="4">
+        <v>149</v>
+      </c>
+      <c r="R446" s="4">
+        <v>18</v>
+      </c>
+      <c r="S446" s="4">
+        <v>18</v>
+      </c>
+      <c r="T446" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U446" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V446" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W446" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X446" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y446" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A447" s="8">
+        <v>46296</v>
+      </c>
+      <c r="B447" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C447" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D447" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E447" s="4">
+        <v>5</v>
+      </c>
+      <c r="F447" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G447" s="10">
+        <v>8096.13</v>
+      </c>
+      <c r="H447" s="10">
+        <v>182940.96</v>
+      </c>
+      <c r="I447" s="4">
+        <v>3585</v>
+      </c>
+      <c r="J447" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.425542535690203E-2</v>
+      </c>
+      <c r="K447" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L447" s="15">
+        <v>0.43472222222222223</v>
+      </c>
+      <c r="M447" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.12222222222222223</v>
+      </c>
+      <c r="N447" s="4">
+        <v>126467</v>
+      </c>
+      <c r="O447" s="4">
+        <v>126502</v>
+      </c>
+      <c r="P447" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>35</v>
+      </c>
+      <c r="Q447" s="4">
+        <v>713</v>
+      </c>
+      <c r="R447" s="4">
+        <v>15</v>
+      </c>
+      <c r="S447" s="4">
+        <v>15</v>
+      </c>
+      <c r="T447" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U447" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V447" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W447" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X447" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y447" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A448" s="8">
+        <v>46296</v>
+      </c>
+      <c r="B448" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C448" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D448" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E448" s="4">
+        <v>11</v>
+      </c>
+      <c r="F448" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Heremilton</v>
+      </c>
+      <c r="G448" s="10">
+        <v>12506.07</v>
+      </c>
+      <c r="H448" s="10">
+        <v>119003.46</v>
+      </c>
+      <c r="I448" s="4">
+        <v>4222</v>
+      </c>
+      <c r="J448" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.10508996965298319</v>
+      </c>
+      <c r="K448" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L448" s="15">
+        <v>0.74097222222222225</v>
+      </c>
+      <c r="M448" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47013888888888894</v>
+      </c>
+      <c r="N448" s="4">
+        <v>367391</v>
+      </c>
+      <c r="O448" s="4">
+        <v>367431</v>
+      </c>
+      <c r="P448" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>40</v>
+      </c>
+      <c r="Q448" s="4">
+        <v>809</v>
+      </c>
+      <c r="R448" s="4">
+        <v>2</v>
+      </c>
+      <c r="S448" s="4">
+        <v>2</v>
+      </c>
+      <c r="T448" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U448" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V448" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W448" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X448" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y448" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A449" s="8">
+        <v>46296</v>
+      </c>
+      <c r="B449" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C449" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D449" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E449" s="4">
+        <v>1</v>
+      </c>
+      <c r="F449" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G449" s="10">
+        <v>13768.88</v>
+      </c>
+      <c r="H449" s="10">
+        <v>136214.88</v>
+      </c>
+      <c r="I449" s="4">
+        <v>6604</v>
+      </c>
+      <c r="J449" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.1010820550588893</v>
+      </c>
+      <c r="K449" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L449" s="15">
+        <v>0.76388888888888884</v>
+      </c>
+      <c r="M449" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.49305555555555552</v>
+      </c>
+      <c r="N449" s="4">
+        <v>106612</v>
+      </c>
+      <c r="O449" s="4">
+        <v>106643</v>
+      </c>
+      <c r="P449" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>31</v>
+      </c>
+      <c r="Q449" s="4">
+        <v>29</v>
+      </c>
+      <c r="R449" s="4">
+        <v>4</v>
+      </c>
+      <c r="S449" s="4">
+        <v>4</v>
+      </c>
+      <c r="T449" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U449" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V449" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W449" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X449" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y449" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A450" s="8">
+        <v>46296</v>
+      </c>
+      <c r="B450" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C450" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D450" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E450" s="4">
+        <v>1</v>
+      </c>
+      <c r="F450" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G450" s="10">
+        <v>7307.82</v>
+      </c>
+      <c r="H450" s="10">
+        <v>68936.05</v>
+      </c>
+      <c r="I450" s="4">
+        <v>1954</v>
+      </c>
+      <c r="J450" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.1060086848608239</v>
+      </c>
+      <c r="K450" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L450" s="15">
+        <v>0.79236111111111107</v>
+      </c>
+      <c r="M450" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.50069444444444433</v>
+      </c>
+      <c r="N450" s="4">
+        <v>276439</v>
+      </c>
+      <c r="O450" s="4">
+        <v>276503</v>
+      </c>
+      <c r="P450" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>64</v>
+      </c>
+      <c r="Q450" s="4">
+        <v>254</v>
+      </c>
+      <c r="R450" s="4">
+        <v>8</v>
+      </c>
+      <c r="S450" s="4">
+        <v>8</v>
+      </c>
+      <c r="T450" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U450" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V450" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W450" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X450" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y450" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A451" s="8">
+        <v>46296</v>
+      </c>
+      <c r="B451" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C451" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D451" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E451" s="4">
+        <v>1</v>
+      </c>
+      <c r="F451" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G451" s="10">
+        <v>1548.42</v>
+      </c>
+      <c r="H451" s="10">
+        <v>48223.5</v>
+      </c>
+      <c r="I451" s="4">
+        <v>269</v>
+      </c>
+      <c r="J451" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.2109241344987403E-2</v>
+      </c>
+      <c r="K451" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L451" s="15">
+        <v>0.70972222222222225</v>
+      </c>
+      <c r="M451" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.41805555555555557</v>
+      </c>
+      <c r="N451" s="4">
+        <v>156431</v>
+      </c>
+      <c r="O451" s="4">
+        <v>156572</v>
+      </c>
+      <c r="P451" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>141</v>
+      </c>
+      <c r="Q451" s="4">
+        <v>2</v>
+      </c>
+      <c r="R451" s="4">
+        <v>1</v>
+      </c>
+      <c r="S451" s="4">
+        <v>1</v>
+      </c>
+      <c r="T451" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U451" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V451" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W451" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X451" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y451" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A452" s="8">
+        <v>46296</v>
+      </c>
+      <c r="B452" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C452" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D452" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E452" s="4">
+        <v>4</v>
+      </c>
+      <c r="F452" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G452" s="10">
+        <v>10079.719999999999</v>
+      </c>
+      <c r="H452" s="10">
+        <v>182931.56</v>
+      </c>
+      <c r="I452" s="4">
+        <v>2661</v>
+      </c>
+      <c r="J452" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.510104434685846E-2</v>
+      </c>
+      <c r="K452" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L452" s="15">
+        <v>0.73055555555555551</v>
+      </c>
+      <c r="M452" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.43888888888888883</v>
+      </c>
+      <c r="N452" s="4">
+        <v>144011</v>
+      </c>
+      <c r="O452" s="4">
+        <v>144077</v>
+      </c>
+      <c r="P452" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>66</v>
+      </c>
+      <c r="Q452" s="4">
+        <v>355</v>
+      </c>
+      <c r="R452" s="4">
+        <v>31</v>
+      </c>
+      <c r="S452" s="4">
+        <v>31</v>
+      </c>
+      <c r="T452" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U452" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V452" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W452" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X452" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y452" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="453" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A453" s="8">
+        <v>46296</v>
+      </c>
+      <c r="B453" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C453" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D453" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E453" s="4">
+        <v>11</v>
+      </c>
+      <c r="F453" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G453" s="10">
+        <v>14997.77</v>
+      </c>
+      <c r="H453" s="10">
+        <v>231117.04</v>
+      </c>
+      <c r="I453" s="4">
+        <v>2050</v>
+      </c>
+      <c r="J453" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.4892532372342604E-2</v>
+      </c>
+      <c r="K453" s="11">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="L453" s="15">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="M453" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="N453" s="4">
+        <v>281467</v>
+      </c>
+      <c r="O453" s="4">
+        <v>281577</v>
+      </c>
+      <c r="P453" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>110</v>
+      </c>
+      <c r="Q453" s="4">
+        <v>352</v>
+      </c>
+      <c r="R453" s="4">
+        <v>43</v>
+      </c>
+      <c r="S453" s="4">
+        <v>43</v>
+      </c>
+      <c r="T453" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U453" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V453" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W453" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X453" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y453" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A454" s="8">
+        <v>46296</v>
+      </c>
+      <c r="B454" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C454" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D454" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E454" s="4">
+        <v>5</v>
+      </c>
+      <c r="F454" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G454" s="10">
+        <v>8643.84</v>
+      </c>
+      <c r="H454" s="10">
+        <v>187927.76</v>
+      </c>
+      <c r="I454" s="4">
+        <v>723</v>
+      </c>
+      <c r="J454" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.5995546373776813E-2</v>
+      </c>
+      <c r="K454" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L454" s="15">
+        <v>0.74652777777777779</v>
+      </c>
+      <c r="M454" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4548611111111111</v>
+      </c>
+      <c r="N454" s="4">
+        <v>14375</v>
+      </c>
+      <c r="O454" s="4">
+        <v>14441</v>
+      </c>
+      <c r="P454" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>66</v>
+      </c>
+      <c r="Q454" s="4">
+        <v>347</v>
+      </c>
+      <c r="R454" s="4">
+        <v>24</v>
+      </c>
+      <c r="S454" s="4">
+        <v>24</v>
+      </c>
+      <c r="T454" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U454" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V454" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W454" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X454" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y454" s="5">
+        <v>38.380000000000003</v>
+      </c>
+    </row>
+    <row r="455" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A455" s="8">
+        <v>46296</v>
+      </c>
+      <c r="B455" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C455" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D455" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E455" s="4">
+        <v>5</v>
+      </c>
+      <c r="F455" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G455" s="10">
+        <v>6042.12</v>
+      </c>
+      <c r="H455" s="10">
+        <v>127329.96</v>
+      </c>
+      <c r="I455" s="4">
+        <v>2951</v>
+      </c>
+      <c r="J455" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.7452461306042977E-2</v>
+      </c>
+      <c r="K455" s="11">
+        <v>0.5625</v>
+      </c>
+      <c r="L455" s="15">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="M455" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.19791666666666663</v>
+      </c>
+      <c r="N455" s="4">
+        <v>126502</v>
+      </c>
+      <c r="O455" s="4">
+        <v>126547</v>
+      </c>
+      <c r="P455" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>45</v>
+      </c>
+      <c r="Q455" s="4">
+        <v>618</v>
+      </c>
+      <c r="R455" s="4">
+        <v>6</v>
+      </c>
+      <c r="S455" s="4">
+        <v>6</v>
+      </c>
+      <c r="T455" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U455" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V455" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W455" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X455" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y455" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J444">
+  <conditionalFormatting sqref="J2:J455">
     <cfRule type="cellIs" dxfId="21" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
@@ -42326,7 +43331,7 @@
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U444">
+  <conditionalFormatting sqref="U2:U455">
     <cfRule type="cellIs" dxfId="19" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
@@ -42349,7 +43354,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V444">
+  <conditionalFormatting sqref="V2:V455">
     <cfRule type="expression" dxfId="12" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
@@ -42375,7 +43380,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D444</xm:sqref>
+          <xm:sqref>D2:D455</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3CCC392-19F8-4D78-B9AB-0D49E4430756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D03638-7582-4130-9CE7-F89F2C599F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="95">
   <si>
     <t>Data</t>
   </si>
@@ -323,6 +323,12 @@
   <si>
     <t>38,38,38,8</t>
   </si>
+  <si>
+    <t>38,8,8</t>
+  </si>
+  <si>
+    <t>9,9,9,9,38</t>
+  </si>
 </sst>
 </file>
 
@@ -525,7 +531,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -599,9 +605,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -611,7 +614,7 @@
     <cellStyle name="Normal 2 2 2" xfId="3" xr:uid="{F6D7429B-6BC2-41D1-B818-FB0128371036}"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="145">
+  <dxfs count="134">
     <dxf>
       <font>
         <b/>
@@ -688,586 +691,6 @@
         <i val="0"/>
         <color rgb="FFFF0000"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[h]:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[h]:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="25" formatCode="hh:mm"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0070C0"/>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1894,6 +1317,509 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[h]:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[h]:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0070C0"/>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -2203,94 +2129,94 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V23" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V23" totalsRowShown="0" headerRowDxfId="133" dataDxfId="131" headerRowBorderDxfId="132" tableBorderDxfId="130" totalsRowBorderDxfId="129" headerRowCellStyle="Normal 2 2 2">
   <autoFilter ref="A1:V23" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="139"/>
-    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="138"/>
-    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="137"/>
-    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="136"/>
-    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="135" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="134" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="133"/>
-    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="132" dataCellStyle="Porcentagem">
+    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="128"/>
+    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="127"/>
+    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="126"/>
+    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="125"/>
+    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="124" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="123" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="122"/>
+    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="121" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="131"/>
-    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="130"/>
-    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="129">
+    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="120"/>
+    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="119"/>
+    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="118">
       <calculatedColumnFormula>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="128" dataCellStyle="Moeda"/>
-    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="127" dataCellStyle="Porcentagem">
+    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="117" dataCellStyle="Moeda"/>
+    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="116" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="126"/>
-    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="125"/>
-    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="124"/>
-    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="123">
+    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="115"/>
+    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="114"/>
+    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="113"/>
+    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="112">
       <calculatedColumnFormula>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="122" dataCellStyle="Moeda 2 2">
+    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="111" dataCellStyle="Moeda 2 2">
       <calculatedColumnFormula>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="121" dataCellStyle="Moeda 3">
+    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="110" dataCellStyle="Moeda 3">
       <calculatedColumnFormula>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="120"/>
-    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="119"/>
-    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="118"/>
+    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="109"/>
+    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="108"/>
+    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="107"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y455" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50" headerRowBorderDxfId="48" tableBorderDxfId="49" totalsRowBorderDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y479" totalsRowShown="0" headerRowDxfId="106" dataDxfId="104" headerRowBorderDxfId="105" tableBorderDxfId="103" totalsRowBorderDxfId="102">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="46"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="45">
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="101"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="100">
       <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="44">
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="99">
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="41">
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="98"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="97"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="96">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="40" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="39" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="38"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="37" dataCellStyle="Normal 2 2 2">
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="95" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="94" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="93"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="92" dataCellStyle="Normal 2 2 2">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="36"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="35"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="34">
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="91"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="90"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="89">
       <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="33"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="32"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="31">
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="88"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="87"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="86">
       <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="30"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="29"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="28"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="27">
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="85"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="84"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="83"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="82">
       <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="26" dataCellStyle="Moeda">
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="81" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="25">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="80">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="24"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="23"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="22"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="79"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="78"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="77"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4076,10 +4002,10 @@
       <c r="D23" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="10">
         <v>9007.2099999999991</v>
       </c>
-      <c r="F23" s="27">
+      <c r="F23" s="10">
         <v>179512.59</v>
       </c>
       <c r="G23" s="4">
@@ -4123,38 +4049,38 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H23">
-    <cfRule type="cellIs" dxfId="117" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="76" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="116" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="75" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R23">
-    <cfRule type="cellIs" dxfId="115" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="74" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="73" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="72" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="71" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="70" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="69" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="68" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S23">
-    <cfRule type="expression" dxfId="108" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -4163,7 +4089,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="107" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4177,7 +4103,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y455"/>
+  <dimension ref="A1:Y479"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -42380,11 +42306,11 @@
       <c r="A445" s="8">
         <v>46296</v>
       </c>
-      <c r="B445" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C445" s="26">
+      <c r="B445" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C445" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -42466,11 +42392,11 @@
       <c r="A446" s="8">
         <v>46296</v>
       </c>
-      <c r="B446" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C446" s="26">
+      <c r="B446" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C446" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -42552,11 +42478,11 @@
       <c r="A447" s="8">
         <v>46296</v>
       </c>
-      <c r="B447" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C447" s="26">
+      <c r="B447" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C447" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -42638,11 +42564,11 @@
       <c r="A448" s="8">
         <v>46296</v>
       </c>
-      <c r="B448" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C448" s="26">
+      <c r="B448" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C448" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -42724,11 +42650,11 @@
       <c r="A449" s="8">
         <v>46296</v>
       </c>
-      <c r="B449" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C449" s="26">
+      <c r="B449" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C449" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -42810,11 +42736,11 @@
       <c r="A450" s="8">
         <v>46296</v>
       </c>
-      <c r="B450" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C450" s="26">
+      <c r="B450" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C450" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -42896,11 +42822,11 @@
       <c r="A451" s="8">
         <v>46296</v>
       </c>
-      <c r="B451" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C451" s="26">
+      <c r="B451" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C451" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -42982,11 +42908,11 @@
       <c r="A452" s="8">
         <v>46296</v>
       </c>
-      <c r="B452" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C452" s="26">
+      <c r="B452" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C452" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -43068,11 +42994,11 @@
       <c r="A453" s="8">
         <v>46296</v>
       </c>
-      <c r="B453" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C453" s="26">
+      <c r="B453" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C453" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -43154,11 +43080,11 @@
       <c r="A454" s="8">
         <v>46296</v>
       </c>
-      <c r="B454" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C454" s="26">
+      <c r="B454" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C454" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -43240,11 +43166,11 @@
       <c r="A455" s="8">
         <v>46296</v>
       </c>
-      <c r="B455" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C455" s="26">
+      <c r="B455" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C455" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -43322,40 +43248,2104 @@
         <v>0</v>
       </c>
     </row>
+    <row r="456" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A456" s="8">
+        <v>46297</v>
+      </c>
+      <c r="B456" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C456" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D456" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E456" s="4">
+        <v>1</v>
+      </c>
+      <c r="F456" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G456" s="10">
+        <v>7315.87</v>
+      </c>
+      <c r="H456" s="10">
+        <v>97436.97</v>
+      </c>
+      <c r="I456" s="4">
+        <v>1154</v>
+      </c>
+      <c r="J456" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.5083102440480234E-2</v>
+      </c>
+      <c r="K456" s="11">
+        <v>0.30555555555555558</v>
+      </c>
+      <c r="L456" s="15">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="M456" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45486111111111105</v>
+      </c>
+      <c r="N456" s="4">
+        <v>276503</v>
+      </c>
+      <c r="O456" s="4">
+        <v>276565</v>
+      </c>
+      <c r="P456" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>62</v>
+      </c>
+      <c r="Q456" s="4">
+        <v>131</v>
+      </c>
+      <c r="R456" s="4">
+        <v>20</v>
+      </c>
+      <c r="S456" s="4">
+        <v>20</v>
+      </c>
+      <c r="T456" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U456" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V456" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W456" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X456" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y456" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="457" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A457" s="8">
+        <v>46297</v>
+      </c>
+      <c r="B457" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C457" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D457" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E457" s="4">
+        <v>1</v>
+      </c>
+      <c r="F457" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G457" s="10">
+        <v>21328.05</v>
+      </c>
+      <c r="H457" s="10">
+        <v>83697.179999999993</v>
+      </c>
+      <c r="I457" s="4">
+        <v>3675</v>
+      </c>
+      <c r="J457" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.25482399765440128</v>
+      </c>
+      <c r="K457" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L457" s="15">
+        <v>0.38194444444444442</v>
+      </c>
+      <c r="M457" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>6.944444444444442E-2</v>
+      </c>
+      <c r="N457" s="4">
+        <v>120652</v>
+      </c>
+      <c r="O457" s="4">
+        <v>120660</v>
+      </c>
+      <c r="P457" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>8</v>
+      </c>
+      <c r="Q457" s="4">
+        <v>300</v>
+      </c>
+      <c r="R457" s="4">
+        <v>1</v>
+      </c>
+      <c r="S457" s="4">
+        <v>1</v>
+      </c>
+      <c r="T457" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U457" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V457" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W457" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X457" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y457" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A458" s="8">
+        <v>46297</v>
+      </c>
+      <c r="B458" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C458" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D458" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E458" s="4">
+        <v>1</v>
+      </c>
+      <c r="F458" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G458" s="10">
+        <v>530.82000000000005</v>
+      </c>
+      <c r="H458" s="10">
+        <v>7594.2</v>
+      </c>
+      <c r="I458" s="4">
+        <v>22</v>
+      </c>
+      <c r="J458" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.9898080113771049E-2</v>
+      </c>
+      <c r="K458" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L458" s="15">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="M458" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.16666666666666663</v>
+      </c>
+      <c r="N458" s="4">
+        <v>292124</v>
+      </c>
+      <c r="O458" s="4">
+        <v>292183</v>
+      </c>
+      <c r="P458" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>59</v>
+      </c>
+      <c r="Q458" s="4">
+        <v>9</v>
+      </c>
+      <c r="R458" s="4">
+        <v>1</v>
+      </c>
+      <c r="S458" s="4">
+        <v>1</v>
+      </c>
+      <c r="T458" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U458" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V458" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W458" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X458" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y458" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A459" s="8">
+        <v>46297</v>
+      </c>
+      <c r="B459" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C459" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D459" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E459" s="4">
+        <v>5</v>
+      </c>
+      <c r="F459" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G459" s="10">
+        <v>9277.34</v>
+      </c>
+      <c r="H459" s="10">
+        <v>146614.56</v>
+      </c>
+      <c r="I459" s="4">
+        <v>2984</v>
+      </c>
+      <c r="J459" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.3277071526866097E-2</v>
+      </c>
+      <c r="K459" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="L459" s="15">
+        <v>0.79861111111111116</v>
+      </c>
+      <c r="M459" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.36111111111111116</v>
+      </c>
+      <c r="N459" s="4">
+        <v>120660</v>
+      </c>
+      <c r="O459" s="4">
+        <v>120714</v>
+      </c>
+      <c r="P459" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>54</v>
+      </c>
+      <c r="Q459" s="4">
+        <v>556</v>
+      </c>
+      <c r="R459" s="4">
+        <v>4</v>
+      </c>
+      <c r="S459" s="4">
+        <v>4</v>
+      </c>
+      <c r="T459" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U459" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V459" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W459" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X459" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y459" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A460" s="8">
+        <v>46297</v>
+      </c>
+      <c r="B460" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C460" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D460" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E460" s="4">
+        <v>2</v>
+      </c>
+      <c r="F460" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G460" s="10">
+        <v>9347.4699999999993</v>
+      </c>
+      <c r="H460" s="10">
+        <v>214620.24</v>
+      </c>
+      <c r="I460" s="4">
+        <v>1625</v>
+      </c>
+      <c r="J460" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.355353437308615E-2</v>
+      </c>
+      <c r="K460" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L460" s="15">
+        <v>0.77986111111111112</v>
+      </c>
+      <c r="M460" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.50902777777777786</v>
+      </c>
+      <c r="N460" s="4">
+        <v>126547</v>
+      </c>
+      <c r="O460" s="4">
+        <v>126632</v>
+      </c>
+      <c r="P460" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>85</v>
+      </c>
+      <c r="Q460" s="4">
+        <v>340</v>
+      </c>
+      <c r="R460" s="4">
+        <v>35</v>
+      </c>
+      <c r="S460" s="4">
+        <v>34</v>
+      </c>
+      <c r="T460" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>1</v>
+      </c>
+      <c r="U460" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.97142857142857142</v>
+      </c>
+      <c r="V460" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W460" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X460" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y460" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="461" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A461" s="8">
+        <v>46297</v>
+      </c>
+      <c r="B461" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C461" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D461" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E461" s="4">
+        <v>5</v>
+      </c>
+      <c r="F461" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G461" s="10">
+        <v>6435.47</v>
+      </c>
+      <c r="H461" s="10">
+        <v>119341.57</v>
+      </c>
+      <c r="I461" s="4">
+        <v>925</v>
+      </c>
+      <c r="J461" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.3924797537019162E-2</v>
+      </c>
+      <c r="K461" s="11">
+        <v>0.31597222222222221</v>
+      </c>
+      <c r="L461" s="15">
+        <v>0.7680555555555556</v>
+      </c>
+      <c r="M461" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45208333333333339</v>
+      </c>
+      <c r="N461" s="4">
+        <v>14441</v>
+      </c>
+      <c r="O461" s="4">
+        <v>14507</v>
+      </c>
+      <c r="P461" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>66</v>
+      </c>
+      <c r="Q461" s="4">
+        <v>176</v>
+      </c>
+      <c r="R461" s="4">
+        <v>24</v>
+      </c>
+      <c r="S461" s="4">
+        <v>24</v>
+      </c>
+      <c r="T461" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U461" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V461" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W461" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X461" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y461" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="462" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A462" s="8">
+        <v>46297</v>
+      </c>
+      <c r="B462" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C462" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D462" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E462" s="4">
+        <v>1</v>
+      </c>
+      <c r="F462" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G462" s="10">
+        <v>1407.66</v>
+      </c>
+      <c r="H462" s="10">
+        <v>10652.29</v>
+      </c>
+      <c r="I462" s="4">
+        <v>37</v>
+      </c>
+      <c r="J462" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.13214623334513048</v>
+      </c>
+      <c r="K462" s="11">
+        <v>0.2951388888888889</v>
+      </c>
+      <c r="L462" s="15">
+        <v>0.62916666666666665</v>
+      </c>
+      <c r="M462" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.33402777777777776</v>
+      </c>
+      <c r="N462" s="4">
+        <v>156572</v>
+      </c>
+      <c r="O462" s="4">
+        <v>156632</v>
+      </c>
+      <c r="P462" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>60</v>
+      </c>
+      <c r="Q462" s="4">
+        <v>11</v>
+      </c>
+      <c r="R462" s="4">
+        <v>2</v>
+      </c>
+      <c r="S462" s="4">
+        <v>2</v>
+      </c>
+      <c r="T462" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U462" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V462" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W462" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X462" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y462" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A463" s="8">
+        <v>46297</v>
+      </c>
+      <c r="B463" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C463" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D463" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E463" s="4">
+        <v>3</v>
+      </c>
+      <c r="F463" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G463" s="10">
+        <v>4722.1000000000004</v>
+      </c>
+      <c r="H463" s="10">
+        <v>77528.509999999995</v>
+      </c>
+      <c r="I463" s="4">
+        <v>537</v>
+      </c>
+      <c r="J463" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.0907916326522989E-2</v>
+      </c>
+      <c r="K463" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L463" s="15">
+        <v>0.7319444444444444</v>
+      </c>
+      <c r="M463" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4194444444444444</v>
+      </c>
+      <c r="N463" s="4">
+        <v>305801</v>
+      </c>
+      <c r="O463" s="4">
+        <v>305858</v>
+      </c>
+      <c r="P463" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>57</v>
+      </c>
+      <c r="Q463" s="4">
+        <v>92</v>
+      </c>
+      <c r="R463" s="4">
+        <v>17</v>
+      </c>
+      <c r="S463" s="4">
+        <v>17</v>
+      </c>
+      <c r="T463" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U463" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V463" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W463" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X463" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y463" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A464" s="8">
+        <v>46297</v>
+      </c>
+      <c r="B464" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C464" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D464" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E464" s="4">
+        <v>1</v>
+      </c>
+      <c r="F464" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G464" s="10">
+        <v>8358.85</v>
+      </c>
+      <c r="H464" s="10">
+        <v>139999.38</v>
+      </c>
+      <c r="I464" s="4">
+        <v>1219</v>
+      </c>
+      <c r="J464" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.9706335842344443E-2</v>
+      </c>
+      <c r="K464" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L464" s="15">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="M464" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.40972222222222221</v>
+      </c>
+      <c r="N464" s="4">
+        <v>144077</v>
+      </c>
+      <c r="O464" s="4">
+        <v>144128</v>
+      </c>
+      <c r="P464" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>51</v>
+      </c>
+      <c r="Q464" s="4">
+        <v>142</v>
+      </c>
+      <c r="R464" s="4">
+        <v>17</v>
+      </c>
+      <c r="S464" s="4">
+        <v>17</v>
+      </c>
+      <c r="T464" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U464" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V464" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W464" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X464" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y464" s="5">
+        <v>38.380000000000003</v>
+      </c>
+    </row>
+    <row r="465" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A465" s="8">
+        <v>46297</v>
+      </c>
+      <c r="B465" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C465" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D465" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E465" s="4">
+        <v>11</v>
+      </c>
+      <c r="F465" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G465" s="10">
+        <v>9147.68</v>
+      </c>
+      <c r="H465" s="10">
+        <v>147663.99</v>
+      </c>
+      <c r="I465" s="4">
+        <v>1098</v>
+      </c>
+      <c r="J465" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.1949294475924704E-2</v>
+      </c>
+      <c r="K465" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L465" s="15">
+        <v>0.75694444444444442</v>
+      </c>
+      <c r="M465" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="N465" s="4">
+        <v>281617</v>
+      </c>
+      <c r="O465" s="4">
+        <v>281735</v>
+      </c>
+      <c r="P465" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>118</v>
+      </c>
+      <c r="Q465" s="4">
+        <v>178</v>
+      </c>
+      <c r="R465" s="4">
+        <v>31</v>
+      </c>
+      <c r="S465" s="4">
+        <v>31</v>
+      </c>
+      <c r="T465" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U465" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V465" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W465" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X465" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y465" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A466" s="8">
+        <v>46297</v>
+      </c>
+      <c r="B466" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C466" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D466" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E466" s="4">
+        <v>5</v>
+      </c>
+      <c r="F466" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G466" s="10">
+        <v>14684.14</v>
+      </c>
+      <c r="H466" s="10">
+        <v>277099.78000000003</v>
+      </c>
+      <c r="I466" s="4">
+        <v>2217</v>
+      </c>
+      <c r="J466" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.2992247052668168E-2</v>
+      </c>
+      <c r="K466" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L466" s="15">
+        <v>0.75</v>
+      </c>
+      <c r="M466" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="N466" s="4">
+        <v>106643</v>
+      </c>
+      <c r="O466" s="4">
+        <v>106674</v>
+      </c>
+      <c r="P466" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>31</v>
+      </c>
+      <c r="Q466" s="4">
+        <v>343</v>
+      </c>
+      <c r="R466" s="4">
+        <v>8</v>
+      </c>
+      <c r="S466" s="4">
+        <v>8</v>
+      </c>
+      <c r="T466" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U466" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V466" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W466" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X466" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y466" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A467" s="8">
+        <v>46300</v>
+      </c>
+      <c r="B467" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C467" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D467" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E467" s="4">
+        <v>1</v>
+      </c>
+      <c r="F467" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G467" s="10">
+        <v>2662.58</v>
+      </c>
+      <c r="H467" s="10">
+        <v>66312.78</v>
+      </c>
+      <c r="I467" s="4">
+        <v>527</v>
+      </c>
+      <c r="J467" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.0151838001664233E-2</v>
+      </c>
+      <c r="K467" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L467" s="15">
+        <v>0.4826388888888889</v>
+      </c>
+      <c r="M467" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.19097222222222221</v>
+      </c>
+      <c r="N467" s="4">
+        <v>292172</v>
+      </c>
+      <c r="O467" s="4">
+        <v>292204</v>
+      </c>
+      <c r="P467" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>32</v>
+      </c>
+      <c r="Q467" s="4">
+        <v>71</v>
+      </c>
+      <c r="R467" s="4">
+        <v>2</v>
+      </c>
+      <c r="S467" s="4">
+        <v>2</v>
+      </c>
+      <c r="T467" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U467" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V467" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W467" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X467" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y467" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A468" s="8">
+        <v>46300</v>
+      </c>
+      <c r="B468" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C468" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D468" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E468" s="4">
+        <v>5</v>
+      </c>
+      <c r="F468" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Heremilton</v>
+      </c>
+      <c r="G468" s="10">
+        <v>63334.46</v>
+      </c>
+      <c r="H468" s="10">
+        <v>996731.26</v>
+      </c>
+      <c r="I468" s="4">
+        <v>10926</v>
+      </c>
+      <c r="J468" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.3542162809261143E-2</v>
+      </c>
+      <c r="K468" s="11">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="L468" s="15">
+        <v>0.81041666666666667</v>
+      </c>
+      <c r="M468" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.53263888888888888</v>
+      </c>
+      <c r="N468" s="4">
+        <v>367835</v>
+      </c>
+      <c r="O468" s="4">
+        <v>367889</v>
+      </c>
+      <c r="P468" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>54</v>
+      </c>
+      <c r="Q468" s="4">
+        <v>1202</v>
+      </c>
+      <c r="R468" s="4">
+        <v>33</v>
+      </c>
+      <c r="S468" s="4">
+        <v>33</v>
+      </c>
+      <c r="T468" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U468" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V468" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W468" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X468" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y468" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A469" s="8">
+        <v>46300</v>
+      </c>
+      <c r="B469" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C469" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D469" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E469" s="4">
+        <v>3</v>
+      </c>
+      <c r="F469" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G469" s="10">
+        <v>10856.39</v>
+      </c>
+      <c r="H469" s="10">
+        <v>151158.64000000001</v>
+      </c>
+      <c r="I469" s="4">
+        <v>1531</v>
+      </c>
+      <c r="J469" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.1821167483380369E-2</v>
+      </c>
+      <c r="K469" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L469" s="15">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="M469" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="N469" s="4">
+        <v>126632</v>
+      </c>
+      <c r="O469" s="4">
+        <v>126676</v>
+      </c>
+      <c r="P469" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>44</v>
+      </c>
+      <c r="Q469" s="4">
+        <v>312</v>
+      </c>
+      <c r="R469" s="4">
+        <v>22</v>
+      </c>
+      <c r="S469" s="4">
+        <v>22</v>
+      </c>
+      <c r="T469" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U469" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V469" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W469" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X469" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y469" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A470" s="8">
+        <v>46300</v>
+      </c>
+      <c r="B470" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C470" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D470" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E470" s="4">
+        <v>1</v>
+      </c>
+      <c r="F470" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G470" s="10">
+        <v>1275.44</v>
+      </c>
+      <c r="H470" s="10">
+        <v>15864.18</v>
+      </c>
+      <c r="I470" s="4">
+        <v>137</v>
+      </c>
+      <c r="J470" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.0397474057909077E-2</v>
+      </c>
+      <c r="K470" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L470" s="15">
+        <v>0.6479166666666667</v>
+      </c>
+      <c r="M470" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.3354166666666667</v>
+      </c>
+      <c r="N470" s="4">
+        <v>156661</v>
+      </c>
+      <c r="O470" s="4">
+        <v>156691</v>
+      </c>
+      <c r="P470" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>30</v>
+      </c>
+      <c r="Q470" s="4">
+        <v>76</v>
+      </c>
+      <c r="R470" s="4">
+        <v>2</v>
+      </c>
+      <c r="S470" s="4">
+        <v>2</v>
+      </c>
+      <c r="T470" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U470" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V470" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W470" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X470" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y470" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A471" s="8">
+        <v>46300</v>
+      </c>
+      <c r="B471" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C471" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D471" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E471" s="4">
+        <v>2</v>
+      </c>
+      <c r="F471" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G471" s="10">
+        <v>12657.88</v>
+      </c>
+      <c r="H471" s="10">
+        <v>263127.61</v>
+      </c>
+      <c r="I471" s="4">
+        <v>245</v>
+      </c>
+      <c r="J471" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.8105480074857973E-2</v>
+      </c>
+      <c r="K471" s="11">
+        <v>0.27430555555555558</v>
+      </c>
+      <c r="L471" s="15">
+        <v>0.79236111111111107</v>
+      </c>
+      <c r="M471" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.51805555555555549</v>
+      </c>
+      <c r="N471" s="4">
+        <v>281766</v>
+      </c>
+      <c r="O471" s="4">
+        <v>281825</v>
+      </c>
+      <c r="P471" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>59</v>
+      </c>
+      <c r="Q471" s="4">
+        <v>245</v>
+      </c>
+      <c r="R471" s="4">
+        <v>48</v>
+      </c>
+      <c r="S471" s="4">
+        <v>47</v>
+      </c>
+      <c r="T471" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>1</v>
+      </c>
+      <c r="U471" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="V471" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W471" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X471" s="4">
+        <v>5</v>
+      </c>
+      <c r="Y471" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="472" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A472" s="8">
+        <v>46300</v>
+      </c>
+      <c r="B472" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C472" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D472" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E472" s="4">
+        <v>1</v>
+      </c>
+      <c r="F472" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G472" s="10">
+        <v>10169.49</v>
+      </c>
+      <c r="H472" s="10">
+        <v>123211.28</v>
+      </c>
+      <c r="I472" s="4">
+        <v>3496</v>
+      </c>
+      <c r="J472" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.2537004728787819E-2</v>
+      </c>
+      <c r="K472" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L472" s="15">
+        <v>0.44722222222222224</v>
+      </c>
+      <c r="M472" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.17638888888888893</v>
+      </c>
+      <c r="N472" s="4">
+        <v>106677</v>
+      </c>
+      <c r="O472" s="4">
+        <v>106699</v>
+      </c>
+      <c r="P472" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>22</v>
+      </c>
+      <c r="Q472" s="4">
+        <v>307</v>
+      </c>
+      <c r="R472" s="4">
+        <v>2</v>
+      </c>
+      <c r="S472" s="4">
+        <v>2</v>
+      </c>
+      <c r="T472" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U472" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V472" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W472" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X472" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y472" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A473" s="8">
+        <v>46300</v>
+      </c>
+      <c r="B473" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C473" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D473" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E473" s="4">
+        <v>1</v>
+      </c>
+      <c r="F473" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G473" s="10">
+        <v>9033.7900000000009</v>
+      </c>
+      <c r="H473" s="10">
+        <v>153227.56</v>
+      </c>
+      <c r="I473" s="4">
+        <v>1938</v>
+      </c>
+      <c r="J473" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.8956691602998844E-2</v>
+      </c>
+      <c r="K473" s="11">
+        <v>0.3263888888888889</v>
+      </c>
+      <c r="L473" s="15">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="M473" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.46527777777777773</v>
+      </c>
+      <c r="N473" s="4">
+        <v>14508</v>
+      </c>
+      <c r="O473" s="4">
+        <v>14572</v>
+      </c>
+      <c r="P473" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>64</v>
+      </c>
+      <c r="Q473" s="4">
+        <v>345</v>
+      </c>
+      <c r="R473" s="4">
+        <v>22</v>
+      </c>
+      <c r="S473" s="4">
+        <v>22</v>
+      </c>
+      <c r="T473" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U473" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V473" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W473" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X473" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y473" s="5">
+        <v>10.38</v>
+      </c>
+    </row>
+    <row r="474" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A474" s="8">
+        <v>46300</v>
+      </c>
+      <c r="B474" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C474" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D474" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E474" s="4">
+        <v>5</v>
+      </c>
+      <c r="F474" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G474" s="10">
+        <v>14452.93</v>
+      </c>
+      <c r="H474" s="10">
+        <v>116696.96000000001</v>
+      </c>
+      <c r="I474" s="4">
+        <v>2197</v>
+      </c>
+      <c r="J474" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.12385009858011725</v>
+      </c>
+      <c r="K474" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L474" s="15">
+        <v>0.76388888888888884</v>
+      </c>
+      <c r="M474" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47222222222222215</v>
+      </c>
+      <c r="N474" s="4">
+        <v>305860</v>
+      </c>
+      <c r="O474" s="4">
+        <v>305906</v>
+      </c>
+      <c r="P474" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>46</v>
+      </c>
+      <c r="Q474" s="4">
+        <v>504</v>
+      </c>
+      <c r="R474" s="4">
+        <v>16</v>
+      </c>
+      <c r="S474" s="4">
+        <v>16</v>
+      </c>
+      <c r="T474" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U474" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V474" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W474" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X474" s="4">
+        <v>4</v>
+      </c>
+      <c r="Y474" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="475" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A475" s="8">
+        <v>46300</v>
+      </c>
+      <c r="B475" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C475" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D475" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E475" s="4">
+        <v>5</v>
+      </c>
+      <c r="F475" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G475" s="10">
+        <v>7520.67</v>
+      </c>
+      <c r="H475" s="10">
+        <v>54089.18</v>
+      </c>
+      <c r="I475" s="4">
+        <v>2768</v>
+      </c>
+      <c r="J475" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.13904204131029532</v>
+      </c>
+      <c r="K475" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L475" s="15">
+        <v>0.77430555555555558</v>
+      </c>
+      <c r="M475" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4826388888888889</v>
+      </c>
+      <c r="N475" s="4">
+        <v>276566</v>
+      </c>
+      <c r="O475" s="4">
+        <v>276623</v>
+      </c>
+      <c r="P475" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>57</v>
+      </c>
+      <c r="Q475" s="4">
+        <v>267</v>
+      </c>
+      <c r="R475" s="4">
+        <v>5</v>
+      </c>
+      <c r="S475" s="4">
+        <v>5</v>
+      </c>
+      <c r="T475" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U475" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V475" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W475" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X475" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y475" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A476" s="8">
+        <v>46300</v>
+      </c>
+      <c r="B476" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C476" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D476" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E476" s="4">
+        <v>1</v>
+      </c>
+      <c r="F476" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G476" s="10">
+        <v>3823.44</v>
+      </c>
+      <c r="H476" s="10">
+        <v>69287.11</v>
+      </c>
+      <c r="I476" s="4">
+        <v>405</v>
+      </c>
+      <c r="J476" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.5182558487430054E-2</v>
+      </c>
+      <c r="K476" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L476" s="15">
+        <v>0.79861111111111116</v>
+      </c>
+      <c r="M476" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.48611111111111116</v>
+      </c>
+      <c r="N476" s="4">
+        <v>120715</v>
+      </c>
+      <c r="O476" s="4">
+        <v>120828</v>
+      </c>
+      <c r="P476" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>113</v>
+      </c>
+      <c r="Q476" s="4">
+        <v>115</v>
+      </c>
+      <c r="R476" s="4">
+        <v>16</v>
+      </c>
+      <c r="S476" s="4">
+        <v>16</v>
+      </c>
+      <c r="T476" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U476" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V476" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W476" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X476" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y476" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A477" s="8">
+        <v>46300</v>
+      </c>
+      <c r="B477" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C477" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D477" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E477" s="4">
+        <v>11</v>
+      </c>
+      <c r="F477" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G477" s="10">
+        <v>13461.47</v>
+      </c>
+      <c r="H477" s="10">
+        <v>199033</v>
+      </c>
+      <c r="I477" s="4">
+        <v>2989</v>
+      </c>
+      <c r="J477" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.7634362140951504E-2</v>
+      </c>
+      <c r="K477" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L477" s="15">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="M477" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="N477" s="4">
+        <v>144186</v>
+      </c>
+      <c r="O477" s="4">
+        <v>144311</v>
+      </c>
+      <c r="P477" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>125</v>
+      </c>
+      <c r="Q477" s="4">
+        <v>235</v>
+      </c>
+      <c r="R477" s="4">
+        <v>22</v>
+      </c>
+      <c r="S477" s="4">
+        <v>22</v>
+      </c>
+      <c r="T477" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U477" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V477" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W477" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X477" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y477" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A478" s="8">
+        <v>46300</v>
+      </c>
+      <c r="B478" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C478" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D478" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E478" s="4">
+        <v>4</v>
+      </c>
+      <c r="F478" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G478" s="10">
+        <v>2965.97</v>
+      </c>
+      <c r="H478" s="10">
+        <v>40516.230000000003</v>
+      </c>
+      <c r="I478" s="4">
+        <v>1109</v>
+      </c>
+      <c r="J478" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.3204491138489425E-2</v>
+      </c>
+      <c r="K478" s="11">
+        <v>0.56944444444444442</v>
+      </c>
+      <c r="L478" s="15">
+        <v>0.74652777777777779</v>
+      </c>
+      <c r="M478" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.17708333333333337</v>
+      </c>
+      <c r="N478" s="4">
+        <v>292204</v>
+      </c>
+      <c r="O478" s="4">
+        <v>292247</v>
+      </c>
+      <c r="P478" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>43</v>
+      </c>
+      <c r="Q478" s="4">
+        <v>202</v>
+      </c>
+      <c r="R478" s="4">
+        <v>5</v>
+      </c>
+      <c r="S478" s="4">
+        <v>5</v>
+      </c>
+      <c r="T478" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U478" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V478" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W478" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X478" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y478" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A479" s="8">
+        <v>46298</v>
+      </c>
+      <c r="B479" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C479" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D479" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E479" s="4">
+        <v>3</v>
+      </c>
+      <c r="F479" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G479" s="10">
+        <v>13116.14</v>
+      </c>
+      <c r="H479" s="10">
+        <v>179913.44</v>
+      </c>
+      <c r="I479" s="4">
+        <v>2596</v>
+      </c>
+      <c r="J479" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.2902502447843798E-2</v>
+      </c>
+      <c r="K479" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L479" s="15">
+        <v>0.51388888888888884</v>
+      </c>
+      <c r="M479" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.20138888888888884</v>
+      </c>
+      <c r="N479" s="4">
+        <v>144128</v>
+      </c>
+      <c r="O479" s="4">
+        <v>144168</v>
+      </c>
+      <c r="P479" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>40</v>
+      </c>
+      <c r="Q479" s="4">
+        <v>405</v>
+      </c>
+      <c r="R479" s="4">
+        <v>8</v>
+      </c>
+      <c r="S479" s="4">
+        <v>8</v>
+      </c>
+      <c r="T479" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U479" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V479" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W479" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X479" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y479" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J455">
-    <cfRule type="cellIs" dxfId="21" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="J2:J479">
+    <cfRule type="cellIs" dxfId="65" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="64" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U455">
-    <cfRule type="cellIs" dxfId="19" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="U2:U479">
+    <cfRule type="cellIs" dxfId="63" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="62" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="61" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="60" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="59" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="57" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V455">
-    <cfRule type="expression" dxfId="12" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="V2:V479">
+    <cfRule type="expression" dxfId="56" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -43364,7 +45354,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -43380,7 +45370,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D455</xm:sqref>
+          <xm:sqref>D2:D479</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8D03638-7582-4130-9CE7-F89F2C599F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E63C4DE-B2CB-4D03-AF2C-3A1AABAEA01D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="95">
   <si>
     <t>Data</t>
   </si>
@@ -531,7 +531,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -605,6 +605,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -614,7 +617,84 @@
     <cellStyle name="Normal 2 2 2" xfId="3" xr:uid="{F6D7429B-6BC2-41D1-B818-FB0128371036}"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="134">
+  <dxfs count="145">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -2129,94 +2209,94 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V23" totalsRowShown="0" headerRowDxfId="133" dataDxfId="131" headerRowBorderDxfId="132" tableBorderDxfId="130" totalsRowBorderDxfId="129" headerRowCellStyle="Normal 2 2 2">
-  <autoFilter ref="A1:V23" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V24" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
+  <autoFilter ref="A1:V24" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="128"/>
-    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="127"/>
-    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="126"/>
-    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="125"/>
-    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="124" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="123" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="122"/>
-    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="121" dataCellStyle="Porcentagem">
+    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="139"/>
+    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="138"/>
+    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="137"/>
+    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="136"/>
+    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="135" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="134" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="133"/>
+    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="132" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="120"/>
-    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="119"/>
-    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="118">
+    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="131"/>
+    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="130"/>
+    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="129">
       <calculatedColumnFormula>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="117" dataCellStyle="Moeda"/>
-    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="116" dataCellStyle="Porcentagem">
+    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="128" dataCellStyle="Moeda"/>
+    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="127" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="115"/>
-    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="114"/>
-    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="113"/>
-    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="112">
+    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="126"/>
+    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="125"/>
+    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="124"/>
+    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="123">
       <calculatedColumnFormula>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="111" dataCellStyle="Moeda 2 2">
+    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="122" dataCellStyle="Moeda 2 2">
       <calculatedColumnFormula>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="110" dataCellStyle="Moeda 3">
+    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="121" dataCellStyle="Moeda 3">
       <calculatedColumnFormula>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="109"/>
-    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="108"/>
-    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="107"/>
+    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="120"/>
+    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="119"/>
+    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="118"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y479" totalsRowShown="0" headerRowDxfId="106" dataDxfId="104" headerRowBorderDxfId="105" tableBorderDxfId="103" totalsRowBorderDxfId="102">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y489" totalsRowShown="0" headerRowDxfId="117" dataDxfId="115" headerRowBorderDxfId="116" tableBorderDxfId="114" totalsRowBorderDxfId="113">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="101"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="100">
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="112"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="111">
       <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="99">
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="110">
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="98"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="97"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="96">
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="109"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="108"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="107">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="95" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="94" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="93"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="92" dataCellStyle="Normal 2 2 2">
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="106" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="105" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="104"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="103" dataCellStyle="Normal 2 2 2">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="91"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="90"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="89">
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="102"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="101"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="100">
       <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="88"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="87"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="86">
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="99"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="98"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="97">
       <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="85"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="84"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="83"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="82">
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="96"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="95"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="94"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="93">
       <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="81" dataCellStyle="Moeda">
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="92" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="80">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="91">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="79"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="78"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="77"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="90"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="89"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="88"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2645,7 +2725,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A050DE7D-8F3F-47CF-9E37-B95AFD2ED76A}">
-  <dimension ref="A1:V23"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="23" bestFit="1" customWidth="1"/>
@@ -4047,40 +4127,94 @@
       <c r="U23" s="4"/>
       <c r="V23" s="5"/>
     </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A24" s="8">
+        <v>46301</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" s="27">
+        <v>6185.78</v>
+      </c>
+      <c r="F24" s="27">
+        <v>89820.800000000003</v>
+      </c>
+      <c r="G24" s="4"/>
+      <c r="H24" s="9">
+        <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
+        <v>6.8868012754284086E-2</v>
+      </c>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4">
+        <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
+        <v>0</v>
+      </c>
+      <c r="L24" s="10">
+        <v>500</v>
+      </c>
+      <c r="M24" s="9">
+        <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
+        <v>8.0830550068059323E-2</v>
+      </c>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="12">
+        <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="R24" s="13" t="e">
+        <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S24" s="14" t="e">
+        <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T24" s="4"/>
+      <c r="U24" s="4"/>
+      <c r="V24" s="5"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H23">
-    <cfRule type="cellIs" dxfId="76" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="H2:H24">
+    <cfRule type="cellIs" dxfId="87" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="86" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R23">
-    <cfRule type="cellIs" dxfId="74" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="R2:R24">
+    <cfRule type="cellIs" dxfId="85" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="84" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="83" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="82" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="81" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="80" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="79" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S23">
-    <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="S2:S24">
+    <cfRule type="expression" dxfId="78" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -4089,7 +4223,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4103,7 +4237,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y479"/>
+  <dimension ref="A1:Y489"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -43252,11 +43386,11 @@
       <c r="A456" s="8">
         <v>46297</v>
       </c>
-      <c r="B456" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C456" s="26">
+      <c r="B456" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C456" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -43338,11 +43472,11 @@
       <c r="A457" s="8">
         <v>46297</v>
       </c>
-      <c r="B457" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C457" s="26">
+      <c r="B457" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C457" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -43424,11 +43558,11 @@
       <c r="A458" s="8">
         <v>46297</v>
       </c>
-      <c r="B458" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C458" s="26">
+      <c r="B458" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C458" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -43510,11 +43644,11 @@
       <c r="A459" s="8">
         <v>46297</v>
       </c>
-      <c r="B459" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C459" s="26">
+      <c r="B459" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C459" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -43596,11 +43730,11 @@
       <c r="A460" s="8">
         <v>46297</v>
       </c>
-      <c r="B460" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C460" s="26">
+      <c r="B460" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C460" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -43682,11 +43816,11 @@
       <c r="A461" s="8">
         <v>46297</v>
       </c>
-      <c r="B461" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C461" s="26">
+      <c r="B461" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C461" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -43768,11 +43902,11 @@
       <c r="A462" s="8">
         <v>46297</v>
       </c>
-      <c r="B462" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C462" s="26">
+      <c r="B462" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C462" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -43854,11 +43988,11 @@
       <c r="A463" s="8">
         <v>46297</v>
       </c>
-      <c r="B463" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C463" s="26">
+      <c r="B463" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C463" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -43940,11 +44074,11 @@
       <c r="A464" s="8">
         <v>46297</v>
       </c>
-      <c r="B464" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C464" s="26">
+      <c r="B464" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C464" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -44026,11 +44160,11 @@
       <c r="A465" s="8">
         <v>46297</v>
       </c>
-      <c r="B465" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C465" s="26">
+      <c r="B465" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C465" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -44112,11 +44246,11 @@
       <c r="A466" s="8">
         <v>46297</v>
       </c>
-      <c r="B466" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C466" s="26">
+      <c r="B466" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C466" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -44198,11 +44332,11 @@
       <c r="A467" s="8">
         <v>46300</v>
       </c>
-      <c r="B467" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C467" s="26">
+      <c r="B467" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C467" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -44284,11 +44418,11 @@
       <c r="A468" s="8">
         <v>46300</v>
       </c>
-      <c r="B468" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C468" s="26">
+      <c r="B468" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C468" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -44370,11 +44504,11 @@
       <c r="A469" s="8">
         <v>46300</v>
       </c>
-      <c r="B469" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C469" s="26">
+      <c r="B469" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C469" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -44456,11 +44590,11 @@
       <c r="A470" s="8">
         <v>46300</v>
       </c>
-      <c r="B470" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C470" s="26">
+      <c r="B470" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C470" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -44542,11 +44676,11 @@
       <c r="A471" s="8">
         <v>46300</v>
       </c>
-      <c r="B471" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C471" s="26">
+      <c r="B471" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C471" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -44628,11 +44762,11 @@
       <c r="A472" s="8">
         <v>46300</v>
       </c>
-      <c r="B472" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C472" s="26">
+      <c r="B472" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C472" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -44714,11 +44848,11 @@
       <c r="A473" s="8">
         <v>46300</v>
       </c>
-      <c r="B473" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C473" s="26">
+      <c r="B473" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C473" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -44800,11 +44934,11 @@
       <c r="A474" s="8">
         <v>46300</v>
       </c>
-      <c r="B474" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C474" s="26">
+      <c r="B474" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C474" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -44886,11 +45020,11 @@
       <c r="A475" s="8">
         <v>46300</v>
       </c>
-      <c r="B475" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C475" s="26">
+      <c r="B475" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C475" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -44972,11 +45106,11 @@
       <c r="A476" s="8">
         <v>46300</v>
       </c>
-      <c r="B476" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C476" s="26">
+      <c r="B476" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C476" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -45058,11 +45192,11 @@
       <c r="A477" s="8">
         <v>46300</v>
       </c>
-      <c r="B477" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C477" s="26">
+      <c r="B477" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C477" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -45144,11 +45278,11 @@
       <c r="A478" s="8">
         <v>46300</v>
       </c>
-      <c r="B478" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C478" s="26">
+      <c r="B478" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C478" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -45230,11 +45364,11 @@
       <c r="A479" s="8">
         <v>46298</v>
       </c>
-      <c r="B479" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C479" s="26">
+      <c r="B479" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C479" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -45312,40 +45446,900 @@
         <v>0</v>
       </c>
     </row>
+    <row r="480" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A480" s="8">
+        <v>46301</v>
+      </c>
+      <c r="B480" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C480" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D480" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E480" s="4">
+        <v>1</v>
+      </c>
+      <c r="F480" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G480" s="10">
+        <v>1829.66</v>
+      </c>
+      <c r="H480" s="10">
+        <v>25503.46</v>
+      </c>
+      <c r="I480" s="4">
+        <v>118.5</v>
+      </c>
+      <c r="J480" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.1741638193405927E-2</v>
+      </c>
+      <c r="K480" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L480" s="15">
+        <v>0.56944444444444442</v>
+      </c>
+      <c r="M480" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.27777777777777773</v>
+      </c>
+      <c r="N480" s="4">
+        <v>292247</v>
+      </c>
+      <c r="O480" s="4">
+        <v>292290</v>
+      </c>
+      <c r="P480" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>43</v>
+      </c>
+      <c r="Q480" s="4">
+        <v>51</v>
+      </c>
+      <c r="R480" s="4">
+        <v>2</v>
+      </c>
+      <c r="S480" s="4">
+        <v>2</v>
+      </c>
+      <c r="T480" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U480" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V480" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W480" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X480" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y480" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A481" s="8">
+        <v>46301</v>
+      </c>
+      <c r="B481" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C481" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D481" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E481" s="4">
+        <v>4</v>
+      </c>
+      <c r="F481" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G481" s="10">
+        <v>1270.51</v>
+      </c>
+      <c r="H481" s="10">
+        <v>33344.06</v>
+      </c>
+      <c r="I481" s="4">
+        <v>59</v>
+      </c>
+      <c r="J481" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.8103038442229294E-2</v>
+      </c>
+      <c r="K481" s="11">
+        <v>0.61458333333333337</v>
+      </c>
+      <c r="L481" s="15">
+        <v>0.78472222222222221</v>
+      </c>
+      <c r="M481" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.17013888888888884</v>
+      </c>
+      <c r="N481" s="4">
+        <v>292290</v>
+      </c>
+      <c r="O481" s="4">
+        <v>292343</v>
+      </c>
+      <c r="P481" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>53</v>
+      </c>
+      <c r="Q481" s="4">
+        <v>24</v>
+      </c>
+      <c r="R481" s="4">
+        <v>6</v>
+      </c>
+      <c r="S481" s="4">
+        <v>6</v>
+      </c>
+      <c r="T481" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U481" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V481" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W481" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X481" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y481" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A482" s="8">
+        <v>46301</v>
+      </c>
+      <c r="B482" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C482" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D482" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E482" s="4">
+        <v>11</v>
+      </c>
+      <c r="F482" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G482" s="10">
+        <v>16301.71</v>
+      </c>
+      <c r="H482" s="10">
+        <v>206976.8</v>
+      </c>
+      <c r="I482" s="4">
+        <v>3472</v>
+      </c>
+      <c r="J482" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.8761049547582146E-2</v>
+      </c>
+      <c r="K482" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L482" s="15">
+        <v>0.75</v>
+      </c>
+      <c r="M482" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="N482" s="4">
+        <v>144311</v>
+      </c>
+      <c r="O482" s="4">
+        <v>144455</v>
+      </c>
+      <c r="P482" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>144</v>
+      </c>
+      <c r="Q482" s="4">
+        <v>248</v>
+      </c>
+      <c r="R482" s="4">
+        <v>31</v>
+      </c>
+      <c r="S482" s="4">
+        <v>31</v>
+      </c>
+      <c r="T482" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U482" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V482" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W482" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X482" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y482" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="483" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A483" s="8">
+        <v>46301</v>
+      </c>
+      <c r="B483" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C483" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D483" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E483" s="4">
+        <v>5</v>
+      </c>
+      <c r="F483" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G483" s="10">
+        <v>10450.99</v>
+      </c>
+      <c r="H483" s="10">
+        <v>122185.55</v>
+      </c>
+      <c r="I483" s="4">
+        <v>1863</v>
+      </c>
+      <c r="J483" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.5533764017103497E-2</v>
+      </c>
+      <c r="K483" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L483" s="15">
+        <v>0.75416666666666665</v>
+      </c>
+      <c r="M483" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44166666666666665</v>
+      </c>
+      <c r="N483" s="4">
+        <v>305906</v>
+      </c>
+      <c r="O483" s="4">
+        <v>305983</v>
+      </c>
+      <c r="P483" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>77</v>
+      </c>
+      <c r="Q483" s="4">
+        <v>300</v>
+      </c>
+      <c r="R483" s="4">
+        <v>25</v>
+      </c>
+      <c r="S483" s="4">
+        <v>25</v>
+      </c>
+      <c r="T483" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U483" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V483" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W483" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X483" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y483" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A484" s="8">
+        <v>46301</v>
+      </c>
+      <c r="B484" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C484" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D484" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E484" s="4">
+        <v>3</v>
+      </c>
+      <c r="F484" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G484" s="10">
+        <v>14818.4</v>
+      </c>
+      <c r="H484" s="10">
+        <v>270443.61</v>
+      </c>
+      <c r="I484" s="4">
+        <v>3409</v>
+      </c>
+      <c r="J484" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.4792938165556956E-2</v>
+      </c>
+      <c r="K484" s="11">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="L484" s="15">
+        <v>0.78125</v>
+      </c>
+      <c r="M484" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4826388888888889</v>
+      </c>
+      <c r="N484" s="4">
+        <v>126676</v>
+      </c>
+      <c r="O484" s="4">
+        <v>126743</v>
+      </c>
+      <c r="P484" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>67</v>
+      </c>
+      <c r="Q484" s="4">
+        <v>383</v>
+      </c>
+      <c r="R484" s="4">
+        <v>23</v>
+      </c>
+      <c r="S484" s="4">
+        <v>23</v>
+      </c>
+      <c r="T484" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U484" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V484" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W484" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X484" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y484" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A485" s="8">
+        <v>46301</v>
+      </c>
+      <c r="B485" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C485" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D485" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E485" s="4">
+        <v>2</v>
+      </c>
+      <c r="F485" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G485" s="10">
+        <v>14479.26</v>
+      </c>
+      <c r="H485" s="10">
+        <v>262607.09999999998</v>
+      </c>
+      <c r="I485" s="4">
+        <v>2642</v>
+      </c>
+      <c r="J485" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.513658998557161E-2</v>
+      </c>
+      <c r="K485" s="11">
+        <v>0.27430555555555558</v>
+      </c>
+      <c r="L485" s="15">
+        <v>0.82638888888888884</v>
+      </c>
+      <c r="M485" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.55208333333333326</v>
+      </c>
+      <c r="N485" s="4">
+        <v>281825</v>
+      </c>
+      <c r="O485" s="4">
+        <v>281896</v>
+      </c>
+      <c r="P485" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>71</v>
+      </c>
+      <c r="Q485" s="4">
+        <v>336</v>
+      </c>
+      <c r="R485" s="4">
+        <v>39</v>
+      </c>
+      <c r="S485" s="4">
+        <v>39</v>
+      </c>
+      <c r="T485" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U485" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V485" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W485" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X485" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y485" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A486" s="8">
+        <v>46301</v>
+      </c>
+      <c r="B486" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C486" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D486" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E486" s="4">
+        <v>1</v>
+      </c>
+      <c r="F486" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G486" s="10">
+        <v>8860.61</v>
+      </c>
+      <c r="H486" s="10">
+        <v>175974.15</v>
+      </c>
+      <c r="I486" s="4">
+        <v>1387</v>
+      </c>
+      <c r="J486" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.0351770416279897E-2</v>
+      </c>
+      <c r="K486" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L486" s="15">
+        <v>0.82152777777777775</v>
+      </c>
+      <c r="M486" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.50902777777777775</v>
+      </c>
+      <c r="N486" s="4">
+        <v>276623</v>
+      </c>
+      <c r="O486" s="4">
+        <v>276772</v>
+      </c>
+      <c r="P486" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>149</v>
+      </c>
+      <c r="Q486" s="4">
+        <v>197</v>
+      </c>
+      <c r="R486" s="4">
+        <v>26</v>
+      </c>
+      <c r="S486" s="4">
+        <v>24</v>
+      </c>
+      <c r="T486" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>2</v>
+      </c>
+      <c r="U486" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="V486" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W486" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="X486" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y486" s="5">
+        <v>13.13</v>
+      </c>
+    </row>
+    <row r="487" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A487" s="8">
+        <v>46301</v>
+      </c>
+      <c r="B487" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C487" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D487" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E487" s="4">
+        <v>3</v>
+      </c>
+      <c r="F487" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G487" s="10">
+        <v>14066.85</v>
+      </c>
+      <c r="H487" s="10">
+        <v>62486.95</v>
+      </c>
+      <c r="I487" s="4">
+        <v>6328</v>
+      </c>
+      <c r="J487" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.22511660434698766</v>
+      </c>
+      <c r="K487" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L487" s="15">
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="M487" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.38750000000000001</v>
+      </c>
+      <c r="N487" s="4">
+        <v>106700</v>
+      </c>
+      <c r="O487" s="4">
+        <v>106739</v>
+      </c>
+      <c r="P487" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>39</v>
+      </c>
+      <c r="Q487" s="4">
+        <v>410</v>
+      </c>
+      <c r="R487" s="4">
+        <v>1</v>
+      </c>
+      <c r="S487" s="4">
+        <v>1</v>
+      </c>
+      <c r="T487" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U487" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V487" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W487" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X487" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y487" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A488" s="8">
+        <v>46301</v>
+      </c>
+      <c r="B488" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C488" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D488" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E488" s="4">
+        <v>5</v>
+      </c>
+      <c r="F488" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G488" s="10">
+        <v>855.67</v>
+      </c>
+      <c r="H488" s="10">
+        <v>17364.759999999998</v>
+      </c>
+      <c r="I488" s="4">
+        <v>59</v>
+      </c>
+      <c r="J488" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.9276235317965815E-2</v>
+      </c>
+      <c r="K488" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L488" s="15">
+        <v>0.71180555555555558</v>
+      </c>
+      <c r="M488" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4201388888888889</v>
+      </c>
+      <c r="N488" s="4">
+        <v>156692</v>
+      </c>
+      <c r="O488" s="4">
+        <v>156744</v>
+      </c>
+      <c r="P488" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>52</v>
+      </c>
+      <c r="Q488" s="4">
+        <v>45</v>
+      </c>
+      <c r="R488" s="4">
+        <v>2</v>
+      </c>
+      <c r="S488" s="4">
+        <v>2</v>
+      </c>
+      <c r="T488" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U488" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V488" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W488" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X488" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y488" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A489" s="8">
+        <v>46301</v>
+      </c>
+      <c r="B489" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C489" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D489" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E489" s="4">
+        <v>1</v>
+      </c>
+      <c r="F489" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G489" s="10">
+        <v>4094.02</v>
+      </c>
+      <c r="H489" s="10">
+        <v>45709.9</v>
+      </c>
+      <c r="I489" s="4">
+        <v>797</v>
+      </c>
+      <c r="J489" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.9565280169066216E-2</v>
+      </c>
+      <c r="K489" s="11">
+        <v>0.2986111111111111</v>
+      </c>
+      <c r="L489" s="15">
+        <v>0.67291666666666672</v>
+      </c>
+      <c r="M489" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.37430555555555561</v>
+      </c>
+      <c r="N489" s="4">
+        <v>14572</v>
+      </c>
+      <c r="O489" s="4">
+        <v>14610</v>
+      </c>
+      <c r="P489" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>38</v>
+      </c>
+      <c r="Q489" s="4">
+        <v>116</v>
+      </c>
+      <c r="R489" s="4">
+        <v>9</v>
+      </c>
+      <c r="S489" s="4">
+        <v>9</v>
+      </c>
+      <c r="T489" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U489" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V489" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W489" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X489" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y489" s="5">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J479">
-    <cfRule type="cellIs" dxfId="65" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="J2:J489">
+    <cfRule type="cellIs" dxfId="76" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="75" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U479">
-    <cfRule type="cellIs" dxfId="63" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="U2:U489">
+    <cfRule type="cellIs" dxfId="74" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="73" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="72" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="71" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="70" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="69" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="68" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V479">
-    <cfRule type="expression" dxfId="56" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="V2:V489">
+    <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -45354,7 +46348,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -45370,7 +46364,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D479</xm:sqref>
+          <xm:sqref>D2:D489</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E63C4DE-B2CB-4D03-AF2C-3A1AABAEA01D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C58B2E-82B2-41F2-9821-83BF54A29B20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1162" uniqueCount="95">
   <si>
     <t>Data</t>
   </si>
@@ -2209,8 +2209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V24" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
-  <autoFilter ref="A1:V24" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V25" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
+  <autoFilter ref="A1:V25" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="139"/>
     <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="138"/>
@@ -2252,7 +2252,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y489" totalsRowShown="0" headerRowDxfId="117" dataDxfId="115" headerRowBorderDxfId="116" tableBorderDxfId="114" totalsRowBorderDxfId="113">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y501" totalsRowShown="0" headerRowDxfId="117" dataDxfId="115" headerRowBorderDxfId="116" tableBorderDxfId="114" totalsRowBorderDxfId="113">
   <tableColumns count="25">
     <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="112"/>
     <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="111">
@@ -2725,7 +2725,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A050DE7D-8F3F-47CF-9E37-B95AFD2ED76A}">
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:V25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="23" bestFit="1" customWidth="1"/>
@@ -4138,10 +4138,10 @@
       <c r="D24" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="10">
         <v>6185.78</v>
       </c>
-      <c r="F24" s="27">
+      <c r="F24" s="10">
         <v>89820.800000000003</v>
       </c>
       <c r="G24" s="4"/>
@@ -4181,8 +4181,70 @@
       <c r="U24" s="4"/>
       <c r="V24" s="5"/>
     </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A25" s="8">
+        <v>46302</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" s="27">
+        <v>8104.3</v>
+      </c>
+      <c r="F25" s="27">
+        <v>95783.11</v>
+      </c>
+      <c r="G25" s="4"/>
+      <c r="H25" s="9">
+        <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
+        <v>8.4610950719808536E-2</v>
+      </c>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4">
+        <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
+        <v>0</v>
+      </c>
+      <c r="L25" s="10">
+        <v>500</v>
+      </c>
+      <c r="M25" s="9">
+        <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
+        <v>6.1695643053687549E-2</v>
+      </c>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4">
+        <v>16</v>
+      </c>
+      <c r="P25" s="4">
+        <v>16</v>
+      </c>
+      <c r="Q25" s="12">
+        <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="R25" s="13">
+        <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="S25" s="14" t="str">
+        <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="T25" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="U25" s="4">
+        <v>38</v>
+      </c>
+      <c r="V25" s="5"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H24">
+  <conditionalFormatting sqref="H2:H25">
     <cfRule type="cellIs" dxfId="87" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
@@ -4190,7 +4252,7 @@
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R24">
+  <conditionalFormatting sqref="R2:R25">
     <cfRule type="cellIs" dxfId="85" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
@@ -4213,7 +4275,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S24">
+  <conditionalFormatting sqref="S2:S25">
     <cfRule type="expression" dxfId="78" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
@@ -4237,7 +4299,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y489"/>
+  <dimension ref="A1:Y501"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -45450,11 +45512,11 @@
       <c r="A480" s="8">
         <v>46301</v>
       </c>
-      <c r="B480" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C480" s="26">
+      <c r="B480" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C480" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -45536,11 +45598,11 @@
       <c r="A481" s="8">
         <v>46301</v>
       </c>
-      <c r="B481" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C481" s="26">
+      <c r="B481" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C481" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -45622,11 +45684,11 @@
       <c r="A482" s="8">
         <v>46301</v>
       </c>
-      <c r="B482" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C482" s="26">
+      <c r="B482" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C482" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -45708,11 +45770,11 @@
       <c r="A483" s="8">
         <v>46301</v>
       </c>
-      <c r="B483" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C483" s="26">
+      <c r="B483" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C483" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -45794,11 +45856,11 @@
       <c r="A484" s="8">
         <v>46301</v>
       </c>
-      <c r="B484" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C484" s="26">
+      <c r="B484" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C484" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -45880,11 +45942,11 @@
       <c r="A485" s="8">
         <v>46301</v>
       </c>
-      <c r="B485" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C485" s="26">
+      <c r="B485" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C485" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -45966,11 +46028,11 @@
       <c r="A486" s="8">
         <v>46301</v>
       </c>
-      <c r="B486" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C486" s="26">
+      <c r="B486" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C486" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -46052,11 +46114,11 @@
       <c r="A487" s="8">
         <v>46301</v>
       </c>
-      <c r="B487" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C487" s="26">
+      <c r="B487" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C487" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -46138,11 +46200,11 @@
       <c r="A488" s="8">
         <v>46301</v>
       </c>
-      <c r="B488" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C488" s="26">
+      <c r="B488" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C488" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -46224,11 +46286,11 @@
       <c r="A489" s="8">
         <v>46301</v>
       </c>
-      <c r="B489" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C489" s="26">
+      <c r="B489" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C489" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -46306,8 +46368,1040 @@
         <v>38</v>
       </c>
     </row>
+    <row r="490" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A490" s="8">
+        <v>46302</v>
+      </c>
+      <c r="B490" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C490" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D490" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E490" s="4">
+        <v>1</v>
+      </c>
+      <c r="F490" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G490" s="10">
+        <v>2365.94</v>
+      </c>
+      <c r="H490" s="10">
+        <v>79712.88</v>
+      </c>
+      <c r="I490" s="4">
+        <v>147</v>
+      </c>
+      <c r="J490" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.9680774298958962E-2</v>
+      </c>
+      <c r="K490" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L490" s="15">
+        <v>0.46319444444444446</v>
+      </c>
+      <c r="M490" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.15069444444444446</v>
+      </c>
+      <c r="N490" s="4">
+        <v>156744</v>
+      </c>
+      <c r="O490" s="4">
+        <v>156775</v>
+      </c>
+      <c r="P490" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>31</v>
+      </c>
+      <c r="Q490" s="4">
+        <v>79</v>
+      </c>
+      <c r="R490" s="4">
+        <v>4</v>
+      </c>
+      <c r="S490" s="4">
+        <v>4</v>
+      </c>
+      <c r="T490" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U490" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V490" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W490" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X490" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y490" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A491" s="8">
+        <v>46302</v>
+      </c>
+      <c r="B491" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C491" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D491" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E491" s="4">
+        <v>1</v>
+      </c>
+      <c r="F491" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Manoel</v>
+      </c>
+      <c r="G491" s="10">
+        <v>167.72</v>
+      </c>
+      <c r="H491" s="10">
+        <v>7965.96</v>
+      </c>
+      <c r="I491" s="4">
+        <v>3</v>
+      </c>
+      <c r="J491" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.1054587268828865E-2</v>
+      </c>
+      <c r="K491" s="11">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L491" s="15">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="M491" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>2.083333333333337E-2</v>
+      </c>
+      <c r="N491" s="4">
+        <v>13146</v>
+      </c>
+      <c r="O491" s="4">
+        <v>13147</v>
+      </c>
+      <c r="P491" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>1</v>
+      </c>
+      <c r="Q491" s="4">
+        <v>5</v>
+      </c>
+      <c r="R491" s="4">
+        <v>1</v>
+      </c>
+      <c r="S491" s="4">
+        <v>1</v>
+      </c>
+      <c r="T491" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U491" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V491" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W491" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X491" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y491" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A492" s="8">
+        <v>46302</v>
+      </c>
+      <c r="B492" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C492" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D492" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E492" s="4">
+        <v>1</v>
+      </c>
+      <c r="F492" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G492" s="10">
+        <v>3470.09</v>
+      </c>
+      <c r="H492" s="10">
+        <v>47314.8</v>
+      </c>
+      <c r="I492" s="4">
+        <v>709</v>
+      </c>
+      <c r="J492" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.3340476975491814E-2</v>
+      </c>
+      <c r="K492" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L492" s="15">
+        <v>0.49305555555555558</v>
+      </c>
+      <c r="M492" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.2013888888888889</v>
+      </c>
+      <c r="N492" s="4">
+        <v>292243</v>
+      </c>
+      <c r="O492" s="4">
+        <v>292286</v>
+      </c>
+      <c r="P492" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>43</v>
+      </c>
+      <c r="Q492" s="4">
+        <v>1</v>
+      </c>
+      <c r="R492" s="4">
+        <v>1</v>
+      </c>
+      <c r="S492" s="4">
+        <v>1</v>
+      </c>
+      <c r="T492" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U492" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V492" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W492" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X492" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y492" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A493" s="8">
+        <v>46302</v>
+      </c>
+      <c r="B493" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C493" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D493" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E493" s="4">
+        <v>11</v>
+      </c>
+      <c r="F493" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G493" s="10">
+        <v>10067.5</v>
+      </c>
+      <c r="H493" s="10">
+        <v>190558.92</v>
+      </c>
+      <c r="I493" s="4">
+        <v>1778</v>
+      </c>
+      <c r="J493" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.2831428725561624E-2</v>
+      </c>
+      <c r="K493" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L493" s="15">
+        <v>0.7270833333333333</v>
+      </c>
+      <c r="M493" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45624999999999999</v>
+      </c>
+      <c r="N493" s="4">
+        <v>106739</v>
+      </c>
+      <c r="O493" s="4">
+        <v>106901</v>
+      </c>
+      <c r="P493" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>162</v>
+      </c>
+      <c r="Q493" s="4">
+        <v>365</v>
+      </c>
+      <c r="R493" s="4">
+        <v>21</v>
+      </c>
+      <c r="S493" s="4">
+        <v>21</v>
+      </c>
+      <c r="T493" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U493" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V493" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W493" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X493" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y493" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="494" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A494" s="8">
+        <v>46302</v>
+      </c>
+      <c r="B494" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C494" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D494" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E494" s="4">
+        <v>5</v>
+      </c>
+      <c r="F494" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G494" s="10">
+        <v>6011.95</v>
+      </c>
+      <c r="H494" s="10">
+        <v>83304.95</v>
+      </c>
+      <c r="I494" s="4">
+        <v>1129</v>
+      </c>
+      <c r="J494" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.2167980414129057E-2</v>
+      </c>
+      <c r="K494" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L494" s="15">
+        <v>0.77430555555555558</v>
+      </c>
+      <c r="M494" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.46180555555555558</v>
+      </c>
+      <c r="N494" s="4">
+        <v>305983</v>
+      </c>
+      <c r="O494" s="4">
+        <v>306071</v>
+      </c>
+      <c r="P494" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>88</v>
+      </c>
+      <c r="Q494" s="4">
+        <v>122</v>
+      </c>
+      <c r="R494" s="4">
+        <v>24</v>
+      </c>
+      <c r="S494" s="4">
+        <v>24</v>
+      </c>
+      <c r="T494" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U494" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V494" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W494" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X494" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y494" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="495" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A495" s="8">
+        <v>46302</v>
+      </c>
+      <c r="B495" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C495" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D495" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E495" s="4">
+        <v>3</v>
+      </c>
+      <c r="F495" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G495" s="10">
+        <v>10067.5</v>
+      </c>
+      <c r="H495" s="10">
+        <v>190558.92</v>
+      </c>
+      <c r="I495" s="4">
+        <v>1778</v>
+      </c>
+      <c r="J495" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.2831428725561624E-2</v>
+      </c>
+      <c r="K495" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L495" s="15">
+        <v>0.80763888888888891</v>
+      </c>
+      <c r="M495" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.51597222222222228</v>
+      </c>
+      <c r="N495" s="4">
+        <v>126743</v>
+      </c>
+      <c r="O495" s="4">
+        <v>126810</v>
+      </c>
+      <c r="P495" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>67</v>
+      </c>
+      <c r="Q495" s="4">
+        <v>365</v>
+      </c>
+      <c r="R495" s="4">
+        <v>21</v>
+      </c>
+      <c r="S495" s="4">
+        <v>21</v>
+      </c>
+      <c r="T495" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U495" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V495" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W495" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X495" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y495" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A496" s="8">
+        <v>46302</v>
+      </c>
+      <c r="B496" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C496" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D496" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E496" s="4">
+        <v>1</v>
+      </c>
+      <c r="F496" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G496" s="10">
+        <v>729.95</v>
+      </c>
+      <c r="H496" s="10">
+        <v>10884.6</v>
+      </c>
+      <c r="I496" s="4">
+        <v>132</v>
+      </c>
+      <c r="J496" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.7062638957793588E-2</v>
+      </c>
+      <c r="K496" s="11">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="L496" s="15">
+        <v>0.75</v>
+      </c>
+      <c r="M496" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.14583333333333337</v>
+      </c>
+      <c r="N496" s="4">
+        <v>292386</v>
+      </c>
+      <c r="O496" s="4">
+        <v>292433</v>
+      </c>
+      <c r="P496" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>47</v>
+      </c>
+      <c r="Q496" s="4">
+        <v>29</v>
+      </c>
+      <c r="R496" s="4">
+        <v>4</v>
+      </c>
+      <c r="S496" s="4">
+        <v>4</v>
+      </c>
+      <c r="T496" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U496" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V496" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W496" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X496" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y496" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A497" s="8">
+        <v>46302</v>
+      </c>
+      <c r="B497" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C497" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D497" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E497" s="4">
+        <v>1</v>
+      </c>
+      <c r="F497" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G497" s="10">
+        <v>10417.92</v>
+      </c>
+      <c r="H497" s="10">
+        <v>311725.05</v>
+      </c>
+      <c r="I497" s="4">
+        <v>2131</v>
+      </c>
+      <c r="J497" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.3420220800349537E-2</v>
+      </c>
+      <c r="K497" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L497" s="15">
+        <v>0.74375000000000002</v>
+      </c>
+      <c r="M497" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45208333333333334</v>
+      </c>
+      <c r="N497" s="4">
+        <v>276772</v>
+      </c>
+      <c r="O497" s="4">
+        <v>276802</v>
+      </c>
+      <c r="P497" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>30</v>
+      </c>
+      <c r="Q497" s="4">
+        <v>4</v>
+      </c>
+      <c r="R497" s="4">
+        <v>2</v>
+      </c>
+      <c r="S497" s="4">
+        <v>2</v>
+      </c>
+      <c r="T497" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U497" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V497" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W497" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X497" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y497" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A498" s="8">
+        <v>46302</v>
+      </c>
+      <c r="B498" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C498" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D498" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E498" s="4">
+        <v>2</v>
+      </c>
+      <c r="F498" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G498" s="10">
+        <v>12598.62</v>
+      </c>
+      <c r="H498" s="10">
+        <v>233879.14</v>
+      </c>
+      <c r="I498" s="4">
+        <v>2926</v>
+      </c>
+      <c r="J498" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.386807904287659E-2</v>
+      </c>
+      <c r="K498" s="11">
+        <v>0.27430555555555558</v>
+      </c>
+      <c r="L498" s="15">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="M498" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.52777777777777779</v>
+      </c>
+      <c r="N498" s="4">
+        <v>281896</v>
+      </c>
+      <c r="O498" s="4">
+        <v>281963</v>
+      </c>
+      <c r="P498" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>67</v>
+      </c>
+      <c r="Q498" s="4">
+        <v>312</v>
+      </c>
+      <c r="R498" s="4">
+        <v>42</v>
+      </c>
+      <c r="S498" s="4">
+        <v>42</v>
+      </c>
+      <c r="T498" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U498" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V498" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W498" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X498" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y498" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="499" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A499" s="8">
+        <v>46302</v>
+      </c>
+      <c r="B499" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C499" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D499" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E499" s="4">
+        <v>1</v>
+      </c>
+      <c r="F499" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G499" s="10">
+        <v>8325.74</v>
+      </c>
+      <c r="H499" s="10">
+        <v>207414.54</v>
+      </c>
+      <c r="I499" s="4">
+        <v>3398</v>
+      </c>
+      <c r="J499" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.0140580308400751E-2</v>
+      </c>
+      <c r="K499" s="11">
+        <v>0.5625</v>
+      </c>
+      <c r="L499" s="15">
+        <v>0.84236111111111112</v>
+      </c>
+      <c r="M499" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.27986111111111112</v>
+      </c>
+      <c r="N499" s="4">
+        <v>14610</v>
+      </c>
+      <c r="O499" s="4">
+        <v>14721</v>
+      </c>
+      <c r="P499" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>111</v>
+      </c>
+      <c r="Q499" s="4">
+        <v>730</v>
+      </c>
+      <c r="R499" s="4">
+        <v>17</v>
+      </c>
+      <c r="S499" s="4">
+        <v>17</v>
+      </c>
+      <c r="T499" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U499" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V499" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W499" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X499" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y499" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="500" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A500" s="8">
+        <v>46302</v>
+      </c>
+      <c r="B500" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C500" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D500" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E500" s="4">
+        <v>1</v>
+      </c>
+      <c r="F500" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G500" s="10">
+        <v>2147.7199999999998</v>
+      </c>
+      <c r="H500" s="10">
+        <v>35039.72</v>
+      </c>
+      <c r="I500" s="4">
+        <v>369</v>
+      </c>
+      <c r="J500" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.129386878662272E-2</v>
+      </c>
+      <c r="K500" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L500" s="15">
+        <v>0.71250000000000002</v>
+      </c>
+      <c r="M500" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4</v>
+      </c>
+      <c r="N500" s="4">
+        <v>144455</v>
+      </c>
+      <c r="O500" s="4">
+        <v>144536</v>
+      </c>
+      <c r="P500" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>81</v>
+      </c>
+      <c r="Q500" s="4">
+        <v>92</v>
+      </c>
+      <c r="R500" s="4">
+        <v>9</v>
+      </c>
+      <c r="S500" s="4">
+        <v>9</v>
+      </c>
+      <c r="T500" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U500" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V500" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W500" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X500" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y500" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="501" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A501" s="8">
+        <v>46302</v>
+      </c>
+      <c r="B501" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C501" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D501" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E501" s="4">
+        <v>3</v>
+      </c>
+      <c r="F501" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G501" s="10">
+        <v>2201.44</v>
+      </c>
+      <c r="H501" s="10">
+        <v>44417.4</v>
+      </c>
+      <c r="I501" s="4">
+        <v>373</v>
+      </c>
+      <c r="J501" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.9562558817040171E-2</v>
+      </c>
+      <c r="K501" s="11">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="L501" s="15">
+        <v>0.71319444444444446</v>
+      </c>
+      <c r="M501" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.23402777777777778</v>
+      </c>
+      <c r="N501" s="4">
+        <v>156775</v>
+      </c>
+      <c r="O501" s="4">
+        <v>156830</v>
+      </c>
+      <c r="P501" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>55</v>
+      </c>
+      <c r="Q501" s="4">
+        <v>54</v>
+      </c>
+      <c r="R501" s="4">
+        <v>14</v>
+      </c>
+      <c r="S501" s="4">
+        <v>14</v>
+      </c>
+      <c r="T501" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U501" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V501" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W501" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X501" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y501" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J489">
+  <conditionalFormatting sqref="J2:J501">
     <cfRule type="cellIs" dxfId="76" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
@@ -46315,7 +47409,7 @@
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U489">
+  <conditionalFormatting sqref="U2:U501">
     <cfRule type="cellIs" dxfId="74" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
@@ -46338,7 +47432,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V489">
+  <conditionalFormatting sqref="V2:V501">
     <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
@@ -46364,7 +47458,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D489</xm:sqref>
+          <xm:sqref>D2:D501</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C58B2E-82B2-41F2-9821-83BF54A29B20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E49996-0B86-45DC-8BCD-398796546988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1162" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="96">
   <si>
     <t>Data</t>
   </si>
@@ -328,6 +328,9 @@
   </si>
   <si>
     <t>9,9,9,9,38</t>
+  </si>
+  <si>
+    <t>9,9,13,13</t>
   </si>
 </sst>
 </file>
@@ -617,469 +620,7 @@
     <cellStyle name="Normal 2 2 2" xfId="3" xr:uid="{F6D7429B-6BC2-41D1-B818-FB0128371036}"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="145">
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="134">
     <dxf>
       <font>
         <b/>
@@ -1677,6 +1218,13 @@
       </border>
     </dxf>
     <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1694,13 +1242,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1736,6 +1277,391 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
     </dxf>
     <dxf>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2209,94 +2135,94 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V25" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
-  <autoFilter ref="A1:V25" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V27" totalsRowShown="0" headerRowDxfId="133" dataDxfId="131" headerRowBorderDxfId="132" tableBorderDxfId="130" totalsRowBorderDxfId="129" headerRowCellStyle="Normal 2 2 2">
+  <autoFilter ref="A1:V27" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="139"/>
-    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="138"/>
-    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="137"/>
-    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="136"/>
-    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="135" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="134" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="133"/>
-    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="132" dataCellStyle="Porcentagem">
+    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="128"/>
+    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="127"/>
+    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="126"/>
+    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="125"/>
+    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="124" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="123" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="122"/>
+    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="121" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="131"/>
-    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="130"/>
-    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="129">
+    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="120"/>
+    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="119"/>
+    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="118">
       <calculatedColumnFormula>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="128" dataCellStyle="Moeda"/>
-    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="127" dataCellStyle="Porcentagem">
+    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="117" dataCellStyle="Moeda"/>
+    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="116" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="126"/>
-    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="125"/>
-    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="124"/>
-    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="123">
+    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="115"/>
+    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="114"/>
+    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="113"/>
+    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="112">
       <calculatedColumnFormula>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="122" dataCellStyle="Moeda 2 2">
+    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="111" dataCellStyle="Moeda 2 2">
       <calculatedColumnFormula>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="121" dataCellStyle="Moeda 3">
+    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="110" dataCellStyle="Moeda 3">
       <calculatedColumnFormula>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="120"/>
-    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="119"/>
-    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="118"/>
+    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="109"/>
+    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="108"/>
+    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="107"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y501" totalsRowShown="0" headerRowDxfId="117" dataDxfId="115" headerRowBorderDxfId="116" tableBorderDxfId="114" totalsRowBorderDxfId="113">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y522" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50" headerRowBorderDxfId="48" tableBorderDxfId="49" totalsRowBorderDxfId="47">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="112"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="111">
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="46"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="45">
       <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="110">
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="44">
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="109"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="108"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="107">
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="41">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="106" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="105" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="104"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="103" dataCellStyle="Normal 2 2 2">
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="40" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="39" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="38"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="37" dataCellStyle="Normal 2 2 2">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="102"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="101"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="100">
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="36"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="35"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="34">
       <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="99"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="98"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="97">
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="33"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="32"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="31">
       <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="96"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="95"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="94"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="93">
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="30"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="29"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="28"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="27">
       <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="92" dataCellStyle="Moeda">
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="26" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="91">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="25">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="90"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="89"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="88"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="24"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="23"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2725,7 +2651,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A050DE7D-8F3F-47CF-9E37-B95AFD2ED76A}">
-  <dimension ref="A1:V25"/>
+  <dimension ref="A1:V27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="23" bestFit="1" customWidth="1"/>
@@ -4192,10 +4118,10 @@
       <c r="D25" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="10">
         <v>8104.3</v>
       </c>
-      <c r="F25" s="27">
+      <c r="F25" s="10">
         <v>95783.11</v>
       </c>
       <c r="G25" s="4"/>
@@ -4243,40 +4169,152 @@
       </c>
       <c r="V25" s="5"/>
     </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A26" s="8">
+        <v>46303</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="27">
+        <v>5994.53</v>
+      </c>
+      <c r="F26" s="27">
+        <v>131439.71</v>
+      </c>
+      <c r="G26" s="4">
+        <v>1808</v>
+      </c>
+      <c r="H26" s="9">
+        <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
+        <v>4.5606689180918002E-2</v>
+      </c>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4">
+        <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
+        <v>0</v>
+      </c>
+      <c r="L26" s="10">
+        <v>500</v>
+      </c>
+      <c r="M26" s="9">
+        <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
+        <v>8.340937488009903E-2</v>
+      </c>
+      <c r="N26" s="4">
+        <v>359</v>
+      </c>
+      <c r="O26" s="4">
+        <v>19</v>
+      </c>
+      <c r="P26" s="4">
+        <v>19</v>
+      </c>
+      <c r="Q26" s="12">
+        <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="R26" s="13">
+        <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="S26" s="14" t="str">
+        <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="T26" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="U26" s="4">
+        <v>0</v>
+      </c>
+      <c r="V26" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A27" s="8">
+        <v>46304</v>
+      </c>
+      <c r="B27" s="8"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="9" t="e">
+        <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4">
+        <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
+        <v>0</v>
+      </c>
+      <c r="L27" s="10"/>
+      <c r="M27" s="9" t="e">
+        <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4"/>
+      <c r="Q27" s="12">
+        <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="R27" s="13" t="e">
+        <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S27" s="14" t="e">
+        <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T27" s="4"/>
+      <c r="U27" s="4"/>
+      <c r="V27" s="5"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H25">
-    <cfRule type="cellIs" dxfId="87" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="H2:H27">
+    <cfRule type="cellIs" dxfId="106" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="105" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R25">
-    <cfRule type="cellIs" dxfId="85" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="R2:R27">
+    <cfRule type="cellIs" dxfId="104" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="103" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="102" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="101" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="100" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="99" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="98" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S25">
-    <cfRule type="expression" dxfId="78" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="S2:S27">
+    <cfRule type="expression" dxfId="97" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -4285,7 +4323,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4299,7 +4337,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y501"/>
+  <dimension ref="A1:Y522"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -46372,11 +46410,11 @@
       <c r="A490" s="8">
         <v>46302</v>
       </c>
-      <c r="B490" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C490" s="26">
+      <c r="B490" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C490" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -46458,11 +46496,11 @@
       <c r="A491" s="8">
         <v>46302</v>
       </c>
-      <c r="B491" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C491" s="26">
+      <c r="B491" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C491" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -46544,11 +46582,11 @@
       <c r="A492" s="8">
         <v>46302</v>
       </c>
-      <c r="B492" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C492" s="26">
+      <c r="B492" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C492" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -46630,11 +46668,11 @@
       <c r="A493" s="8">
         <v>46302</v>
       </c>
-      <c r="B493" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C493" s="26">
+      <c r="B493" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C493" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -46716,11 +46754,11 @@
       <c r="A494" s="8">
         <v>46302</v>
       </c>
-      <c r="B494" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C494" s="26">
+      <c r="B494" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C494" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -46802,11 +46840,11 @@
       <c r="A495" s="8">
         <v>46302</v>
       </c>
-      <c r="B495" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C495" s="26">
+      <c r="B495" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C495" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -46888,11 +46926,11 @@
       <c r="A496" s="8">
         <v>46302</v>
       </c>
-      <c r="B496" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C496" s="26">
+      <c r="B496" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C496" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -46974,11 +47012,11 @@
       <c r="A497" s="8">
         <v>46302</v>
       </c>
-      <c r="B497" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C497" s="26">
+      <c r="B497" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C497" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -47060,11 +47098,11 @@
       <c r="A498" s="8">
         <v>46302</v>
       </c>
-      <c r="B498" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C498" s="26">
+      <c r="B498" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C498" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -47146,11 +47184,11 @@
       <c r="A499" s="8">
         <v>46302</v>
       </c>
-      <c r="B499" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C499" s="26">
+      <c r="B499" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C499" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -47232,11 +47270,11 @@
       <c r="A500" s="8">
         <v>46302</v>
       </c>
-      <c r="B500" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C500" s="26">
+      <c r="B500" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C500" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -47318,11 +47356,11 @@
       <c r="A501" s="8">
         <v>46302</v>
       </c>
-      <c r="B501" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C501" s="26">
+      <c r="B501" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C501" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -47400,40 +47438,1846 @@
         <v>0</v>
       </c>
     </row>
+    <row r="502" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A502" s="8">
+        <v>46303</v>
+      </c>
+      <c r="B502" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C502" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D502" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E502" s="4">
+        <v>5</v>
+      </c>
+      <c r="F502" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Heremilton</v>
+      </c>
+      <c r="G502" s="10">
+        <v>54917.27</v>
+      </c>
+      <c r="H502" s="10">
+        <v>795207.48</v>
+      </c>
+      <c r="I502" s="4">
+        <v>9760</v>
+      </c>
+      <c r="J502" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.9060303607808113E-2</v>
+      </c>
+      <c r="K502" s="11">
+        <v>0.27986111111111112</v>
+      </c>
+      <c r="L502" s="15">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="M502" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.55347222222222225</v>
+      </c>
+      <c r="N502" s="4">
+        <v>368062</v>
+      </c>
+      <c r="O502" s="4">
+        <v>368100</v>
+      </c>
+      <c r="P502" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>38</v>
+      </c>
+      <c r="Q502" s="4">
+        <v>1948</v>
+      </c>
+      <c r="R502" s="4">
+        <v>34</v>
+      </c>
+      <c r="S502" s="4">
+        <v>34</v>
+      </c>
+      <c r="T502" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U502" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V502" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W502" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X502" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y502" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="503" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A503" s="8">
+        <v>46303</v>
+      </c>
+      <c r="B503" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C503" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D503" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E503" s="4">
+        <v>11</v>
+      </c>
+      <c r="F503" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G503" s="10">
+        <v>12215.24</v>
+      </c>
+      <c r="H503" s="10">
+        <v>320378.76</v>
+      </c>
+      <c r="I503" s="4">
+        <v>5773</v>
+      </c>
+      <c r="J503" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.8127496342142034E-2</v>
+      </c>
+      <c r="K503" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L503" s="15">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="M503" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.43750000000000006</v>
+      </c>
+      <c r="N503" s="4">
+        <v>106902</v>
+      </c>
+      <c r="O503" s="4">
+        <v>107024</v>
+      </c>
+      <c r="P503" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>122</v>
+      </c>
+      <c r="Q503" s="4">
+        <v>12</v>
+      </c>
+      <c r="R503" s="4">
+        <v>2</v>
+      </c>
+      <c r="S503" s="4">
+        <v>2</v>
+      </c>
+      <c r="T503" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U503" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V503" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W503" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X503" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y503" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="504" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A504" s="8">
+        <v>46303</v>
+      </c>
+      <c r="B504" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C504" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D504" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E504" s="4">
+        <v>1</v>
+      </c>
+      <c r="F504" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G504" s="10">
+        <v>14427.01</v>
+      </c>
+      <c r="H504" s="10">
+        <v>287130.32</v>
+      </c>
+      <c r="I504" s="4">
+        <v>4484</v>
+      </c>
+      <c r="J504" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.0245512212015786E-2</v>
+      </c>
+      <c r="K504" s="11">
+        <v>0.31944444444444442</v>
+      </c>
+      <c r="L504" s="15">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="M504" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.16666666666666669</v>
+      </c>
+      <c r="N504" s="4">
+        <v>14722</v>
+      </c>
+      <c r="O504" s="4">
+        <v>14745</v>
+      </c>
+      <c r="P504" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>23</v>
+      </c>
+      <c r="Q504" s="4">
+        <v>15</v>
+      </c>
+      <c r="R504" s="4">
+        <v>2</v>
+      </c>
+      <c r="S504" s="4">
+        <v>2</v>
+      </c>
+      <c r="T504" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U504" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V504" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W504" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X504" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y504" s="5">
+        <v>38.380000000000003</v>
+      </c>
+    </row>
+    <row r="505" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A505" s="8">
+        <v>46303</v>
+      </c>
+      <c r="B505" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C505" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D505" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E505" s="4">
+        <v>5</v>
+      </c>
+      <c r="F505" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G505" s="10">
+        <v>6355.51</v>
+      </c>
+      <c r="H505" s="10">
+        <v>68977.039999999994</v>
+      </c>
+      <c r="I505" s="4">
+        <v>754</v>
+      </c>
+      <c r="J505" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>9.2139500332284491E-2</v>
+      </c>
+      <c r="K505" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L505" s="15">
+        <v>0.77013888888888893</v>
+      </c>
+      <c r="M505" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45763888888888893</v>
+      </c>
+      <c r="N505" s="4">
+        <v>306072</v>
+      </c>
+      <c r="O505" s="4">
+        <v>306160</v>
+      </c>
+      <c r="P505" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>88</v>
+      </c>
+      <c r="Q505" s="4">
+        <v>165</v>
+      </c>
+      <c r="R505" s="4">
+        <v>22</v>
+      </c>
+      <c r="S505" s="4">
+        <v>22</v>
+      </c>
+      <c r="T505" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U505" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V505" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W505" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X505" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y505" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="506" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A506" s="8">
+        <v>46303</v>
+      </c>
+      <c r="B506" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C506" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D506" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E506" s="4">
+        <v>3</v>
+      </c>
+      <c r="F506" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G506" s="10">
+        <v>4102.62</v>
+      </c>
+      <c r="H506" s="10">
+        <v>113588.33</v>
+      </c>
+      <c r="I506" s="4">
+        <v>609</v>
+      </c>
+      <c r="J506" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.6118323070688685E-2</v>
+      </c>
+      <c r="K506" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L506" s="15">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="M506" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.43055555555555552</v>
+      </c>
+      <c r="N506" s="4">
+        <v>276802</v>
+      </c>
+      <c r="O506" s="4">
+        <v>276851</v>
+      </c>
+      <c r="P506" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>49</v>
+      </c>
+      <c r="Q506" s="4">
+        <v>136</v>
+      </c>
+      <c r="R506" s="4">
+        <v>14</v>
+      </c>
+      <c r="S506" s="4">
+        <v>14</v>
+      </c>
+      <c r="T506" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U506" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V506" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W506" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X506" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y506" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="507" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A507" s="8">
+        <v>46303</v>
+      </c>
+      <c r="B507" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C507" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D507" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E507" s="4">
+        <v>1</v>
+      </c>
+      <c r="F507" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G507" s="10">
+        <v>6839.32</v>
+      </c>
+      <c r="H507" s="10">
+        <v>90468.19</v>
+      </c>
+      <c r="I507" s="4">
+        <v>1530</v>
+      </c>
+      <c r="J507" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.5599169166532448E-2</v>
+      </c>
+      <c r="K507" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L507" s="15">
+        <v>0.69513888888888886</v>
+      </c>
+      <c r="M507" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.38263888888888886</v>
+      </c>
+      <c r="N507" s="4">
+        <v>292433</v>
+      </c>
+      <c r="O507" s="4">
+        <v>292474</v>
+      </c>
+      <c r="P507" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>41</v>
+      </c>
+      <c r="Q507" s="4">
+        <v>125</v>
+      </c>
+      <c r="R507" s="4">
+        <v>18</v>
+      </c>
+      <c r="S507" s="4">
+        <v>18</v>
+      </c>
+      <c r="T507" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U507" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V507" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W507" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X507" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y507" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="508" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A508" s="8">
+        <v>46303</v>
+      </c>
+      <c r="B508" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C508" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D508" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E508" s="4">
+        <v>11</v>
+      </c>
+      <c r="F508" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G508" s="10">
+        <v>12692.21</v>
+      </c>
+      <c r="H508" s="10">
+        <v>202839.55</v>
+      </c>
+      <c r="I508" s="4">
+        <v>1938</v>
+      </c>
+      <c r="J508" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.2572659030253219E-2</v>
+      </c>
+      <c r="K508" s="11">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="L508" s="15">
+        <v>0.74444444444444446</v>
+      </c>
+      <c r="M508" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="N508" s="4">
+        <v>144536</v>
+      </c>
+      <c r="O508" s="4">
+        <v>144677</v>
+      </c>
+      <c r="P508" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>141</v>
+      </c>
+      <c r="Q508" s="4">
+        <v>325</v>
+      </c>
+      <c r="R508" s="4">
+        <v>34</v>
+      </c>
+      <c r="S508" s="4">
+        <v>34</v>
+      </c>
+      <c r="T508" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U508" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V508" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W508" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X508" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y508" s="5">
+        <v>38.380000000000003</v>
+      </c>
+    </row>
+    <row r="509" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A509" s="8">
+        <v>46303</v>
+      </c>
+      <c r="B509" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C509" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D509" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E509" s="4">
+        <v>3</v>
+      </c>
+      <c r="F509" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G509" s="10">
+        <v>5759.81</v>
+      </c>
+      <c r="H509" s="10">
+        <v>111313.76</v>
+      </c>
+      <c r="I509" s="4">
+        <v>795</v>
+      </c>
+      <c r="J509" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.174391737373709E-2</v>
+      </c>
+      <c r="K509" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L509" s="15">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="M509" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.39583333333333337</v>
+      </c>
+      <c r="N509" s="4">
+        <v>126810</v>
+      </c>
+      <c r="O509" s="4">
+        <v>126860</v>
+      </c>
+      <c r="P509" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>50</v>
+      </c>
+      <c r="Q509" s="4">
+        <v>104</v>
+      </c>
+      <c r="R509" s="4">
+        <v>17</v>
+      </c>
+      <c r="S509" s="4">
+        <v>17</v>
+      </c>
+      <c r="T509" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U509" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V509" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W509" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X509" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y509" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="510" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A510" s="8">
+        <v>46303</v>
+      </c>
+      <c r="B510" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C510" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D510" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E510" s="4">
+        <v>1</v>
+      </c>
+      <c r="F510" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G510" s="10">
+        <v>3075.28</v>
+      </c>
+      <c r="H510" s="10">
+        <v>41356.01</v>
+      </c>
+      <c r="I510" s="4">
+        <v>620</v>
+      </c>
+      <c r="J510" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.4361138804251187E-2</v>
+      </c>
+      <c r="K510" s="11">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L510" s="15">
+        <v>0.71944444444444444</v>
+      </c>
+      <c r="M510" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.38611111111111113</v>
+      </c>
+      <c r="N510" s="4">
+        <v>156830</v>
+      </c>
+      <c r="O510" s="4">
+        <v>157003</v>
+      </c>
+      <c r="P510" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>173</v>
+      </c>
+      <c r="Q510" s="4">
+        <v>138</v>
+      </c>
+      <c r="R510" s="4">
+        <v>12</v>
+      </c>
+      <c r="S510" s="4">
+        <v>12</v>
+      </c>
+      <c r="T510" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U510" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V510" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W510" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X510" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y510" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="511" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A511" s="8">
+        <v>46303</v>
+      </c>
+      <c r="B511" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C511" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D511" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E511" s="4">
+        <v>1</v>
+      </c>
+      <c r="F511" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G511" s="10">
+        <v>12050.21</v>
+      </c>
+      <c r="H511" s="10">
+        <v>206944.9</v>
+      </c>
+      <c r="I511" s="4">
+        <v>5981</v>
+      </c>
+      <c r="J511" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.8229074502440019E-2</v>
+      </c>
+      <c r="K511" s="11">
+        <v>0.65625</v>
+      </c>
+      <c r="L511" s="15">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="M511" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>4.166666666666663E-2</v>
+      </c>
+      <c r="N511" s="4">
+        <v>14745</v>
+      </c>
+      <c r="O511" s="4">
+        <v>14754</v>
+      </c>
+      <c r="P511" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>9</v>
+      </c>
+      <c r="Q511" s="4">
+        <v>588</v>
+      </c>
+      <c r="R511" s="4">
+        <v>3</v>
+      </c>
+      <c r="S511" s="4">
+        <v>0</v>
+      </c>
+      <c r="T511" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>3</v>
+      </c>
+      <c r="U511" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0</v>
+      </c>
+      <c r="V511" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W511" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="X511" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y511" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="512" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A512" s="8">
+        <v>46304</v>
+      </c>
+      <c r="B512" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C512" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D512" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E512" s="4">
+        <v>5</v>
+      </c>
+      <c r="F512" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G512" s="10">
+        <v>3572.31</v>
+      </c>
+      <c r="H512" s="10">
+        <v>71910.12</v>
+      </c>
+      <c r="I512" s="4">
+        <v>1494</v>
+      </c>
+      <c r="J512" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.9677430659272992E-2</v>
+      </c>
+      <c r="K512" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L512" s="15">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="M512" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.43750000000000006</v>
+      </c>
+      <c r="N512" s="4">
+        <v>107024</v>
+      </c>
+      <c r="O512" s="4">
+        <v>107076</v>
+      </c>
+      <c r="P512" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>52</v>
+      </c>
+      <c r="Q512" s="4">
+        <v>10</v>
+      </c>
+      <c r="R512" s="4">
+        <v>9</v>
+      </c>
+      <c r="S512" s="4">
+        <v>9</v>
+      </c>
+      <c r="T512" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U512" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V512" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W512" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X512" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y512" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="513" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A513" s="8">
+        <v>46304</v>
+      </c>
+      <c r="B513" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C513" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D513" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E513" s="4">
+        <v>1</v>
+      </c>
+      <c r="F513" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G513" s="10">
+        <v>8073.15</v>
+      </c>
+      <c r="H513" s="10">
+        <v>152901.45000000001</v>
+      </c>
+      <c r="I513" s="4">
+        <v>1519</v>
+      </c>
+      <c r="J513" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.2799695490134323E-2</v>
+      </c>
+      <c r="K513" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L513" s="15">
+        <v>0.73819444444444449</v>
+      </c>
+      <c r="M513" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.42569444444444449</v>
+      </c>
+      <c r="N513" s="4">
+        <v>292474</v>
+      </c>
+      <c r="O513" s="4">
+        <v>292517</v>
+      </c>
+      <c r="P513" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>43</v>
+      </c>
+      <c r="Q513" s="4">
+        <v>147</v>
+      </c>
+      <c r="R513" s="4">
+        <v>18</v>
+      </c>
+      <c r="S513" s="4">
+        <v>18</v>
+      </c>
+      <c r="T513" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U513" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V513" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W513" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X513" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y513" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="514" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A514" s="8">
+        <v>46304</v>
+      </c>
+      <c r="B514" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C514" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D514" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E514" s="4">
+        <v>1</v>
+      </c>
+      <c r="F514" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G514" s="10">
+        <v>12152.4</v>
+      </c>
+      <c r="H514" s="10">
+        <v>207808.59</v>
+      </c>
+      <c r="I514" s="4">
+        <v>5993</v>
+      </c>
+      <c r="J514" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.8478814566808812E-2</v>
+      </c>
+      <c r="K514" s="11">
+        <v>0.30486111111111114</v>
+      </c>
+      <c r="L514" s="15">
+        <v>0.75138888888888888</v>
+      </c>
+      <c r="M514" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44652777777777775</v>
+      </c>
+      <c r="N514" s="4">
+        <v>14754</v>
+      </c>
+      <c r="O514" s="4">
+        <v>14782</v>
+      </c>
+      <c r="P514" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>28</v>
+      </c>
+      <c r="Q514" s="4">
+        <v>15</v>
+      </c>
+      <c r="R514" s="4">
+        <v>4</v>
+      </c>
+      <c r="S514" s="4">
+        <v>4</v>
+      </c>
+      <c r="T514" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U514" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V514" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W514" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="X514" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y514" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="515" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A515" s="8">
+        <v>46304</v>
+      </c>
+      <c r="B515" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C515" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D515" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E515" s="4">
+        <v>11</v>
+      </c>
+      <c r="F515" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G515" s="10">
+        <v>8387.43</v>
+      </c>
+      <c r="H515" s="10">
+        <v>168450.99</v>
+      </c>
+      <c r="I515" s="4">
+        <v>1174</v>
+      </c>
+      <c r="J515" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.9791515027605364E-2</v>
+      </c>
+      <c r="K515" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L515" s="15">
+        <v>0.75138888888888888</v>
+      </c>
+      <c r="M515" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.48055555555555557</v>
+      </c>
+      <c r="N515" s="4">
+        <v>144677</v>
+      </c>
+      <c r="O515" s="4">
+        <v>144822</v>
+      </c>
+      <c r="P515" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>145</v>
+      </c>
+      <c r="Q515" s="4">
+        <v>143</v>
+      </c>
+      <c r="R515" s="4">
+        <v>16</v>
+      </c>
+      <c r="S515" s="4">
+        <v>15</v>
+      </c>
+      <c r="T515" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>1</v>
+      </c>
+      <c r="U515" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.9375</v>
+      </c>
+      <c r="V515" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W515" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X515" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y515" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="516" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A516" s="8">
+        <v>46304</v>
+      </c>
+      <c r="B516" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C516" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D516" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E516" s="4">
+        <v>2</v>
+      </c>
+      <c r="F516" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G516" s="10">
+        <v>12325.53</v>
+      </c>
+      <c r="H516" s="10">
+        <v>176127.26</v>
+      </c>
+      <c r="I516" s="4">
+        <v>3129</v>
+      </c>
+      <c r="J516" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.9980819550590864E-2</v>
+      </c>
+      <c r="K516" s="11">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="L516" s="15">
+        <v>0.79236111111111107</v>
+      </c>
+      <c r="M516" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.51458333333333328</v>
+      </c>
+      <c r="N516" s="4">
+        <v>281964</v>
+      </c>
+      <c r="O516" s="4">
+        <v>282029</v>
+      </c>
+      <c r="P516" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>65</v>
+      </c>
+      <c r="Q516" s="4">
+        <v>304</v>
+      </c>
+      <c r="R516" s="4">
+        <v>34</v>
+      </c>
+      <c r="S516" s="4">
+        <v>34</v>
+      </c>
+      <c r="T516" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U516" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V516" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W516" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X516" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y516" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="517" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A517" s="8">
+        <v>46304</v>
+      </c>
+      <c r="B517" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C517" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D517" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E517" s="4">
+        <v>3</v>
+      </c>
+      <c r="F517" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G517" s="10">
+        <v>6192.89</v>
+      </c>
+      <c r="H517" s="10">
+        <v>142671.84</v>
+      </c>
+      <c r="I517" s="4">
+        <v>1141</v>
+      </c>
+      <c r="J517" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.3406533482711097E-2</v>
+      </c>
+      <c r="K517" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L517" s="15">
+        <v>0.8041666666666667</v>
+      </c>
+      <c r="M517" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.51249999999999996</v>
+      </c>
+      <c r="N517" s="4">
+        <v>126860</v>
+      </c>
+      <c r="O517" s="4">
+        <v>126935</v>
+      </c>
+      <c r="P517" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>75</v>
+      </c>
+      <c r="Q517" s="4">
+        <v>169</v>
+      </c>
+      <c r="R517" s="4">
+        <v>19</v>
+      </c>
+      <c r="S517" s="4">
+        <v>17</v>
+      </c>
+      <c r="T517" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>2</v>
+      </c>
+      <c r="U517" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="V517" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W517" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X517" s="4">
+        <v>4</v>
+      </c>
+      <c r="Y517" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="518" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A518" s="8">
+        <v>46304</v>
+      </c>
+      <c r="B518" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C518" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D518" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E518" s="4">
+        <v>5</v>
+      </c>
+      <c r="F518" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G518" s="10">
+        <v>11542.94</v>
+      </c>
+      <c r="H518" s="10">
+        <v>248336.8</v>
+      </c>
+      <c r="I518" s="4">
+        <v>2574</v>
+      </c>
+      <c r="J518" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.6480988721768181E-2</v>
+      </c>
+      <c r="K518" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L518" s="15">
+        <v>0.80069444444444449</v>
+      </c>
+      <c r="M518" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.48819444444444449</v>
+      </c>
+      <c r="N518" s="4">
+        <v>306160</v>
+      </c>
+      <c r="O518" s="4">
+        <v>306240</v>
+      </c>
+      <c r="P518" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>80</v>
+      </c>
+      <c r="Q518" s="4">
+        <v>358</v>
+      </c>
+      <c r="R518" s="4">
+        <v>37</v>
+      </c>
+      <c r="S518" s="4">
+        <v>37</v>
+      </c>
+      <c r="T518" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U518" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V518" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W518" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X518" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y518" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="519" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A519" s="8">
+        <v>46304</v>
+      </c>
+      <c r="B519" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C519" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D519" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E519" s="4">
+        <v>1</v>
+      </c>
+      <c r="F519" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G519" s="10">
+        <v>4983.6400000000003</v>
+      </c>
+      <c r="H519" s="10">
+        <v>129842.06</v>
+      </c>
+      <c r="I519" s="4">
+        <v>956</v>
+      </c>
+      <c r="J519" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.8382323878718504E-2</v>
+      </c>
+      <c r="K519" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L519" s="15">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="M519" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.43055555555555552</v>
+      </c>
+      <c r="N519" s="4">
+        <v>276851</v>
+      </c>
+      <c r="O519" s="4">
+        <v>276917</v>
+      </c>
+      <c r="P519" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>66</v>
+      </c>
+      <c r="Q519" s="4">
+        <v>166</v>
+      </c>
+      <c r="R519" s="4">
+        <v>6</v>
+      </c>
+      <c r="S519" s="4">
+        <v>6</v>
+      </c>
+      <c r="T519" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U519" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V519" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W519" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X519" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y519" s="5">
+        <v>38.380000000000003</v>
+      </c>
+    </row>
+    <row r="520" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A520" s="8">
+        <v>46304</v>
+      </c>
+      <c r="B520" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C520" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D520" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E520" s="4">
+        <v>1</v>
+      </c>
+      <c r="F520" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G520" s="10">
+        <v>6869.81</v>
+      </c>
+      <c r="H520" s="10">
+        <v>158166.76</v>
+      </c>
+      <c r="I520" s="4">
+        <v>3125</v>
+      </c>
+      <c r="J520" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.3433968047395043E-2</v>
+      </c>
+      <c r="K520" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L520" s="15">
+        <v>0.70416666666666672</v>
+      </c>
+      <c r="M520" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.39166666666666672</v>
+      </c>
+      <c r="N520" s="4">
+        <v>120909</v>
+      </c>
+      <c r="O520" s="4">
+        <v>120939</v>
+      </c>
+      <c r="P520" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>30</v>
+      </c>
+      <c r="Q520" s="4">
+        <v>967</v>
+      </c>
+      <c r="R520" s="4">
+        <v>8</v>
+      </c>
+      <c r="S520" s="4">
+        <v>8</v>
+      </c>
+      <c r="T520" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U520" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V520" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W520" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X520" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y520" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="521" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A521" s="8">
+        <v>46304</v>
+      </c>
+      <c r="B521" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C521" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D521" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E521" s="4">
+        <v>1</v>
+      </c>
+      <c r="F521" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G521" s="10">
+        <v>2841.14</v>
+      </c>
+      <c r="H521" s="10">
+        <v>25089.89</v>
+      </c>
+      <c r="I521" s="4">
+        <v>164</v>
+      </c>
+      <c r="J521" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.11323843986561918</v>
+      </c>
+      <c r="K521" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L521" s="15">
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="M521" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.38333333333333336</v>
+      </c>
+      <c r="N521" s="4">
+        <v>157003</v>
+      </c>
+      <c r="O521" s="4">
+        <v>157065</v>
+      </c>
+      <c r="P521" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>62</v>
+      </c>
+      <c r="Q521" s="4">
+        <v>30</v>
+      </c>
+      <c r="R521" s="4">
+        <v>3</v>
+      </c>
+      <c r="S521" s="4">
+        <v>3</v>
+      </c>
+      <c r="T521" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U521" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V521" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W521" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X521" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y521" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A522" s="8">
+        <v>46305</v>
+      </c>
+      <c r="B522" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C522" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D522" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E522" s="4">
+        <v>1</v>
+      </c>
+      <c r="F522" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G522" s="10">
+        <v>2473.9499999999998</v>
+      </c>
+      <c r="H522" s="10">
+        <v>29026.86</v>
+      </c>
+      <c r="I522" s="4">
+        <v>208</v>
+      </c>
+      <c r="J522" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.5229680371903802E-2</v>
+      </c>
+      <c r="K522" s="11">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L522" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="M522" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.16666666666666669</v>
+      </c>
+      <c r="N522" s="4">
+        <v>157065</v>
+      </c>
+      <c r="O522" s="4">
+        <v>157101</v>
+      </c>
+      <c r="P522" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>36</v>
+      </c>
+      <c r="Q522" s="4">
+        <v>23</v>
+      </c>
+      <c r="R522" s="4">
+        <v>13</v>
+      </c>
+      <c r="S522" s="4">
+        <v>13</v>
+      </c>
+      <c r="T522" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U522" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V522" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W522" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X522" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y522" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J501">
-    <cfRule type="cellIs" dxfId="76" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="J2:J522">
+    <cfRule type="cellIs" dxfId="21" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="20" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U501">
-    <cfRule type="cellIs" dxfId="74" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="U2:U522">
+    <cfRule type="cellIs" dxfId="19" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="18" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="17" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V501">
-    <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="V2:V522">
+    <cfRule type="expression" dxfId="12" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -47442,7 +49286,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -47458,7 +49302,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D501</xm:sqref>
+          <xm:sqref>D2:D522</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E49996-0B86-45DC-8BCD-398796546988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{897FDDB8-4589-406F-9D57-74B66091774D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha2" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1237" uniqueCount="101">
   <si>
     <t>Data</t>
   </si>
@@ -332,6 +332,21 @@
   <si>
     <t>9,9,13,13</t>
   </si>
+  <si>
+    <t>13,13,13,13,13,13,13,13,13,13</t>
+  </si>
+  <si>
+    <t>BER6A86</t>
+  </si>
+  <si>
+    <t>9,9,38,38,38</t>
+  </si>
+  <si>
+    <t>13,13,13,13,13,13,13,27</t>
+  </si>
+  <si>
+    <t>13,13,13,13,13,13</t>
+  </si>
 </sst>
 </file>
 
@@ -534,7 +549,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -608,9 +623,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -621,6 +633,391 @@
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="134">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1218,13 +1615,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1242,6 +1632,13 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1277,391 +1674,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
     </dxf>
     <dxf>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2178,51 +2190,51 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y522" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50" headerRowBorderDxfId="48" tableBorderDxfId="49" totalsRowBorderDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y533" totalsRowShown="0" headerRowDxfId="106" dataDxfId="104" headerRowBorderDxfId="105" tableBorderDxfId="103" totalsRowBorderDxfId="102">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="46"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="45">
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="101"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="100">
       <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="44">
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="99">
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="41">
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="98"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="97"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="96">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="40" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="39" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="38"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="37" dataCellStyle="Normal 2 2 2">
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="95" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="94" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="93"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="92" dataCellStyle="Normal 2 2 2">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="36"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="35"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="34">
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="91"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="90"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="89">
       <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="33"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="32"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="31">
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="88"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="87"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="86">
       <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="30"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="29"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="28"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="27">
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="85"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="84"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="83"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="82">
       <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="26" dataCellStyle="Moeda">
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="81" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="25">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="80">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="24"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="23"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="22"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="79"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="78"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="77"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2630,7 +2642,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="B11" t="s">
         <v>38</v>
@@ -4180,10 +4192,10 @@
       <c r="D26" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="10">
         <v>5994.53</v>
       </c>
-      <c r="F26" s="27">
+      <c r="F26" s="10">
         <v>131439.71</v>
       </c>
       <c r="G26" s="4">
@@ -4239,17 +4251,27 @@
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
-        <v>46304</v>
-      </c>
-      <c r="B27" s="8"/>
+        <v>46308</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>44</v>
+      </c>
       <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="9" t="e">
+      <c r="D27" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="10">
+        <v>8191.62</v>
+      </c>
+      <c r="F27" s="10">
+        <v>144115.01</v>
+      </c>
+      <c r="G27" s="4">
+        <v>1700</v>
+      </c>
+      <c r="H27" s="9">
         <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
-        <v>#DIV/0!</v>
+        <v>5.6840852316493606E-2</v>
       </c>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
@@ -4257,25 +4279,33 @@
         <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
         <v>0</v>
       </c>
-      <c r="L27" s="10"/>
-      <c r="M27" s="9" t="e">
+      <c r="L27" s="10">
+        <v>500</v>
+      </c>
+      <c r="M27" s="9">
         <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N27" s="4"/>
-      <c r="O27" s="4"/>
-      <c r="P27" s="4"/>
+        <v>6.103798760196396E-2</v>
+      </c>
+      <c r="N27" s="4">
+        <v>346</v>
+      </c>
+      <c r="O27" s="4">
+        <v>16</v>
+      </c>
+      <c r="P27" s="4">
+        <v>16</v>
+      </c>
       <c r="Q27" s="12">
         <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
         <v>0</v>
       </c>
-      <c r="R27" s="13" t="e">
+      <c r="R27" s="13">
         <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S27" s="14" t="e">
+        <v>1</v>
+      </c>
+      <c r="S27" s="14" t="str">
         <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
-        <v>#DIV/0!</v>
+        <v>Atendeu a Meta</v>
       </c>
       <c r="T27" s="4"/>
       <c r="U27" s="4"/>
@@ -4283,38 +4313,38 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H2:H27">
-    <cfRule type="cellIs" dxfId="106" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="76" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="75" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R27">
-    <cfRule type="cellIs" dxfId="104" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="74" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="73" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="72" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="71" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="70" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="69" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="68" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S2:S27">
-    <cfRule type="expression" dxfId="97" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -4323,7 +4353,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4337,7 +4367,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y522"/>
+  <dimension ref="A1:Y533"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -14781,7 +14811,7 @@
       </c>
       <c r="F122" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Manoel</v>
+        <v/>
       </c>
       <c r="G122" s="10">
         <v>1490.48</v>
@@ -23036,7 +23066,7 @@
       </c>
       <c r="F218" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Manoel</v>
+        <v/>
       </c>
       <c r="G218" s="10">
         <v>709.78</v>
@@ -27594,7 +27624,7 @@
       </c>
       <c r="F271" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Manoel</v>
+        <v/>
       </c>
       <c r="G271" s="10">
         <v>512.91</v>
@@ -33182,7 +33212,7 @@
       </c>
       <c r="F336" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Manoel</v>
+        <v/>
       </c>
       <c r="G336" s="10">
         <v>358.18</v>
@@ -33870,7 +33900,7 @@
       </c>
       <c r="F344" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Manoel</v>
+        <v/>
       </c>
       <c r="G344" s="10">
         <v>127.39</v>
@@ -35246,7 +35276,7 @@
       </c>
       <c r="F360" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Manoel</v>
+        <v/>
       </c>
       <c r="G360" s="10">
         <v>795.97</v>
@@ -46512,7 +46542,7 @@
       </c>
       <c r="F491" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Manoel</v>
+        <v/>
       </c>
       <c r="G491" s="10">
         <v>167.72</v>
@@ -47442,11 +47472,11 @@
       <c r="A502" s="8">
         <v>46303</v>
       </c>
-      <c r="B502" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C502" s="26">
+      <c r="B502" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C502" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -47528,11 +47558,11 @@
       <c r="A503" s="8">
         <v>46303</v>
       </c>
-      <c r="B503" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C503" s="26">
+      <c r="B503" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C503" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -47614,11 +47644,11 @@
       <c r="A504" s="8">
         <v>46303</v>
       </c>
-      <c r="B504" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C504" s="26">
+      <c r="B504" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C504" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -47700,11 +47730,11 @@
       <c r="A505" s="8">
         <v>46303</v>
       </c>
-      <c r="B505" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C505" s="26">
+      <c r="B505" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C505" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -47786,11 +47816,11 @@
       <c r="A506" s="8">
         <v>46303</v>
       </c>
-      <c r="B506" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C506" s="26">
+      <c r="B506" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C506" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -47872,11 +47902,11 @@
       <c r="A507" s="8">
         <v>46303</v>
       </c>
-      <c r="B507" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C507" s="26">
+      <c r="B507" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C507" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -47958,11 +47988,11 @@
       <c r="A508" s="8">
         <v>46303</v>
       </c>
-      <c r="B508" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C508" s="26">
+      <c r="B508" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C508" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -48044,11 +48074,11 @@
       <c r="A509" s="8">
         <v>46303</v>
       </c>
-      <c r="B509" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C509" s="26">
+      <c r="B509" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C509" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -48130,11 +48160,11 @@
       <c r="A510" s="8">
         <v>46303</v>
       </c>
-      <c r="B510" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C510" s="26">
+      <c r="B510" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C510" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -48216,11 +48246,11 @@
       <c r="A511" s="8">
         <v>46303</v>
       </c>
-      <c r="B511" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C511" s="26">
+      <c r="B511" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C511" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -48302,11 +48332,11 @@
       <c r="A512" s="8">
         <v>46304</v>
       </c>
-      <c r="B512" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C512" s="26">
+      <c r="B512" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C512" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -48388,11 +48418,11 @@
       <c r="A513" s="8">
         <v>46304</v>
       </c>
-      <c r="B513" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C513" s="26">
+      <c r="B513" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C513" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -48474,11 +48504,11 @@
       <c r="A514" s="8">
         <v>46304</v>
       </c>
-      <c r="B514" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C514" s="26">
+      <c r="B514" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C514" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -48560,11 +48590,11 @@
       <c r="A515" s="8">
         <v>46304</v>
       </c>
-      <c r="B515" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C515" s="26">
+      <c r="B515" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C515" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -48646,11 +48676,11 @@
       <c r="A516" s="8">
         <v>46304</v>
       </c>
-      <c r="B516" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C516" s="26">
+      <c r="B516" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C516" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -48732,11 +48762,11 @@
       <c r="A517" s="8">
         <v>46304</v>
       </c>
-      <c r="B517" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C517" s="26">
+      <c r="B517" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C517" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -48818,11 +48848,11 @@
       <c r="A518" s="8">
         <v>46304</v>
       </c>
-      <c r="B518" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C518" s="26">
+      <c r="B518" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C518" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -48904,11 +48934,11 @@
       <c r="A519" s="8">
         <v>46304</v>
       </c>
-      <c r="B519" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C519" s="26">
+      <c r="B519" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C519" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -48990,11 +49020,11 @@
       <c r="A520" s="8">
         <v>46304</v>
       </c>
-      <c r="B520" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C520" s="26">
+      <c r="B520" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C520" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -49076,11 +49106,11 @@
       <c r="A521" s="8">
         <v>46304</v>
       </c>
-      <c r="B521" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C521" s="26">
+      <c r="B521" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C521" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -49162,11 +49192,11 @@
       <c r="A522" s="8">
         <v>46305</v>
       </c>
-      <c r="B522" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C522" s="26">
+      <c r="B522" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C522" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -49244,40 +49274,986 @@
         <v>0</v>
       </c>
     </row>
+    <row r="523" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A523" s="8">
+        <v>46308</v>
+      </c>
+      <c r="B523" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C523" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D523" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E523" s="4">
+        <v>1</v>
+      </c>
+      <c r="F523" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G523" s="10">
+        <v>3617.26</v>
+      </c>
+      <c r="H523" s="10">
+        <v>114238.16</v>
+      </c>
+      <c r="I523" s="4">
+        <v>995</v>
+      </c>
+      <c r="J523" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.1664200473817156E-2</v>
+      </c>
+      <c r="K523" s="11">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L523" s="15">
+        <v>0.80138888888888893</v>
+      </c>
+      <c r="M523" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.46805555555555561</v>
+      </c>
+      <c r="N523" s="4">
+        <v>157124</v>
+      </c>
+      <c r="O523" s="4">
+        <v>157213</v>
+      </c>
+      <c r="P523" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>89</v>
+      </c>
+      <c r="Q523" s="4">
+        <v>128</v>
+      </c>
+      <c r="R523" s="4">
+        <v>10</v>
+      </c>
+      <c r="S523" s="4">
+        <v>10</v>
+      </c>
+      <c r="T523" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U523" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V523" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W523" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X523" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y523" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="524" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A524" s="8">
+        <v>46308</v>
+      </c>
+      <c r="B524" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C524" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D524" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E524" s="4">
+        <v>2</v>
+      </c>
+      <c r="F524" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G524" s="10">
+        <v>13755.73</v>
+      </c>
+      <c r="H524" s="10">
+        <v>261029.64</v>
+      </c>
+      <c r="I524" s="4">
+        <v>2586</v>
+      </c>
+      <c r="J524" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.2697961810007472E-2</v>
+      </c>
+      <c r="K524" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L524" s="15">
+        <v>0.74097222222222225</v>
+      </c>
+      <c r="M524" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47013888888888894</v>
+      </c>
+      <c r="N524" s="4">
+        <v>144822</v>
+      </c>
+      <c r="O524" s="4">
+        <v>144874</v>
+      </c>
+      <c r="P524" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>52</v>
+      </c>
+      <c r="Q524" s="4">
+        <v>359</v>
+      </c>
+      <c r="R524" s="4">
+        <v>38</v>
+      </c>
+      <c r="S524" s="4">
+        <v>28</v>
+      </c>
+      <c r="T524" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>10</v>
+      </c>
+      <c r="U524" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.73684210526315785</v>
+      </c>
+      <c r="V524" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W524" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X524" s="4">
+        <v>10</v>
+      </c>
+      <c r="Y524" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="525" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A525" s="8">
+        <v>46308</v>
+      </c>
+      <c r="B525" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C525" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D525" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E525" s="4">
+        <v>1</v>
+      </c>
+      <c r="F525" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Manoel</v>
+      </c>
+      <c r="G525" s="10">
+        <v>303.91000000000003</v>
+      </c>
+      <c r="H525" s="10">
+        <v>3447.53</v>
+      </c>
+      <c r="I525" s="4">
+        <v>55</v>
+      </c>
+      <c r="J525" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.8152967486867406E-2</v>
+      </c>
+      <c r="K525" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L525" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="M525" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.1875</v>
+      </c>
+      <c r="N525" s="4">
+        <v>63919</v>
+      </c>
+      <c r="O525" s="4">
+        <v>63949</v>
+      </c>
+      <c r="P525" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>30</v>
+      </c>
+      <c r="Q525" s="4">
+        <v>6</v>
+      </c>
+      <c r="R525" s="4">
+        <v>1</v>
+      </c>
+      <c r="S525" s="4">
+        <v>1</v>
+      </c>
+      <c r="T525" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U525" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V525" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W525" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X525" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y525" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="526" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A526" s="8">
+        <v>46308</v>
+      </c>
+      <c r="B526" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C526" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D526" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E526" s="4">
+        <v>11</v>
+      </c>
+      <c r="F526" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G526" s="10">
+        <v>18965.39</v>
+      </c>
+      <c r="H526" s="10">
+        <v>491416.8</v>
+      </c>
+      <c r="I526" s="4">
+        <v>2888</v>
+      </c>
+      <c r="J526" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.8593287815963967E-2</v>
+      </c>
+      <c r="K526" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L526" s="15">
+        <v>0.78333333333333333</v>
+      </c>
+      <c r="M526" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.51249999999999996</v>
+      </c>
+      <c r="N526" s="4">
+        <v>107056</v>
+      </c>
+      <c r="O526" s="4">
+        <v>107222</v>
+      </c>
+      <c r="P526" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>166</v>
+      </c>
+      <c r="Q526" s="4">
+        <v>230</v>
+      </c>
+      <c r="R526" s="4">
+        <v>24</v>
+      </c>
+      <c r="S526" s="4">
+        <v>24</v>
+      </c>
+      <c r="T526" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U526" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V526" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W526" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X526" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y526" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="527" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A527" s="8">
+        <v>46308</v>
+      </c>
+      <c r="B527" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C527" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D527" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E527" s="4">
+        <v>5</v>
+      </c>
+      <c r="F527" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G527" s="10">
+        <v>9205</v>
+      </c>
+      <c r="H527" s="10">
+        <v>119510.17</v>
+      </c>
+      <c r="I527" s="4">
+        <v>918</v>
+      </c>
+      <c r="J527" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.7022733713791897E-2</v>
+      </c>
+      <c r="K527" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L527" s="15">
+        <v>0.70138888888888884</v>
+      </c>
+      <c r="M527" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.40972222222222215</v>
+      </c>
+      <c r="N527" s="4">
+        <v>126935</v>
+      </c>
+      <c r="O527" s="4">
+        <v>127015</v>
+      </c>
+      <c r="P527" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>80</v>
+      </c>
+      <c r="Q527" s="4">
+        <v>119</v>
+      </c>
+      <c r="R527" s="4">
+        <v>24</v>
+      </c>
+      <c r="S527" s="4">
+        <v>23</v>
+      </c>
+      <c r="T527" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>1</v>
+      </c>
+      <c r="U527" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="V527" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W527" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X527" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y527" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="528" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A528" s="8">
+        <v>46308</v>
+      </c>
+      <c r="B528" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C528" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D528" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E528" s="4">
+        <v>1</v>
+      </c>
+      <c r="F528" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G528" s="10">
+        <v>3047.73</v>
+      </c>
+      <c r="H528" s="10">
+        <v>50931.76</v>
+      </c>
+      <c r="I528" s="4">
+        <v>1047</v>
+      </c>
+      <c r="J528" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.9839479334701962E-2</v>
+      </c>
+      <c r="K528" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L528" s="15">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="M528" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="N528" s="4">
+        <v>292517</v>
+      </c>
+      <c r="O528" s="4">
+        <v>292552</v>
+      </c>
+      <c r="P528" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>35</v>
+      </c>
+      <c r="Q528" s="4">
+        <v>97</v>
+      </c>
+      <c r="R528" s="4">
+        <v>4</v>
+      </c>
+      <c r="S528" s="4">
+        <v>4</v>
+      </c>
+      <c r="T528" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U528" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V528" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W528" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X528" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y528" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A529" s="8">
+        <v>46308</v>
+      </c>
+      <c r="B529" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C529" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D529" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E529" s="4">
+        <v>3</v>
+      </c>
+      <c r="F529" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G529" s="10">
+        <v>9400.43</v>
+      </c>
+      <c r="H529" s="10">
+        <v>191038.47</v>
+      </c>
+      <c r="I529" s="4">
+        <v>1711</v>
+      </c>
+      <c r="J529" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.9207000035123814E-2</v>
+      </c>
+      <c r="K529" s="11">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L529" s="15">
+        <v>0.79513888888888884</v>
+      </c>
+      <c r="M529" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.46180555555555552</v>
+      </c>
+      <c r="N529" s="4">
+        <v>282030</v>
+      </c>
+      <c r="O529" s="4">
+        <v>282098</v>
+      </c>
+      <c r="P529" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>68</v>
+      </c>
+      <c r="Q529" s="4">
+        <v>257</v>
+      </c>
+      <c r="R529" s="4">
+        <v>22</v>
+      </c>
+      <c r="S529" s="4">
+        <v>15</v>
+      </c>
+      <c r="T529" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>7</v>
+      </c>
+      <c r="U529" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.68181818181818177</v>
+      </c>
+      <c r="V529" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W529" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X529" s="4">
+        <v>8</v>
+      </c>
+      <c r="Y529" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="530" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A530" s="8">
+        <v>46308</v>
+      </c>
+      <c r="B530" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C530" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D530" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E530" s="4">
+        <v>1</v>
+      </c>
+      <c r="F530" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G530" s="10">
+        <v>7143.37</v>
+      </c>
+      <c r="H530" s="10">
+        <v>170266.68</v>
+      </c>
+      <c r="I530" s="4">
+        <v>2088</v>
+      </c>
+      <c r="J530" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.1954010027093966E-2</v>
+      </c>
+      <c r="K530" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L530" s="15">
+        <v>0.87013888888888891</v>
+      </c>
+      <c r="M530" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.55763888888888891</v>
+      </c>
+      <c r="N530" s="4">
+        <v>306252</v>
+      </c>
+      <c r="O530" s="4">
+        <v>306371</v>
+      </c>
+      <c r="P530" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>119</v>
+      </c>
+      <c r="Q530" s="4">
+        <v>131</v>
+      </c>
+      <c r="R530" s="4">
+        <v>20</v>
+      </c>
+      <c r="S530" s="4">
+        <v>14</v>
+      </c>
+      <c r="T530" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>6</v>
+      </c>
+      <c r="U530" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.7</v>
+      </c>
+      <c r="V530" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W530" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X530" s="4">
+        <v>6</v>
+      </c>
+      <c r="Y530" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="531" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A531" s="8">
+        <v>46308</v>
+      </c>
+      <c r="B531" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C531" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D531" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E531" s="4">
+        <v>4</v>
+      </c>
+      <c r="F531" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G531" s="10">
+        <v>1999.41</v>
+      </c>
+      <c r="H531" s="10">
+        <v>47673.84</v>
+      </c>
+      <c r="I531" s="4">
+        <v>775</v>
+      </c>
+      <c r="J531" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.1939352902975728E-2</v>
+      </c>
+      <c r="K531" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L531" s="15">
+        <v>0.75694444444444442</v>
+      </c>
+      <c r="M531" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="N531" s="4">
+        <v>120940</v>
+      </c>
+      <c r="O531" s="4">
+        <v>120995</v>
+      </c>
+      <c r="P531" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>55</v>
+      </c>
+      <c r="Q531" s="4">
+        <v>175</v>
+      </c>
+      <c r="R531" s="4">
+        <v>10</v>
+      </c>
+      <c r="S531" s="4">
+        <v>10</v>
+      </c>
+      <c r="T531" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U531" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V531" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W531" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X531" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y531" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A532" s="8">
+        <v>46308</v>
+      </c>
+      <c r="B532" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C532" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D532" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E532" s="4">
+        <v>1</v>
+      </c>
+      <c r="F532" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G532" s="10">
+        <v>6267.12</v>
+      </c>
+      <c r="H532" s="10">
+        <v>365974.7</v>
+      </c>
+      <c r="I532" s="4">
+        <v>618</v>
+      </c>
+      <c r="J532" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>1.712446242868701E-2</v>
+      </c>
+      <c r="K532" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L532" s="15">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="M532" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.46874999999999994</v>
+      </c>
+      <c r="N532" s="4">
+        <v>276917</v>
+      </c>
+      <c r="O532" s="4">
+        <v>276963</v>
+      </c>
+      <c r="P532" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>46</v>
+      </c>
+      <c r="Q532" s="4">
+        <v>167</v>
+      </c>
+      <c r="R532" s="4">
+        <v>7</v>
+      </c>
+      <c r="S532" s="4">
+        <v>7</v>
+      </c>
+      <c r="T532" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U532" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V532" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W532" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X532" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y532" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A533" s="8">
+        <v>46308</v>
+      </c>
+      <c r="B533" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C533" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D533" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E533" s="4">
+        <v>3</v>
+      </c>
+      <c r="F533" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G533" s="10">
+        <v>7340.19</v>
+      </c>
+      <c r="H533" s="10">
+        <v>77754.899999999994</v>
+      </c>
+      <c r="I533" s="4">
+        <v>2073</v>
+      </c>
+      <c r="J533" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>9.440163899638479E-2</v>
+      </c>
+      <c r="K533" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L533" s="15">
+        <v>0.76388888888888884</v>
+      </c>
+      <c r="M533" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45138888888888884</v>
+      </c>
+      <c r="N533" s="4">
+        <v>14782</v>
+      </c>
+      <c r="O533" s="4">
+        <v>14835</v>
+      </c>
+      <c r="P533" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>53</v>
+      </c>
+      <c r="Q533" s="4">
+        <v>106</v>
+      </c>
+      <c r="R533" s="4">
+        <v>14</v>
+      </c>
+      <c r="S533" s="4">
+        <v>14</v>
+      </c>
+      <c r="T533" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U533" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V533" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W533" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X533" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y533" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J522">
-    <cfRule type="cellIs" dxfId="21" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="J2:J533">
+    <cfRule type="cellIs" dxfId="65" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="64" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U522">
-    <cfRule type="cellIs" dxfId="19" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="U2:U533">
+    <cfRule type="cellIs" dxfId="63" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="62" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="61" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="60" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="59" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="57" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V522">
-    <cfRule type="expression" dxfId="12" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="V2:V533">
+    <cfRule type="expression" dxfId="56" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -49286,7 +50262,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -49302,7 +50278,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D522</xm:sqref>
+          <xm:sqref>D2:D533</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{897FDDB8-4589-406F-9D57-74B66091774D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F10287B3-53A4-404B-BD01-484547CB70DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1237" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="103">
   <si>
     <t>Data</t>
   </si>
@@ -347,6 +347,12 @@
   <si>
     <t>13,13,13,13,13,13</t>
   </si>
+  <si>
+    <t>13,13,13,13,13,13,13,13,13,13,13,13,13,13,13,13,13,38</t>
+  </si>
+  <si>
+    <t>38,38,38,38,38,38,38,38,38</t>
+  </si>
 </sst>
 </file>
 
@@ -549,7 +555,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -623,6 +629,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -632,7 +641,161 @@
     <cellStyle name="Normal 2 2 2" xfId="3" xr:uid="{F6D7429B-6BC2-41D1-B818-FB0128371036}"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="134">
+  <dxfs count="156">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -2147,94 +2310,94 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V27" totalsRowShown="0" headerRowDxfId="133" dataDxfId="131" headerRowBorderDxfId="132" tableBorderDxfId="130" totalsRowBorderDxfId="129" headerRowCellStyle="Normal 2 2 2">
-  <autoFilter ref="A1:V27" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V30" totalsRowShown="0" headerRowDxfId="155" dataDxfId="153" headerRowBorderDxfId="154" tableBorderDxfId="152" totalsRowBorderDxfId="151" headerRowCellStyle="Normal 2 2 2">
+  <autoFilter ref="A1:V30" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="128"/>
-    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="127"/>
-    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="126"/>
-    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="125"/>
-    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="124" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="123" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="122"/>
-    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="121" dataCellStyle="Porcentagem">
+    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="150"/>
+    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="149"/>
+    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="148"/>
+    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="147"/>
+    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="146" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="145" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="144"/>
+    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="143" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="120"/>
-    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="119"/>
-    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="118">
+    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="142"/>
+    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="141"/>
+    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="140">
       <calculatedColumnFormula>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="117" dataCellStyle="Moeda"/>
-    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="116" dataCellStyle="Porcentagem">
+    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="139" dataCellStyle="Moeda"/>
+    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="138" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="115"/>
-    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="114"/>
-    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="113"/>
-    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="112">
+    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="137"/>
+    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="136"/>
+    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="135"/>
+    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="134">
       <calculatedColumnFormula>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="111" dataCellStyle="Moeda 2 2">
+    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="133" dataCellStyle="Moeda 2 2">
       <calculatedColumnFormula>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="110" dataCellStyle="Moeda 3">
+    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="132" dataCellStyle="Moeda 3">
       <calculatedColumnFormula>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="109"/>
-    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="108"/>
-    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="107"/>
+    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="131"/>
+    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="130"/>
+    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="129"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y533" totalsRowShown="0" headerRowDxfId="106" dataDxfId="104" headerRowBorderDxfId="105" tableBorderDxfId="103" totalsRowBorderDxfId="102">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y559" totalsRowShown="0" headerRowDxfId="128" dataDxfId="126" headerRowBorderDxfId="127" tableBorderDxfId="125" totalsRowBorderDxfId="124">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="101"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="100">
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="123"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="122">
       <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="99">
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="121">
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="98"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="97"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="96">
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="120"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="119"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="118">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="95" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="94" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="93"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="92" dataCellStyle="Normal 2 2 2">
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="117" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="116" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="115"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="114" dataCellStyle="Normal 2 2 2">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="91"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="90"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="89">
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="113"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="112"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="111">
       <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="88"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="87"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="86">
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="110"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="109"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="108">
       <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="85"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="84"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="83"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="82">
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="107"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="106"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="105"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="104">
       <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="81" dataCellStyle="Moeda">
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="103" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="80">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="102">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="79"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="78"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="77"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="101"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="100"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="99"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2663,7 +2826,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A050DE7D-8F3F-47CF-9E37-B95AFD2ED76A}">
-  <dimension ref="A1:V27"/>
+  <dimension ref="A1:V30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="23" bestFit="1" customWidth="1"/>
@@ -4311,40 +4474,218 @@
       <c r="U27" s="4"/>
       <c r="V27" s="5"/>
     </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A28" s="8">
+        <v>46309</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" s="10">
+        <v>9402.9500000000007</v>
+      </c>
+      <c r="F28" s="10">
+        <v>196694.44</v>
+      </c>
+      <c r="G28" s="4">
+        <v>2046</v>
+      </c>
+      <c r="H28" s="9">
+        <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
+        <v>4.7804859151077177E-2</v>
+      </c>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4">
+        <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
+        <v>0</v>
+      </c>
+      <c r="L28" s="10">
+        <v>500</v>
+      </c>
+      <c r="M28" s="9">
+        <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
+        <v>5.31748015250533E-2</v>
+      </c>
+      <c r="N28" s="4">
+        <v>432</v>
+      </c>
+      <c r="O28" s="4">
+        <v>33</v>
+      </c>
+      <c r="P28" s="4">
+        <v>32</v>
+      </c>
+      <c r="Q28" s="12">
+        <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
+        <v>1</v>
+      </c>
+      <c r="R28" s="13">
+        <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
+        <v>0.96969696969696972</v>
+      </c>
+      <c r="S28" s="14" t="str">
+        <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="T28" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="U28" s="4">
+        <v>1</v>
+      </c>
+      <c r="V28" s="5">
+        <v>13.38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A29" s="8">
+        <v>46310</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" s="27">
+        <v>3879.95</v>
+      </c>
+      <c r="F29" s="27">
+        <v>86853.79</v>
+      </c>
+      <c r="G29" s="4">
+        <v>623</v>
+      </c>
+      <c r="H29" s="9">
+        <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
+        <v>4.4672201408827411E-2</v>
+      </c>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4">
+        <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
+        <v>0</v>
+      </c>
+      <c r="L29" s="10">
+        <v>500</v>
+      </c>
+      <c r="M29" s="9">
+        <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
+        <v>0.12886764004690782</v>
+      </c>
+      <c r="N29" s="4">
+        <v>98</v>
+      </c>
+      <c r="O29" s="4">
+        <v>22</v>
+      </c>
+      <c r="P29" s="4">
+        <v>22</v>
+      </c>
+      <c r="Q29" s="12">
+        <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="R29" s="13">
+        <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="S29" s="14" t="str">
+        <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="T29" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="U29" s="4">
+        <v>0</v>
+      </c>
+      <c r="V29" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="9" t="e">
+        <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4">
+        <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
+        <v>0</v>
+      </c>
+      <c r="L30" s="10"/>
+      <c r="M30" s="9" t="e">
+        <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="4"/>
+      <c r="Q30" s="12">
+        <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="R30" s="13" t="e">
+        <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S30" s="14" t="e">
+        <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T30" s="4"/>
+      <c r="U30" s="4"/>
+      <c r="V30" s="5"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H27">
-    <cfRule type="cellIs" dxfId="76" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="H2:H30">
+    <cfRule type="cellIs" dxfId="98" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="97" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R27">
-    <cfRule type="cellIs" dxfId="74" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="R2:R30">
+    <cfRule type="cellIs" dxfId="96" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="95" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="94" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="93" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="92" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="91" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="90" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S27">
-    <cfRule type="expression" dxfId="67" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="S2:S30">
+    <cfRule type="expression" dxfId="89" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -4353,7 +4694,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="88" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4367,7 +4708,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y533"/>
+  <dimension ref="A1:Y559"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -49278,11 +49619,11 @@
       <c r="A523" s="8">
         <v>46308</v>
       </c>
-      <c r="B523" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C523" s="26">
+      <c r="B523" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C523" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -49364,11 +49705,11 @@
       <c r="A524" s="8">
         <v>46308</v>
       </c>
-      <c r="B524" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C524" s="26">
+      <c r="B524" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C524" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -49450,11 +49791,11 @@
       <c r="A525" s="8">
         <v>46308</v>
       </c>
-      <c r="B525" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C525" s="26">
+      <c r="B525" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C525" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -49536,11 +49877,11 @@
       <c r="A526" s="8">
         <v>46308</v>
       </c>
-      <c r="B526" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C526" s="26">
+      <c r="B526" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C526" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -49622,11 +49963,11 @@
       <c r="A527" s="8">
         <v>46308</v>
       </c>
-      <c r="B527" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C527" s="26">
+      <c r="B527" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C527" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -49708,11 +50049,11 @@
       <c r="A528" s="8">
         <v>46308</v>
       </c>
-      <c r="B528" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C528" s="26">
+      <c r="B528" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C528" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -49794,11 +50135,11 @@
       <c r="A529" s="8">
         <v>46308</v>
       </c>
-      <c r="B529" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C529" s="26">
+      <c r="B529" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C529" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -49880,11 +50221,11 @@
       <c r="A530" s="8">
         <v>46308</v>
       </c>
-      <c r="B530" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C530" s="26">
+      <c r="B530" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C530" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -49966,11 +50307,11 @@
       <c r="A531" s="8">
         <v>46308</v>
       </c>
-      <c r="B531" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C531" s="26">
+      <c r="B531" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C531" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -50052,11 +50393,11 @@
       <c r="A532" s="8">
         <v>46308</v>
       </c>
-      <c r="B532" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C532" s="26">
+      <c r="B532" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C532" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -50138,11 +50479,11 @@
       <c r="A533" s="8">
         <v>46308</v>
       </c>
-      <c r="B533" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C533" s="26">
+      <c r="B533" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C533" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -50220,40 +50561,2276 @@
         <v>0</v>
       </c>
     </row>
+    <row r="534" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A534" s="8">
+        <v>46309</v>
+      </c>
+      <c r="B534" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C534" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D534" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E534" s="4">
+        <v>1</v>
+      </c>
+      <c r="F534" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G534" s="10">
+        <v>1098.01</v>
+      </c>
+      <c r="H534" s="10">
+        <v>20422.439999999999</v>
+      </c>
+      <c r="I534" s="4">
+        <v>46</v>
+      </c>
+      <c r="J534" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.3764878241777184E-2</v>
+      </c>
+      <c r="K534" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L534" s="15">
+        <v>0.46527777777777779</v>
+      </c>
+      <c r="M534" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.15277777777777779</v>
+      </c>
+      <c r="N534" s="4">
+        <v>157213</v>
+      </c>
+      <c r="O534" s="4">
+        <v>157244</v>
+      </c>
+      <c r="P534" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>31</v>
+      </c>
+      <c r="Q534" s="4">
+        <v>13</v>
+      </c>
+      <c r="R534" s="4">
+        <v>2</v>
+      </c>
+      <c r="S534" s="4">
+        <v>2</v>
+      </c>
+      <c r="T534" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U534" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V534" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W534" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X534" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y534" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="535" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A535" s="8">
+        <v>46309</v>
+      </c>
+      <c r="B535" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C535" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D535" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E535" s="4">
+        <v>1</v>
+      </c>
+      <c r="F535" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G535" s="10">
+        <v>252.53</v>
+      </c>
+      <c r="H535" s="10">
+        <v>4830.92</v>
+      </c>
+      <c r="I535" s="4">
+        <v>52</v>
+      </c>
+      <c r="J535" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.2273686999577719E-2</v>
+      </c>
+      <c r="K535" s="11">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="L535" s="15">
+        <v>0.69305555555555554</v>
+      </c>
+      <c r="M535" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.15138888888888891</v>
+      </c>
+      <c r="N535" s="4">
+        <v>157244</v>
+      </c>
+      <c r="O535" s="4">
+        <v>157271</v>
+      </c>
+      <c r="P535" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>27</v>
+      </c>
+      <c r="Q535" s="4">
+        <v>8</v>
+      </c>
+      <c r="R535" s="4">
+        <v>1</v>
+      </c>
+      <c r="S535" s="4">
+        <v>1</v>
+      </c>
+      <c r="T535" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U535" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V535" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W535" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="X535" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y535" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="536" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A536" s="8">
+        <v>46309</v>
+      </c>
+      <c r="B536" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C536" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D536" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E536" s="4">
+        <v>1</v>
+      </c>
+      <c r="F536" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G536" s="10">
+        <v>11128.1</v>
+      </c>
+      <c r="H536" s="10">
+        <v>187786.85</v>
+      </c>
+      <c r="I536" s="4">
+        <v>1893</v>
+      </c>
+      <c r="J536" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.925920797968548E-2</v>
+      </c>
+      <c r="K536" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L536" s="15">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="M536" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.24999999999999994</v>
+      </c>
+      <c r="N536" s="4">
+        <v>276963</v>
+      </c>
+      <c r="O536" s="4">
+        <v>276973</v>
+      </c>
+      <c r="P536" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>10</v>
+      </c>
+      <c r="Q536" s="4">
+        <v>126</v>
+      </c>
+      <c r="R536" s="4">
+        <v>15</v>
+      </c>
+      <c r="S536" s="4">
+        <v>15</v>
+      </c>
+      <c r="T536" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U536" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V536" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W536" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="X536" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y536" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="537" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A537" s="8">
+        <v>46309</v>
+      </c>
+      <c r="B537" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C537" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D537" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E537" s="4">
+        <v>1</v>
+      </c>
+      <c r="F537" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G537" s="10">
+        <v>8095.23</v>
+      </c>
+      <c r="H537" s="10">
+        <v>137132.24</v>
+      </c>
+      <c r="I537" s="4">
+        <v>1131</v>
+      </c>
+      <c r="J537" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.9032288833027156E-2</v>
+      </c>
+      <c r="K537" s="11">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="L537" s="15">
+        <v>0.80069444444444449</v>
+      </c>
+      <c r="M537" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.25902777777777786</v>
+      </c>
+      <c r="N537" s="4">
+        <v>276973</v>
+      </c>
+      <c r="O537" s="4">
+        <v>277016</v>
+      </c>
+      <c r="P537" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>43</v>
+      </c>
+      <c r="Q537" s="4">
+        <v>22</v>
+      </c>
+      <c r="R537" s="4">
+        <v>3</v>
+      </c>
+      <c r="S537" s="4">
+        <v>3</v>
+      </c>
+      <c r="T537" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U537" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V537" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W537" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X537" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y537" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="538" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A538" s="8">
+        <v>46309</v>
+      </c>
+      <c r="B538" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C538" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D538" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E538" s="4">
+        <v>1</v>
+      </c>
+      <c r="F538" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Manoel</v>
+      </c>
+      <c r="G538" s="10">
+        <v>150.69</v>
+      </c>
+      <c r="H538" s="10">
+        <v>2452.3200000000002</v>
+      </c>
+      <c r="I538" s="4">
+        <v>28</v>
+      </c>
+      <c r="J538" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.1447935016637305E-2</v>
+      </c>
+      <c r="K538" s="11">
+        <v>0.34027777777777779</v>
+      </c>
+      <c r="L538" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="M538" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.15972222222222221</v>
+      </c>
+      <c r="N538" s="4">
+        <v>64003</v>
+      </c>
+      <c r="O538" s="4">
+        <v>64090</v>
+      </c>
+      <c r="P538" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>87</v>
+      </c>
+      <c r="Q538" s="4">
+        <v>4</v>
+      </c>
+      <c r="R538" s="4">
+        <v>1</v>
+      </c>
+      <c r="S538" s="4">
+        <v>1</v>
+      </c>
+      <c r="T538" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U538" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V538" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W538" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="X538" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y538" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="539" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A539" s="8">
+        <v>46309</v>
+      </c>
+      <c r="B539" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C539" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D539" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E539" s="4">
+        <v>2</v>
+      </c>
+      <c r="F539" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G539" s="10">
+        <v>14455.55</v>
+      </c>
+      <c r="H539" s="10">
+        <v>238709.99</v>
+      </c>
+      <c r="I539" s="4">
+        <v>309</v>
+      </c>
+      <c r="J539" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.0556954486906893E-2</v>
+      </c>
+      <c r="K539" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L539" s="15">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M539" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="N539" s="4">
+        <v>144874</v>
+      </c>
+      <c r="O539" s="4">
+        <v>144928</v>
+      </c>
+      <c r="P539" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>54</v>
+      </c>
+      <c r="Q539" s="4">
+        <v>309</v>
+      </c>
+      <c r="R539" s="4">
+        <v>49</v>
+      </c>
+      <c r="S539" s="4">
+        <v>32</v>
+      </c>
+      <c r="T539" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>17</v>
+      </c>
+      <c r="U539" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.65306122448979587</v>
+      </c>
+      <c r="V539" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W539" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X539" s="4">
+        <v>17</v>
+      </c>
+      <c r="Y539" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="540" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A540" s="8">
+        <v>46309</v>
+      </c>
+      <c r="B540" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C540" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D540" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E540" s="4">
+        <v>3</v>
+      </c>
+      <c r="F540" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G540" s="10">
+        <v>13122.86</v>
+      </c>
+      <c r="H540" s="10">
+        <v>207843.31</v>
+      </c>
+      <c r="I540" s="4">
+        <v>384</v>
+      </c>
+      <c r="J540" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.3138236203031994E-2</v>
+      </c>
+      <c r="K540" s="11">
+        <v>0.2951388888888889</v>
+      </c>
+      <c r="L540" s="15">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="M540" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47569444444444448</v>
+      </c>
+      <c r="N540" s="4">
+        <v>282092</v>
+      </c>
+      <c r="O540" s="4">
+        <v>282155</v>
+      </c>
+      <c r="P540" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>63</v>
+      </c>
+      <c r="Q540" s="4">
+        <v>384</v>
+      </c>
+      <c r="R540" s="4">
+        <v>23</v>
+      </c>
+      <c r="S540" s="4">
+        <v>23</v>
+      </c>
+      <c r="T540" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U540" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V540" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W540" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X540" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y540" s="5">
+        <v>38.380000000000003</v>
+      </c>
+    </row>
+    <row r="541" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A541" s="8">
+        <v>46309</v>
+      </c>
+      <c r="B541" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C541" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D541" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E541" s="4">
+        <v>5</v>
+      </c>
+      <c r="F541" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G541" s="10">
+        <v>7959.01</v>
+      </c>
+      <c r="H541" s="10">
+        <v>154841.13</v>
+      </c>
+      <c r="I541" s="4">
+        <v>1358</v>
+      </c>
+      <c r="J541" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.140113611932437E-2</v>
+      </c>
+      <c r="K541" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L541" s="15">
+        <v>0.82777777777777772</v>
+      </c>
+      <c r="M541" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.53611111111111098</v>
+      </c>
+      <c r="N541" s="4">
+        <v>127015</v>
+      </c>
+      <c r="O541" s="4">
+        <v>127114</v>
+      </c>
+      <c r="P541" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>99</v>
+      </c>
+      <c r="Q541" s="4">
+        <v>206</v>
+      </c>
+      <c r="R541" s="4">
+        <v>33</v>
+      </c>
+      <c r="S541" s="4">
+        <v>33</v>
+      </c>
+      <c r="T541" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U541" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V541" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W541" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X541" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y541" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="542" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A542" s="8">
+        <v>46309</v>
+      </c>
+      <c r="B542" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C542" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D542" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E542" s="4">
+        <v>11</v>
+      </c>
+      <c r="F542" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G542" s="10">
+        <v>14890.94</v>
+      </c>
+      <c r="H542" s="10">
+        <v>233814.87</v>
+      </c>
+      <c r="I542" s="4">
+        <v>1742</v>
+      </c>
+      <c r="J542" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.3686881848019336E-2</v>
+      </c>
+      <c r="K542" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L542" s="15">
+        <v>0.75416666666666665</v>
+      </c>
+      <c r="M542" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.48333333333333334</v>
+      </c>
+      <c r="N542" s="4">
+        <v>107222</v>
+      </c>
+      <c r="O542" s="4">
+        <v>107359</v>
+      </c>
+      <c r="P542" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>137</v>
+      </c>
+      <c r="Q542" s="4">
+        <v>263</v>
+      </c>
+      <c r="R542" s="4">
+        <v>55</v>
+      </c>
+      <c r="S542" s="4">
+        <v>55</v>
+      </c>
+      <c r="T542" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U542" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V542" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W542" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X542" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y542" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="543" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A543" s="8">
+        <v>46309</v>
+      </c>
+      <c r="B543" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C543" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D543" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E543" s="4">
+        <v>1</v>
+      </c>
+      <c r="F543" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G543" s="10">
+        <v>6968.18</v>
+      </c>
+      <c r="H543" s="10">
+        <v>127048</v>
+      </c>
+      <c r="I543" s="4">
+        <v>1036</v>
+      </c>
+      <c r="J543" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.4846829544738997E-2</v>
+      </c>
+      <c r="K543" s="11">
+        <v>0.31805555555555554</v>
+      </c>
+      <c r="L543" s="15">
+        <v>0.77569444444444446</v>
+      </c>
+      <c r="M543" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45763888888888893</v>
+      </c>
+      <c r="N543" s="4">
+        <v>14836</v>
+      </c>
+      <c r="O543" s="4">
+        <v>14887</v>
+      </c>
+      <c r="P543" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>51</v>
+      </c>
+      <c r="Q543" s="4">
+        <v>128</v>
+      </c>
+      <c r="R543" s="4">
+        <v>20</v>
+      </c>
+      <c r="S543" s="4">
+        <v>20</v>
+      </c>
+      <c r="T543" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U543" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V543" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W543" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X543" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y543" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="544" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A544" s="8">
+        <v>46309</v>
+      </c>
+      <c r="B544" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C544" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D544" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E544" s="4">
+        <v>5</v>
+      </c>
+      <c r="F544" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G544" s="10">
+        <v>6502.31</v>
+      </c>
+      <c r="H544" s="10">
+        <v>265619.03000000003</v>
+      </c>
+      <c r="I544" s="4">
+        <v>1193</v>
+      </c>
+      <c r="J544" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.447983489737162E-2</v>
+      </c>
+      <c r="K544" s="11">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L544" s="15">
+        <v>0.74305555555555558</v>
+      </c>
+      <c r="M544" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.40972222222222227</v>
+      </c>
+      <c r="N544" s="4">
+        <v>120995</v>
+      </c>
+      <c r="O544" s="4">
+        <v>121026</v>
+      </c>
+      <c r="P544" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>31</v>
+      </c>
+      <c r="Q544" s="4">
+        <v>90</v>
+      </c>
+      <c r="R544" s="4">
+        <v>6</v>
+      </c>
+      <c r="S544" s="4">
+        <v>6</v>
+      </c>
+      <c r="T544" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U544" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V544" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W544" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X544" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y544" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="545" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A545" s="8">
+        <v>46309</v>
+      </c>
+      <c r="B545" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C545" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D545" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E545" s="4">
+        <v>1</v>
+      </c>
+      <c r="F545" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G545" s="10">
+        <v>3867.98</v>
+      </c>
+      <c r="H545" s="10">
+        <v>64157.66</v>
+      </c>
+      <c r="I545" s="4">
+        <v>614</v>
+      </c>
+      <c r="J545" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.0288670129178649E-2</v>
+      </c>
+      <c r="K545" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L545" s="15">
+        <v>0.78263888888888888</v>
+      </c>
+      <c r="M545" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47013888888888888</v>
+      </c>
+      <c r="N545" s="4">
+        <v>306371</v>
+      </c>
+      <c r="O545" s="4">
+        <v>306473</v>
+      </c>
+      <c r="P545" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>102</v>
+      </c>
+      <c r="Q545" s="4">
+        <v>68</v>
+      </c>
+      <c r="R545" s="4">
+        <v>11</v>
+      </c>
+      <c r="S545" s="4">
+        <v>11</v>
+      </c>
+      <c r="T545" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U545" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V545" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W545" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X545" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y545" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="546" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A546" s="8">
+        <v>46309</v>
+      </c>
+      <c r="B546" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C546" s="16">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D546" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E546" s="4">
+        <v>1</v>
+      </c>
+      <c r="F546" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G546" s="10">
+        <v>4424.1499999999996</v>
+      </c>
+      <c r="H546" s="10">
+        <v>63867.06</v>
+      </c>
+      <c r="I546" s="4">
+        <v>1147</v>
+      </c>
+      <c r="J546" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.9271233089483061E-2</v>
+      </c>
+      <c r="K546" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L546" s="15">
+        <v>0.70138888888888884</v>
+      </c>
+      <c r="M546" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.38888888888888884</v>
+      </c>
+      <c r="N546" s="4">
+        <v>292552</v>
+      </c>
+      <c r="O546" s="4">
+        <v>292587</v>
+      </c>
+      <c r="P546" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>35</v>
+      </c>
+      <c r="Q546" s="4">
+        <v>132</v>
+      </c>
+      <c r="R546" s="4">
+        <v>13</v>
+      </c>
+      <c r="S546" s="4">
+        <v>13</v>
+      </c>
+      <c r="T546" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U546" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V546" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W546" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X546" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y546" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="547" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A547" s="8">
+        <v>46310</v>
+      </c>
+      <c r="B547" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C547" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D547" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E547" s="4">
+        <v>1</v>
+      </c>
+      <c r="F547" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G547" s="10">
+        <v>3401.16</v>
+      </c>
+      <c r="H547" s="10">
+        <v>57085.32</v>
+      </c>
+      <c r="I547" s="4">
+        <v>463</v>
+      </c>
+      <c r="J547" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.9580291395406035E-2</v>
+      </c>
+      <c r="K547" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L547" s="15">
+        <v>0.76666666666666672</v>
+      </c>
+      <c r="M547" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45416666666666672</v>
+      </c>
+      <c r="N547" s="4">
+        <v>157271</v>
+      </c>
+      <c r="O547" s="4">
+        <v>157454</v>
+      </c>
+      <c r="P547" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>183</v>
+      </c>
+      <c r="Q547" s="4">
+        <v>76</v>
+      </c>
+      <c r="R547" s="4">
+        <v>13</v>
+      </c>
+      <c r="S547" s="4">
+        <v>13</v>
+      </c>
+      <c r="T547" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U547" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V547" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W547" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X547" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y547" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A548" s="8">
+        <v>46310</v>
+      </c>
+      <c r="B548" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C548" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D548" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E548" s="4">
+        <v>1</v>
+      </c>
+      <c r="F548" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G548" s="10">
+        <v>5719.08</v>
+      </c>
+      <c r="H548" s="10">
+        <v>171535.65</v>
+      </c>
+      <c r="I548" s="4">
+        <v>1197</v>
+      </c>
+      <c r="J548" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.3340474705986771E-2</v>
+      </c>
+      <c r="K548" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L548" s="15">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="M548" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.40624999999999994</v>
+      </c>
+      <c r="N548" s="4">
+        <v>277016</v>
+      </c>
+      <c r="O548" s="4">
+        <v>277067</v>
+      </c>
+      <c r="P548" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>51</v>
+      </c>
+      <c r="Q548" s="4">
+        <v>2</v>
+      </c>
+      <c r="R548" s="4">
+        <v>1</v>
+      </c>
+      <c r="S548" s="4">
+        <v>1</v>
+      </c>
+      <c r="T548" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U548" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V548" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W548" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X548" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y548" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="549" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A549" s="8">
+        <v>46310</v>
+      </c>
+      <c r="B549" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C549" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D549" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E549" s="4">
+        <v>1</v>
+      </c>
+      <c r="F549" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G549" s="10">
+        <v>544.91</v>
+      </c>
+      <c r="H549" s="10">
+        <v>21965.86</v>
+      </c>
+      <c r="I549" s="4">
+        <v>55</v>
+      </c>
+      <c r="J549" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.480713252292421E-2</v>
+      </c>
+      <c r="K549" s="11">
+        <v>0.66249999999999998</v>
+      </c>
+      <c r="L549" s="15">
+        <v>0.76666666666666672</v>
+      </c>
+      <c r="M549" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.10416666666666674</v>
+      </c>
+      <c r="N549" s="4">
+        <v>157454</v>
+      </c>
+      <c r="O549" s="4">
+        <v>157483</v>
+      </c>
+      <c r="P549" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>29</v>
+      </c>
+      <c r="Q549" s="4">
+        <v>16</v>
+      </c>
+      <c r="R549" s="4">
+        <v>2</v>
+      </c>
+      <c r="S549" s="4">
+        <v>2</v>
+      </c>
+      <c r="T549" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U549" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V549" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W549" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X549" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y549" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="550" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A550" s="8">
+        <v>46310</v>
+      </c>
+      <c r="B550" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C550" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D550" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E550" s="4">
+        <v>1</v>
+      </c>
+      <c r="F550" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Manoel</v>
+      </c>
+      <c r="G550" s="10">
+        <v>312.38</v>
+      </c>
+      <c r="H550" s="10">
+        <v>3803.2</v>
+      </c>
+      <c r="I550" s="4">
+        <v>30</v>
+      </c>
+      <c r="J550" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.2136095919225924E-2</v>
+      </c>
+      <c r="K550" s="11">
+        <v>0.31944444444444442</v>
+      </c>
+      <c r="L550" s="15">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="M550" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.1388888888888889</v>
+      </c>
+      <c r="N550" s="4">
+        <v>60148</v>
+      </c>
+      <c r="O550" s="4">
+        <v>60192</v>
+      </c>
+      <c r="P550" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>44</v>
+      </c>
+      <c r="Q550" s="4">
+        <v>1</v>
+      </c>
+      <c r="R550" s="4">
+        <v>1</v>
+      </c>
+      <c r="S550" s="4">
+        <v>1</v>
+      </c>
+      <c r="T550" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U550" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V550" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W550" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X550" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y550" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="551" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A551" s="8">
+        <v>46310</v>
+      </c>
+      <c r="B551" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C551" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D551" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E551" s="4">
+        <v>3</v>
+      </c>
+      <c r="F551" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Manoel</v>
+      </c>
+      <c r="G551" s="10">
+        <v>554.45000000000005</v>
+      </c>
+      <c r="H551" s="10">
+        <v>11397.52</v>
+      </c>
+      <c r="I551" s="4">
+        <v>103</v>
+      </c>
+      <c r="J551" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.8646547670019448E-2</v>
+      </c>
+      <c r="K551" s="11">
+        <v>0.5625</v>
+      </c>
+      <c r="L551" s="15">
+        <v>0.72152777777777777</v>
+      </c>
+      <c r="M551" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.15902777777777777</v>
+      </c>
+      <c r="N551" s="4">
+        <v>60192</v>
+      </c>
+      <c r="O551" s="4">
+        <v>60207</v>
+      </c>
+      <c r="P551" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>15</v>
+      </c>
+      <c r="Q551" s="4">
+        <v>22</v>
+      </c>
+      <c r="R551" s="4">
+        <v>2</v>
+      </c>
+      <c r="S551" s="4">
+        <v>2</v>
+      </c>
+      <c r="T551" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U551" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V551" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W551" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X551" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y551" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="552" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A552" s="8">
+        <v>46310</v>
+      </c>
+      <c r="B552" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C552" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D552" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E552" s="4">
+        <v>2</v>
+      </c>
+      <c r="F552" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G552" s="10">
+        <v>12671.38</v>
+      </c>
+      <c r="H552" s="10">
+        <v>232058.53</v>
+      </c>
+      <c r="I552" s="4">
+        <v>1736</v>
+      </c>
+      <c r="J552" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.4604241438571552E-2</v>
+      </c>
+      <c r="K552" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L552" s="15">
+        <v>0.71597222222222223</v>
+      </c>
+      <c r="M552" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44513888888888892</v>
+      </c>
+      <c r="N552" s="4">
+        <v>144928</v>
+      </c>
+      <c r="O552" s="4">
+        <v>144998</v>
+      </c>
+      <c r="P552" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>70</v>
+      </c>
+      <c r="Q552" s="4">
+        <v>309</v>
+      </c>
+      <c r="R552" s="4">
+        <v>47</v>
+      </c>
+      <c r="S552" s="4">
+        <v>47</v>
+      </c>
+      <c r="T552" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U552" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V552" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W552" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X552" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y552" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="553" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A553" s="8">
+        <v>46310</v>
+      </c>
+      <c r="B553" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C553" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D553" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E553" s="4">
+        <v>3</v>
+      </c>
+      <c r="F553" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G553" s="10">
+        <v>11255.22</v>
+      </c>
+      <c r="H553" s="10">
+        <v>144639.26</v>
+      </c>
+      <c r="I553" s="4">
+        <v>1186</v>
+      </c>
+      <c r="J553" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.7815801878411153E-2</v>
+      </c>
+      <c r="K553" s="11">
+        <v>0.3</v>
+      </c>
+      <c r="L553" s="15">
+        <v>0.74236111111111114</v>
+      </c>
+      <c r="M553" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44236111111111115</v>
+      </c>
+      <c r="N553" s="4">
+        <v>282155</v>
+      </c>
+      <c r="O553" s="4">
+        <v>282196</v>
+      </c>
+      <c r="P553" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>41</v>
+      </c>
+      <c r="Q553" s="4">
+        <v>162</v>
+      </c>
+      <c r="R553" s="4">
+        <v>42</v>
+      </c>
+      <c r="S553" s="4">
+        <v>42</v>
+      </c>
+      <c r="T553" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U553" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V553" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W553" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X553" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y553" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="554" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A554" s="8">
+        <v>46310</v>
+      </c>
+      <c r="B554" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C554" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D554" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E554" s="4">
+        <v>5</v>
+      </c>
+      <c r="F554" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G554" s="10">
+        <v>13722.62</v>
+      </c>
+      <c r="H554" s="10">
+        <v>195984.25</v>
+      </c>
+      <c r="I554" s="4">
+        <v>2983</v>
+      </c>
+      <c r="J554" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.0018993873232169E-2</v>
+      </c>
+      <c r="K554" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L554" s="15">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="M554" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.53125</v>
+      </c>
+      <c r="N554" s="4">
+        <v>127114</v>
+      </c>
+      <c r="O554" s="4">
+        <v>127217</v>
+      </c>
+      <c r="P554" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>103</v>
+      </c>
+      <c r="Q554" s="4">
+        <v>349</v>
+      </c>
+      <c r="R554" s="4">
+        <v>29</v>
+      </c>
+      <c r="S554" s="4">
+        <v>23</v>
+      </c>
+      <c r="T554" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>6</v>
+      </c>
+      <c r="U554" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>0.7931034482758621</v>
+      </c>
+      <c r="V554" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="W554" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X554" s="4">
+        <v>6</v>
+      </c>
+      <c r="Y554" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="555" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A555" s="8">
+        <v>46310</v>
+      </c>
+      <c r="B555" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C555" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D555" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E555" s="4">
+        <v>5</v>
+      </c>
+      <c r="F555" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G555" s="10">
+        <v>23400.09</v>
+      </c>
+      <c r="H555" s="10">
+        <v>555992.39</v>
+      </c>
+      <c r="I555" s="4">
+        <v>5385</v>
+      </c>
+      <c r="J555" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.2087068853586283E-2</v>
+      </c>
+      <c r="K555" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L555" s="15">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="M555" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="N555" s="4">
+        <v>107359</v>
+      </c>
+      <c r="O555" s="4">
+        <v>107388</v>
+      </c>
+      <c r="P555" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>29</v>
+      </c>
+      <c r="Q555" s="4">
+        <v>544</v>
+      </c>
+      <c r="R555" s="4">
+        <v>31</v>
+      </c>
+      <c r="S555" s="4">
+        <v>31</v>
+      </c>
+      <c r="T555" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U555" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V555" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W555" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X555" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y555" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="556" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A556" s="8">
+        <v>46310</v>
+      </c>
+      <c r="B556" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C556" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D556" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E556" s="4">
+        <v>11</v>
+      </c>
+      <c r="F556" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G556" s="10">
+        <v>15815.19</v>
+      </c>
+      <c r="H556" s="10">
+        <v>247315.65</v>
+      </c>
+      <c r="I556" s="4">
+        <v>2462</v>
+      </c>
+      <c r="J556" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.3947388691334331E-2</v>
+      </c>
+      <c r="K556" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L556" s="15">
+        <v>0.73611111111111116</v>
+      </c>
+      <c r="M556" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44444444444444448</v>
+      </c>
+      <c r="N556" s="4">
+        <v>121036</v>
+      </c>
+      <c r="O556" s="4">
+        <v>121162</v>
+      </c>
+      <c r="P556" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>126</v>
+      </c>
+      <c r="Q556" s="4">
+        <v>525</v>
+      </c>
+      <c r="R556" s="4">
+        <v>32</v>
+      </c>
+      <c r="S556" s="4">
+        <v>32</v>
+      </c>
+      <c r="T556" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U556" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V556" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W556" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X556" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y556" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="557" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A557" s="8">
+        <v>46310</v>
+      </c>
+      <c r="B557" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C557" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D557" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E557" s="4">
+        <v>1</v>
+      </c>
+      <c r="F557" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G557" s="10">
+        <v>5875.38</v>
+      </c>
+      <c r="H557" s="10">
+        <v>107635.26</v>
+      </c>
+      <c r="I557" s="4">
+        <v>1146</v>
+      </c>
+      <c r="J557" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.4586015772154967E-2</v>
+      </c>
+      <c r="K557" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L557" s="15">
+        <v>0.73124999999999996</v>
+      </c>
+      <c r="M557" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.41874999999999996</v>
+      </c>
+      <c r="N557" s="4">
+        <v>292587</v>
+      </c>
+      <c r="O557" s="4">
+        <v>292657</v>
+      </c>
+      <c r="P557" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>70</v>
+      </c>
+      <c r="Q557" s="4">
+        <v>173</v>
+      </c>
+      <c r="R557" s="4">
+        <v>21</v>
+      </c>
+      <c r="S557" s="4">
+        <v>21</v>
+      </c>
+      <c r="T557" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U557" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V557" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W557" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X557" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y557" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="558" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A558" s="8">
+        <v>46310</v>
+      </c>
+      <c r="B558" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C558" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D558" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E558" s="4">
+        <v>1</v>
+      </c>
+      <c r="F558" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Wesley</v>
+      </c>
+      <c r="G558" s="10">
+        <v>11616.88</v>
+      </c>
+      <c r="H558" s="10">
+        <v>178265.55</v>
+      </c>
+      <c r="I558" s="4">
+        <v>1767</v>
+      </c>
+      <c r="J558" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.5166152405778902E-2</v>
+      </c>
+      <c r="K558" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L558" s="15">
+        <v>0.67013888888888884</v>
+      </c>
+      <c r="M558" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.35763888888888884</v>
+      </c>
+      <c r="N558" s="4">
+        <v>306473</v>
+      </c>
+      <c r="O558" s="4">
+        <v>306487</v>
+      </c>
+      <c r="P558" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>14</v>
+      </c>
+      <c r="Q558" s="4">
+        <v>288</v>
+      </c>
+      <c r="R558" s="4">
+        <v>36</v>
+      </c>
+      <c r="S558" s="4">
+        <v>36</v>
+      </c>
+      <c r="T558" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U558" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V558" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W558" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X558" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y558" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="559" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A559" s="8">
+        <v>46310</v>
+      </c>
+      <c r="B559" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C559" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D559" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E559" s="4">
+        <v>5</v>
+      </c>
+      <c r="F559" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G559" s="10">
+        <v>7760.6</v>
+      </c>
+      <c r="H559" s="10">
+        <v>89353.73</v>
+      </c>
+      <c r="I559" s="4">
+        <v>1241</v>
+      </c>
+      <c r="J559" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.6852557805924838E-2</v>
+      </c>
+      <c r="K559" s="11">
+        <v>0.30555555555555558</v>
+      </c>
+      <c r="L559" s="15">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="M559" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47222222222222221</v>
+      </c>
+      <c r="N559" s="4">
+        <v>14890</v>
+      </c>
+      <c r="O559" s="4">
+        <v>14920</v>
+      </c>
+      <c r="P559" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>30</v>
+      </c>
+      <c r="Q559" s="4">
+        <v>190</v>
+      </c>
+      <c r="R559" s="4">
+        <v>7</v>
+      </c>
+      <c r="S559" s="4">
+        <v>7</v>
+      </c>
+      <c r="T559" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U559" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V559" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W559" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X559" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y559" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J533">
-    <cfRule type="cellIs" dxfId="65" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="J2:J559">
+    <cfRule type="cellIs" dxfId="87" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="86" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U533">
-    <cfRule type="cellIs" dxfId="63" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="U2:U559">
+    <cfRule type="cellIs" dxfId="85" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="84" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="83" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="82" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="81" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="80" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="79" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V533">
-    <cfRule type="expression" dxfId="56" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="V2:V559">
+    <cfRule type="expression" dxfId="78" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -50262,7 +52839,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -50278,7 +52855,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D533</xm:sqref>
+          <xm:sqref>D2:D559</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F10287B3-53A4-404B-BD01-484547CB70DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD52F93-27D0-456E-9E05-76809CF36B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="107">
   <si>
     <t>Data</t>
   </si>
@@ -210,9 +210,6 @@
     <t>Osvaldo</t>
   </si>
   <si>
-    <t>Wesley</t>
-  </si>
-  <si>
     <t>Edilson</t>
   </si>
   <si>
@@ -352,6 +349,21 @@
   </si>
   <si>
     <t>38,38,38,38,38,38,38,38,38</t>
+  </si>
+  <si>
+    <t>38,38,38,38,38,38,38</t>
+  </si>
+  <si>
+    <t>9,21,42</t>
+  </si>
+  <si>
+    <t>13,13,9</t>
+  </si>
+  <si>
+    <t>Juscelino</t>
+  </si>
+  <si>
+    <t>bem</t>
   </si>
 </sst>
 </file>
@@ -641,546 +653,7 @@
     <cellStyle name="Normal 2 2 2" xfId="3" xr:uid="{F6D7429B-6BC2-41D1-B818-FB0128371036}"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="156">
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF00B050"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FFFF0000"/>
-        <family val="2"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="134">
     <dxf>
       <font>
         <b/>
@@ -1778,6 +1251,13 @@
       </border>
     </dxf>
     <dxf>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FF000000"/>
@@ -1795,13 +1275,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1837,6 +1310,391 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
     </dxf>
     <dxf>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2310,94 +2168,94 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V30" totalsRowShown="0" headerRowDxfId="155" dataDxfId="153" headerRowBorderDxfId="154" tableBorderDxfId="152" totalsRowBorderDxfId="151" headerRowCellStyle="Normal 2 2 2">
-  <autoFilter ref="A1:V30" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V31" totalsRowShown="0" headerRowDxfId="133" dataDxfId="131" headerRowBorderDxfId="132" tableBorderDxfId="130" totalsRowBorderDxfId="129" headerRowCellStyle="Normal 2 2 2">
+  <autoFilter ref="A1:V31" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="150"/>
-    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="149"/>
-    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="148"/>
-    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="147"/>
-    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="146" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="145" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="144"/>
-    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="143" dataCellStyle="Porcentagem">
+    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="128"/>
+    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="127"/>
+    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="126"/>
+    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="125"/>
+    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="124" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="123" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="122"/>
+    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="121" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="142"/>
-    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="141"/>
-    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="140">
+    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="120"/>
+    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="119"/>
+    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="118">
       <calculatedColumnFormula>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="139" dataCellStyle="Moeda"/>
-    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="138" dataCellStyle="Porcentagem">
+    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="117" dataCellStyle="Moeda"/>
+    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="116" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="137"/>
-    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="136"/>
-    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="135"/>
-    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="134">
+    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="115"/>
+    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="114"/>
+    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="113"/>
+    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="112">
       <calculatedColumnFormula>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="133" dataCellStyle="Moeda 2 2">
+    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="111" dataCellStyle="Moeda 2 2">
       <calculatedColumnFormula>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="132" dataCellStyle="Moeda 3">
+    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="110" dataCellStyle="Moeda 3">
       <calculatedColumnFormula>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="131"/>
-    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="130"/>
-    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="129"/>
+    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="109"/>
+    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="108"/>
+    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="107"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y559" totalsRowShown="0" headerRowDxfId="128" dataDxfId="126" headerRowBorderDxfId="127" tableBorderDxfId="125" totalsRowBorderDxfId="124">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y588" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50" headerRowBorderDxfId="48" tableBorderDxfId="49" totalsRowBorderDxfId="47">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="123"/>
-    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="122">
+    <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="46"/>
+    <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="45">
       <calculatedColumnFormula>YEAR(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="121">
+    <tableColumn id="5" xr3:uid="{90D6CF8C-ACE3-46EA-828E-BB258996DD8F}" name="Mês" dataDxfId="44">
       <calculatedColumnFormula>MONTH(Tabela32[[#This Row],[Data]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="120"/>
-    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="119"/>
-    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="118">
+    <tableColumn id="2" xr3:uid="{9E2D603E-103D-4F88-A5C8-5E9A03E2A3EE}" name="Placa" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{7935B67B-4456-42E7-8B2D-EAF1D5C1B4F9}" name="Rota" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{74C94A9C-B298-4701-847E-59C66BC8BBC2}" name="Motorista" dataDxfId="41">
       <calculatedColumnFormula>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="117" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="116" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="115"/>
-    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="114" dataCellStyle="Normal 2 2 2">
+    <tableColumn id="6" xr3:uid="{694C94D7-8F01-480E-AA0C-B9B0FA8D2345}" name="Valor Frete" dataDxfId="40" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{7D623530-7EED-4526-B289-B392FA2EF883}" name="Valor Mercadoria" dataDxfId="39" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{3D927A69-B557-47A5-A269-05DEBEF85C73}" name="Peso" dataDxfId="38"/>
+    <tableColumn id="9" xr3:uid="{69BC588C-6D01-4257-B2D9-CF2D843D1C40}" name="% Frete" dataDxfId="37" dataCellStyle="Normal 2 2 2">
       <calculatedColumnFormula>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="113"/>
-    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="112"/>
-    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="111">
+    <tableColumn id="10" xr3:uid="{FC8CD81E-7FD3-41D6-921B-F1A94EDAF621}" name="Hr Saida" dataDxfId="36"/>
+    <tableColumn id="11" xr3:uid="{3B907CC4-B262-4107-87FF-1E75280AC1BF}" name="Hr Chegada" dataDxfId="35"/>
+    <tableColumn id="12" xr3:uid="{ED725939-179A-4D21-873C-15774DD68F53}" name="Tempo" dataDxfId="34">
       <calculatedColumnFormula>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="110"/>
-    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="109"/>
-    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="108">
+    <tableColumn id="13" xr3:uid="{74EA350D-6976-4E2D-A058-0785043C5735}" name="Km Saída" dataDxfId="33"/>
+    <tableColumn id="14" xr3:uid="{496AFEAD-5BFE-466C-B0AF-20375AAEECFC}" name="Km Chegada" dataDxfId="32"/>
+    <tableColumn id="15" xr3:uid="{AB2841F1-639E-4525-98D9-0FAED04E102B}" name="Km/Dia" dataDxfId="31">
       <calculatedColumnFormula>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="107"/>
-    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="106"/>
-    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="105"/>
-    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="104">
+    <tableColumn id="16" xr3:uid="{D83FBC01-4652-43E1-B278-CE34A958D106}" name="Vols" dataDxfId="30"/>
+    <tableColumn id="17" xr3:uid="{CA7BF05C-1770-40EE-89A9-C80AA88EFC06}" name="Entregas" dataDxfId="29"/>
+    <tableColumn id="18" xr3:uid="{037F6348-AFD4-431D-99B0-8147EA9E213B}" name="Realizadas" dataDxfId="28"/>
+    <tableColumn id="19" xr3:uid="{196A1910-314C-450C-B67A-E51295FA6A18}" name=" Retornadas" dataDxfId="27">
       <calculatedColumnFormula>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="103" dataCellStyle="Moeda">
+    <tableColumn id="20" xr3:uid="{F0BBC004-BAAB-43E2-A50E-1DD3FAEFD5F0}" name="% Entrega" dataDxfId="26" dataCellStyle="Moeda">
       <calculatedColumnFormula>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="102">
+    <tableColumn id="21" xr3:uid="{BB53A276-7721-4934-9C42-DB7E1D2740B3}" name="Meta" dataDxfId="25">
       <calculatedColumnFormula>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="101"/>
-    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="100"/>
-    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="99"/>
+    <tableColumn id="22" xr3:uid="{CE1DD687-26CA-4D2F-BCFC-661EB14CAD0F}" name="Cidade Destino" dataDxfId="24"/>
+    <tableColumn id="23" xr3:uid="{F8FFD74E-1FF0-45CC-9EA9-8E8EA807957C}" name="Nfs Voltaram" dataDxfId="23"/>
+    <tableColumn id="24" xr3:uid="{2EC98F08-AFB3-40A3-B3CE-1C9A788E39CD}" name="Ocorrência" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2728,7 +2586,7 @@
         <v>22</v>
       </c>
       <c r="B1" t="s">
-        <v>55</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -2736,7 +2594,7 @@
         <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2752,7 +2610,7 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2760,7 +2618,7 @@
         <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2800,12 +2658,12 @@
         <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B11" t="s">
         <v>38</v>
@@ -2826,7 +2684,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A050DE7D-8F3F-47CF-9E37-B95AFD2ED76A}">
-  <dimension ref="A1:V30"/>
+  <dimension ref="A1:V31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="23" bestFit="1" customWidth="1"/>
@@ -2993,11 +2851,11 @@
         <v>46238</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E3" s="10">
         <v>7461.93</v>
@@ -3315,11 +3173,11 @@
         <v>46253</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E8" s="10">
         <v>8971</v>
@@ -3377,7 +3235,7 @@
         <v>46268</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4" t="s">
@@ -3433,7 +3291,7 @@
         <v>46269</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4" t="s">
@@ -3833,11 +3691,11 @@
         <v>46287</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E17" s="10">
         <v>4118.54</v>
@@ -4072,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="U20" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="V20" s="5"/>
     </row>
@@ -4081,11 +3939,11 @@
         <v>46294</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
@@ -4129,11 +3987,11 @@
         <v>46295</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
@@ -4553,10 +4411,10 @@
       <c r="D29" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E29" s="27">
+      <c r="E29" s="10">
         <v>3879.95</v>
       </c>
-      <c r="F29" s="27">
+      <c r="F29" s="10">
         <v>86853.79</v>
       </c>
       <c r="G29" s="4">
@@ -4611,16 +4469,28 @@
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
+      <c r="A30" s="8">
+        <v>46311</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>44</v>
+      </c>
       <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="9" t="e">
+      <c r="D30" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="10">
+        <v>11165.89</v>
+      </c>
+      <c r="F30" s="10">
+        <v>183889.61</v>
+      </c>
+      <c r="G30" s="4">
+        <v>2241</v>
+      </c>
+      <c r="H30" s="9">
         <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
-        <v>#DIV/0!</v>
+        <v>6.0720613850885868E-2</v>
       </c>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
@@ -4628,64 +4498,146 @@
         <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
         <v>0</v>
       </c>
-      <c r="L30" s="10"/>
-      <c r="M30" s="9" t="e">
+      <c r="L30" s="10">
+        <v>500</v>
+      </c>
+      <c r="M30" s="9">
         <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N30" s="4"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="4"/>
+        <v>4.4779233898954766E-2</v>
+      </c>
+      <c r="N30" s="4">
+        <v>208</v>
+      </c>
+      <c r="O30" s="4">
+        <v>16</v>
+      </c>
+      <c r="P30" s="4">
+        <v>16</v>
+      </c>
       <c r="Q30" s="12">
         <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
         <v>0</v>
       </c>
-      <c r="R30" s="13" t="e">
+      <c r="R30" s="13">
         <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S30" s="14" t="e">
+        <v>1</v>
+      </c>
+      <c r="S30" s="14" t="str">
         <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T30" s="4"/>
-      <c r="U30" s="4"/>
-      <c r="V30" s="5"/>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="T30" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="U30" s="4">
+        <v>0</v>
+      </c>
+      <c r="V30" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A31" s="8">
+        <v>46314</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="27">
+        <v>4218.16</v>
+      </c>
+      <c r="F31" s="27">
+        <v>91137.94</v>
+      </c>
+      <c r="G31" s="4">
+        <v>790</v>
+      </c>
+      <c r="H31" s="9">
+        <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
+        <v>4.6283249325143841E-2</v>
+      </c>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4">
+        <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
+        <v>0</v>
+      </c>
+      <c r="L31" s="10">
+        <v>500</v>
+      </c>
+      <c r="M31" s="9">
+        <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
+        <v>0.11853509587118555</v>
+      </c>
+      <c r="N31" s="4">
+        <v>97</v>
+      </c>
+      <c r="O31" s="4">
+        <v>13</v>
+      </c>
+      <c r="P31" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q31" s="12">
+        <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="R31" s="13">
+        <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="S31" s="14" t="str">
+        <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="T31" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="U31" s="4">
+        <v>0</v>
+      </c>
+      <c r="V31" s="5">
+        <v>38.380000000000003</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H30">
-    <cfRule type="cellIs" dxfId="98" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="H2:H31">
+    <cfRule type="cellIs" dxfId="106" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="105" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R30">
-    <cfRule type="cellIs" dxfId="96" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="R2:R31">
+    <cfRule type="cellIs" dxfId="104" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="95" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="103" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="102" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="101" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="100" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="99" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="98" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S30">
-    <cfRule type="expression" dxfId="89" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="S2:S31">
+    <cfRule type="expression" dxfId="97" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -4694,7 +4646,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4708,7 +4660,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y559"/>
+  <dimension ref="A1:Y588"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -4749,7 +4701,7 @@
         <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -5434,7 +5386,7 @@
       </c>
       <c r="F9" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G9" s="10">
         <v>6077.29</v>
@@ -5864,7 +5816,7 @@
       </c>
       <c r="F14" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G14" s="10">
         <v>15984.44</v>
@@ -7068,7 +7020,7 @@
       </c>
       <c r="F28" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G28" s="10">
         <v>10766.57</v>
@@ -7991,7 +7943,7 @@
         <v>2</v>
       </c>
       <c r="Y38" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.25">
@@ -8186,7 +8138,7 @@
       </c>
       <c r="F41" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G41" s="10">
         <v>10933.65</v>
@@ -8765,7 +8717,7 @@
         <v>2</v>
       </c>
       <c r="Y47" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.25">
@@ -8788,7 +8740,7 @@
       </c>
       <c r="F48" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G48" s="10">
         <v>6699.26</v>
@@ -9023,7 +8975,7 @@
         <v>2</v>
       </c>
       <c r="Y50" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.25">
@@ -9648,7 +9600,7 @@
       </c>
       <c r="F58" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G58" s="10">
         <v>5884.88</v>
@@ -10055,7 +10007,7 @@
         <v>3</v>
       </c>
       <c r="Y62" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.25">
@@ -10336,7 +10288,7 @@
       </c>
       <c r="F66" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G66" s="10">
         <v>12632.35</v>
@@ -11196,7 +11148,7 @@
       </c>
       <c r="F76" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G76" s="10">
         <v>10304.700000000001</v>
@@ -12205,7 +12157,7 @@
         <v>3</v>
       </c>
       <c r="Y87" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.25">
@@ -12228,7 +12180,7 @@
       </c>
       <c r="F88" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G88" s="10">
         <v>7158.89</v>
@@ -12973,7 +12925,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W96" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="X96" s="4">
         <v>0</v>
@@ -13346,7 +13298,7 @@
       </c>
       <c r="F101" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G101" s="10">
         <v>7088.01</v>
@@ -14120,7 +14072,7 @@
       </c>
       <c r="F110" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G110" s="10">
         <v>8968.25</v>
@@ -14550,7 +14502,7 @@
       </c>
       <c r="F115" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G115" s="10">
         <v>6952.52</v>
@@ -14865,7 +14817,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W118" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="X118" s="4">
         <v>0</v>
@@ -15639,7 +15591,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W127" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X127" s="4">
         <v>0</v>
@@ -15840,7 +15792,7 @@
       </c>
       <c r="F130" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G130" s="10">
         <v>6967.71</v>
@@ -16247,7 +16199,7 @@
         <v>7</v>
       </c>
       <c r="Y134" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="135" spans="1:25" x14ac:dyDescent="0.25">
@@ -16333,7 +16285,7 @@
         <v>3</v>
       </c>
       <c r="Y135" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="136" spans="1:25" x14ac:dyDescent="0.25">
@@ -16935,7 +16887,7 @@
         <v>5</v>
       </c>
       <c r="Y142" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="143" spans="1:25" x14ac:dyDescent="0.25">
@@ -17044,7 +16996,7 @@
       </c>
       <c r="F144" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G144" s="10">
         <v>12213.47</v>
@@ -17279,7 +17231,7 @@
         <v>3</v>
       </c>
       <c r="Y146" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="147" spans="1:25" x14ac:dyDescent="0.25">
@@ -17789,7 +17741,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W152" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="X152" s="4">
         <v>0</v>
@@ -18076,7 +18028,7 @@
       </c>
       <c r="F156" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G156" s="10">
         <v>4996.9399999999996</v>
@@ -18420,7 +18372,7 @@
       </c>
       <c r="F160" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G160" s="10">
         <v>4179.62</v>
@@ -18569,7 +18521,7 @@
         <v>3</v>
       </c>
       <c r="Y161" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="162" spans="1:25" x14ac:dyDescent="0.25">
@@ -19343,7 +19295,7 @@
         <v>4</v>
       </c>
       <c r="Y170" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="171" spans="1:25" x14ac:dyDescent="0.25">
@@ -19624,7 +19576,7 @@
       </c>
       <c r="F174" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G174" s="10">
         <v>5030.4399999999996</v>
@@ -20483,7 +20435,7 @@
       </c>
       <c r="F184" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G184" s="10">
         <v>4475.83</v>
@@ -20999,7 +20951,7 @@
       </c>
       <c r="F190" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G190" s="10">
         <v>5645.21</v>
@@ -21836,7 +21788,7 @@
         <v>14</v>
       </c>
       <c r="Y199" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="200" spans="1:25" x14ac:dyDescent="0.25">
@@ -22375,7 +22327,7 @@
       </c>
       <c r="F206" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G206" s="10">
         <v>10576.51</v>
@@ -23493,7 +23445,7 @@
       </c>
       <c r="F219" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G219" s="10">
         <v>10475.75</v>
@@ -23550,7 +23502,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W219" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="X219" s="4">
         <v>0</v>
@@ -24238,7 +24190,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W227" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X227" s="4">
         <v>0</v>
@@ -24324,7 +24276,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W228" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X228" s="4">
         <v>0</v>
@@ -24697,7 +24649,7 @@
       </c>
       <c r="F233" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G233" s="10">
         <v>10367.19</v>
@@ -24932,7 +24884,7 @@
         <v>8</v>
       </c>
       <c r="Y235" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="236" spans="1:25" x14ac:dyDescent="0.25">
@@ -24955,7 +24907,7 @@
       </c>
       <c r="F236" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G236" s="10">
         <v>8185.35</v>
@@ -26044,7 +25996,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W248" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="X248" s="4">
         <v>0</v>
@@ -26394,7 +26346,7 @@
         <v>2</v>
       </c>
       <c r="Y252" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="253" spans="1:25" x14ac:dyDescent="0.25">
@@ -26652,7 +26604,7 @@
         <v>0</v>
       </c>
       <c r="Y255" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="256" spans="1:25" x14ac:dyDescent="0.25">
@@ -26738,7 +26690,7 @@
         <v>9</v>
       </c>
       <c r="Y256" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="257" spans="1:25" x14ac:dyDescent="0.25">
@@ -27019,7 +26971,7 @@
       </c>
       <c r="F260" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G260" s="10">
         <v>8483.69</v>
@@ -27879,7 +27831,7 @@
       </c>
       <c r="F270" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G270" s="10">
         <v>12077</v>
@@ -28567,7 +28519,7 @@
       </c>
       <c r="F278" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G278" s="10">
         <v>11866.81</v>
@@ -29746,7 +29698,7 @@
         <v>4</v>
       </c>
       <c r="Y291" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="292" spans="1:25" x14ac:dyDescent="0.25">
@@ -29941,7 +29893,7 @@
       </c>
       <c r="F294" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G294" s="10">
         <v>6797.35</v>
@@ -30285,7 +30237,7 @@
       </c>
       <c r="F298" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G298" s="10">
         <v>5227.76</v>
@@ -31122,7 +31074,7 @@
         <v>4</v>
       </c>
       <c r="Y307" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="308" spans="1:25" x14ac:dyDescent="0.25">
@@ -31403,7 +31355,7 @@
       </c>
       <c r="F311" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G311" s="10">
         <v>7035.69</v>
@@ -31747,7 +31699,7 @@
       </c>
       <c r="F315" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G315" s="10">
         <v>15059.51</v>
@@ -32154,7 +32106,7 @@
         <v>3</v>
       </c>
       <c r="Y319" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="320" spans="1:25" x14ac:dyDescent="0.25">
@@ -32521,7 +32473,7 @@
       </c>
       <c r="F324" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G324" s="10">
         <v>13839.81</v>
@@ -33381,7 +33333,7 @@
       </c>
       <c r="F334" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G334" s="10">
         <v>12275.41</v>
@@ -33874,7 +33826,7 @@
         <v>0</v>
       </c>
       <c r="Y339" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="340" spans="1:25" x14ac:dyDescent="0.25">
@@ -34384,7 +34336,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W345" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X345" s="4">
         <v>0</v>
@@ -35015,7 +34967,7 @@
       </c>
       <c r="F353" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G353" s="10">
         <v>11713.19</v>
@@ -35164,7 +35116,7 @@
         <v>2</v>
       </c>
       <c r="Y354" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="355" spans="1:25" x14ac:dyDescent="0.25">
@@ -35422,7 +35374,7 @@
         <v>3</v>
       </c>
       <c r="Y357" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="358" spans="1:25" x14ac:dyDescent="0.25">
@@ -35445,7 +35397,7 @@
       </c>
       <c r="F358" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G358" s="10">
         <v>7236.81</v>
@@ -35766,7 +35718,7 @@
         <v>4</v>
       </c>
       <c r="Y361" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="362" spans="1:25" x14ac:dyDescent="0.25">
@@ -36133,7 +36085,7 @@
       </c>
       <c r="F366" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G366" s="10">
         <v>9000.1200000000008</v>
@@ -36712,7 +36664,7 @@
         <v>4</v>
       </c>
       <c r="Y372" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="373" spans="1:25" x14ac:dyDescent="0.25">
@@ -37142,7 +37094,7 @@
         <v>5</v>
       </c>
       <c r="Y377" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="378" spans="1:25" x14ac:dyDescent="0.25">
@@ -37337,7 +37289,7 @@
       </c>
       <c r="F380" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G380" s="10">
         <v>8171.1</v>
@@ -37830,7 +37782,7 @@
         <v>4</v>
       </c>
       <c r="Y385" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="386" spans="1:25" x14ac:dyDescent="0.25">
@@ -38082,7 +38034,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W388" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="X388" s="4">
         <v>0</v>
@@ -38111,7 +38063,7 @@
       </c>
       <c r="F389" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G389" s="10">
         <v>12520.8</v>
@@ -38455,7 +38407,7 @@
       </c>
       <c r="F393" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G393" s="10">
         <v>9266.7900000000009</v>
@@ -38862,7 +38814,7 @@
         <v>0</v>
       </c>
       <c r="Y397" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="398" spans="1:25" x14ac:dyDescent="0.25">
@@ -39550,7 +39502,7 @@
         <v>0</v>
       </c>
       <c r="Y405" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="406" spans="1:25" x14ac:dyDescent="0.25">
@@ -39831,7 +39783,7 @@
       </c>
       <c r="F409" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G409" s="10">
         <v>9289.91</v>
@@ -40433,7 +40385,7 @@
       </c>
       <c r="F416" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G416" s="10">
         <v>9218.99</v>
@@ -40496,7 +40448,7 @@
         <v>3</v>
       </c>
       <c r="Y416" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="417" spans="1:25" x14ac:dyDescent="0.25">
@@ -40920,7 +40872,7 @@
         <v>Não Atendeu a Meta</v>
       </c>
       <c r="W421" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="X421" s="4">
         <v>2</v>
@@ -41895,7 +41847,7 @@
       </c>
       <c r="F433" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G433" s="10">
         <v>8588.69</v>
@@ -42153,7 +42105,7 @@
       </c>
       <c r="F436" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G436" s="10">
         <v>5957.62</v>
@@ -42382,7 +42334,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W438" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="X438" s="4">
         <v>0</v>
@@ -43013,7 +42965,7 @@
       </c>
       <c r="F446" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G446" s="10">
         <v>5728.99</v>
@@ -43592,7 +43544,7 @@
         <v>1</v>
       </c>
       <c r="Y452" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="453" spans="1:25" x14ac:dyDescent="0.25">
@@ -43936,7 +43888,7 @@
         <v>0</v>
       </c>
       <c r="Y456" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="457" spans="1:25" x14ac:dyDescent="0.25">
@@ -44366,7 +44318,7 @@
         <v>2</v>
       </c>
       <c r="Y461" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="462" spans="1:25" x14ac:dyDescent="0.25">
@@ -44475,7 +44427,7 @@
       </c>
       <c r="F463" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G463" s="10">
         <v>4722.1000000000004</v>
@@ -45226,7 +45178,7 @@
         <v>5</v>
       </c>
       <c r="Y471" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="472" spans="1:25" x14ac:dyDescent="0.25">
@@ -45421,7 +45373,7 @@
       </c>
       <c r="F474" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G474" s="10">
         <v>14452.93</v>
@@ -45484,7 +45436,7 @@
         <v>4</v>
       </c>
       <c r="Y474" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="475" spans="1:25" x14ac:dyDescent="0.25">
@@ -46172,7 +46124,7 @@
         <v>0</v>
       </c>
       <c r="Y482" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="483" spans="1:25" x14ac:dyDescent="0.25">
@@ -46195,7 +46147,7 @@
       </c>
       <c r="F483" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G483" s="10">
         <v>10450.99</v>
@@ -46510,7 +46462,7 @@
         <v>Não Atendeu a Meta</v>
       </c>
       <c r="W486" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="X486" s="4">
         <v>2</v>
@@ -47141,7 +47093,7 @@
       </c>
       <c r="F494" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G494" s="10">
         <v>6011.95</v>
@@ -48087,7 +48039,7 @@
       </c>
       <c r="F505" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G505" s="10">
         <v>6355.51</v>
@@ -48660,13 +48612,13 @@
         <v>Não Atendeu a Meta</v>
       </c>
       <c r="W511" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="X511" s="4">
         <v>3</v>
       </c>
       <c r="Y511" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="512" spans="1:25" x14ac:dyDescent="0.25">
@@ -48918,7 +48870,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W514" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="X514" s="4">
         <v>0</v>
@@ -49182,7 +49134,7 @@
         <v>4</v>
       </c>
       <c r="Y517" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="518" spans="1:25" x14ac:dyDescent="0.25">
@@ -49205,7 +49157,7 @@
       </c>
       <c r="F518" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G518" s="10">
         <v>11542.94</v>
@@ -49784,7 +49736,7 @@
         <v>10</v>
       </c>
       <c r="Y524" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="525" spans="1:25" x14ac:dyDescent="0.25">
@@ -49800,7 +49752,7 @@
         <v>10</v>
       </c>
       <c r="D525" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E525" s="4">
         <v>1</v>
@@ -49956,7 +49908,7 @@
         <v>2</v>
       </c>
       <c r="Y526" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="527" spans="1:25" x14ac:dyDescent="0.25">
@@ -50214,7 +50166,7 @@
         <v>8</v>
       </c>
       <c r="Y529" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="530" spans="1:25" x14ac:dyDescent="0.25">
@@ -50237,7 +50189,7 @@
       </c>
       <c r="F530" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G530" s="10">
         <v>7143.37</v>
@@ -50300,7 +50252,7 @@
         <v>6</v>
       </c>
       <c r="Y530" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="531" spans="1:25" x14ac:dyDescent="0.25">
@@ -50724,7 +50676,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W535" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="X535" s="4">
         <v>0</v>
@@ -50810,7 +50762,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W536" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="X536" s="4">
         <v>0</v>
@@ -50918,7 +50870,7 @@
         <v>10</v>
       </c>
       <c r="D538" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E538" s="4">
         <v>1</v>
@@ -50982,7 +50934,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="W538" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="X538" s="4">
         <v>0</v>
@@ -51074,7 +51026,7 @@
         <v>17</v>
       </c>
       <c r="Y539" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="540" spans="1:25" x14ac:dyDescent="0.25">
@@ -51527,7 +51479,7 @@
       </c>
       <c r="F545" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G545" s="10">
         <v>3867.98</v>
@@ -51683,11 +51635,11 @@
       <c r="A547" s="8">
         <v>46310</v>
       </c>
-      <c r="B547" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C547" s="26">
+      <c r="B547" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C547" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -51769,11 +51721,11 @@
       <c r="A548" s="8">
         <v>46310</v>
       </c>
-      <c r="B548" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C548" s="26">
+      <c r="B548" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C548" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -51855,11 +51807,11 @@
       <c r="A549" s="8">
         <v>46310</v>
       </c>
-      <c r="B549" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C549" s="26">
+      <c r="B549" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C549" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -51941,16 +51893,16 @@
       <c r="A550" s="8">
         <v>46310</v>
       </c>
-      <c r="B550" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C550" s="26">
+      <c r="B550" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C550" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
       <c r="D550" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E550" s="4">
         <v>1</v>
@@ -52027,16 +51979,16 @@
       <c r="A551" s="8">
         <v>46310</v>
       </c>
-      <c r="B551" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C551" s="26">
+      <c r="B551" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C551" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
       <c r="D551" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E551" s="4">
         <v>3</v>
@@ -52113,11 +52065,11 @@
       <c r="A552" s="8">
         <v>46310</v>
       </c>
-      <c r="B552" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C552" s="26">
+      <c r="B552" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C552" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -52199,11 +52151,11 @@
       <c r="A553" s="8">
         <v>46310</v>
       </c>
-      <c r="B553" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C553" s="26">
+      <c r="B553" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C553" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -52278,18 +52230,18 @@
         <v>0</v>
       </c>
       <c r="Y553" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="554" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A554" s="8">
         <v>46310</v>
       </c>
-      <c r="B554" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C554" s="26">
+      <c r="B554" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C554" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -52364,18 +52316,18 @@
         <v>6</v>
       </c>
       <c r="Y554" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="555" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A555" s="8">
         <v>46310</v>
       </c>
-      <c r="B555" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C555" s="26">
+      <c r="B555" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C555" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -52457,11 +52409,11 @@
       <c r="A556" s="8">
         <v>46310</v>
       </c>
-      <c r="B556" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C556" s="26">
+      <c r="B556" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C556" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -52543,11 +52495,11 @@
       <c r="A557" s="8">
         <v>46310</v>
       </c>
-      <c r="B557" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C557" s="26">
+      <c r="B557" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C557" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -52629,11 +52581,11 @@
       <c r="A558" s="8">
         <v>46310</v>
       </c>
-      <c r="B558" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C558" s="26">
+      <c r="B558" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C558" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -52645,7 +52597,7 @@
       </c>
       <c r="F558" s="4" t="str">
         <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
-        <v>Wesley</v>
+        <v>Juscelino</v>
       </c>
       <c r="G558" s="10">
         <v>11616.88</v>
@@ -52715,11 +52667,11 @@
       <c r="A559" s="8">
         <v>46310</v>
       </c>
-      <c r="B559" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C559" s="26">
+      <c r="B559" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C559" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -52797,40 +52749,2534 @@
         <v>0</v>
       </c>
     </row>
+    <row r="560" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A560" s="8">
+        <v>46311</v>
+      </c>
+      <c r="B560" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C560" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D560" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E560" s="4">
+        <v>1</v>
+      </c>
+      <c r="F560" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G560" s="10">
+        <v>4321.76</v>
+      </c>
+      <c r="H560" s="10">
+        <v>116117.12</v>
+      </c>
+      <c r="I560" s="4">
+        <v>1096</v>
+      </c>
+      <c r="J560" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.7218973395137606E-2</v>
+      </c>
+      <c r="K560" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L560" s="15">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="M560" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="N560" s="4">
+        <v>292652</v>
+      </c>
+      <c r="O560" s="4">
+        <v>292693</v>
+      </c>
+      <c r="P560" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>41</v>
+      </c>
+      <c r="Q560" s="4">
+        <v>189</v>
+      </c>
+      <c r="R560" s="4">
+        <v>9</v>
+      </c>
+      <c r="S560" s="4">
+        <v>9</v>
+      </c>
+      <c r="T560" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U560" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V560" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W560" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X560" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y560" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="561" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A561" s="8">
+        <v>46311</v>
+      </c>
+      <c r="B561" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C561" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D561" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E561" s="4">
+        <v>11</v>
+      </c>
+      <c r="F561" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G561" s="10">
+        <v>20290.310000000001</v>
+      </c>
+      <c r="H561" s="10">
+        <v>374606.54</v>
+      </c>
+      <c r="I561" s="4">
+        <v>3804</v>
+      </c>
+      <c r="J561" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.4164323986441887E-2</v>
+      </c>
+      <c r="K561" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L561" s="15">
+        <v>0.80277777777777781</v>
+      </c>
+      <c r="M561" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.53194444444444455</v>
+      </c>
+      <c r="N561" s="4">
+        <v>107388</v>
+      </c>
+      <c r="O561" s="4">
+        <v>107527</v>
+      </c>
+      <c r="P561" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>139</v>
+      </c>
+      <c r="Q561" s="4">
+        <v>347</v>
+      </c>
+      <c r="R561" s="4">
+        <v>42</v>
+      </c>
+      <c r="S561" s="4">
+        <v>42</v>
+      </c>
+      <c r="T561" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U561" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V561" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W561" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X561" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y561" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="562" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A562" s="8">
+        <v>46311</v>
+      </c>
+      <c r="B562" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C562" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D562" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E562" s="4">
+        <v>4</v>
+      </c>
+      <c r="F562" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Manoel</v>
+      </c>
+      <c r="G562" s="10">
+        <v>526.25</v>
+      </c>
+      <c r="H562" s="10">
+        <v>2322</v>
+      </c>
+      <c r="I562" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="J562" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.2266365202411714</v>
+      </c>
+      <c r="K562" s="11">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="L562" s="15">
+        <v>0.79861111111111116</v>
+      </c>
+      <c r="M562" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.13194444444444453</v>
+      </c>
+      <c r="N562" s="4">
+        <v>64241</v>
+      </c>
+      <c r="O562" s="4">
+        <v>64293</v>
+      </c>
+      <c r="P562" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>52</v>
+      </c>
+      <c r="Q562" s="4">
+        <v>4</v>
+      </c>
+      <c r="R562" s="4">
+        <v>3</v>
+      </c>
+      <c r="S562" s="4">
+        <v>3</v>
+      </c>
+      <c r="T562" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U562" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V562" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W562" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X562" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y562" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="563" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A563" s="8">
+        <v>46311</v>
+      </c>
+      <c r="B563" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C563" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D563" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E563" s="4">
+        <v>5</v>
+      </c>
+      <c r="F563" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Heremilton</v>
+      </c>
+      <c r="G563" s="10">
+        <v>2406.34</v>
+      </c>
+      <c r="H563" s="10">
+        <v>92852.1</v>
+      </c>
+      <c r="I563" s="4">
+        <v>534</v>
+      </c>
+      <c r="J563" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.5915838198597555E-2</v>
+      </c>
+      <c r="K563" s="11">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="L563" s="15">
+        <v>0.75694444444444442</v>
+      </c>
+      <c r="M563" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="N563" s="4">
+        <v>368827</v>
+      </c>
+      <c r="O563" s="4">
+        <v>368863</v>
+      </c>
+      <c r="P563" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>36</v>
+      </c>
+      <c r="Q563" s="4">
+        <v>160</v>
+      </c>
+      <c r="R563" s="4">
+        <v>2</v>
+      </c>
+      <c r="S563" s="4">
+        <v>2</v>
+      </c>
+      <c r="T563" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U563" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V563" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W563" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X563" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y563" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="564" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A564" s="8">
+        <v>46311</v>
+      </c>
+      <c r="B564" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C564" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D564" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E564" s="4">
+        <v>5</v>
+      </c>
+      <c r="F564" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G564" s="10">
+        <v>17104.04</v>
+      </c>
+      <c r="H564" s="10">
+        <v>202419.4</v>
+      </c>
+      <c r="I564" s="4">
+        <v>2512</v>
+      </c>
+      <c r="J564" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.4498027362989919E-2</v>
+      </c>
+      <c r="K564" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L564" s="15">
+        <v>0.79097222222222219</v>
+      </c>
+      <c r="M564" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4993055555555555</v>
+      </c>
+      <c r="N564" s="4">
+        <v>127217</v>
+      </c>
+      <c r="O564" s="4">
+        <v>127272</v>
+      </c>
+      <c r="P564" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>55</v>
+      </c>
+      <c r="Q564" s="4">
+        <v>582</v>
+      </c>
+      <c r="R564" s="4">
+        <v>24</v>
+      </c>
+      <c r="S564" s="4">
+        <v>24</v>
+      </c>
+      <c r="T564" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U564" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V564" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W564" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X564" s="4">
+        <v>8</v>
+      </c>
+      <c r="Y564" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="565" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A565" s="8">
+        <v>46311</v>
+      </c>
+      <c r="B565" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C565" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D565" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E565" s="4">
+        <v>1</v>
+      </c>
+      <c r="F565" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Juscelino</v>
+      </c>
+      <c r="G565" s="10">
+        <v>10648.92</v>
+      </c>
+      <c r="H565" s="10">
+        <v>182671.14</v>
+      </c>
+      <c r="I565" s="4">
+        <v>2349</v>
+      </c>
+      <c r="J565" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.8295579695840288E-2</v>
+      </c>
+      <c r="K565" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L565" s="15">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="M565" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.54166666666666674</v>
+      </c>
+      <c r="N565" s="4">
+        <v>306487</v>
+      </c>
+      <c r="O565" s="4">
+        <v>306655</v>
+      </c>
+      <c r="P565" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>168</v>
+      </c>
+      <c r="Q565" s="4">
+        <v>232</v>
+      </c>
+      <c r="R565" s="4">
+        <v>27</v>
+      </c>
+      <c r="S565" s="4">
+        <v>27</v>
+      </c>
+      <c r="T565" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U565" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V565" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W565" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X565" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y565" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="566" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A566" s="8">
+        <v>46311</v>
+      </c>
+      <c r="B566" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C566" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D566" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E566" s="4">
+        <v>1</v>
+      </c>
+      <c r="F566" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G566" s="10">
+        <v>4788.5</v>
+      </c>
+      <c r="H566" s="10">
+        <v>259988.06</v>
+      </c>
+      <c r="I566" s="4">
+        <v>453</v>
+      </c>
+      <c r="J566" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>1.8418153510588141E-2</v>
+      </c>
+      <c r="K566" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L566" s="15">
+        <v>0.78680555555555554</v>
+      </c>
+      <c r="M566" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.49513888888888885</v>
+      </c>
+      <c r="N566" s="4">
+        <v>277067</v>
+      </c>
+      <c r="O566" s="4">
+        <v>277111</v>
+      </c>
+      <c r="P566" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>44</v>
+      </c>
+      <c r="Q566" s="4">
+        <v>263</v>
+      </c>
+      <c r="R566" s="4">
+        <v>5</v>
+      </c>
+      <c r="S566" s="4">
+        <v>5</v>
+      </c>
+      <c r="T566" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U566" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V566" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W566" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X566" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y566" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="567" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A567" s="8">
+        <v>46311</v>
+      </c>
+      <c r="B567" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C567" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D567" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E567" s="4">
+        <v>5</v>
+      </c>
+      <c r="F567" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G567" s="10">
+        <v>2629.81</v>
+      </c>
+      <c r="H567" s="10">
+        <v>28173.65</v>
+      </c>
+      <c r="I567" s="4">
+        <v>473</v>
+      </c>
+      <c r="J567" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>9.3342893093369156E-2</v>
+      </c>
+      <c r="K567" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L567" s="15">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="M567" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44791666666666663</v>
+      </c>
+      <c r="N567" s="4">
+        <v>157454</v>
+      </c>
+      <c r="O567" s="4">
+        <v>157496</v>
+      </c>
+      <c r="P567" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>42</v>
+      </c>
+      <c r="Q567" s="4">
+        <v>229</v>
+      </c>
+      <c r="R567" s="4">
+        <v>4</v>
+      </c>
+      <c r="S567" s="4">
+        <v>4</v>
+      </c>
+      <c r="T567" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U567" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V567" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W567" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X567" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y567" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="568" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A568" s="8">
+        <v>46311</v>
+      </c>
+      <c r="B568" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C568" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D568" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E568" s="4">
+        <v>3</v>
+      </c>
+      <c r="F568" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G568" s="10">
+        <v>6168.57</v>
+      </c>
+      <c r="H568" s="10">
+        <v>144733.09</v>
+      </c>
+      <c r="I568" s="4">
+        <v>1027</v>
+      </c>
+      <c r="J568" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.2620315782658964E-2</v>
+      </c>
+      <c r="K568" s="11">
+        <v>0.29652777777777778</v>
+      </c>
+      <c r="L568" s="15">
+        <v>0.75416666666666665</v>
+      </c>
+      <c r="M568" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45763888888888887</v>
+      </c>
+      <c r="N568" s="4">
+        <v>14920</v>
+      </c>
+      <c r="O568" s="4">
+        <v>14972</v>
+      </c>
+      <c r="P568" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>52</v>
+      </c>
+      <c r="Q568" s="4">
+        <v>182</v>
+      </c>
+      <c r="R568" s="4">
+        <v>14</v>
+      </c>
+      <c r="S568" s="4">
+        <v>14</v>
+      </c>
+      <c r="T568" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U568" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V568" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W568" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X568" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y568" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="569" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A569" s="8">
+        <v>46311</v>
+      </c>
+      <c r="B569" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C569" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D569" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E569" s="4">
+        <v>1</v>
+      </c>
+      <c r="F569" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G569" s="10">
+        <v>13054.51</v>
+      </c>
+      <c r="H569" s="10">
+        <v>46649.95</v>
+      </c>
+      <c r="I569" s="4">
+        <v>723</v>
+      </c>
+      <c r="J569" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.27983974259350763</v>
+      </c>
+      <c r="K569" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L569" s="15">
+        <v>0.75</v>
+      </c>
+      <c r="M569" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="N569" s="4">
+        <v>121162</v>
+      </c>
+      <c r="O569" s="4">
+        <v>121193</v>
+      </c>
+      <c r="P569" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>31</v>
+      </c>
+      <c r="Q569" s="4">
+        <v>723</v>
+      </c>
+      <c r="R569" s="4">
+        <v>2</v>
+      </c>
+      <c r="S569" s="4">
+        <v>2</v>
+      </c>
+      <c r="T569" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U569" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V569" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W569" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X569" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y569" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="570" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A570" s="8">
+        <v>46311</v>
+      </c>
+      <c r="B570" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C570" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D570" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E570" s="4">
+        <v>2</v>
+      </c>
+      <c r="F570" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G570" s="10">
+        <v>11529.31</v>
+      </c>
+      <c r="H570" s="10">
+        <v>271037.05</v>
+      </c>
+      <c r="I570" s="4">
+        <v>293</v>
+      </c>
+      <c r="J570" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.2537763748535483E-2</v>
+      </c>
+      <c r="K570" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L570" s="15">
+        <v>0.75069444444444444</v>
+      </c>
+      <c r="M570" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45902777777777776</v>
+      </c>
+      <c r="N570" s="4">
+        <v>144998</v>
+      </c>
+      <c r="O570" s="4">
+        <v>145063</v>
+      </c>
+      <c r="P570" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>65</v>
+      </c>
+      <c r="Q570" s="4">
+        <v>293</v>
+      </c>
+      <c r="R570" s="4">
+        <v>31</v>
+      </c>
+      <c r="S570" s="4">
+        <v>31</v>
+      </c>
+      <c r="T570" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U570" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V570" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W570" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X570" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y570" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="571" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A571" s="8">
+        <v>46311</v>
+      </c>
+      <c r="B571" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C571" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D571" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E571" s="4">
+        <v>3</v>
+      </c>
+      <c r="F571" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G571" s="10">
+        <v>12697.95</v>
+      </c>
+      <c r="H571" s="10">
+        <v>378975.83</v>
+      </c>
+      <c r="I571" s="4">
+        <v>2688</v>
+      </c>
+      <c r="J571" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.3505962636192391E-2</v>
+      </c>
+      <c r="K571" s="11">
+        <v>0.29722222222222222</v>
+      </c>
+      <c r="L571" s="15">
+        <v>0.74097222222222225</v>
+      </c>
+      <c r="M571" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44375000000000003</v>
+      </c>
+      <c r="N571" s="4">
+        <v>282196</v>
+      </c>
+      <c r="O571" s="4">
+        <v>282242</v>
+      </c>
+      <c r="P571" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>46</v>
+      </c>
+      <c r="Q571" s="4">
+        <v>479</v>
+      </c>
+      <c r="R571" s="4">
+        <v>17</v>
+      </c>
+      <c r="S571" s="4">
+        <v>17</v>
+      </c>
+      <c r="T571" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U571" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V571" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W571" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X571" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y571" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="572" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A572" s="8">
+        <v>46312</v>
+      </c>
+      <c r="B572" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C572" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D572" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E572" s="4">
+        <v>1</v>
+      </c>
+      <c r="F572" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G572" s="10">
+        <v>867.03</v>
+      </c>
+      <c r="H572" s="10">
+        <v>753.26</v>
+      </c>
+      <c r="I572" s="4">
+        <v>6.8</v>
+      </c>
+      <c r="J572" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>1.1510368265937392</v>
+      </c>
+      <c r="K572" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L572" s="15">
+        <v>0.43402777777777779</v>
+      </c>
+      <c r="M572" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.1423611111111111</v>
+      </c>
+      <c r="N572" s="4">
+        <v>277111</v>
+      </c>
+      <c r="O572" s="4">
+        <v>277151</v>
+      </c>
+      <c r="P572" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>40</v>
+      </c>
+      <c r="Q572" s="4">
+        <v>1</v>
+      </c>
+      <c r="R572" s="4">
+        <v>1</v>
+      </c>
+      <c r="S572" s="4">
+        <v>1</v>
+      </c>
+      <c r="T572" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U572" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V572" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W572" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X572" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y572" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="573" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A573" s="8">
+        <v>46312</v>
+      </c>
+      <c r="B573" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C573" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D573" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E573" s="4">
+        <v>5</v>
+      </c>
+      <c r="F573" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G573" s="10">
+        <v>6149.17</v>
+      </c>
+      <c r="H573" s="10">
+        <v>141433.56</v>
+      </c>
+      <c r="I573" s="4">
+        <v>2878</v>
+      </c>
+      <c r="J573" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.3477446229876419E-2</v>
+      </c>
+      <c r="K573" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L573" s="15">
+        <v>0.44791666666666669</v>
+      </c>
+      <c r="M573" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.13541666666666669</v>
+      </c>
+      <c r="N573" s="4">
+        <v>107527</v>
+      </c>
+      <c r="O573" s="4">
+        <v>107561</v>
+      </c>
+      <c r="P573" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>34</v>
+      </c>
+      <c r="Q573" s="4">
+        <v>572</v>
+      </c>
+      <c r="R573" s="4">
+        <v>8</v>
+      </c>
+      <c r="S573" s="4">
+        <v>8</v>
+      </c>
+      <c r="T573" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U573" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V573" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W573" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X573" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y573" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="574" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A574" s="8">
+        <v>46312</v>
+      </c>
+      <c r="B574" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C574" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D574" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E574" s="4">
+        <v>1</v>
+      </c>
+      <c r="F574" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G574" s="10">
+        <v>3522.15</v>
+      </c>
+      <c r="H574" s="10">
+        <v>46897.99</v>
+      </c>
+      <c r="I574" s="4">
+        <v>425</v>
+      </c>
+      <c r="J574" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.5102365794354947E-2</v>
+      </c>
+      <c r="K574" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L574" s="15">
+        <v>0.47430555555555554</v>
+      </c>
+      <c r="M574" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.18263888888888885</v>
+      </c>
+      <c r="N574" s="4">
+        <v>157496</v>
+      </c>
+      <c r="O574" s="4">
+        <v>157517</v>
+      </c>
+      <c r="P574" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>21</v>
+      </c>
+      <c r="Q574" s="4">
+        <v>56</v>
+      </c>
+      <c r="R574" s="4">
+        <v>17</v>
+      </c>
+      <c r="S574" s="4">
+        <v>17</v>
+      </c>
+      <c r="T574" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U574" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V574" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W574" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X574" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y574" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="575" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A575" s="8">
+        <v>46312</v>
+      </c>
+      <c r="B575" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C575" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D575" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E575" s="4">
+        <v>11</v>
+      </c>
+      <c r="F575" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G575" s="10">
+        <v>7057.02</v>
+      </c>
+      <c r="H575" s="10">
+        <v>111266.01</v>
+      </c>
+      <c r="I575" s="4">
+        <v>964</v>
+      </c>
+      <c r="J575" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.3424760176086128E-2</v>
+      </c>
+      <c r="K575" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L575" s="15">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="M575" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.21180555555555552</v>
+      </c>
+      <c r="N575" s="4">
+        <v>145063</v>
+      </c>
+      <c r="O575" s="4">
+        <v>145183</v>
+      </c>
+      <c r="P575" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>120</v>
+      </c>
+      <c r="Q575" s="4">
+        <v>115</v>
+      </c>
+      <c r="R575" s="4">
+        <v>19</v>
+      </c>
+      <c r="S575" s="4">
+        <v>19</v>
+      </c>
+      <c r="T575" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U575" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V575" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W575" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X575" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y575" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="576" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A576" s="8">
+        <v>46314</v>
+      </c>
+      <c r="B576" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C576" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D576" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E576" s="4">
+        <v>3</v>
+      </c>
+      <c r="F576" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Manoel</v>
+      </c>
+      <c r="G576" s="10">
+        <v>350.56</v>
+      </c>
+      <c r="H576" s="10">
+        <v>13187.31</v>
+      </c>
+      <c r="I576" s="4">
+        <v>74</v>
+      </c>
+      <c r="J576" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.6583131813842246E-2</v>
+      </c>
+      <c r="K576" s="11">
+        <v>0.625</v>
+      </c>
+      <c r="L576" s="15">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="M576" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>9.722222222222221E-2</v>
+      </c>
+      <c r="N576" s="4">
+        <v>64345</v>
+      </c>
+      <c r="O576" s="4">
+        <v>64401</v>
+      </c>
+      <c r="P576" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>56</v>
+      </c>
+      <c r="Q576" s="4">
+        <v>12</v>
+      </c>
+      <c r="R576" s="4">
+        <v>1</v>
+      </c>
+      <c r="S576" s="4">
+        <v>1</v>
+      </c>
+      <c r="T576" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U576" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V576" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W576" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X576" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y576" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="577" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A577" s="8">
+        <v>46314</v>
+      </c>
+      <c r="B577" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C577" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D577" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E577" s="4">
+        <v>1</v>
+      </c>
+      <c r="F577" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G577" s="10">
+        <v>10650.83</v>
+      </c>
+      <c r="H577" s="10">
+        <v>96416.72</v>
+      </c>
+      <c r="I577" s="4">
+        <v>2218</v>
+      </c>
+      <c r="J577" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>0.11046662860964364</v>
+      </c>
+      <c r="K577" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L577" s="15">
+        <v>0.78819444444444442</v>
+      </c>
+      <c r="M577" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47569444444444442</v>
+      </c>
+      <c r="N577" s="4">
+        <v>127272</v>
+      </c>
+      <c r="O577" s="4">
+        <v>127326</v>
+      </c>
+      <c r="P577" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>54</v>
+      </c>
+      <c r="Q577" s="4">
+        <v>349</v>
+      </c>
+      <c r="R577" s="4">
+        <v>21</v>
+      </c>
+      <c r="S577" s="4">
+        <v>21</v>
+      </c>
+      <c r="T577" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U577" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V577" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W577" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X577" s="4">
+        <v>3</v>
+      </c>
+      <c r="Y577" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="578" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A578" s="8">
+        <v>46314</v>
+      </c>
+      <c r="B578" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C578" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D578" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E578" s="4">
+        <v>5</v>
+      </c>
+      <c r="F578" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G578" s="10">
+        <v>9934.5300000000007</v>
+      </c>
+      <c r="H578" s="10">
+        <v>147864.54</v>
+      </c>
+      <c r="I578" s="4">
+        <v>2293</v>
+      </c>
+      <c r="J578" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.7186696688739569E-2</v>
+      </c>
+      <c r="K578" s="11">
+        <v>0.31805555555555554</v>
+      </c>
+      <c r="L578" s="15">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="M578" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.50486111111111109</v>
+      </c>
+      <c r="N578" s="4">
+        <v>282254</v>
+      </c>
+      <c r="O578" s="4">
+        <v>282336</v>
+      </c>
+      <c r="P578" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>82</v>
+      </c>
+      <c r="Q578" s="4">
+        <v>250</v>
+      </c>
+      <c r="R578" s="4">
+        <v>33</v>
+      </c>
+      <c r="S578" s="4">
+        <v>33</v>
+      </c>
+      <c r="T578" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U578" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V578" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W578" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X578" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y578" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="579" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A579" s="8">
+        <v>46314</v>
+      </c>
+      <c r="B579" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C579" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D579" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E579" s="4">
+        <v>11</v>
+      </c>
+      <c r="F579" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G579" s="10">
+        <v>13799.75</v>
+      </c>
+      <c r="H579" s="10">
+        <v>261701.28</v>
+      </c>
+      <c r="I579" s="4">
+        <v>2250</v>
+      </c>
+      <c r="J579" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.2730922829265489E-2</v>
+      </c>
+      <c r="K579" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L579" s="15">
+        <v>0.79305555555555551</v>
+      </c>
+      <c r="M579" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.52222222222222214</v>
+      </c>
+      <c r="N579" s="4">
+        <v>107561</v>
+      </c>
+      <c r="O579" s="4">
+        <v>107711</v>
+      </c>
+      <c r="P579" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>150</v>
+      </c>
+      <c r="Q579" s="4">
+        <v>384</v>
+      </c>
+      <c r="R579" s="4">
+        <v>33</v>
+      </c>
+      <c r="S579" s="4">
+        <v>33</v>
+      </c>
+      <c r="T579" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U579" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V579" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W579" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X579" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y579" s="5">
+        <v>38.380000000000003</v>
+      </c>
+    </row>
+    <row r="580" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A580" s="8">
+        <v>46314</v>
+      </c>
+      <c r="B580" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C580" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D580" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E580" s="4">
+        <v>5</v>
+      </c>
+      <c r="F580" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Heremilton</v>
+      </c>
+      <c r="G580" s="10">
+        <v>17819.759999999998</v>
+      </c>
+      <c r="H580" s="10">
+        <v>343768.23</v>
+      </c>
+      <c r="I580" s="4">
+        <v>4415</v>
+      </c>
+      <c r="J580" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.1836552784415242E-2</v>
+      </c>
+      <c r="K580" s="11">
+        <v>0.27638888888888891</v>
+      </c>
+      <c r="L580" s="15">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="M580" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.45277777777777772</v>
+      </c>
+      <c r="N580" s="4">
+        <v>369199</v>
+      </c>
+      <c r="O580" s="4">
+        <v>369235</v>
+      </c>
+      <c r="P580" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>36</v>
+      </c>
+      <c r="Q580" s="4">
+        <v>670</v>
+      </c>
+      <c r="R580" s="4">
+        <v>16</v>
+      </c>
+      <c r="S580" s="4">
+        <v>16</v>
+      </c>
+      <c r="T580" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U580" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V580" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W580" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X580" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y580" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="581" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A581" s="8">
+        <v>46314</v>
+      </c>
+      <c r="B581" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C581" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D581" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E581" s="4">
+        <v>5</v>
+      </c>
+      <c r="F581" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G581" s="10">
+        <v>4789.96</v>
+      </c>
+      <c r="H581" s="10">
+        <v>79727.63</v>
+      </c>
+      <c r="I581" s="4">
+        <v>870</v>
+      </c>
+      <c r="J581" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.007904662411262E-2</v>
+      </c>
+      <c r="K581" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L581" s="15">
+        <v>0.71527777777777779</v>
+      </c>
+      <c r="M581" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.40277777777777779</v>
+      </c>
+      <c r="N581" s="4">
+        <v>277151</v>
+      </c>
+      <c r="O581" s="4">
+        <v>277217</v>
+      </c>
+      <c r="P581" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>66</v>
+      </c>
+      <c r="Q581" s="4">
+        <v>152</v>
+      </c>
+      <c r="R581" s="4">
+        <v>14</v>
+      </c>
+      <c r="S581" s="4">
+        <v>14</v>
+      </c>
+      <c r="T581" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U581" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V581" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W581" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X581" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y581" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="582" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A582" s="8">
+        <v>46314</v>
+      </c>
+      <c r="B582" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C582" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D582" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E582" s="4">
+        <v>1</v>
+      </c>
+      <c r="F582" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G582" s="10">
+        <v>2364.9299999999998</v>
+      </c>
+      <c r="H582" s="10">
+        <v>63772.87</v>
+      </c>
+      <c r="I582" s="4">
+        <v>629</v>
+      </c>
+      <c r="J582" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.7083637603262949E-2</v>
+      </c>
+      <c r="K582" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L582" s="15">
+        <v>0.57847222222222228</v>
+      </c>
+      <c r="M582" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.26597222222222228</v>
+      </c>
+      <c r="N582" s="4">
+        <v>157561</v>
+      </c>
+      <c r="O582" s="4">
+        <v>157659</v>
+      </c>
+      <c r="P582" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>98</v>
+      </c>
+      <c r="Q582" s="4">
+        <v>67</v>
+      </c>
+      <c r="R582" s="4">
+        <v>5</v>
+      </c>
+      <c r="S582" s="4">
+        <v>5</v>
+      </c>
+      <c r="T582" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U582" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V582" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W582" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X582" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y582" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="583" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A583" s="8">
+        <v>46314</v>
+      </c>
+      <c r="B583" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C583" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D583" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E583" s="4">
+        <v>1</v>
+      </c>
+      <c r="F583" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G583" s="10">
+        <v>1558.36</v>
+      </c>
+      <c r="H583" s="10">
+        <v>24322.73</v>
+      </c>
+      <c r="I583" s="4">
+        <v>56</v>
+      </c>
+      <c r="J583" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>6.4070110550912662E-2</v>
+      </c>
+      <c r="K583" s="11">
+        <v>0.58819444444444446</v>
+      </c>
+      <c r="L583" s="15">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="M583" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.10972222222222217</v>
+      </c>
+      <c r="N583" s="4">
+        <v>157659</v>
+      </c>
+      <c r="O583" s="4">
+        <v>157700</v>
+      </c>
+      <c r="P583" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>41</v>
+      </c>
+      <c r="Q583" s="4">
+        <v>52</v>
+      </c>
+      <c r="R583" s="4">
+        <v>3</v>
+      </c>
+      <c r="S583" s="4">
+        <v>3</v>
+      </c>
+      <c r="T583" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U583" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V583" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W583" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X583" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y583" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="584" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A584" s="8">
+        <v>46314</v>
+      </c>
+      <c r="B584" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C584" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D584" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E584" s="4">
+        <v>2</v>
+      </c>
+      <c r="F584" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Gilberto</v>
+      </c>
+      <c r="G584" s="10">
+        <v>9440.3799999999992</v>
+      </c>
+      <c r="H584" s="10">
+        <v>171185.29</v>
+      </c>
+      <c r="I584" s="4">
+        <v>3022</v>
+      </c>
+      <c r="J584" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.5147144944521803E-2</v>
+      </c>
+      <c r="K584" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L584" s="15">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="M584" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.43055555555555552</v>
+      </c>
+      <c r="N584" s="4">
+        <v>121193</v>
+      </c>
+      <c r="O584" s="4">
+        <v>121242</v>
+      </c>
+      <c r="P584" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>49</v>
+      </c>
+      <c r="Q584" s="4">
+        <v>606</v>
+      </c>
+      <c r="R584" s="4">
+        <v>19</v>
+      </c>
+      <c r="S584" s="4">
+        <v>19</v>
+      </c>
+      <c r="T584" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U584" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V584" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W584" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X584" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y584" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="585" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A585" s="8">
+        <v>46314</v>
+      </c>
+      <c r="B585" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C585" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D585" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E585" s="4">
+        <v>1</v>
+      </c>
+      <c r="F585" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G585" s="10">
+        <v>10512.32</v>
+      </c>
+      <c r="H585" s="10">
+        <v>225921.51</v>
+      </c>
+      <c r="I585" s="4">
+        <v>4140</v>
+      </c>
+      <c r="J585" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.6530850471033058E-2</v>
+      </c>
+      <c r="K585" s="11">
+        <v>0.3263888888888889</v>
+      </c>
+      <c r="L585" s="15">
+        <v>0.75</v>
+      </c>
+      <c r="M585" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4236111111111111</v>
+      </c>
+      <c r="N585" s="4">
+        <v>14889</v>
+      </c>
+      <c r="O585" s="4">
+        <v>14998</v>
+      </c>
+      <c r="P585" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>109</v>
+      </c>
+      <c r="Q585" s="4">
+        <v>445</v>
+      </c>
+      <c r="R585" s="4">
+        <v>7</v>
+      </c>
+      <c r="S585" s="4">
+        <v>7</v>
+      </c>
+      <c r="T585" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U585" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V585" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W585" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X585" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y585" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A586" s="8">
+        <v>46314</v>
+      </c>
+      <c r="B586" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C586" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D586" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E586" s="4">
+        <v>4</v>
+      </c>
+      <c r="F586" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Juscelino</v>
+      </c>
+      <c r="G586" s="10">
+        <v>7808.9</v>
+      </c>
+      <c r="H586" s="10">
+        <v>161554.95000000001</v>
+      </c>
+      <c r="I586" s="4">
+        <v>3215</v>
+      </c>
+      <c r="J586" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.8335875811914147E-2</v>
+      </c>
+      <c r="K586" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L586" s="15">
+        <v>0.73611111111111116</v>
+      </c>
+      <c r="M586" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.42361111111111116</v>
+      </c>
+      <c r="N586" s="4">
+        <v>306655</v>
+      </c>
+      <c r="O586" s="4">
+        <v>306713</v>
+      </c>
+      <c r="P586" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>58</v>
+      </c>
+      <c r="Q586" s="4">
+        <v>480</v>
+      </c>
+      <c r="R586" s="4">
+        <v>11</v>
+      </c>
+      <c r="S586" s="4">
+        <v>11</v>
+      </c>
+      <c r="T586" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U586" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V586" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W586" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X586" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y586" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="587" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A587" s="8">
+        <v>46314</v>
+      </c>
+      <c r="B587" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C587" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D587" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E587" s="4">
+        <v>3</v>
+      </c>
+      <c r="F587" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G587" s="10">
+        <v>5825.17</v>
+      </c>
+      <c r="H587" s="10">
+        <v>111862.03</v>
+      </c>
+      <c r="I587" s="4">
+        <v>869</v>
+      </c>
+      <c r="J587" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.2074595821298794E-2</v>
+      </c>
+      <c r="K587" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L587" s="15">
+        <v>0.75</v>
+      </c>
+      <c r="M587" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4375</v>
+      </c>
+      <c r="N587" s="4">
+        <v>145183</v>
+      </c>
+      <c r="O587" s="4">
+        <v>145236</v>
+      </c>
+      <c r="P587" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>53</v>
+      </c>
+      <c r="Q587" s="4">
+        <v>146</v>
+      </c>
+      <c r="R587" s="4">
+        <v>19</v>
+      </c>
+      <c r="S587" s="4">
+        <v>19</v>
+      </c>
+      <c r="T587" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U587" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V587" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W587" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X587" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y587" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="588" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A588" s="8">
+        <v>46314</v>
+      </c>
+      <c r="B588" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C588" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D588" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E588" s="4">
+        <v>3</v>
+      </c>
+      <c r="F588" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G588" s="10">
+        <v>8578.77</v>
+      </c>
+      <c r="H588" s="10">
+        <v>161474.5</v>
+      </c>
+      <c r="I588" s="4">
+        <v>1516</v>
+      </c>
+      <c r="J588" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.3127707470839051E-2</v>
+      </c>
+      <c r="K588" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L588" s="15">
+        <v>0.7416666666666667</v>
+      </c>
+      <c r="M588" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4291666666666667</v>
+      </c>
+      <c r="N588" s="4">
+        <v>292707</v>
+      </c>
+      <c r="O588" s="4">
+        <v>292762</v>
+      </c>
+      <c r="P588" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>55</v>
+      </c>
+      <c r="Q588" s="4">
+        <v>275</v>
+      </c>
+      <c r="R588" s="4">
+        <v>29</v>
+      </c>
+      <c r="S588" s="4">
+        <v>29</v>
+      </c>
+      <c r="T588" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U588" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V588" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W588" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X588" s="4">
+        <v>2</v>
+      </c>
+      <c r="Y588" s="5">
+        <v>9.9</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J559">
-    <cfRule type="cellIs" dxfId="87" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="J2:J588">
+    <cfRule type="cellIs" dxfId="21" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="20" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U559">
-    <cfRule type="cellIs" dxfId="85" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="U2:U588">
+    <cfRule type="cellIs" dxfId="19" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="18" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="17" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V559">
-    <cfRule type="expression" dxfId="78" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="V2:V588">
+    <cfRule type="expression" dxfId="12" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -52839,7 +55285,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52855,7 +55301,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D559</xm:sqref>
+          <xm:sqref>D2:D588</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD52F93-27D0-456E-9E05-76809CF36B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD13BAD-C08D-4362-BF6C-367C0BA10BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="106">
   <si>
     <t>Data</t>
   </si>
@@ -362,9 +362,6 @@
   <si>
     <t>Juscelino</t>
   </si>
-  <si>
-    <t>bem</t>
-  </si>
 </sst>
 </file>
 
@@ -653,7 +650,7 @@
     <cellStyle name="Normal 2 2 2" xfId="3" xr:uid="{F6D7429B-6BC2-41D1-B818-FB0128371036}"/>
     <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="134">
+  <dxfs count="145">
     <dxf>
       <font>
         <b/>
@@ -1697,6 +1694,83 @@
       </font>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF00B050"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFFF0000"/>
+        <family val="2"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -2168,50 +2242,50 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V31" totalsRowShown="0" headerRowDxfId="133" dataDxfId="131" headerRowBorderDxfId="132" tableBorderDxfId="130" totalsRowBorderDxfId="129" headerRowCellStyle="Normal 2 2 2">
-  <autoFilter ref="A1:V31" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FC542174-E978-4F11-84D0-04B8EC2335EF}" name="Tabela35" displayName="Tabela35" ref="A1:V33" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" totalsRowBorderDxfId="140" headerRowCellStyle="Normal 2 2 2">
+  <autoFilter ref="A1:V33" xr:uid="{DCE91C63-7150-4B05-9681-4C03C82B532C}"/>
   <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="128"/>
-    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="127"/>
-    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="126"/>
-    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="125"/>
-    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="124" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="123" dataCellStyle="Moeda"/>
-    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="122"/>
-    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="121" dataCellStyle="Porcentagem">
+    <tableColumn id="1" xr3:uid="{26A85748-1AED-4A71-96D3-23AF97AC5D2B}" name="Data" dataDxfId="139"/>
+    <tableColumn id="25" xr3:uid="{D413966D-CDFC-4875-A3AE-6AE9D849E75F}" name="Placa" dataDxfId="138"/>
+    <tableColumn id="3" xr3:uid="{D30CA2C3-D31F-4082-8392-1A98EB60EDD3}" name="Carreta" dataDxfId="137"/>
+    <tableColumn id="4" xr3:uid="{758E5D51-7D49-4A69-8227-C9CE8E4A907A}" name="Motorista" dataDxfId="136"/>
+    <tableColumn id="6" xr3:uid="{842361EA-39E1-4EF7-90A4-9BDC9C0966DF}" name="Valor Frete" dataDxfId="135" dataCellStyle="Moeda"/>
+    <tableColumn id="7" xr3:uid="{D4C1D57F-C6B7-49EE-9F7B-47EBA6030041}" name="Valor Mercadoria" dataDxfId="134" dataCellStyle="Moeda"/>
+    <tableColumn id="8" xr3:uid="{C79AB3D8-0BFF-4FFE-B20B-E81367BFEEFC}" name="Peso" dataDxfId="133"/>
+    <tableColumn id="9" xr3:uid="{7D4ACBB5-8F17-463A-A61F-84A8EFF41604}" name="% Frete" dataDxfId="132" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="120"/>
-    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="119"/>
-    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="118">
+    <tableColumn id="10" xr3:uid="{B93772F3-4DD6-4AA9-86E6-5E65788A8D0A}" name="Hr Saida" dataDxfId="131"/>
+    <tableColumn id="11" xr3:uid="{DC726A91-384E-47C4-A94A-9095E8138925}" name="Hr Chegada" dataDxfId="130"/>
+    <tableColumn id="12" xr3:uid="{9A37D38C-D321-47A3-881E-B95F03E5DB0D}" name="Tempo" dataDxfId="129">
       <calculatedColumnFormula>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="117" dataCellStyle="Moeda"/>
-    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="116" dataCellStyle="Porcentagem">
+    <tableColumn id="13" xr3:uid="{E5643091-5008-4800-BF73-88DFC566FBE9}" name="Frete" dataDxfId="128" dataCellStyle="Moeda"/>
+    <tableColumn id="14" xr3:uid="{5E8F8636-0E97-4E52-8561-725D1AD8BAF1}" name="% Frete T" dataDxfId="127" dataCellStyle="Porcentagem">
       <calculatedColumnFormula>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="115"/>
-    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="114"/>
-    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="113"/>
-    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="112">
+    <tableColumn id="16" xr3:uid="{F64AFFB0-A5D7-49FD-8B66-BD3FBD830A8C}" name="Vols" dataDxfId="126"/>
+    <tableColumn id="17" xr3:uid="{36B8097A-82AA-4880-AA26-8A84D3BFDAE9}" name="Qtde Entregas" dataDxfId="125"/>
+    <tableColumn id="18" xr3:uid="{8BF06732-0C91-4852-86A9-342D98B30169}" name="Entregas Realizadas" dataDxfId="124"/>
+    <tableColumn id="19" xr3:uid="{20BD31A4-57AA-4F11-A73A-2B181C01798B}" name=" Retornadas" dataDxfId="123">
       <calculatedColumnFormula>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="111" dataCellStyle="Moeda 2 2">
+    <tableColumn id="20" xr3:uid="{F3EDF45C-B4E9-4FE6-A74A-C49CA0273F75}" name="% Entrega" dataDxfId="122" dataCellStyle="Moeda 2 2">
       <calculatedColumnFormula>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="110" dataCellStyle="Moeda 3">
+    <tableColumn id="21" xr3:uid="{25A768B3-401C-4B3F-B390-C9B4AA1DD346}" name="Meta" dataDxfId="121" dataCellStyle="Moeda 3">
       <calculatedColumnFormula>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="109"/>
-    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="108"/>
-    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="107"/>
+    <tableColumn id="22" xr3:uid="{F55B1675-851F-46DE-9F3E-6389EFBFB7B9}" name="Cidade Destino" dataDxfId="120"/>
+    <tableColumn id="23" xr3:uid="{D7BA1AAD-39A7-4F74-8E2B-3DAD30E78669}" name="Nfs Voltaram" dataDxfId="119"/>
+    <tableColumn id="24" xr3:uid="{3938B063-E851-4B1A-B457-042DD7442897}" name="Código ocorrência" dataDxfId="118"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y588" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50" headerRowBorderDxfId="48" tableBorderDxfId="49" totalsRowBorderDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{82009C12-8110-4F05-A50D-013940C9873F}" name="Tabela32" displayName="Tabela32" ref="A1:Y597" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50" headerRowBorderDxfId="48" tableBorderDxfId="49" totalsRowBorderDxfId="47">
   <tableColumns count="25">
     <tableColumn id="1" xr3:uid="{B118DAB0-A500-46F5-A61D-A15BA1838F69}" name="Data" dataDxfId="46"/>
     <tableColumn id="25" xr3:uid="{DAA903FE-736A-4CBF-95D8-B9E859203B97}" name="Ano" dataDxfId="45">
@@ -2684,7 +2758,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A050DE7D-8F3F-47CF-9E37-B95AFD2ED76A}">
-  <dimension ref="A1:V31"/>
+  <dimension ref="A1:V33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="23" bestFit="1" customWidth="1"/>
@@ -4547,10 +4621,10 @@
       <c r="D31" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E31" s="27">
+      <c r="E31" s="10">
         <v>4218.16</v>
       </c>
-      <c r="F31" s="27">
+      <c r="F31" s="10">
         <v>91137.94</v>
       </c>
       <c r="G31" s="4">
@@ -4595,7 +4669,7 @@
         <v>Atendeu a Meta</v>
       </c>
       <c r="T31" s="4" t="s">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="U31" s="4">
         <v>0</v>
@@ -4604,40 +4678,176 @@
         <v>38.380000000000003</v>
       </c>
     </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A32" s="8">
+        <v>46315</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E32" s="27">
+        <v>13436.17</v>
+      </c>
+      <c r="F32" s="27">
+        <v>222024.45</v>
+      </c>
+      <c r="G32" s="4">
+        <v>1806</v>
+      </c>
+      <c r="H32" s="9">
+        <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
+        <v>6.0516623281805224E-2</v>
+      </c>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4">
+        <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
+        <v>0</v>
+      </c>
+      <c r="L32" s="10">
+        <v>500</v>
+      </c>
+      <c r="M32" s="9">
+        <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
+        <v>3.7212985545732151E-2</v>
+      </c>
+      <c r="N32" s="4">
+        <v>323</v>
+      </c>
+      <c r="O32" s="4">
+        <v>54</v>
+      </c>
+      <c r="P32" s="4">
+        <v>46</v>
+      </c>
+      <c r="Q32" s="12">
+        <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
+        <v>8</v>
+      </c>
+      <c r="R32" s="13">
+        <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
+        <v>0.85185185185185186</v>
+      </c>
+      <c r="S32" s="14" t="str">
+        <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Não Atendeu a Meta</v>
+      </c>
+      <c r="T32" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="U32" s="4">
+        <v>8</v>
+      </c>
+      <c r="V32" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A33" s="8">
+        <v>46315</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E33" s="27">
+        <v>8690.0400000000009</v>
+      </c>
+      <c r="F33" s="27">
+        <v>162493.32999999999</v>
+      </c>
+      <c r="G33" s="4">
+        <v>2340</v>
+      </c>
+      <c r="H33" s="9">
+        <f>Tabela35[[#This Row],[Valor Frete]]/Tabela35[[#This Row],[Valor Mercadoria]]</f>
+        <v>5.3479364352986065E-2</v>
+      </c>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4">
+        <f>Tabela35[[#This Row],[Hr Chegada]]-Tabela35[[#This Row],[Hr Saida]]</f>
+        <v>0</v>
+      </c>
+      <c r="L33" s="10">
+        <v>500</v>
+      </c>
+      <c r="M33" s="9">
+        <f>Tabela35[[#This Row],[Frete]]/Tabela35[[#This Row],[Valor Frete]]</f>
+        <v>5.7537134466584726E-2</v>
+      </c>
+      <c r="N33" s="4">
+        <v>621</v>
+      </c>
+      <c r="O33" s="4">
+        <v>1</v>
+      </c>
+      <c r="P33" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="12">
+        <f>Tabela35[[#This Row],[Qtde Entregas]]-Tabela35[[#This Row],[Entregas Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="R33" s="13">
+        <f>Tabela35[[#This Row],[Entregas Realizadas]]/Tabela35[[#This Row],[Qtde Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="S33" s="14" t="str">
+        <f>IF(Tabela35[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="T33" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="U33" s="4">
+        <v>0</v>
+      </c>
+      <c r="V33" s="5">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H31">
-    <cfRule type="cellIs" dxfId="106" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="H2:H33">
+    <cfRule type="cellIs" dxfId="117" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="2" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="116" priority="2" operator="greaterThanOrEqual">
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R31">
-    <cfRule type="cellIs" dxfId="104" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="R2:R33">
+    <cfRule type="cellIs" dxfId="115" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="114" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="113" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>90</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="10" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="112" priority="10" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="11" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="111" priority="11" stopIfTrue="1" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="12" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="110" priority="12" stopIfTrue="1" operator="greaterThan">
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="13" stopIfTrue="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="109" priority="13" stopIfTrue="1" operator="greaterThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S31">
-    <cfRule type="expression" dxfId="97" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="S2:S33">
+    <cfRule type="expression" dxfId="108" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
     <cfRule type="expression" priority="4" stopIfTrue="1">
@@ -4646,7 +4856,7 @@
     <cfRule type="expression" priority="5" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",S2)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="107" priority="6" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Atendeu a Meta",S2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4660,7 +4870,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49CA93CC-B655-4DE0-B90B-BE96AD645946}">
-  <dimension ref="A1:Y588"/>
+  <dimension ref="A1:Y597"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -52753,11 +52963,11 @@
       <c r="A560" s="8">
         <v>46311</v>
       </c>
-      <c r="B560" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C560" s="26">
+      <c r="B560" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C560" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -52839,11 +53049,11 @@
       <c r="A561" s="8">
         <v>46311</v>
       </c>
-      <c r="B561" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C561" s="26">
+      <c r="B561" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C561" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -52925,11 +53135,11 @@
       <c r="A562" s="8">
         <v>46311</v>
       </c>
-      <c r="B562" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C562" s="26">
+      <c r="B562" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C562" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -53011,11 +53221,11 @@
       <c r="A563" s="8">
         <v>46311</v>
       </c>
-      <c r="B563" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C563" s="26">
+      <c r="B563" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C563" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -53097,11 +53307,11 @@
       <c r="A564" s="8">
         <v>46311</v>
       </c>
-      <c r="B564" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C564" s="26">
+      <c r="B564" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C564" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -53183,11 +53393,11 @@
       <c r="A565" s="8">
         <v>46311</v>
       </c>
-      <c r="B565" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C565" s="26">
+      <c r="B565" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C565" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -53269,11 +53479,11 @@
       <c r="A566" s="8">
         <v>46311</v>
       </c>
-      <c r="B566" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C566" s="26">
+      <c r="B566" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C566" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -53355,11 +53565,11 @@
       <c r="A567" s="8">
         <v>46311</v>
       </c>
-      <c r="B567" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C567" s="26">
+      <c r="B567" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C567" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -53441,11 +53651,11 @@
       <c r="A568" s="8">
         <v>46311</v>
       </c>
-      <c r="B568" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C568" s="26">
+      <c r="B568" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C568" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -53527,11 +53737,11 @@
       <c r="A569" s="8">
         <v>46311</v>
       </c>
-      <c r="B569" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C569" s="26">
+      <c r="B569" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C569" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -53613,11 +53823,11 @@
       <c r="A570" s="8">
         <v>46311</v>
       </c>
-      <c r="B570" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C570" s="26">
+      <c r="B570" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C570" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -53699,11 +53909,11 @@
       <c r="A571" s="8">
         <v>46311</v>
       </c>
-      <c r="B571" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C571" s="26">
+      <c r="B571" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C571" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -53785,11 +53995,11 @@
       <c r="A572" s="8">
         <v>46312</v>
       </c>
-      <c r="B572" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C572" s="26">
+      <c r="B572" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C572" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -53871,11 +54081,11 @@
       <c r="A573" s="8">
         <v>46312</v>
       </c>
-      <c r="B573" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C573" s="26">
+      <c r="B573" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C573" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -53957,11 +54167,11 @@
       <c r="A574" s="8">
         <v>46312</v>
       </c>
-      <c r="B574" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C574" s="26">
+      <c r="B574" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C574" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -54043,11 +54253,11 @@
       <c r="A575" s="8">
         <v>46312</v>
       </c>
-      <c r="B575" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C575" s="26">
+      <c r="B575" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C575" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -54129,11 +54339,11 @@
       <c r="A576" s="8">
         <v>46314</v>
       </c>
-      <c r="B576" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C576" s="26">
+      <c r="B576" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C576" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -54215,11 +54425,11 @@
       <c r="A577" s="8">
         <v>46314</v>
       </c>
-      <c r="B577" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C577" s="26">
+      <c r="B577" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C577" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -54301,11 +54511,11 @@
       <c r="A578" s="8">
         <v>46314</v>
       </c>
-      <c r="B578" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C578" s="26">
+      <c r="B578" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C578" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -54387,11 +54597,11 @@
       <c r="A579" s="8">
         <v>46314</v>
       </c>
-      <c r="B579" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C579" s="26">
+      <c r="B579" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C579" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -54473,11 +54683,11 @@
       <c r="A580" s="8">
         <v>46314</v>
       </c>
-      <c r="B580" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C580" s="26">
+      <c r="B580" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C580" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -54559,11 +54769,11 @@
       <c r="A581" s="8">
         <v>46314</v>
       </c>
-      <c r="B581" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C581" s="26">
+      <c r="B581" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C581" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -54645,11 +54855,11 @@
       <c r="A582" s="8">
         <v>46314</v>
       </c>
-      <c r="B582" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C582" s="26">
+      <c r="B582" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C582" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -54731,11 +54941,11 @@
       <c r="A583" s="8">
         <v>46314</v>
       </c>
-      <c r="B583" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C583" s="26">
+      <c r="B583" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C583" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -54817,11 +55027,11 @@
       <c r="A584" s="8">
         <v>46314</v>
       </c>
-      <c r="B584" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C584" s="26">
+      <c r="B584" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C584" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -54903,11 +55113,11 @@
       <c r="A585" s="8">
         <v>46314</v>
       </c>
-      <c r="B585" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C585" s="26">
+      <c r="B585" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C585" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -54989,11 +55199,11 @@
       <c r="A586" s="8">
         <v>46314</v>
       </c>
-      <c r="B586" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C586" s="26">
+      <c r="B586" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C586" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -55075,11 +55285,11 @@
       <c r="A587" s="8">
         <v>46314</v>
       </c>
-      <c r="B587" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C587" s="26">
+      <c r="B587" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C587" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -55161,11 +55371,11 @@
       <c r="A588" s="8">
         <v>46314</v>
       </c>
-      <c r="B588" s="26">
-        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
-        <v>2026</v>
-      </c>
-      <c r="C588" s="26">
+      <c r="B588" s="16">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C588" s="16">
         <f>MONTH(Tabela32[[#This Row],[Data]])</f>
         <v>10</v>
       </c>
@@ -55243,8 +55453,782 @@
         <v>9.9</v>
       </c>
     </row>
+    <row r="589" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A589" s="8">
+        <v>46315</v>
+      </c>
+      <c r="B589" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C589" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D589" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E589" s="4">
+        <v>5</v>
+      </c>
+      <c r="F589" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Juscelino</v>
+      </c>
+      <c r="G589" s="10">
+        <v>8910.6200000000008</v>
+      </c>
+      <c r="H589" s="10">
+        <v>154705.03</v>
+      </c>
+      <c r="I589" s="4">
+        <v>1791</v>
+      </c>
+      <c r="J589" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.759748083174801E-2</v>
+      </c>
+      <c r="K589" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L589" s="15">
+        <v>0.69166666666666665</v>
+      </c>
+      <c r="M589" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.37916666666666665</v>
+      </c>
+      <c r="N589" s="4">
+        <v>306713</v>
+      </c>
+      <c r="O589" s="4">
+        <v>306802</v>
+      </c>
+      <c r="P589" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>89</v>
+      </c>
+      <c r="Q589" s="4">
+        <v>308</v>
+      </c>
+      <c r="R589" s="4">
+        <v>14</v>
+      </c>
+      <c r="S589" s="4">
+        <v>14</v>
+      </c>
+      <c r="T589" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U589" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V589" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W589" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X589" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y589" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="590" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A590" s="8">
+        <v>46315</v>
+      </c>
+      <c r="B590" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C590" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D590" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E590" s="4">
+        <v>11</v>
+      </c>
+      <c r="F590" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Edilson</v>
+      </c>
+      <c r="G590" s="10">
+        <v>31294.400000000001</v>
+      </c>
+      <c r="H590" s="10">
+        <v>774001.49</v>
+      </c>
+      <c r="I590" s="4">
+        <v>6346</v>
+      </c>
+      <c r="J590" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>4.0431963509527616E-2</v>
+      </c>
+      <c r="K590" s="11">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="L590" s="15">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="M590" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.43750000000000006</v>
+      </c>
+      <c r="N590" s="4">
+        <v>107711</v>
+      </c>
+      <c r="O590" s="4">
+        <v>107835</v>
+      </c>
+      <c r="P590" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>124</v>
+      </c>
+      <c r="Q590" s="4">
+        <v>17</v>
+      </c>
+      <c r="R590" s="4">
+        <v>1</v>
+      </c>
+      <c r="S590" s="4">
+        <v>1</v>
+      </c>
+      <c r="T590" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U590" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V590" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W590" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X590" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y590" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="591" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A591" s="8">
+        <v>46315</v>
+      </c>
+      <c r="B591" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C591" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D591" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E591" s="4">
+        <v>3</v>
+      </c>
+      <c r="F591" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Rosinaldo</v>
+      </c>
+      <c r="G591" s="10">
+        <v>10343.709999999999</v>
+      </c>
+      <c r="H591" s="10">
+        <v>357847.19</v>
+      </c>
+      <c r="I591" s="4">
+        <v>2447</v>
+      </c>
+      <c r="J591" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>2.8905382769667688E-2</v>
+      </c>
+      <c r="K591" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L591" s="15">
+        <v>0.73055555555555551</v>
+      </c>
+      <c r="M591" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.43888888888888883</v>
+      </c>
+      <c r="N591" s="4">
+        <v>292762</v>
+      </c>
+      <c r="O591" s="4">
+        <v>292852</v>
+      </c>
+      <c r="P591" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>90</v>
+      </c>
+      <c r="Q591" s="4">
+        <v>271</v>
+      </c>
+      <c r="R591" s="4">
+        <v>16</v>
+      </c>
+      <c r="S591" s="4">
+        <v>16</v>
+      </c>
+      <c r="T591" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U591" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V591" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W591" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X591" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y591" s="5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="592" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A592" s="8">
+        <v>46315</v>
+      </c>
+      <c r="B592" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C592" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D592" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E592" s="4">
+        <v>1</v>
+      </c>
+      <c r="F592" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Paulo</v>
+      </c>
+      <c r="G592" s="10">
+        <v>4937.08</v>
+      </c>
+      <c r="H592" s="10">
+        <v>53124.21</v>
+      </c>
+      <c r="I592" s="4">
+        <v>671</v>
+      </c>
+      <c r="J592" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>9.2934652581186619E-2</v>
+      </c>
+      <c r="K592" s="11">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="L592" s="15">
+        <v>0.69722222222222219</v>
+      </c>
+      <c r="M592" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.4055555555555555</v>
+      </c>
+      <c r="N592" s="4">
+        <v>157700</v>
+      </c>
+      <c r="O592" s="4">
+        <v>157777</v>
+      </c>
+      <c r="P592" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>77</v>
+      </c>
+      <c r="Q592" s="4">
+        <v>87</v>
+      </c>
+      <c r="R592" s="4">
+        <v>6</v>
+      </c>
+      <c r="S592" s="4">
+        <v>6</v>
+      </c>
+      <c r="T592" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U592" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V592" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W592" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X592" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y592" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="593" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A593" s="8">
+        <v>46315</v>
+      </c>
+      <c r="B593" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C593" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D593" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E593" s="4">
+        <v>3</v>
+      </c>
+      <c r="F593" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Osvaldo</v>
+      </c>
+      <c r="G593" s="10">
+        <v>11018.08</v>
+      </c>
+      <c r="H593" s="10">
+        <v>296007.76</v>
+      </c>
+      <c r="I593" s="4">
+        <v>1833</v>
+      </c>
+      <c r="J593" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>3.72222674162326E-2</v>
+      </c>
+      <c r="K593" s="11">
+        <v>0.30355324074074075</v>
+      </c>
+      <c r="L593" s="15">
+        <v>0.71319444444444446</v>
+      </c>
+      <c r="M593" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.40964120370370372</v>
+      </c>
+      <c r="N593" s="4">
+        <v>145236</v>
+      </c>
+      <c r="O593" s="4">
+        <v>145287</v>
+      </c>
+      <c r="P593" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>51</v>
+      </c>
+      <c r="Q593" s="4">
+        <v>380</v>
+      </c>
+      <c r="R593" s="4">
+        <v>27</v>
+      </c>
+      <c r="S593" s="4">
+        <v>27</v>
+      </c>
+      <c r="T593" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U593" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V593" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W593" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X593" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y593" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="594" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A594" s="8">
+        <v>46315</v>
+      </c>
+      <c r="B594" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C594" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D594" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E594" s="4">
+        <v>1</v>
+      </c>
+      <c r="F594" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Sandro</v>
+      </c>
+      <c r="G594" s="10">
+        <v>8422.27</v>
+      </c>
+      <c r="H594" s="10">
+        <v>108755.44</v>
+      </c>
+      <c r="I594" s="4">
+        <v>1434</v>
+      </c>
+      <c r="J594" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.744228702490652E-2</v>
+      </c>
+      <c r="K594" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L594" s="15">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="M594" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.44791666666666663</v>
+      </c>
+      <c r="N594" s="4">
+        <v>277217</v>
+      </c>
+      <c r="O594" s="4">
+        <v>277388</v>
+      </c>
+      <c r="P594" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>171</v>
+      </c>
+      <c r="Q594" s="4">
+        <v>161</v>
+      </c>
+      <c r="R594" s="4">
+        <v>31</v>
+      </c>
+      <c r="S594" s="4">
+        <v>31</v>
+      </c>
+      <c r="T594" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U594" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V594" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W594" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="X594" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y594" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="595" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A595" s="8">
+        <v>46315</v>
+      </c>
+      <c r="B595" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C595" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D595" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E595" s="4">
+        <v>5</v>
+      </c>
+      <c r="F595" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Jerson</v>
+      </c>
+      <c r="G595" s="10">
+        <v>10335.64</v>
+      </c>
+      <c r="H595" s="10">
+        <v>126768.55</v>
+      </c>
+      <c r="I595" s="4">
+        <v>1443</v>
+      </c>
+      <c r="J595" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>8.1531578613149705E-2</v>
+      </c>
+      <c r="K595" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L595" s="15">
+        <v>0.78125</v>
+      </c>
+      <c r="M595" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.46875</v>
+      </c>
+      <c r="N595" s="4">
+        <v>282336</v>
+      </c>
+      <c r="O595" s="4">
+        <v>282391</v>
+      </c>
+      <c r="P595" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>55</v>
+      </c>
+      <c r="Q595" s="4">
+        <v>185</v>
+      </c>
+      <c r="R595" s="4">
+        <v>30</v>
+      </c>
+      <c r="S595" s="4">
+        <v>30</v>
+      </c>
+      <c r="T595" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U595" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V595" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W595" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X595" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y595" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="596" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A596" s="8">
+        <v>46315</v>
+      </c>
+      <c r="B596" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C596" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D596" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E596" s="4">
+        <v>1</v>
+      </c>
+      <c r="F596" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>William</v>
+      </c>
+      <c r="G596" s="10">
+        <v>11945.55</v>
+      </c>
+      <c r="H596" s="10">
+        <v>159995.82</v>
+      </c>
+      <c r="I596" s="4">
+        <v>2035</v>
+      </c>
+      <c r="J596" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>7.4661638035293659E-2</v>
+      </c>
+      <c r="K596" s="11">
+        <v>0.3125</v>
+      </c>
+      <c r="L596" s="15">
+        <v>0.78472222222222221</v>
+      </c>
+      <c r="M596" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.47222222222222221</v>
+      </c>
+      <c r="N596" s="4">
+        <v>127326</v>
+      </c>
+      <c r="O596" s="4">
+        <v>127397</v>
+      </c>
+      <c r="P596" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>71</v>
+      </c>
+      <c r="Q596" s="4">
+        <v>277</v>
+      </c>
+      <c r="R596" s="4">
+        <v>28</v>
+      </c>
+      <c r="S596" s="4">
+        <v>28</v>
+      </c>
+      <c r="T596" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U596" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V596" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W596" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X596" s="4">
+        <v>1</v>
+      </c>
+      <c r="Y596" s="5">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="597" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A597" s="8">
+        <v>46315</v>
+      </c>
+      <c r="B597" s="26">
+        <f>YEAR(Tabela32[[#This Row],[Data]])</f>
+        <v>2026</v>
+      </c>
+      <c r="C597" s="26">
+        <f>MONTH(Tabela32[[#This Row],[Data]])</f>
+        <v>10</v>
+      </c>
+      <c r="D597" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E597" s="4">
+        <v>11</v>
+      </c>
+      <c r="F597" s="4" t="str">
+        <f>IFERROR(VLOOKUP(Tabela32[[#This Row],[Placa]],Planilha2!$A$1:$B$12,2,0),"")</f>
+        <v>Arnaldo</v>
+      </c>
+      <c r="G597" s="10">
+        <v>12821.04</v>
+      </c>
+      <c r="H597" s="10">
+        <v>228080.39</v>
+      </c>
+      <c r="I597" s="4">
+        <v>2382</v>
+      </c>
+      <c r="J597" s="17">
+        <f>IFERROR(Tabela32[[#This Row],[Valor Frete]]/Tabela32[[#This Row],[Valor Mercadoria]],"")</f>
+        <v>5.6212811631898736E-2</v>
+      </c>
+      <c r="K597" s="11">
+        <v>0.27430555555555558</v>
+      </c>
+      <c r="L597" s="15">
+        <v>0.78125</v>
+      </c>
+      <c r="M597" s="15">
+        <f>Tabela32[[#This Row],[Hr Chegada]]-Tabela32[[#This Row],[Hr Saida]]</f>
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="N597" s="4">
+        <v>15040</v>
+      </c>
+      <c r="O597" s="4">
+        <v>15182</v>
+      </c>
+      <c r="P597" s="4">
+        <f>Tabela32[[#This Row],[Km Chegada]]-Tabela32[[#This Row],[Km Saída]]</f>
+        <v>142</v>
+      </c>
+      <c r="Q597" s="4">
+        <v>510</v>
+      </c>
+      <c r="R597" s="4">
+        <v>35</v>
+      </c>
+      <c r="S597" s="4">
+        <v>35</v>
+      </c>
+      <c r="T597" s="12">
+        <f>Tabela32[[#This Row],[Entregas]]-Tabela32[[#This Row],[Realizadas]]</f>
+        <v>0</v>
+      </c>
+      <c r="U597" s="18">
+        <f>Tabela32[[#This Row],[Realizadas]]/Tabela32[[#This Row],[Entregas]]</f>
+        <v>1</v>
+      </c>
+      <c r="V597" s="19" t="str">
+        <f>IF(Tabela32[[#This Row],[% Entrega]]&gt;=96%,"Atendeu a Meta","Não Atendeu a Meta")</f>
+        <v>Atendeu a Meta</v>
+      </c>
+      <c r="W597" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="X597" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y597" s="5">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J588">
+  <conditionalFormatting sqref="J2:J597">
     <cfRule type="cellIs" dxfId="21" priority="1" operator="lessThan">
       <formula>0.05</formula>
     </cfRule>
@@ -55252,7 +56236,7 @@
       <formula>0.05</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U588">
+  <conditionalFormatting sqref="U2:U597">
     <cfRule type="cellIs" dxfId="19" priority="7" stopIfTrue="1" operator="lessThanOrEqual">
       <formula>0.949</formula>
     </cfRule>
@@ -55275,7 +56259,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V588">
+  <conditionalFormatting sqref="V2:V597">
     <cfRule type="expression" dxfId="12" priority="3" stopIfTrue="1">
       <formula>NOT(ISERROR(SEARCH("Não Atendeu a Meta",V2)))</formula>
     </cfRule>
@@ -55301,7 +56285,7 @@
           <x14:formula1>
             <xm:f>Planilha2!$A$1:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D588</xm:sqref>
+          <xm:sqref>D2:D597</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Saida_BEL.xlsx
+++ b/Saida_BEL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manoel\Documents\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD13BAD-C08D-4362-BF6C-367C0BA10BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54FC57D3-0B51-43D1-89CB-F4A1AB6A1DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{B4DF3242-8F2B-4ADB-9A16-64AB3DBBB1AB}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1443" uniqueCount="107">
   <si>
     <t>Data</t>
   </si>
@@ -361,6 +361,9 @@
   </si>
   <si>
     <t>Juscelino</t>
+  </si>
+  <si>
+    <t>13,13,13,38</t>
   </si>
 </sst>
 </file>
@@ -804,509 +807,6 @@
         <i val="0"/>
         <color rgb="FFFF0000"/>
       </font>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
- 